--- a/template_produzione.xlsx
+++ b/template_produzione.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maxporte.sharepoint.com/sites/MPCloud/Documenti condivisi/MPX/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="662" documentId="8_{CC15ACFE-ED8D-4D36-8DB1-DE3148A82591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1780C1C-3E1C-4A2A-ABC1-E34C1CD1D4ED}"/>
+  <xr:revisionPtr revIDLastSave="671" documentId="8_{CC15ACFE-ED8D-4D36-8DB1-DE3148A82591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B977DFE4-DF18-41AD-A5C5-B94323CA001B}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{2F1D62B1-3FD5-4D97-A455-0CD2ABF42920}"/>
   </bookViews>
@@ -584,7 +584,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -621,78 +621,8 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
@@ -730,6 +660,73 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -766,38 +763,73 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1147,74 +1179,74 @@
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="36" t="s">
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="36" t="s">
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="X1" s="37"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="37"/>
-      <c r="AE1" s="37"/>
-      <c r="AF1" s="37"/>
-      <c r="AG1" s="37"/>
-      <c r="AH1" s="38"/>
-      <c r="AI1" s="36" t="s">
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="46"/>
+      <c r="AA1" s="46"/>
+      <c r="AB1" s="46"/>
+      <c r="AC1" s="46"/>
+      <c r="AD1" s="46"/>
+      <c r="AE1" s="46"/>
+      <c r="AF1" s="46"/>
+      <c r="AG1" s="46"/>
+      <c r="AH1" s="47"/>
+      <c r="AI1" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="AJ1" s="37"/>
-      <c r="AK1" s="37"/>
-      <c r="AL1" s="37"/>
-      <c r="AM1" s="38"/>
-      <c r="AN1" s="36" t="s">
+      <c r="AJ1" s="46"/>
+      <c r="AK1" s="46"/>
+      <c r="AL1" s="46"/>
+      <c r="AM1" s="47"/>
+      <c r="AN1" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="AO1" s="37"/>
-      <c r="AP1" s="37"/>
-      <c r="AQ1" s="37"/>
-      <c r="AR1" s="38"/>
+      <c r="AO1" s="46"/>
+      <c r="AP1" s="46"/>
+      <c r="AQ1" s="46"/>
+      <c r="AR1" s="47"/>
       <c r="AS1" s="7"/>
       <c r="AT1" s="7"/>
       <c r="AU1" s="7"/>
       <c r="AV1" s="7"/>
       <c r="AW1" s="7"/>
       <c r="AX1" s="7"/>
-      <c r="AY1" s="33" t="s">
+      <c r="AY1" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="AZ1" s="33"/>
-      <c r="BA1" s="33"/>
-      <c r="BB1" s="33"/>
-      <c r="BC1" s="33"/>
-      <c r="BD1" s="33"/>
-      <c r="BE1" s="33"/>
-      <c r="BF1" s="33"/>
-      <c r="BG1" s="33"/>
-      <c r="BH1" s="33"/>
-      <c r="BI1" s="33"/>
+      <c r="AZ1" s="42"/>
+      <c r="BA1" s="42"/>
+      <c r="BB1" s="42"/>
+      <c r="BC1" s="42"/>
+      <c r="BD1" s="42"/>
+      <c r="BE1" s="42"/>
+      <c r="BF1" s="42"/>
+      <c r="BG1" s="42"/>
+      <c r="BH1" s="42"/>
+      <c r="BI1" s="42"/>
     </row>
     <row r="2" spans="1:62" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
@@ -1222,68 +1254,68 @@
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="39" t="s">
+      <c r="F2" s="88" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="45" t="s">
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
-      <c r="V2" s="47"/>
-      <c r="W2" s="45" t="s">
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18"/>
+      <c r="R2" s="18"/>
+      <c r="S2" s="18"/>
+      <c r="T2" s="18"/>
+      <c r="U2" s="18"/>
+      <c r="V2" s="19"/>
+      <c r="W2" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="X2" s="46"/>
-      <c r="Y2" s="46"/>
-      <c r="Z2" s="46"/>
-      <c r="AA2" s="46"/>
-      <c r="AB2" s="46"/>
-      <c r="AC2" s="46"/>
-      <c r="AD2" s="46"/>
-      <c r="AE2" s="46"/>
-      <c r="AF2" s="46"/>
-      <c r="AG2" s="46"/>
-      <c r="AH2" s="47"/>
-      <c r="AI2" s="51" t="s">
+      <c r="X2" s="18"/>
+      <c r="Y2" s="18"/>
+      <c r="Z2" s="18"/>
+      <c r="AA2" s="18"/>
+      <c r="AB2" s="18"/>
+      <c r="AC2" s="18"/>
+      <c r="AD2" s="18"/>
+      <c r="AE2" s="18"/>
+      <c r="AF2" s="18"/>
+      <c r="AG2" s="18"/>
+      <c r="AH2" s="19"/>
+      <c r="AI2" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="AJ2" s="52"/>
-      <c r="AK2" s="52"/>
-      <c r="AL2" s="52"/>
-      <c r="AM2" s="53"/>
-      <c r="AN2" s="51" t="s">
+      <c r="AJ2" s="24"/>
+      <c r="AK2" s="24"/>
+      <c r="AL2" s="24"/>
+      <c r="AM2" s="25"/>
+      <c r="AN2" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="AO2" s="52"/>
-      <c r="AP2" s="52"/>
-      <c r="AQ2" s="52"/>
-      <c r="AR2" s="53"/>
-      <c r="AY2" s="34" t="s">
+      <c r="AO2" s="24"/>
+      <c r="AP2" s="24"/>
+      <c r="AQ2" s="24"/>
+      <c r="AR2" s="25"/>
+      <c r="AY2" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="AZ2" s="34"/>
-      <c r="BA2" s="34"/>
-      <c r="BB2" s="34"/>
-      <c r="BC2" s="34"/>
-      <c r="BD2" s="34"/>
-      <c r="BE2" s="34"/>
-      <c r="BF2" s="34"/>
-      <c r="BG2" s="34"/>
-      <c r="BH2" s="34"/>
-      <c r="BI2" s="34"/>
+      <c r="AZ2" s="43"/>
+      <c r="BA2" s="43"/>
+      <c r="BB2" s="43"/>
+      <c r="BC2" s="43"/>
+      <c r="BD2" s="43"/>
+      <c r="BE2" s="43"/>
+      <c r="BF2" s="43"/>
+      <c r="BG2" s="43"/>
+      <c r="BH2" s="43"/>
+      <c r="BI2" s="43"/>
     </row>
     <row r="3" spans="1:62" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4"/>
@@ -1291,56 +1323,56 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="49"/>
-      <c r="N3" s="49"/>
-      <c r="O3" s="49"/>
-      <c r="P3" s="49"/>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="49"/>
-      <c r="U3" s="49"/>
-      <c r="V3" s="50"/>
-      <c r="W3" s="48"/>
-      <c r="X3" s="49"/>
-      <c r="Y3" s="49"/>
-      <c r="Z3" s="49"/>
-      <c r="AA3" s="49"/>
-      <c r="AB3" s="49"/>
-      <c r="AC3" s="49"/>
-      <c r="AD3" s="49"/>
-      <c r="AE3" s="49"/>
-      <c r="AF3" s="49"/>
-      <c r="AG3" s="49"/>
-      <c r="AH3" s="50"/>
-      <c r="AI3" s="54"/>
-      <c r="AJ3" s="55"/>
-      <c r="AK3" s="55"/>
-      <c r="AL3" s="55"/>
-      <c r="AM3" s="56"/>
-      <c r="AN3" s="54"/>
-      <c r="AO3" s="55"/>
-      <c r="AP3" s="55"/>
-      <c r="AQ3" s="55"/>
-      <c r="AR3" s="56"/>
-      <c r="AY3" s="35"/>
-      <c r="AZ3" s="35"/>
-      <c r="BA3" s="35"/>
-      <c r="BB3" s="35"/>
-      <c r="BC3" s="35"/>
-      <c r="BD3" s="35"/>
-      <c r="BE3" s="35"/>
-      <c r="BF3" s="35"/>
-      <c r="BG3" s="35"/>
-      <c r="BH3" s="35"/>
-      <c r="BI3" s="35"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="22"/>
+      <c r="W3" s="20"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
+      <c r="Z3" s="21"/>
+      <c r="AA3" s="21"/>
+      <c r="AB3" s="21"/>
+      <c r="AC3" s="21"/>
+      <c r="AD3" s="21"/>
+      <c r="AE3" s="21"/>
+      <c r="AF3" s="21"/>
+      <c r="AG3" s="21"/>
+      <c r="AH3" s="22"/>
+      <c r="AI3" s="26"/>
+      <c r="AJ3" s="27"/>
+      <c r="AK3" s="27"/>
+      <c r="AL3" s="27"/>
+      <c r="AM3" s="28"/>
+      <c r="AN3" s="26"/>
+      <c r="AO3" s="27"/>
+      <c r="AP3" s="27"/>
+      <c r="AQ3" s="27"/>
+      <c r="AR3" s="28"/>
+      <c r="AY3" s="44"/>
+      <c r="AZ3" s="44"/>
+      <c r="BA3" s="44"/>
+      <c r="BB3" s="44"/>
+      <c r="BC3" s="44"/>
+      <c r="BD3" s="44"/>
+      <c r="BE3" s="44"/>
+      <c r="BF3" s="44"/>
+      <c r="BG3" s="44"/>
+      <c r="BH3" s="44"/>
+      <c r="BI3" s="44"/>
     </row>
     <row r="4" spans="1:62" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
@@ -1348,66 +1380,66 @@
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="57" t="s">
+      <c r="F4" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="59"/>
-      <c r="K4" s="57" t="s">
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="57" t="s">
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="56"/>
+      <c r="P4" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="Q4" s="58"/>
-      <c r="R4" s="58"/>
-      <c r="S4" s="58"/>
-      <c r="T4" s="59"/>
-      <c r="U4" s="57" t="s">
+      <c r="Q4" s="55"/>
+      <c r="R4" s="55"/>
+      <c r="S4" s="55"/>
+      <c r="T4" s="56"/>
+      <c r="U4" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="V4" s="58"/>
-      <c r="W4" s="58"/>
-      <c r="X4" s="58"/>
-      <c r="Y4" s="58"/>
-      <c r="Z4" s="58"/>
-      <c r="AA4" s="58"/>
-      <c r="AB4" s="58"/>
-      <c r="AC4" s="58"/>
-      <c r="AD4" s="58"/>
-      <c r="AE4" s="58"/>
-      <c r="AF4" s="58"/>
-      <c r="AG4" s="58"/>
-      <c r="AH4" s="59"/>
-      <c r="AI4" s="60" t="s">
+      <c r="V4" s="55"/>
+      <c r="W4" s="55"/>
+      <c r="X4" s="55"/>
+      <c r="Y4" s="55"/>
+      <c r="Z4" s="55"/>
+      <c r="AA4" s="55"/>
+      <c r="AB4" s="55"/>
+      <c r="AC4" s="55"/>
+      <c r="AD4" s="55"/>
+      <c r="AE4" s="55"/>
+      <c r="AF4" s="55"/>
+      <c r="AG4" s="55"/>
+      <c r="AH4" s="56"/>
+      <c r="AI4" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="AJ4" s="61"/>
-      <c r="AK4" s="61"/>
-      <c r="AL4" s="61"/>
-      <c r="AM4" s="61"/>
-      <c r="AN4" s="61"/>
-      <c r="AO4" s="61"/>
-      <c r="AP4" s="61"/>
-      <c r="AQ4" s="61"/>
-      <c r="AR4" s="62"/>
-      <c r="AY4" s="35"/>
-      <c r="AZ4" s="35"/>
-      <c r="BA4" s="35"/>
-      <c r="BB4" s="35"/>
-      <c r="BC4" s="35"/>
-      <c r="BD4" s="35"/>
-      <c r="BE4" s="35"/>
-      <c r="BF4" s="35"/>
-      <c r="BG4" s="35"/>
-      <c r="BH4" s="35"/>
-      <c r="BI4" s="35"/>
+      <c r="AJ4" s="58"/>
+      <c r="AK4" s="58"/>
+      <c r="AL4" s="58"/>
+      <c r="AM4" s="58"/>
+      <c r="AN4" s="58"/>
+      <c r="AO4" s="58"/>
+      <c r="AP4" s="58"/>
+      <c r="AQ4" s="58"/>
+      <c r="AR4" s="59"/>
+      <c r="AY4" s="44"/>
+      <c r="AZ4" s="44"/>
+      <c r="BA4" s="44"/>
+      <c r="BB4" s="44"/>
+      <c r="BC4" s="44"/>
+      <c r="BD4" s="44"/>
+      <c r="BE4" s="44"/>
+      <c r="BF4" s="44"/>
+      <c r="BG4" s="44"/>
+      <c r="BH4" s="44"/>
+      <c r="BI4" s="44"/>
     </row>
     <row r="5" spans="1:62" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
@@ -1415,53 +1447,53 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
-      <c r="F5" s="45" t="s">
+      <c r="F5" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="47"/>
-      <c r="K5" s="51" t="s">
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="53"/>
-      <c r="P5" s="51" t="s">
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="Q5" s="52"/>
-      <c r="R5" s="52"/>
-      <c r="S5" s="52"/>
-      <c r="T5" s="53"/>
-      <c r="U5" s="72" t="s">
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
+      <c r="S5" s="24"/>
+      <c r="T5" s="25"/>
+      <c r="U5" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="V5" s="73"/>
-      <c r="W5" s="73"/>
-      <c r="X5" s="73"/>
-      <c r="Y5" s="73"/>
-      <c r="Z5" s="73"/>
-      <c r="AA5" s="73"/>
-      <c r="AB5" s="73"/>
-      <c r="AC5" s="73"/>
-      <c r="AD5" s="73"/>
-      <c r="AE5" s="73"/>
-      <c r="AF5" s="73"/>
-      <c r="AG5" s="73"/>
-      <c r="AH5" s="74"/>
-      <c r="AI5" s="63"/>
-      <c r="AJ5" s="64"/>
-      <c r="AK5" s="64"/>
-      <c r="AL5" s="64"/>
-      <c r="AM5" s="64"/>
-      <c r="AN5" s="64"/>
-      <c r="AO5" s="64"/>
-      <c r="AP5" s="64"/>
-      <c r="AQ5" s="64"/>
-      <c r="AR5" s="65"/>
+      <c r="V5" s="30"/>
+      <c r="W5" s="30"/>
+      <c r="X5" s="30"/>
+      <c r="Y5" s="30"/>
+      <c r="Z5" s="30"/>
+      <c r="AA5" s="30"/>
+      <c r="AB5" s="30"/>
+      <c r="AC5" s="30"/>
+      <c r="AD5" s="30"/>
+      <c r="AE5" s="30"/>
+      <c r="AF5" s="30"/>
+      <c r="AG5" s="30"/>
+      <c r="AH5" s="31"/>
+      <c r="AI5" s="60"/>
+      <c r="AJ5" s="61"/>
+      <c r="AK5" s="61"/>
+      <c r="AL5" s="61"/>
+      <c r="AM5" s="61"/>
+      <c r="AN5" s="61"/>
+      <c r="AO5" s="61"/>
+      <c r="AP5" s="61"/>
+      <c r="AQ5" s="61"/>
+      <c r="AR5" s="62"/>
     </row>
     <row r="6" spans="1:62" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
@@ -1469,45 +1501,45 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="55"/>
-      <c r="N6" s="55"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="54"/>
-      <c r="Q6" s="55"/>
-      <c r="R6" s="55"/>
-      <c r="S6" s="55"/>
-      <c r="T6" s="56"/>
-      <c r="U6" s="75"/>
-      <c r="V6" s="76"/>
-      <c r="W6" s="76"/>
-      <c r="X6" s="76"/>
-      <c r="Y6" s="76"/>
-      <c r="Z6" s="76"/>
-      <c r="AA6" s="76"/>
-      <c r="AB6" s="76"/>
-      <c r="AC6" s="76"/>
-      <c r="AD6" s="76"/>
-      <c r="AE6" s="76"/>
-      <c r="AF6" s="76"/>
-      <c r="AG6" s="76"/>
-      <c r="AH6" s="77"/>
-      <c r="AI6" s="66"/>
-      <c r="AJ6" s="67"/>
-      <c r="AK6" s="67"/>
-      <c r="AL6" s="67"/>
-      <c r="AM6" s="67"/>
-      <c r="AN6" s="67"/>
-      <c r="AO6" s="67"/>
-      <c r="AP6" s="67"/>
-      <c r="AQ6" s="67"/>
-      <c r="AR6" s="68"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="27"/>
+      <c r="S6" s="27"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="33"/>
+      <c r="W6" s="33"/>
+      <c r="X6" s="33"/>
+      <c r="Y6" s="33"/>
+      <c r="Z6" s="33"/>
+      <c r="AA6" s="33"/>
+      <c r="AB6" s="33"/>
+      <c r="AC6" s="33"/>
+      <c r="AD6" s="33"/>
+      <c r="AE6" s="33"/>
+      <c r="AF6" s="33"/>
+      <c r="AG6" s="33"/>
+      <c r="AH6" s="34"/>
+      <c r="AI6" s="63"/>
+      <c r="AJ6" s="64"/>
+      <c r="AK6" s="64"/>
+      <c r="AL6" s="64"/>
+      <c r="AM6" s="64"/>
+      <c r="AN6" s="64"/>
+      <c r="AO6" s="64"/>
+      <c r="AP6" s="64"/>
+      <c r="AQ6" s="64"/>
+      <c r="AR6" s="65"/>
     </row>
     <row r="7" spans="1:62" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
@@ -1553,263 +1585,263 @@
       <c r="AO7" s="4"/>
     </row>
     <row r="8" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="18" t="s">
+      <c r="B8" s="36"/>
+      <c r="C8" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="18" t="s">
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="31" t="s">
+      <c r="L8" s="37"/>
+      <c r="M8" s="37"/>
+      <c r="N8" s="37"/>
+      <c r="O8" s="37"/>
+      <c r="P8" s="37"/>
+      <c r="Q8" s="37"/>
+      <c r="R8" s="36"/>
+      <c r="S8" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="T8" s="32"/>
-      <c r="U8" s="31" t="s">
+      <c r="T8" s="39"/>
+      <c r="U8" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="V8" s="32"/>
-      <c r="W8" s="31" t="s">
+      <c r="V8" s="39"/>
+      <c r="W8" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="X8" s="32"/>
-      <c r="Y8" s="18" t="s">
+      <c r="X8" s="39"/>
+      <c r="Y8" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="Z8" s="20"/>
-      <c r="AA8" s="18" t="s">
+      <c r="Z8" s="36"/>
+      <c r="AA8" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="AB8" s="20"/>
-      <c r="AC8" s="18" t="s">
+      <c r="AB8" s="36"/>
+      <c r="AC8" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="AD8" s="19"/>
-      <c r="AE8" s="19"/>
-      <c r="AF8" s="20"/>
-      <c r="AG8" s="18" t="s">
+      <c r="AD8" s="37"/>
+      <c r="AE8" s="37"/>
+      <c r="AF8" s="36"/>
+      <c r="AG8" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="AH8" s="19"/>
-      <c r="AI8" s="20"/>
-      <c r="AJ8" s="18" t="s">
+      <c r="AH8" s="37"/>
+      <c r="AI8" s="36"/>
+      <c r="AJ8" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="AK8" s="19"/>
-      <c r="AL8" s="20"/>
-      <c r="AM8" s="18" t="s">
+      <c r="AK8" s="37"/>
+      <c r="AL8" s="36"/>
+      <c r="AM8" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="AN8" s="19"/>
-      <c r="AO8" s="20"/>
-      <c r="AP8" s="18" t="s">
+      <c r="AN8" s="80"/>
+      <c r="AO8" s="81"/>
+      <c r="AP8" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="AQ8" s="19"/>
-      <c r="AR8" s="20"/>
-      <c r="AS8" s="18" t="s">
+      <c r="AQ8" s="37"/>
+      <c r="AR8" s="36"/>
+      <c r="AS8" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="AT8" s="19"/>
-      <c r="AU8" s="19"/>
-      <c r="AV8" s="19"/>
-      <c r="AW8" s="19"/>
-      <c r="AX8" s="19"/>
-      <c r="AY8" s="19"/>
-      <c r="AZ8" s="20"/>
-      <c r="BA8" s="18" t="s">
+      <c r="AT8" s="37"/>
+      <c r="AU8" s="37"/>
+      <c r="AV8" s="37"/>
+      <c r="AW8" s="37"/>
+      <c r="AX8" s="37"/>
+      <c r="AY8" s="37"/>
+      <c r="AZ8" s="36"/>
+      <c r="BA8" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="BB8" s="19"/>
-      <c r="BC8" s="20"/>
-      <c r="BD8" s="69" t="s">
+      <c r="BB8" s="37"/>
+      <c r="BC8" s="36"/>
+      <c r="BD8" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="BE8" s="69"/>
-      <c r="BF8" s="69"/>
-      <c r="BG8" s="69"/>
-      <c r="BH8" s="69"/>
-      <c r="BI8" s="69"/>
+      <c r="BE8" s="66"/>
+      <c r="BF8" s="66"/>
+      <c r="BG8" s="66"/>
+      <c r="BH8" s="66"/>
+      <c r="BI8" s="66"/>
       <c r="BJ8" s="8"/>
     </row>
     <row r="9" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="78" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="23" t="s">
+      <c r="B9" s="78"/>
+      <c r="C9" s="94" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23" t="s">
+      <c r="D9" s="94"/>
+      <c r="E9" s="94"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="94"/>
+      <c r="J9" s="94"/>
+      <c r="K9" s="94" t="s">
         <v>31</v>
       </c>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="21" t="s">
+      <c r="L9" s="94"/>
+      <c r="M9" s="94"/>
+      <c r="N9" s="94"/>
+      <c r="O9" s="94"/>
+      <c r="P9" s="94"/>
+      <c r="Q9" s="94"/>
+      <c r="R9" s="94"/>
+      <c r="S9" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="T9" s="21"/>
-      <c r="U9" s="21" t="s">
+      <c r="T9" s="83"/>
+      <c r="U9" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="V9" s="21"/>
-      <c r="W9" s="21" t="s">
+      <c r="V9" s="83"/>
+      <c r="W9" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="X9" s="21"/>
-      <c r="Y9" s="21" t="s">
+      <c r="X9" s="83"/>
+      <c r="Y9" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="Z9" s="21"/>
-      <c r="AA9" s="22" t="s">
+      <c r="Z9" s="83"/>
+      <c r="AA9" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="AB9" s="22"/>
-      <c r="AC9" s="24" t="s">
+      <c r="AB9" s="84"/>
+      <c r="AC9" s="85" t="s">
         <v>33</v>
       </c>
-      <c r="AD9" s="25"/>
-      <c r="AE9" s="25"/>
-      <c r="AF9" s="26"/>
-      <c r="AG9" s="24" t="s">
+      <c r="AD9" s="86"/>
+      <c r="AE9" s="86"/>
+      <c r="AF9" s="87"/>
+      <c r="AG9" s="85" t="s">
         <v>34</v>
       </c>
-      <c r="AH9" s="25"/>
-      <c r="AI9" s="26"/>
-      <c r="AJ9" s="23" t="s">
+      <c r="AH9" s="86"/>
+      <c r="AI9" s="87"/>
+      <c r="AJ9" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="AK9" s="23"/>
-      <c r="AL9" s="23"/>
-      <c r="AM9" s="23" t="s">
+      <c r="AK9" s="82"/>
+      <c r="AL9" s="82"/>
+      <c r="AM9" s="82" t="s">
         <v>36</v>
       </c>
-      <c r="AN9" s="23"/>
-      <c r="AO9" s="23"/>
-      <c r="AP9" s="21" t="s">
+      <c r="AN9" s="82"/>
+      <c r="AO9" s="82"/>
+      <c r="AP9" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="AQ9" s="21"/>
-      <c r="AR9" s="21"/>
-      <c r="AS9" s="23" t="s">
+      <c r="AQ9" s="83"/>
+      <c r="AR9" s="83"/>
+      <c r="AS9" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="AT9" s="23"/>
-      <c r="AU9" s="23"/>
-      <c r="AV9" s="23"/>
-      <c r="AW9" s="23"/>
-      <c r="AX9" s="23"/>
-      <c r="AY9" s="23"/>
-      <c r="AZ9" s="23"/>
-      <c r="BA9" s="21" t="s">
+      <c r="AT9" s="94"/>
+      <c r="AU9" s="94"/>
+      <c r="AV9" s="94"/>
+      <c r="AW9" s="94"/>
+      <c r="AX9" s="94"/>
+      <c r="AY9" s="94"/>
+      <c r="AZ9" s="94"/>
+      <c r="BA9" s="83" t="s">
         <v>39</v>
       </c>
-      <c r="BB9" s="21"/>
-      <c r="BC9" s="21"/>
-      <c r="BD9" s="70" t="s">
+      <c r="BB9" s="83"/>
+      <c r="BC9" s="83"/>
+      <c r="BD9" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="BE9" s="70"/>
-      <c r="BF9" s="70"/>
-      <c r="BG9" s="70"/>
-      <c r="BH9" s="70"/>
-      <c r="BI9" s="70"/>
+      <c r="BE9" s="67"/>
+      <c r="BF9" s="67"/>
+      <c r="BG9" s="67"/>
+      <c r="BH9" s="67"/>
+      <c r="BI9" s="67"/>
       <c r="BJ9" s="10"/>
     </row>
     <row r="10" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="29"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="27"/>
-      <c r="M10" s="27"/>
-      <c r="N10" s="27"/>
-      <c r="O10" s="27"/>
-      <c r="P10" s="27"/>
-      <c r="Q10" s="27"/>
-      <c r="R10" s="27"/>
-      <c r="S10" s="27"/>
-      <c r="T10" s="27"/>
-      <c r="U10" s="27"/>
-      <c r="V10" s="27"/>
-      <c r="W10" s="27"/>
-      <c r="X10" s="27"/>
-      <c r="Y10" s="27"/>
-      <c r="Z10" s="27"/>
-      <c r="AA10" s="30"/>
-      <c r="AB10" s="30"/>
-      <c r="AC10" s="27"/>
-      <c r="AD10" s="27"/>
-      <c r="AE10" s="27"/>
-      <c r="AF10" s="27"/>
-      <c r="AG10" s="27"/>
-      <c r="AH10" s="27"/>
-      <c r="AI10" s="27"/>
-      <c r="AJ10" s="27"/>
-      <c r="AK10" s="27"/>
-      <c r="AL10" s="27"/>
-      <c r="AM10" s="27"/>
-      <c r="AN10" s="27"/>
-      <c r="AO10" s="27"/>
-      <c r="AP10" s="27"/>
-      <c r="AQ10" s="27"/>
-      <c r="AR10" s="27"/>
-      <c r="AS10" s="27"/>
-      <c r="AT10" s="27"/>
-      <c r="AU10" s="27"/>
-      <c r="AV10" s="27"/>
-      <c r="AW10" s="27"/>
-      <c r="AX10" s="27"/>
-      <c r="AY10" s="27"/>
-      <c r="AZ10" s="27"/>
-      <c r="BA10" s="27"/>
-      <c r="BB10" s="27"/>
-      <c r="BC10" s="27"/>
-      <c r="BD10" s="27"/>
-      <c r="BE10" s="27"/>
-      <c r="BF10" s="27"/>
-      <c r="BG10" s="27"/>
-      <c r="BH10" s="27"/>
-      <c r="BI10" s="27"/>
+      <c r="A10" s="69"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="68"/>
+      <c r="K10" s="68"/>
+      <c r="L10" s="68"/>
+      <c r="M10" s="68"/>
+      <c r="N10" s="68"/>
+      <c r="O10" s="68"/>
+      <c r="P10" s="68"/>
+      <c r="Q10" s="68"/>
+      <c r="R10" s="68"/>
+      <c r="S10" s="68"/>
+      <c r="T10" s="68"/>
+      <c r="U10" s="68"/>
+      <c r="V10" s="68"/>
+      <c r="W10" s="68"/>
+      <c r="X10" s="68"/>
+      <c r="Y10" s="68"/>
+      <c r="Z10" s="68"/>
+      <c r="AA10" s="70"/>
+      <c r="AB10" s="70"/>
+      <c r="AC10" s="68"/>
+      <c r="AD10" s="68"/>
+      <c r="AE10" s="68"/>
+      <c r="AF10" s="68"/>
+      <c r="AG10" s="68"/>
+      <c r="AH10" s="68"/>
+      <c r="AI10" s="68"/>
+      <c r="AJ10" s="68"/>
+      <c r="AK10" s="68"/>
+      <c r="AL10" s="68"/>
+      <c r="AM10" s="68"/>
+      <c r="AN10" s="68"/>
+      <c r="AO10" s="68"/>
+      <c r="AP10" s="68"/>
+      <c r="AQ10" s="68"/>
+      <c r="AR10" s="68"/>
+      <c r="AS10" s="68"/>
+      <c r="AT10" s="68"/>
+      <c r="AU10" s="68"/>
+      <c r="AV10" s="68"/>
+      <c r="AW10" s="68"/>
+      <c r="AX10" s="68"/>
+      <c r="AY10" s="68"/>
+      <c r="AZ10" s="68"/>
+      <c r="BA10" s="68"/>
+      <c r="BB10" s="68"/>
+      <c r="BC10" s="68"/>
+      <c r="BD10" s="68"/>
+      <c r="BE10" s="68"/>
+      <c r="BF10" s="68"/>
+      <c r="BG10" s="68"/>
+      <c r="BH10" s="68"/>
+      <c r="BI10" s="68"/>
     </row>
     <row r="11" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
+      <c r="A11" s="40"/>
+      <c r="B11" s="40"/>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
@@ -1834,8 +1866,8 @@
       <c r="X11" s="15"/>
       <c r="Y11" s="15"/>
       <c r="Z11" s="15"/>
-      <c r="AA11" s="17"/>
-      <c r="AB11" s="17"/>
+      <c r="AA11" s="41"/>
+      <c r="AB11" s="41"/>
       <c r="AC11" s="15"/>
       <c r="AD11" s="15"/>
       <c r="AE11" s="15"/>
@@ -1871,8 +1903,8 @@
       <c r="BI11" s="15"/>
     </row>
     <row r="12" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
+      <c r="A12" s="40"/>
+      <c r="B12" s="40"/>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
@@ -1897,8 +1929,8 @@
       <c r="X12" s="15"/>
       <c r="Y12" s="15"/>
       <c r="Z12" s="15"/>
-      <c r="AA12" s="17"/>
-      <c r="AB12" s="17"/>
+      <c r="AA12" s="41"/>
+      <c r="AB12" s="41"/>
       <c r="AC12" s="15"/>
       <c r="AD12" s="15"/>
       <c r="AE12" s="15"/>
@@ -1934,8 +1966,8 @@
       <c r="BI12" s="15"/>
     </row>
     <row r="13" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
+      <c r="A13" s="40"/>
+      <c r="B13" s="40"/>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
@@ -1960,8 +1992,8 @@
       <c r="X13" s="15"/>
       <c r="Y13" s="15"/>
       <c r="Z13" s="15"/>
-      <c r="AA13" s="17"/>
-      <c r="AB13" s="17"/>
+      <c r="AA13" s="41"/>
+      <c r="AB13" s="41"/>
       <c r="AC13" s="15"/>
       <c r="AD13" s="15"/>
       <c r="AE13" s="15"/>
@@ -1997,8 +2029,8 @@
       <c r="BI13" s="15"/>
     </row>
     <row r="14" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
+      <c r="A14" s="40"/>
+      <c r="B14" s="40"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
@@ -2023,8 +2055,8 @@
       <c r="X14" s="15"/>
       <c r="Y14" s="15"/>
       <c r="Z14" s="15"/>
-      <c r="AA14" s="17"/>
-      <c r="AB14" s="17"/>
+      <c r="AA14" s="41"/>
+      <c r="AB14" s="41"/>
       <c r="AC14" s="15"/>
       <c r="AD14" s="15"/>
       <c r="AE14" s="15"/>
@@ -2060,8 +2092,8 @@
       <c r="BI14" s="15"/>
     </row>
     <row r="15" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
+      <c r="A15" s="40"/>
+      <c r="B15" s="40"/>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
@@ -2086,8 +2118,8 @@
       <c r="X15" s="15"/>
       <c r="Y15" s="15"/>
       <c r="Z15" s="15"/>
-      <c r="AA15" s="17"/>
-      <c r="AB15" s="17"/>
+      <c r="AA15" s="41"/>
+      <c r="AB15" s="41"/>
       <c r="AC15" s="15"/>
       <c r="AD15" s="15"/>
       <c r="AE15" s="15"/>
@@ -2123,8 +2155,8 @@
       <c r="BI15" s="15"/>
     </row>
     <row r="16" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
+      <c r="A16" s="40"/>
+      <c r="B16" s="40"/>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
@@ -2149,8 +2181,8 @@
       <c r="X16" s="15"/>
       <c r="Y16" s="15"/>
       <c r="Z16" s="15"/>
-      <c r="AA16" s="17"/>
-      <c r="AB16" s="17"/>
+      <c r="AA16" s="41"/>
+      <c r="AB16" s="41"/>
       <c r="AC16" s="15"/>
       <c r="AD16" s="15"/>
       <c r="AE16" s="15"/>
@@ -2186,8 +2218,8 @@
       <c r="BI16" s="15"/>
     </row>
     <row r="17" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
+      <c r="A17" s="40"/>
+      <c r="B17" s="40"/>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
@@ -2212,8 +2244,8 @@
       <c r="X17" s="15"/>
       <c r="Y17" s="15"/>
       <c r="Z17" s="15"/>
-      <c r="AA17" s="17"/>
-      <c r="AB17" s="17"/>
+      <c r="AA17" s="41"/>
+      <c r="AB17" s="41"/>
       <c r="AC17" s="15"/>
       <c r="AD17" s="15"/>
       <c r="AE17" s="15"/>
@@ -2249,8 +2281,8 @@
       <c r="BI17" s="15"/>
     </row>
     <row r="18" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
+      <c r="A18" s="40"/>
+      <c r="B18" s="40"/>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
@@ -2275,8 +2307,8 @@
       <c r="X18" s="15"/>
       <c r="Y18" s="15"/>
       <c r="Z18" s="15"/>
-      <c r="AA18" s="17"/>
-      <c r="AB18" s="17"/>
+      <c r="AA18" s="41"/>
+      <c r="AB18" s="41"/>
       <c r="AC18" s="15"/>
       <c r="AD18" s="15"/>
       <c r="AE18" s="15"/>
@@ -2312,8 +2344,8 @@
       <c r="BI18" s="15"/>
     </row>
     <row r="19" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
+      <c r="A19" s="40"/>
+      <c r="B19" s="40"/>
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
@@ -2338,8 +2370,8 @@
       <c r="X19" s="15"/>
       <c r="Y19" s="15"/>
       <c r="Z19" s="15"/>
-      <c r="AA19" s="17"/>
-      <c r="AB19" s="17"/>
+      <c r="AA19" s="41"/>
+      <c r="AB19" s="41"/>
       <c r="AC19" s="15"/>
       <c r="AD19" s="15"/>
       <c r="AE19" s="15"/>
@@ -2375,8 +2407,8 @@
       <c r="BI19" s="15"/>
     </row>
     <row r="20" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
+      <c r="A20" s="40"/>
+      <c r="B20" s="40"/>
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
@@ -2401,8 +2433,8 @@
       <c r="X20" s="15"/>
       <c r="Y20" s="15"/>
       <c r="Z20" s="15"/>
-      <c r="AA20" s="17"/>
-      <c r="AB20" s="17"/>
+      <c r="AA20" s="41"/>
+      <c r="AB20" s="41"/>
       <c r="AC20" s="15"/>
       <c r="AD20" s="15"/>
       <c r="AE20" s="15"/>
@@ -2438,8 +2470,8 @@
       <c r="BI20" s="15"/>
     </row>
     <row r="21" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
+      <c r="A21" s="40"/>
+      <c r="B21" s="40"/>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
@@ -2464,8 +2496,8 @@
       <c r="X21" s="15"/>
       <c r="Y21" s="15"/>
       <c r="Z21" s="15"/>
-      <c r="AA21" s="17"/>
-      <c r="AB21" s="17"/>
+      <c r="AA21" s="41"/>
+      <c r="AB21" s="41"/>
       <c r="AC21" s="15"/>
       <c r="AD21" s="15"/>
       <c r="AE21" s="15"/>
@@ -2501,8 +2533,8 @@
       <c r="BI21" s="15"/>
     </row>
     <row r="22" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
+      <c r="A22" s="40"/>
+      <c r="B22" s="40"/>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
@@ -2527,8 +2559,8 @@
       <c r="X22" s="15"/>
       <c r="Y22" s="15"/>
       <c r="Z22" s="15"/>
-      <c r="AA22" s="17"/>
-      <c r="AB22" s="17"/>
+      <c r="AA22" s="41"/>
+      <c r="AB22" s="41"/>
       <c r="AC22" s="15"/>
       <c r="AD22" s="15"/>
       <c r="AE22" s="15"/>
@@ -2564,8 +2596,8 @@
       <c r="BI22" s="15"/>
     </row>
     <row r="23" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
+      <c r="A23" s="40"/>
+      <c r="B23" s="40"/>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
@@ -2590,8 +2622,8 @@
       <c r="X23" s="15"/>
       <c r="Y23" s="15"/>
       <c r="Z23" s="15"/>
-      <c r="AA23" s="17"/>
-      <c r="AB23" s="17"/>
+      <c r="AA23" s="41"/>
+      <c r="AB23" s="41"/>
       <c r="AC23" s="15"/>
       <c r="AD23" s="15"/>
       <c r="AE23" s="15"/>
@@ -2627,8 +2659,8 @@
       <c r="BI23" s="15"/>
     </row>
     <row r="24" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
+      <c r="A24" s="40"/>
+      <c r="B24" s="40"/>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
@@ -2653,8 +2685,8 @@
       <c r="X24" s="15"/>
       <c r="Y24" s="15"/>
       <c r="Z24" s="15"/>
-      <c r="AA24" s="17"/>
-      <c r="AB24" s="17"/>
+      <c r="AA24" s="41"/>
+      <c r="AB24" s="41"/>
       <c r="AC24" s="15"/>
       <c r="AD24" s="15"/>
       <c r="AE24" s="15"/>
@@ -2690,8 +2722,8 @@
       <c r="BI24" s="15"/>
     </row>
     <row r="25" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
+      <c r="A25" s="40"/>
+      <c r="B25" s="40"/>
       <c r="C25" s="15"/>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
@@ -2716,8 +2748,8 @@
       <c r="X25" s="15"/>
       <c r="Y25" s="15"/>
       <c r="Z25" s="15"/>
-      <c r="AA25" s="17"/>
-      <c r="AB25" s="17"/>
+      <c r="AA25" s="41"/>
+      <c r="AB25" s="41"/>
       <c r="AC25" s="15"/>
       <c r="AD25" s="15"/>
       <c r="AE25" s="15"/>
@@ -2753,8 +2785,8 @@
       <c r="BI25" s="15"/>
     </row>
     <row r="26" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
+      <c r="A26" s="40"/>
+      <c r="B26" s="40"/>
       <c r="C26" s="15"/>
       <c r="D26" s="15"/>
       <c r="E26" s="15"/>
@@ -2779,8 +2811,8 @@
       <c r="X26" s="15"/>
       <c r="Y26" s="15"/>
       <c r="Z26" s="15"/>
-      <c r="AA26" s="17"/>
-      <c r="AB26" s="17"/>
+      <c r="AA26" s="41"/>
+      <c r="AB26" s="41"/>
       <c r="AC26" s="15"/>
       <c r="AD26" s="15"/>
       <c r="AE26" s="15"/>
@@ -2816,8 +2848,8 @@
       <c r="BI26" s="15"/>
     </row>
     <row r="27" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
+      <c r="A27" s="40"/>
+      <c r="B27" s="40"/>
       <c r="C27" s="15"/>
       <c r="D27" s="15"/>
       <c r="E27" s="15"/>
@@ -2842,8 +2874,8 @@
       <c r="X27" s="15"/>
       <c r="Y27" s="15"/>
       <c r="Z27" s="15"/>
-      <c r="AA27" s="17"/>
-      <c r="AB27" s="17"/>
+      <c r="AA27" s="41"/>
+      <c r="AB27" s="41"/>
       <c r="AC27" s="15"/>
       <c r="AD27" s="15"/>
       <c r="AE27" s="15"/>
@@ -2879,8 +2911,8 @@
       <c r="BI27" s="15"/>
     </row>
     <row r="28" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
+      <c r="A28" s="40"/>
+      <c r="B28" s="40"/>
       <c r="C28" s="15"/>
       <c r="D28" s="15"/>
       <c r="E28" s="15"/>
@@ -2905,8 +2937,8 @@
       <c r="X28" s="15"/>
       <c r="Y28" s="15"/>
       <c r="Z28" s="15"/>
-      <c r="AA28" s="17"/>
-      <c r="AB28" s="17"/>
+      <c r="AA28" s="41"/>
+      <c r="AB28" s="41"/>
       <c r="AC28" s="15"/>
       <c r="AD28" s="15"/>
       <c r="AE28" s="15"/>
@@ -2942,8 +2974,8 @@
       <c r="BI28" s="15"/>
     </row>
     <row r="29" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="16"/>
-      <c r="B29" s="16"/>
+      <c r="A29" s="40"/>
+      <c r="B29" s="40"/>
       <c r="C29" s="15"/>
       <c r="D29" s="15"/>
       <c r="E29" s="15"/>
@@ -2968,8 +3000,8 @@
       <c r="X29" s="15"/>
       <c r="Y29" s="15"/>
       <c r="Z29" s="15"/>
-      <c r="AA29" s="17"/>
-      <c r="AB29" s="17"/>
+      <c r="AA29" s="41"/>
+      <c r="AB29" s="41"/>
       <c r="AC29" s="15"/>
       <c r="AD29" s="15"/>
       <c r="AE29" s="15"/>
@@ -3005,8 +3037,8 @@
       <c r="BI29" s="15"/>
     </row>
     <row r="30" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="16"/>
-      <c r="B30" s="16"/>
+      <c r="A30" s="40"/>
+      <c r="B30" s="40"/>
       <c r="C30" s="15"/>
       <c r="D30" s="15"/>
       <c r="E30" s="15"/>
@@ -3031,8 +3063,8 @@
       <c r="X30" s="15"/>
       <c r="Y30" s="15"/>
       <c r="Z30" s="15"/>
-      <c r="AA30" s="17"/>
-      <c r="AB30" s="17"/>
+      <c r="AA30" s="41"/>
+      <c r="AB30" s="41"/>
       <c r="AC30" s="15"/>
       <c r="AD30" s="15"/>
       <c r="AE30" s="15"/>
@@ -4743,9 +4775,9 @@
       <c r="AI65" s="6"/>
       <c r="AJ65" s="6"/>
       <c r="AK65" s="6"/>
-      <c r="AL65" s="71"/>
-      <c r="AM65" s="71"/>
-      <c r="AN65" s="71"/>
+      <c r="AL65" s="16"/>
+      <c r="AM65" s="16"/>
+      <c r="AN65" s="16"/>
     </row>
     <row r="66" spans="1:41" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4"/>
@@ -4921,6 +4953,372 @@
     </row>
   </sheetData>
   <mergeCells count="390">
+    <mergeCell ref="AS29:AZ29"/>
+    <mergeCell ref="BA29:BC29"/>
+    <mergeCell ref="BD29:BI29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:J30"/>
+    <mergeCell ref="K30:R30"/>
+    <mergeCell ref="S30:T30"/>
+    <mergeCell ref="U30:V30"/>
+    <mergeCell ref="AA30:AB30"/>
+    <mergeCell ref="AC30:AF30"/>
+    <mergeCell ref="AJ30:AL30"/>
+    <mergeCell ref="AM30:AO30"/>
+    <mergeCell ref="AP30:AR30"/>
+    <mergeCell ref="AS30:AZ30"/>
+    <mergeCell ref="BA30:BC30"/>
+    <mergeCell ref="BD30:BI30"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:J29"/>
+    <mergeCell ref="K29:R29"/>
+    <mergeCell ref="S29:T29"/>
+    <mergeCell ref="U29:V29"/>
+    <mergeCell ref="W29:X29"/>
+    <mergeCell ref="Y29:Z29"/>
+    <mergeCell ref="AA29:AB29"/>
+    <mergeCell ref="AC29:AF29"/>
+    <mergeCell ref="AG27:AI27"/>
+    <mergeCell ref="AJ27:AL27"/>
+    <mergeCell ref="AM27:AO27"/>
+    <mergeCell ref="AP27:AR27"/>
+    <mergeCell ref="W27:X27"/>
+    <mergeCell ref="Y27:Z27"/>
+    <mergeCell ref="AA27:AB27"/>
+    <mergeCell ref="AC27:AF27"/>
+    <mergeCell ref="AG29:AI29"/>
+    <mergeCell ref="AJ29:AL29"/>
+    <mergeCell ref="AM29:AO29"/>
+    <mergeCell ref="AP29:AR29"/>
+    <mergeCell ref="AS27:AZ27"/>
+    <mergeCell ref="BA27:BC27"/>
+    <mergeCell ref="BD27:BI27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:J28"/>
+    <mergeCell ref="K28:R28"/>
+    <mergeCell ref="S28:T28"/>
+    <mergeCell ref="U28:V28"/>
+    <mergeCell ref="W28:X28"/>
+    <mergeCell ref="Y28:Z28"/>
+    <mergeCell ref="AA28:AB28"/>
+    <mergeCell ref="AC28:AF28"/>
+    <mergeCell ref="AG28:AI28"/>
+    <mergeCell ref="AJ28:AL28"/>
+    <mergeCell ref="AM28:AO28"/>
+    <mergeCell ref="AP28:AR28"/>
+    <mergeCell ref="AS28:AZ28"/>
+    <mergeCell ref="BA28:BC28"/>
+    <mergeCell ref="BD28:BI28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:J27"/>
+    <mergeCell ref="K27:R27"/>
+    <mergeCell ref="S27:T27"/>
+    <mergeCell ref="U27:V27"/>
+    <mergeCell ref="AG26:AI26"/>
+    <mergeCell ref="AJ26:AL26"/>
+    <mergeCell ref="AM26:AO26"/>
+    <mergeCell ref="AP26:AR26"/>
+    <mergeCell ref="AS26:AZ26"/>
+    <mergeCell ref="BA26:BC26"/>
+    <mergeCell ref="BD26:BI26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:J25"/>
+    <mergeCell ref="K25:R25"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:J26"/>
+    <mergeCell ref="K26:R26"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="W26:X26"/>
+    <mergeCell ref="Y26:Z26"/>
+    <mergeCell ref="AA26:AB26"/>
+    <mergeCell ref="AC26:AF26"/>
+    <mergeCell ref="AC25:AF25"/>
+    <mergeCell ref="AP23:AR23"/>
+    <mergeCell ref="AC23:AF23"/>
+    <mergeCell ref="AG23:AI23"/>
+    <mergeCell ref="AJ23:AL23"/>
+    <mergeCell ref="AM23:AO23"/>
+    <mergeCell ref="AS25:AZ25"/>
+    <mergeCell ref="BA25:BC25"/>
+    <mergeCell ref="BD25:BI25"/>
+    <mergeCell ref="C23:J23"/>
+    <mergeCell ref="K23:R23"/>
+    <mergeCell ref="AG25:AI25"/>
+    <mergeCell ref="AJ25:AL25"/>
+    <mergeCell ref="AM25:AO25"/>
+    <mergeCell ref="AP25:AR25"/>
+    <mergeCell ref="AS23:AZ23"/>
+    <mergeCell ref="BA23:BC23"/>
+    <mergeCell ref="BD23:BI23"/>
+    <mergeCell ref="AG24:AI24"/>
+    <mergeCell ref="AJ24:AL24"/>
+    <mergeCell ref="AM24:AO24"/>
+    <mergeCell ref="AP24:AR24"/>
+    <mergeCell ref="AS24:AZ24"/>
+    <mergeCell ref="BA24:BC24"/>
+    <mergeCell ref="BD24:BI24"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="W23:X23"/>
+    <mergeCell ref="Y23:Z23"/>
+    <mergeCell ref="AA23:AB23"/>
+    <mergeCell ref="W25:X25"/>
+    <mergeCell ref="Y25:Z25"/>
+    <mergeCell ref="AA25:AB25"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:J24"/>
+    <mergeCell ref="K24:R24"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="W24:X24"/>
+    <mergeCell ref="Y24:Z24"/>
+    <mergeCell ref="AA24:AB24"/>
+    <mergeCell ref="AC24:AF24"/>
+    <mergeCell ref="AP21:AR21"/>
+    <mergeCell ref="AS21:AZ21"/>
+    <mergeCell ref="BA21:BC21"/>
+    <mergeCell ref="BD21:BI21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:J22"/>
+    <mergeCell ref="K22:R22"/>
+    <mergeCell ref="S22:T22"/>
+    <mergeCell ref="U22:V22"/>
+    <mergeCell ref="W22:X22"/>
+    <mergeCell ref="Y22:Z22"/>
+    <mergeCell ref="AA22:AB22"/>
+    <mergeCell ref="AC22:AF22"/>
+    <mergeCell ref="AG22:AI22"/>
+    <mergeCell ref="AJ22:AL22"/>
+    <mergeCell ref="AM22:AO22"/>
+    <mergeCell ref="AP22:AR22"/>
+    <mergeCell ref="AS22:AZ22"/>
+    <mergeCell ref="BA22:BC22"/>
+    <mergeCell ref="BD22:BI22"/>
+    <mergeCell ref="AM21:AO21"/>
+    <mergeCell ref="AJ19:AL19"/>
+    <mergeCell ref="AM19:AO19"/>
+    <mergeCell ref="AP19:AR19"/>
+    <mergeCell ref="AS19:AZ19"/>
+    <mergeCell ref="BA19:BC19"/>
+    <mergeCell ref="BD19:BI19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:J20"/>
+    <mergeCell ref="K20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="U20:V20"/>
+    <mergeCell ref="W20:X20"/>
+    <mergeCell ref="Y20:Z20"/>
+    <mergeCell ref="AA20:AB20"/>
+    <mergeCell ref="AC20:AF20"/>
+    <mergeCell ref="AG20:AI20"/>
+    <mergeCell ref="AJ20:AL20"/>
+    <mergeCell ref="AM20:AO20"/>
+    <mergeCell ref="AP20:AR20"/>
+    <mergeCell ref="AS20:AZ20"/>
+    <mergeCell ref="BA20:BC20"/>
+    <mergeCell ref="BD20:BI20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:J19"/>
+    <mergeCell ref="K19:R19"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="U19:V19"/>
+    <mergeCell ref="W19:X19"/>
+    <mergeCell ref="Y19:Z19"/>
+    <mergeCell ref="AA19:AB19"/>
+    <mergeCell ref="AC19:AF19"/>
+    <mergeCell ref="AG17:AI17"/>
+    <mergeCell ref="K17:R17"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="U17:V17"/>
+    <mergeCell ref="W17:X17"/>
+    <mergeCell ref="Y17:Z17"/>
+    <mergeCell ref="AA17:AB17"/>
+    <mergeCell ref="AC17:AF17"/>
+    <mergeCell ref="AG19:AI19"/>
+    <mergeCell ref="AJ17:AL17"/>
+    <mergeCell ref="AM17:AO17"/>
+    <mergeCell ref="AP17:AR17"/>
+    <mergeCell ref="AS17:AZ17"/>
+    <mergeCell ref="BA17:BC17"/>
+    <mergeCell ref="BD17:BI17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:J18"/>
+    <mergeCell ref="K18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="U18:V18"/>
+    <mergeCell ref="W18:X18"/>
+    <mergeCell ref="Y18:Z18"/>
+    <mergeCell ref="AA18:AB18"/>
+    <mergeCell ref="AC18:AF18"/>
+    <mergeCell ref="AG18:AI18"/>
+    <mergeCell ref="AJ18:AL18"/>
+    <mergeCell ref="AM18:AO18"/>
+    <mergeCell ref="AP18:AR18"/>
+    <mergeCell ref="AS18:AZ18"/>
+    <mergeCell ref="BA18:BC18"/>
+    <mergeCell ref="BD18:BI18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:J17"/>
+    <mergeCell ref="AJ15:AL15"/>
+    <mergeCell ref="AM15:AO15"/>
+    <mergeCell ref="AP15:AR15"/>
+    <mergeCell ref="AS15:AZ15"/>
+    <mergeCell ref="BA15:BC15"/>
+    <mergeCell ref="BD15:BI15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:J16"/>
+    <mergeCell ref="K16:R16"/>
+    <mergeCell ref="S16:T16"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="Y16:Z16"/>
+    <mergeCell ref="AA16:AB16"/>
+    <mergeCell ref="AC16:AF16"/>
+    <mergeCell ref="AG16:AI16"/>
+    <mergeCell ref="AJ16:AL16"/>
+    <mergeCell ref="AM16:AO16"/>
+    <mergeCell ref="AP16:AR16"/>
+    <mergeCell ref="AS16:AZ16"/>
+    <mergeCell ref="BA16:BC16"/>
+    <mergeCell ref="BD16:BI16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:J15"/>
+    <mergeCell ref="K15:R15"/>
+    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="U15:V15"/>
+    <mergeCell ref="W15:X15"/>
+    <mergeCell ref="Y15:Z15"/>
+    <mergeCell ref="AA15:AB15"/>
+    <mergeCell ref="AC15:AF15"/>
+    <mergeCell ref="AG13:AI13"/>
+    <mergeCell ref="K13:R13"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="W13:X13"/>
+    <mergeCell ref="Y13:Z13"/>
+    <mergeCell ref="AA13:AB13"/>
+    <mergeCell ref="AC13:AF13"/>
+    <mergeCell ref="AG15:AI15"/>
+    <mergeCell ref="AJ13:AL13"/>
+    <mergeCell ref="AM13:AO13"/>
+    <mergeCell ref="AP13:AR13"/>
+    <mergeCell ref="AS13:AZ13"/>
+    <mergeCell ref="BA13:BC13"/>
+    <mergeCell ref="BD13:BI13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="K14:R14"/>
+    <mergeCell ref="S14:T14"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="W14:X14"/>
+    <mergeCell ref="Y14:Z14"/>
+    <mergeCell ref="AA14:AB14"/>
+    <mergeCell ref="AC14:AF14"/>
+    <mergeCell ref="AG14:AI14"/>
+    <mergeCell ref="AJ14:AL14"/>
+    <mergeCell ref="AM14:AO14"/>
+    <mergeCell ref="AP14:AR14"/>
+    <mergeCell ref="AS14:AZ14"/>
+    <mergeCell ref="BA14:BC14"/>
+    <mergeCell ref="BD14:BI14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:J13"/>
+    <mergeCell ref="AG11:AI11"/>
+    <mergeCell ref="AJ11:AL11"/>
+    <mergeCell ref="AM11:AO11"/>
+    <mergeCell ref="AP11:AR11"/>
+    <mergeCell ref="AS11:AZ11"/>
+    <mergeCell ref="BA11:BC11"/>
+    <mergeCell ref="BD11:BI11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="K12:R12"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="U12:V12"/>
+    <mergeCell ref="W12:X12"/>
+    <mergeCell ref="Y12:Z12"/>
+    <mergeCell ref="AA12:AB12"/>
+    <mergeCell ref="AC12:AF12"/>
+    <mergeCell ref="AG12:AI12"/>
+    <mergeCell ref="AJ12:AL12"/>
+    <mergeCell ref="AM12:AO12"/>
+    <mergeCell ref="AP12:AR12"/>
+    <mergeCell ref="AS12:AZ12"/>
+    <mergeCell ref="BA12:BC12"/>
+    <mergeCell ref="BD12:BI12"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:J11"/>
+    <mergeCell ref="K11:R11"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="W11:X11"/>
+    <mergeCell ref="Y11:Z11"/>
+    <mergeCell ref="AA11:AB11"/>
+    <mergeCell ref="AC11:AF11"/>
+    <mergeCell ref="BA8:BC8"/>
+    <mergeCell ref="Y9:Z9"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AJ9:AL9"/>
+    <mergeCell ref="AM9:AO9"/>
+    <mergeCell ref="AP9:AR9"/>
+    <mergeCell ref="AS9:AZ9"/>
+    <mergeCell ref="BA9:BC9"/>
+    <mergeCell ref="AG9:AI9"/>
+    <mergeCell ref="AC9:AF9"/>
+    <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="AC8:AF8"/>
+    <mergeCell ref="AG8:AI8"/>
+    <mergeCell ref="AJ8:AL8"/>
+    <mergeCell ref="AM8:AO8"/>
+    <mergeCell ref="AP8:AR8"/>
+    <mergeCell ref="AJ10:AL10"/>
+    <mergeCell ref="AM10:AO10"/>
+    <mergeCell ref="AP10:AR10"/>
+    <mergeCell ref="AS10:AZ10"/>
+    <mergeCell ref="BA10:BC10"/>
+    <mergeCell ref="BD10:BI10"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:J9"/>
+    <mergeCell ref="K9:R9"/>
+    <mergeCell ref="S9:T9"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="W9:X9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="K10:R10"/>
+    <mergeCell ref="S10:T10"/>
+    <mergeCell ref="U10:V10"/>
+    <mergeCell ref="W10:X10"/>
+    <mergeCell ref="Y10:Z10"/>
+    <mergeCell ref="AA10:AB10"/>
+    <mergeCell ref="AC10:AF10"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="AS8:AZ8"/>
+    <mergeCell ref="W8:X8"/>
+    <mergeCell ref="Y8:Z8"/>
+    <mergeCell ref="AY1:BI1"/>
+    <mergeCell ref="AY2:BI4"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="F2:J3"/>
+    <mergeCell ref="K1:V1"/>
+    <mergeCell ref="K2:V3"/>
+    <mergeCell ref="W1:AH1"/>
+    <mergeCell ref="W2:AH3"/>
+    <mergeCell ref="AI1:AM1"/>
+    <mergeCell ref="AN1:AR1"/>
+    <mergeCell ref="AI2:AM3"/>
+    <mergeCell ref="AN2:AR3"/>
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="K4:O4"/>
+    <mergeCell ref="P4:T4"/>
+    <mergeCell ref="AI4:AR6"/>
+    <mergeCell ref="U4:AH4"/>
+    <mergeCell ref="BD8:BI8"/>
+    <mergeCell ref="BD9:BI9"/>
+    <mergeCell ref="AG10:AI10"/>
     <mergeCell ref="W30:X30"/>
     <mergeCell ref="Y30:Z30"/>
     <mergeCell ref="AL65:AN65"/>
@@ -4945,372 +5343,6 @@
     <mergeCell ref="AC21:AF21"/>
     <mergeCell ref="AG21:AI21"/>
     <mergeCell ref="AJ21:AL21"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="AS8:AZ8"/>
-    <mergeCell ref="W8:X8"/>
-    <mergeCell ref="Y8:Z8"/>
-    <mergeCell ref="AY1:BI1"/>
-    <mergeCell ref="AY2:BI4"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="F2:J3"/>
-    <mergeCell ref="K1:V1"/>
-    <mergeCell ref="K2:V3"/>
-    <mergeCell ref="W1:AH1"/>
-    <mergeCell ref="W2:AH3"/>
-    <mergeCell ref="AI1:AM1"/>
-    <mergeCell ref="AN1:AR1"/>
-    <mergeCell ref="AI2:AM3"/>
-    <mergeCell ref="AN2:AR3"/>
-    <mergeCell ref="F4:J4"/>
-    <mergeCell ref="K4:O4"/>
-    <mergeCell ref="P4:T4"/>
-    <mergeCell ref="AI4:AR6"/>
-    <mergeCell ref="U4:AH4"/>
-    <mergeCell ref="BD8:BI8"/>
-    <mergeCell ref="BD9:BI9"/>
-    <mergeCell ref="AG10:AI10"/>
-    <mergeCell ref="AJ10:AL10"/>
-    <mergeCell ref="AM10:AO10"/>
-    <mergeCell ref="AP10:AR10"/>
-    <mergeCell ref="AS10:AZ10"/>
-    <mergeCell ref="BA10:BC10"/>
-    <mergeCell ref="BD10:BI10"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:J9"/>
-    <mergeCell ref="K9:R9"/>
-    <mergeCell ref="S9:T9"/>
-    <mergeCell ref="U9:V9"/>
-    <mergeCell ref="W9:X9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="K10:R10"/>
-    <mergeCell ref="S10:T10"/>
-    <mergeCell ref="U10:V10"/>
-    <mergeCell ref="W10:X10"/>
-    <mergeCell ref="Y10:Z10"/>
-    <mergeCell ref="AA10:AB10"/>
-    <mergeCell ref="AC10:AF10"/>
-    <mergeCell ref="C11:J11"/>
-    <mergeCell ref="K11:R11"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="W11:X11"/>
-    <mergeCell ref="Y11:Z11"/>
-    <mergeCell ref="AA11:AB11"/>
-    <mergeCell ref="AC11:AF11"/>
-    <mergeCell ref="BA8:BC8"/>
-    <mergeCell ref="Y9:Z9"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AJ9:AL9"/>
-    <mergeCell ref="AM9:AO9"/>
-    <mergeCell ref="AP9:AR9"/>
-    <mergeCell ref="AS9:AZ9"/>
-    <mergeCell ref="BA9:BC9"/>
-    <mergeCell ref="AG9:AI9"/>
-    <mergeCell ref="AC9:AF9"/>
-    <mergeCell ref="AA8:AB8"/>
-    <mergeCell ref="AC8:AF8"/>
-    <mergeCell ref="AG8:AI8"/>
-    <mergeCell ref="AJ8:AL8"/>
-    <mergeCell ref="AM8:AO8"/>
-    <mergeCell ref="AP8:AR8"/>
-    <mergeCell ref="AG11:AI11"/>
-    <mergeCell ref="AJ11:AL11"/>
-    <mergeCell ref="AM11:AO11"/>
-    <mergeCell ref="AP11:AR11"/>
-    <mergeCell ref="AS11:AZ11"/>
-    <mergeCell ref="BA11:BC11"/>
-    <mergeCell ref="BD11:BI11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:J12"/>
-    <mergeCell ref="K12:R12"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="U12:V12"/>
-    <mergeCell ref="W12:X12"/>
-    <mergeCell ref="Y12:Z12"/>
-    <mergeCell ref="AA12:AB12"/>
-    <mergeCell ref="AC12:AF12"/>
-    <mergeCell ref="AG12:AI12"/>
-    <mergeCell ref="AJ12:AL12"/>
-    <mergeCell ref="AM12:AO12"/>
-    <mergeCell ref="AP12:AR12"/>
-    <mergeCell ref="AS12:AZ12"/>
-    <mergeCell ref="BA12:BC12"/>
-    <mergeCell ref="BD12:BI12"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="AJ13:AL13"/>
-    <mergeCell ref="AM13:AO13"/>
-    <mergeCell ref="AP13:AR13"/>
-    <mergeCell ref="AS13:AZ13"/>
-    <mergeCell ref="BA13:BC13"/>
-    <mergeCell ref="BD13:BI13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:J14"/>
-    <mergeCell ref="K14:R14"/>
-    <mergeCell ref="S14:T14"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="W14:X14"/>
-    <mergeCell ref="Y14:Z14"/>
-    <mergeCell ref="AA14:AB14"/>
-    <mergeCell ref="AC14:AF14"/>
-    <mergeCell ref="AG14:AI14"/>
-    <mergeCell ref="AJ14:AL14"/>
-    <mergeCell ref="AM14:AO14"/>
-    <mergeCell ref="AP14:AR14"/>
-    <mergeCell ref="AS14:AZ14"/>
-    <mergeCell ref="BA14:BC14"/>
-    <mergeCell ref="BD14:BI14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="K15:R15"/>
-    <mergeCell ref="S15:T15"/>
-    <mergeCell ref="U15:V15"/>
-    <mergeCell ref="W15:X15"/>
-    <mergeCell ref="Y15:Z15"/>
-    <mergeCell ref="AA15:AB15"/>
-    <mergeCell ref="AC15:AF15"/>
-    <mergeCell ref="AG13:AI13"/>
-    <mergeCell ref="K13:R13"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="W13:X13"/>
-    <mergeCell ref="Y13:Z13"/>
-    <mergeCell ref="AA13:AB13"/>
-    <mergeCell ref="AC13:AF13"/>
-    <mergeCell ref="AG15:AI15"/>
-    <mergeCell ref="AJ15:AL15"/>
-    <mergeCell ref="AM15:AO15"/>
-    <mergeCell ref="AP15:AR15"/>
-    <mergeCell ref="AS15:AZ15"/>
-    <mergeCell ref="BA15:BC15"/>
-    <mergeCell ref="BD15:BI15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:J16"/>
-    <mergeCell ref="K16:R16"/>
-    <mergeCell ref="S16:T16"/>
-    <mergeCell ref="U16:V16"/>
-    <mergeCell ref="W16:X16"/>
-    <mergeCell ref="Y16:Z16"/>
-    <mergeCell ref="AA16:AB16"/>
-    <mergeCell ref="AC16:AF16"/>
-    <mergeCell ref="AG16:AI16"/>
-    <mergeCell ref="AJ16:AL16"/>
-    <mergeCell ref="AM16:AO16"/>
-    <mergeCell ref="AP16:AR16"/>
-    <mergeCell ref="AS16:AZ16"/>
-    <mergeCell ref="BA16:BC16"/>
-    <mergeCell ref="BD16:BI16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:J15"/>
-    <mergeCell ref="AJ17:AL17"/>
-    <mergeCell ref="AM17:AO17"/>
-    <mergeCell ref="AP17:AR17"/>
-    <mergeCell ref="AS17:AZ17"/>
-    <mergeCell ref="BA17:BC17"/>
-    <mergeCell ref="BD17:BI17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:J18"/>
-    <mergeCell ref="K18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="U18:V18"/>
-    <mergeCell ref="W18:X18"/>
-    <mergeCell ref="Y18:Z18"/>
-    <mergeCell ref="AA18:AB18"/>
-    <mergeCell ref="AC18:AF18"/>
-    <mergeCell ref="AG18:AI18"/>
-    <mergeCell ref="AJ18:AL18"/>
-    <mergeCell ref="AM18:AO18"/>
-    <mergeCell ref="AP18:AR18"/>
-    <mergeCell ref="AS18:AZ18"/>
-    <mergeCell ref="BA18:BC18"/>
-    <mergeCell ref="BD18:BI18"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:J17"/>
-    <mergeCell ref="K19:R19"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="U19:V19"/>
-    <mergeCell ref="W19:X19"/>
-    <mergeCell ref="Y19:Z19"/>
-    <mergeCell ref="AA19:AB19"/>
-    <mergeCell ref="AC19:AF19"/>
-    <mergeCell ref="AG17:AI17"/>
-    <mergeCell ref="K17:R17"/>
-    <mergeCell ref="S17:T17"/>
-    <mergeCell ref="U17:V17"/>
-    <mergeCell ref="W17:X17"/>
-    <mergeCell ref="Y17:Z17"/>
-    <mergeCell ref="AA17:AB17"/>
-    <mergeCell ref="AC17:AF17"/>
-    <mergeCell ref="AG19:AI19"/>
-    <mergeCell ref="AJ19:AL19"/>
-    <mergeCell ref="AM19:AO19"/>
-    <mergeCell ref="AP19:AR19"/>
-    <mergeCell ref="AS19:AZ19"/>
-    <mergeCell ref="BA19:BC19"/>
-    <mergeCell ref="BD19:BI19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:J20"/>
-    <mergeCell ref="K20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="U20:V20"/>
-    <mergeCell ref="W20:X20"/>
-    <mergeCell ref="Y20:Z20"/>
-    <mergeCell ref="AA20:AB20"/>
-    <mergeCell ref="AC20:AF20"/>
-    <mergeCell ref="AG20:AI20"/>
-    <mergeCell ref="AJ20:AL20"/>
-    <mergeCell ref="AM20:AO20"/>
-    <mergeCell ref="AP20:AR20"/>
-    <mergeCell ref="AS20:AZ20"/>
-    <mergeCell ref="BA20:BC20"/>
-    <mergeCell ref="BD20:BI20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:J19"/>
-    <mergeCell ref="AP21:AR21"/>
-    <mergeCell ref="AS21:AZ21"/>
-    <mergeCell ref="BA21:BC21"/>
-    <mergeCell ref="BD21:BI21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:J22"/>
-    <mergeCell ref="K22:R22"/>
-    <mergeCell ref="S22:T22"/>
-    <mergeCell ref="U22:V22"/>
-    <mergeCell ref="W22:X22"/>
-    <mergeCell ref="Y22:Z22"/>
-    <mergeCell ref="AA22:AB22"/>
-    <mergeCell ref="AC22:AF22"/>
-    <mergeCell ref="AG22:AI22"/>
-    <mergeCell ref="AJ22:AL22"/>
-    <mergeCell ref="AM22:AO22"/>
-    <mergeCell ref="AP22:AR22"/>
-    <mergeCell ref="AS22:AZ22"/>
-    <mergeCell ref="BA22:BC22"/>
-    <mergeCell ref="BD22:BI22"/>
-    <mergeCell ref="AM21:AO21"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:J24"/>
-    <mergeCell ref="K24:R24"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="W24:X24"/>
-    <mergeCell ref="Y24:Z24"/>
-    <mergeCell ref="AA24:AB24"/>
-    <mergeCell ref="AC24:AF24"/>
-    <mergeCell ref="C23:J23"/>
-    <mergeCell ref="K23:R23"/>
-    <mergeCell ref="AG25:AI25"/>
-    <mergeCell ref="AJ25:AL25"/>
-    <mergeCell ref="AM25:AO25"/>
-    <mergeCell ref="AP25:AR25"/>
-    <mergeCell ref="AS23:AZ23"/>
-    <mergeCell ref="BA23:BC23"/>
-    <mergeCell ref="BD23:BI23"/>
-    <mergeCell ref="AG24:AI24"/>
-    <mergeCell ref="AJ24:AL24"/>
-    <mergeCell ref="AM24:AO24"/>
-    <mergeCell ref="AP24:AR24"/>
-    <mergeCell ref="AS24:AZ24"/>
-    <mergeCell ref="BA24:BC24"/>
-    <mergeCell ref="BD24:BI24"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="W23:X23"/>
-    <mergeCell ref="Y23:Z23"/>
-    <mergeCell ref="AA23:AB23"/>
-    <mergeCell ref="W25:X25"/>
-    <mergeCell ref="Y25:Z25"/>
-    <mergeCell ref="AA25:AB25"/>
-    <mergeCell ref="AC25:AF25"/>
-    <mergeCell ref="AP23:AR23"/>
-    <mergeCell ref="AC23:AF23"/>
-    <mergeCell ref="AG23:AI23"/>
-    <mergeCell ref="AJ23:AL23"/>
-    <mergeCell ref="AM23:AO23"/>
-    <mergeCell ref="AS25:AZ25"/>
-    <mergeCell ref="BA25:BC25"/>
-    <mergeCell ref="BD25:BI25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:J26"/>
-    <mergeCell ref="K26:R26"/>
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="U26:V26"/>
-    <mergeCell ref="W26:X26"/>
-    <mergeCell ref="Y26:Z26"/>
-    <mergeCell ref="AA26:AB26"/>
-    <mergeCell ref="AC26:AF26"/>
-    <mergeCell ref="AG26:AI26"/>
-    <mergeCell ref="AJ26:AL26"/>
-    <mergeCell ref="AM26:AO26"/>
-    <mergeCell ref="AP26:AR26"/>
-    <mergeCell ref="AS26:AZ26"/>
-    <mergeCell ref="BA26:BC26"/>
-    <mergeCell ref="BD26:BI26"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:J25"/>
-    <mergeCell ref="K25:R25"/>
-    <mergeCell ref="S25:T25"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="AS27:AZ27"/>
-    <mergeCell ref="BA27:BC27"/>
-    <mergeCell ref="BD27:BI27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:J28"/>
-    <mergeCell ref="K28:R28"/>
-    <mergeCell ref="S28:T28"/>
-    <mergeCell ref="U28:V28"/>
-    <mergeCell ref="W28:X28"/>
-    <mergeCell ref="Y28:Z28"/>
-    <mergeCell ref="AA28:AB28"/>
-    <mergeCell ref="AC28:AF28"/>
-    <mergeCell ref="AG28:AI28"/>
-    <mergeCell ref="AJ28:AL28"/>
-    <mergeCell ref="AM28:AO28"/>
-    <mergeCell ref="AP28:AR28"/>
-    <mergeCell ref="AS28:AZ28"/>
-    <mergeCell ref="BA28:BC28"/>
-    <mergeCell ref="BD28:BI28"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:J27"/>
-    <mergeCell ref="K27:R27"/>
-    <mergeCell ref="S27:T27"/>
-    <mergeCell ref="U27:V27"/>
-    <mergeCell ref="AC29:AF29"/>
-    <mergeCell ref="AG27:AI27"/>
-    <mergeCell ref="AJ27:AL27"/>
-    <mergeCell ref="AM27:AO27"/>
-    <mergeCell ref="AP27:AR27"/>
-    <mergeCell ref="W27:X27"/>
-    <mergeCell ref="Y27:Z27"/>
-    <mergeCell ref="AA27:AB27"/>
-    <mergeCell ref="AC27:AF27"/>
-    <mergeCell ref="AG29:AI29"/>
-    <mergeCell ref="AJ29:AL29"/>
-    <mergeCell ref="AM29:AO29"/>
-    <mergeCell ref="AP29:AR29"/>
-    <mergeCell ref="AS29:AZ29"/>
-    <mergeCell ref="BA29:BC29"/>
-    <mergeCell ref="BD29:BI29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:J30"/>
-    <mergeCell ref="K30:R30"/>
-    <mergeCell ref="S30:T30"/>
-    <mergeCell ref="U30:V30"/>
-    <mergeCell ref="AA30:AB30"/>
-    <mergeCell ref="AC30:AF30"/>
-    <mergeCell ref="AJ30:AL30"/>
-    <mergeCell ref="AM30:AO30"/>
-    <mergeCell ref="AP30:AR30"/>
-    <mergeCell ref="AS30:AZ30"/>
-    <mergeCell ref="BA30:BC30"/>
-    <mergeCell ref="BD30:BI30"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:J29"/>
-    <mergeCell ref="K29:R29"/>
-    <mergeCell ref="S29:T29"/>
-    <mergeCell ref="U29:V29"/>
-    <mergeCell ref="W29:X29"/>
-    <mergeCell ref="Y29:Z29"/>
-    <mergeCell ref="AA29:AB29"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -5338,74 +5370,74 @@
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="36" t="s">
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="36" t="s">
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="X1" s="37"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="37"/>
-      <c r="AE1" s="37"/>
-      <c r="AF1" s="37"/>
-      <c r="AG1" s="37"/>
-      <c r="AH1" s="38"/>
-      <c r="AI1" s="36" t="s">
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="46"/>
+      <c r="AA1" s="46"/>
+      <c r="AB1" s="46"/>
+      <c r="AC1" s="46"/>
+      <c r="AD1" s="46"/>
+      <c r="AE1" s="46"/>
+      <c r="AF1" s="46"/>
+      <c r="AG1" s="46"/>
+      <c r="AH1" s="47"/>
+      <c r="AI1" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="AJ1" s="37"/>
-      <c r="AK1" s="37"/>
-      <c r="AL1" s="37"/>
-      <c r="AM1" s="38"/>
-      <c r="AN1" s="36" t="s">
+      <c r="AJ1" s="46"/>
+      <c r="AK1" s="46"/>
+      <c r="AL1" s="46"/>
+      <c r="AM1" s="47"/>
+      <c r="AN1" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="AO1" s="37"/>
-      <c r="AP1" s="37"/>
-      <c r="AQ1" s="37"/>
-      <c r="AR1" s="38"/>
+      <c r="AO1" s="46"/>
+      <c r="AP1" s="46"/>
+      <c r="AQ1" s="46"/>
+      <c r="AR1" s="47"/>
       <c r="AS1" s="7"/>
       <c r="AT1" s="7"/>
       <c r="AU1" s="7"/>
       <c r="AV1" s="7"/>
       <c r="AW1" s="7"/>
       <c r="AX1" s="7"/>
-      <c r="AY1" s="33" t="s">
+      <c r="AY1" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="AZ1" s="33"/>
-      <c r="BA1" s="33"/>
-      <c r="BB1" s="33"/>
-      <c r="BC1" s="33"/>
-      <c r="BD1" s="33"/>
-      <c r="BE1" s="33"/>
-      <c r="BF1" s="33"/>
-      <c r="BG1" s="33"/>
-      <c r="BH1" s="33"/>
-      <c r="BI1" s="33"/>
+      <c r="AZ1" s="42"/>
+      <c r="BA1" s="42"/>
+      <c r="BB1" s="42"/>
+      <c r="BC1" s="42"/>
+      <c r="BD1" s="42"/>
+      <c r="BE1" s="42"/>
+      <c r="BF1" s="42"/>
+      <c r="BG1" s="42"/>
+      <c r="BH1" s="42"/>
+      <c r="BI1" s="42"/>
     </row>
     <row r="2" spans="1:61" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
@@ -5413,68 +5445,68 @@
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="39" t="s">
+      <c r="F2" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="45" t="s">
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
-      <c r="V2" s="47"/>
-      <c r="W2" s="45" t="s">
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18"/>
+      <c r="R2" s="18"/>
+      <c r="S2" s="18"/>
+      <c r="T2" s="18"/>
+      <c r="U2" s="18"/>
+      <c r="V2" s="19"/>
+      <c r="W2" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="X2" s="46"/>
-      <c r="Y2" s="46"/>
-      <c r="Z2" s="46"/>
-      <c r="AA2" s="46"/>
-      <c r="AB2" s="46"/>
-      <c r="AC2" s="46"/>
-      <c r="AD2" s="46"/>
-      <c r="AE2" s="46"/>
-      <c r="AF2" s="46"/>
-      <c r="AG2" s="46"/>
-      <c r="AH2" s="47"/>
-      <c r="AI2" s="51" t="s">
+      <c r="X2" s="18"/>
+      <c r="Y2" s="18"/>
+      <c r="Z2" s="18"/>
+      <c r="AA2" s="18"/>
+      <c r="AB2" s="18"/>
+      <c r="AC2" s="18"/>
+      <c r="AD2" s="18"/>
+      <c r="AE2" s="18"/>
+      <c r="AF2" s="18"/>
+      <c r="AG2" s="18"/>
+      <c r="AH2" s="19"/>
+      <c r="AI2" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="AJ2" s="52"/>
-      <c r="AK2" s="52"/>
-      <c r="AL2" s="52"/>
-      <c r="AM2" s="53"/>
-      <c r="AN2" s="51" t="s">
+      <c r="AJ2" s="24"/>
+      <c r="AK2" s="24"/>
+      <c r="AL2" s="24"/>
+      <c r="AM2" s="25"/>
+      <c r="AN2" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="AO2" s="52"/>
-      <c r="AP2" s="52"/>
-      <c r="AQ2" s="52"/>
-      <c r="AR2" s="53"/>
-      <c r="AY2" s="34" t="s">
+      <c r="AO2" s="24"/>
+      <c r="AP2" s="24"/>
+      <c r="AQ2" s="24"/>
+      <c r="AR2" s="25"/>
+      <c r="AY2" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="AZ2" s="34"/>
-      <c r="BA2" s="34"/>
-      <c r="BB2" s="34"/>
-      <c r="BC2" s="34"/>
-      <c r="BD2" s="34"/>
-      <c r="BE2" s="34"/>
-      <c r="BF2" s="34"/>
-      <c r="BG2" s="34"/>
-      <c r="BH2" s="34"/>
-      <c r="BI2" s="34"/>
+      <c r="AZ2" s="43"/>
+      <c r="BA2" s="43"/>
+      <c r="BB2" s="43"/>
+      <c r="BC2" s="43"/>
+      <c r="BD2" s="43"/>
+      <c r="BE2" s="43"/>
+      <c r="BF2" s="43"/>
+      <c r="BG2" s="43"/>
+      <c r="BH2" s="43"/>
+      <c r="BI2" s="43"/>
     </row>
     <row r="3" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4"/>
@@ -5482,56 +5514,56 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="49"/>
-      <c r="N3" s="49"/>
-      <c r="O3" s="49"/>
-      <c r="P3" s="49"/>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="49"/>
-      <c r="U3" s="49"/>
-      <c r="V3" s="50"/>
-      <c r="W3" s="48"/>
-      <c r="X3" s="49"/>
-      <c r="Y3" s="49"/>
-      <c r="Z3" s="49"/>
-      <c r="AA3" s="49"/>
-      <c r="AB3" s="49"/>
-      <c r="AC3" s="49"/>
-      <c r="AD3" s="49"/>
-      <c r="AE3" s="49"/>
-      <c r="AF3" s="49"/>
-      <c r="AG3" s="49"/>
-      <c r="AH3" s="50"/>
-      <c r="AI3" s="54"/>
-      <c r="AJ3" s="55"/>
-      <c r="AK3" s="55"/>
-      <c r="AL3" s="55"/>
-      <c r="AM3" s="56"/>
-      <c r="AN3" s="54"/>
-      <c r="AO3" s="55"/>
-      <c r="AP3" s="55"/>
-      <c r="AQ3" s="55"/>
-      <c r="AR3" s="56"/>
-      <c r="AY3" s="35"/>
-      <c r="AZ3" s="35"/>
-      <c r="BA3" s="35"/>
-      <c r="BB3" s="35"/>
-      <c r="BC3" s="35"/>
-      <c r="BD3" s="35"/>
-      <c r="BE3" s="35"/>
-      <c r="BF3" s="35"/>
-      <c r="BG3" s="35"/>
-      <c r="BH3" s="35"/>
-      <c r="BI3" s="35"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="22"/>
+      <c r="W3" s="20"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
+      <c r="Z3" s="21"/>
+      <c r="AA3" s="21"/>
+      <c r="AB3" s="21"/>
+      <c r="AC3" s="21"/>
+      <c r="AD3" s="21"/>
+      <c r="AE3" s="21"/>
+      <c r="AF3" s="21"/>
+      <c r="AG3" s="21"/>
+      <c r="AH3" s="22"/>
+      <c r="AI3" s="26"/>
+      <c r="AJ3" s="27"/>
+      <c r="AK3" s="27"/>
+      <c r="AL3" s="27"/>
+      <c r="AM3" s="28"/>
+      <c r="AN3" s="26"/>
+      <c r="AO3" s="27"/>
+      <c r="AP3" s="27"/>
+      <c r="AQ3" s="27"/>
+      <c r="AR3" s="28"/>
+      <c r="AY3" s="44"/>
+      <c r="AZ3" s="44"/>
+      <c r="BA3" s="44"/>
+      <c r="BB3" s="44"/>
+      <c r="BC3" s="44"/>
+      <c r="BD3" s="44"/>
+      <c r="BE3" s="44"/>
+      <c r="BF3" s="44"/>
+      <c r="BG3" s="44"/>
+      <c r="BH3" s="44"/>
+      <c r="BI3" s="44"/>
     </row>
     <row r="4" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
@@ -5539,66 +5571,66 @@
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="57" t="s">
+      <c r="F4" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="59"/>
-      <c r="K4" s="57" t="s">
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="57" t="s">
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="56"/>
+      <c r="P4" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="Q4" s="58"/>
-      <c r="R4" s="58"/>
-      <c r="S4" s="58"/>
-      <c r="T4" s="59"/>
-      <c r="U4" s="57" t="s">
+      <c r="Q4" s="55"/>
+      <c r="R4" s="55"/>
+      <c r="S4" s="55"/>
+      <c r="T4" s="56"/>
+      <c r="U4" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="V4" s="58"/>
-      <c r="W4" s="58"/>
-      <c r="X4" s="58"/>
-      <c r="Y4" s="58"/>
-      <c r="Z4" s="58"/>
-      <c r="AA4" s="58"/>
-      <c r="AB4" s="58"/>
-      <c r="AC4" s="58"/>
-      <c r="AD4" s="58"/>
-      <c r="AE4" s="58"/>
-      <c r="AF4" s="58"/>
-      <c r="AG4" s="58"/>
-      <c r="AH4" s="59"/>
-      <c r="AI4" s="60" t="s">
+      <c r="V4" s="55"/>
+      <c r="W4" s="55"/>
+      <c r="X4" s="55"/>
+      <c r="Y4" s="55"/>
+      <c r="Z4" s="55"/>
+      <c r="AA4" s="55"/>
+      <c r="AB4" s="55"/>
+      <c r="AC4" s="55"/>
+      <c r="AD4" s="55"/>
+      <c r="AE4" s="55"/>
+      <c r="AF4" s="55"/>
+      <c r="AG4" s="55"/>
+      <c r="AH4" s="56"/>
+      <c r="AI4" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="AJ4" s="61"/>
-      <c r="AK4" s="61"/>
-      <c r="AL4" s="61"/>
-      <c r="AM4" s="61"/>
-      <c r="AN4" s="61"/>
-      <c r="AO4" s="61"/>
-      <c r="AP4" s="61"/>
-      <c r="AQ4" s="61"/>
-      <c r="AR4" s="62"/>
-      <c r="AY4" s="35"/>
-      <c r="AZ4" s="35"/>
-      <c r="BA4" s="35"/>
-      <c r="BB4" s="35"/>
-      <c r="BC4" s="35"/>
-      <c r="BD4" s="35"/>
-      <c r="BE4" s="35"/>
-      <c r="BF4" s="35"/>
-      <c r="BG4" s="35"/>
-      <c r="BH4" s="35"/>
-      <c r="BI4" s="35"/>
+      <c r="AJ4" s="58"/>
+      <c r="AK4" s="58"/>
+      <c r="AL4" s="58"/>
+      <c r="AM4" s="58"/>
+      <c r="AN4" s="58"/>
+      <c r="AO4" s="58"/>
+      <c r="AP4" s="58"/>
+      <c r="AQ4" s="58"/>
+      <c r="AR4" s="59"/>
+      <c r="AY4" s="44"/>
+      <c r="AZ4" s="44"/>
+      <c r="BA4" s="44"/>
+      <c r="BB4" s="44"/>
+      <c r="BC4" s="44"/>
+      <c r="BD4" s="44"/>
+      <c r="BE4" s="44"/>
+      <c r="BF4" s="44"/>
+      <c r="BG4" s="44"/>
+      <c r="BH4" s="44"/>
+      <c r="BI4" s="44"/>
     </row>
     <row r="5" spans="1:61" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
@@ -5606,53 +5638,53 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
-      <c r="F5" s="45" t="s">
+      <c r="F5" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="47"/>
-      <c r="K5" s="51" t="s">
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="53"/>
-      <c r="P5" s="51" t="s">
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="Q5" s="52"/>
-      <c r="R5" s="52"/>
-      <c r="S5" s="52"/>
-      <c r="T5" s="53"/>
-      <c r="U5" s="72" t="s">
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
+      <c r="S5" s="24"/>
+      <c r="T5" s="25"/>
+      <c r="U5" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="V5" s="73"/>
-      <c r="W5" s="73"/>
-      <c r="X5" s="73"/>
-      <c r="Y5" s="73"/>
-      <c r="Z5" s="73"/>
-      <c r="AA5" s="73"/>
-      <c r="AB5" s="73"/>
-      <c r="AC5" s="73"/>
-      <c r="AD5" s="73"/>
-      <c r="AE5" s="73"/>
-      <c r="AF5" s="73"/>
-      <c r="AG5" s="73"/>
-      <c r="AH5" s="74"/>
-      <c r="AI5" s="63"/>
-      <c r="AJ5" s="64"/>
-      <c r="AK5" s="64"/>
-      <c r="AL5" s="64"/>
-      <c r="AM5" s="64"/>
-      <c r="AN5" s="64"/>
-      <c r="AO5" s="64"/>
-      <c r="AP5" s="64"/>
-      <c r="AQ5" s="64"/>
-      <c r="AR5" s="65"/>
+      <c r="V5" s="30"/>
+      <c r="W5" s="30"/>
+      <c r="X5" s="30"/>
+      <c r="Y5" s="30"/>
+      <c r="Z5" s="30"/>
+      <c r="AA5" s="30"/>
+      <c r="AB5" s="30"/>
+      <c r="AC5" s="30"/>
+      <c r="AD5" s="30"/>
+      <c r="AE5" s="30"/>
+      <c r="AF5" s="30"/>
+      <c r="AG5" s="30"/>
+      <c r="AH5" s="31"/>
+      <c r="AI5" s="60"/>
+      <c r="AJ5" s="61"/>
+      <c r="AK5" s="61"/>
+      <c r="AL5" s="61"/>
+      <c r="AM5" s="61"/>
+      <c r="AN5" s="61"/>
+      <c r="AO5" s="61"/>
+      <c r="AP5" s="61"/>
+      <c r="AQ5" s="61"/>
+      <c r="AR5" s="62"/>
     </row>
     <row r="6" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
@@ -5660,45 +5692,45 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="55"/>
-      <c r="N6" s="55"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="54"/>
-      <c r="Q6" s="55"/>
-      <c r="R6" s="55"/>
-      <c r="S6" s="55"/>
-      <c r="T6" s="56"/>
-      <c r="U6" s="75"/>
-      <c r="V6" s="76"/>
-      <c r="W6" s="76"/>
-      <c r="X6" s="76"/>
-      <c r="Y6" s="76"/>
-      <c r="Z6" s="76"/>
-      <c r="AA6" s="76"/>
-      <c r="AB6" s="76"/>
-      <c r="AC6" s="76"/>
-      <c r="AD6" s="76"/>
-      <c r="AE6" s="76"/>
-      <c r="AF6" s="76"/>
-      <c r="AG6" s="76"/>
-      <c r="AH6" s="77"/>
-      <c r="AI6" s="66"/>
-      <c r="AJ6" s="67"/>
-      <c r="AK6" s="67"/>
-      <c r="AL6" s="67"/>
-      <c r="AM6" s="67"/>
-      <c r="AN6" s="67"/>
-      <c r="AO6" s="67"/>
-      <c r="AP6" s="67"/>
-      <c r="AQ6" s="67"/>
-      <c r="AR6" s="68"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="27"/>
+      <c r="S6" s="27"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="33"/>
+      <c r="W6" s="33"/>
+      <c r="X6" s="33"/>
+      <c r="Y6" s="33"/>
+      <c r="Z6" s="33"/>
+      <c r="AA6" s="33"/>
+      <c r="AB6" s="33"/>
+      <c r="AC6" s="33"/>
+      <c r="AD6" s="33"/>
+      <c r="AE6" s="33"/>
+      <c r="AF6" s="33"/>
+      <c r="AG6" s="33"/>
+      <c r="AH6" s="34"/>
+      <c r="AI6" s="63"/>
+      <c r="AJ6" s="64"/>
+      <c r="AK6" s="64"/>
+      <c r="AL6" s="64"/>
+      <c r="AM6" s="64"/>
+      <c r="AN6" s="64"/>
+      <c r="AO6" s="64"/>
+      <c r="AP6" s="64"/>
+      <c r="AQ6" s="64"/>
+      <c r="AR6" s="65"/>
     </row>
     <row r="7" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
@@ -5807,73 +5839,73 @@
       <c r="BI8" s="8"/>
     </row>
     <row r="9" spans="1:61" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="82" t="s">
+      <c r="A9" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="82"/>
-      <c r="C9" s="82"/>
-      <c r="D9" s="82"/>
-      <c r="E9" s="82"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="82"/>
-      <c r="H9" s="82"/>
-      <c r="I9" s="82"/>
-      <c r="J9" s="82"/>
-      <c r="K9" s="82"/>
-      <c r="L9" s="82"/>
-      <c r="M9" s="82"/>
-      <c r="N9" s="82"/>
-      <c r="O9" s="82"/>
-      <c r="P9" s="82"/>
-      <c r="Q9" s="82"/>
-      <c r="R9" s="82"/>
-      <c r="S9" s="82"/>
-      <c r="T9" s="83"/>
-      <c r="U9" s="84" t="s">
+      <c r="B9" s="71"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="71"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="71"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="71"/>
+      <c r="S9" s="71"/>
+      <c r="T9" s="72"/>
+      <c r="U9" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="V9" s="82"/>
-      <c r="W9" s="82"/>
-      <c r="X9" s="82"/>
-      <c r="Y9" s="82"/>
-      <c r="Z9" s="82"/>
-      <c r="AA9" s="82"/>
-      <c r="AB9" s="82"/>
-      <c r="AC9" s="82"/>
-      <c r="AD9" s="82"/>
-      <c r="AE9" s="82"/>
-      <c r="AF9" s="82"/>
-      <c r="AG9" s="82"/>
-      <c r="AH9" s="82"/>
-      <c r="AI9" s="82"/>
-      <c r="AJ9" s="82"/>
-      <c r="AK9" s="82"/>
-      <c r="AL9" s="82"/>
-      <c r="AM9" s="82"/>
-      <c r="AN9" s="82"/>
-      <c r="AO9" s="83"/>
-      <c r="AP9" s="84" t="s">
+      <c r="V9" s="71"/>
+      <c r="W9" s="71"/>
+      <c r="X9" s="71"/>
+      <c r="Y9" s="71"/>
+      <c r="Z9" s="71"/>
+      <c r="AA9" s="71"/>
+      <c r="AB9" s="71"/>
+      <c r="AC9" s="71"/>
+      <c r="AD9" s="71"/>
+      <c r="AE9" s="71"/>
+      <c r="AF9" s="71"/>
+      <c r="AG9" s="71"/>
+      <c r="AH9" s="71"/>
+      <c r="AI9" s="71"/>
+      <c r="AJ9" s="71"/>
+      <c r="AK9" s="71"/>
+      <c r="AL9" s="71"/>
+      <c r="AM9" s="71"/>
+      <c r="AN9" s="71"/>
+      <c r="AO9" s="72"/>
+      <c r="AP9" s="73" t="s">
         <v>51</v>
       </c>
-      <c r="AQ9" s="82"/>
-      <c r="AR9" s="82"/>
-      <c r="AS9" s="82"/>
-      <c r="AT9" s="82"/>
-      <c r="AU9" s="82"/>
-      <c r="AV9" s="82"/>
-      <c r="AW9" s="82"/>
-      <c r="AX9" s="82"/>
-      <c r="AY9" s="82"/>
-      <c r="AZ9" s="82"/>
-      <c r="BA9" s="82"/>
-      <c r="BB9" s="82"/>
-      <c r="BC9" s="82"/>
-      <c r="BD9" s="82"/>
-      <c r="BE9" s="82"/>
-      <c r="BF9" s="82"/>
-      <c r="BG9" s="82"/>
-      <c r="BH9" s="82"/>
-      <c r="BI9" s="82"/>
+      <c r="AQ9" s="71"/>
+      <c r="AR9" s="71"/>
+      <c r="AS9" s="71"/>
+      <c r="AT9" s="71"/>
+      <c r="AU9" s="71"/>
+      <c r="AV9" s="71"/>
+      <c r="AW9" s="71"/>
+      <c r="AX9" s="71"/>
+      <c r="AY9" s="71"/>
+      <c r="AZ9" s="71"/>
+      <c r="BA9" s="71"/>
+      <c r="BB9" s="71"/>
+      <c r="BC9" s="71"/>
+      <c r="BD9" s="71"/>
+      <c r="BE9" s="71"/>
+      <c r="BF9" s="71"/>
+      <c r="BG9" s="71"/>
+      <c r="BH9" s="71"/>
+      <c r="BI9" s="71"/>
     </row>
     <row r="10" spans="1:61" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="11"/>
@@ -5938,121 +5970,121 @@
       <c r="BI10" s="10"/>
     </row>
     <row r="11" spans="1:61" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="78"/>
-      <c r="J11" s="78"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="74"/>
+      <c r="H11" s="74"/>
+      <c r="I11" s="74"/>
+      <c r="J11" s="74"/>
       <c r="K11" s="9"/>
-      <c r="L11" s="78" t="s">
+      <c r="L11" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="M11" s="78"/>
-      <c r="O11" s="78" t="s">
+      <c r="M11" s="74"/>
+      <c r="O11" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="P11" s="78"/>
+      <c r="P11" s="74"/>
       <c r="Q11" s="9"/>
       <c r="R11" s="14"/>
       <c r="S11" s="9"/>
       <c r="T11" s="13"/>
-      <c r="U11" s="81" t="s">
+      <c r="U11" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="V11" s="78"/>
-      <c r="W11" s="78"/>
-      <c r="X11" s="78"/>
-      <c r="Y11" s="78"/>
-      <c r="Z11" s="78"/>
-      <c r="AA11" s="78"/>
-      <c r="AB11" s="78"/>
-      <c r="AC11" s="78"/>
-      <c r="AD11" s="78"/>
-      <c r="AE11" s="78"/>
+      <c r="V11" s="74"/>
+      <c r="W11" s="74"/>
+      <c r="X11" s="74"/>
+      <c r="Y11" s="74"/>
+      <c r="Z11" s="74"/>
+      <c r="AA11" s="74"/>
+      <c r="AB11" s="74"/>
+      <c r="AC11" s="74"/>
+      <c r="AD11" s="74"/>
+      <c r="AE11" s="74"/>
       <c r="AF11" s="9"/>
-      <c r="AG11" s="78" t="s">
+      <c r="AG11" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="AH11" s="78"/>
+      <c r="AH11" s="74"/>
       <c r="AI11" s="9"/>
-      <c r="AJ11" s="78" t="s">
+      <c r="AJ11" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="AK11" s="78"/>
+      <c r="AK11" s="74"/>
       <c r="AL11" s="9"/>
       <c r="AM11" s="14"/>
       <c r="AN11" s="9"/>
       <c r="AO11" s="13"/>
-      <c r="AP11" s="79" t="s">
+      <c r="AP11" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="AQ11" s="80"/>
-      <c r="AR11" s="80"/>
-      <c r="AS11" s="80"/>
-      <c r="AT11" s="80"/>
-      <c r="AU11" s="80"/>
-      <c r="AV11" s="80"/>
-      <c r="AW11" s="80"/>
-      <c r="AX11" s="80"/>
-      <c r="AY11" s="80"/>
-      <c r="AZ11" s="80"/>
-      <c r="BA11" s="80"/>
+      <c r="AQ11" s="77"/>
+      <c r="AR11" s="77"/>
+      <c r="AS11" s="77"/>
+      <c r="AT11" s="77"/>
+      <c r="AU11" s="77"/>
+      <c r="AV11" s="77"/>
+      <c r="AW11" s="77"/>
+      <c r="AX11" s="77"/>
+      <c r="AY11" s="77"/>
+      <c r="AZ11" s="77"/>
+      <c r="BA11" s="77"/>
       <c r="BB11" s="10"/>
-      <c r="BC11" s="80" t="s">
+      <c r="BC11" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="BD11" s="80"/>
-      <c r="BE11" s="80"/>
-      <c r="BF11" s="80"/>
-      <c r="BG11" s="80"/>
-      <c r="BH11" s="80"/>
-      <c r="BI11" s="80"/>
+      <c r="BD11" s="77"/>
+      <c r="BE11" s="77"/>
+      <c r="BF11" s="77"/>
+      <c r="BG11" s="77"/>
+      <c r="BH11" s="77"/>
+      <c r="BI11" s="77"/>
     </row>
     <row r="12" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="78"/>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="78"/>
+      <c r="A12" s="74"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="74"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="74"/>
       <c r="K12" s="9"/>
-      <c r="L12" s="78"/>
-      <c r="M12" s="78"/>
+      <c r="L12" s="74"/>
+      <c r="M12" s="74"/>
       <c r="N12" s="9"/>
-      <c r="O12" s="78"/>
-      <c r="P12" s="78"/>
+      <c r="O12" s="74"/>
+      <c r="P12" s="74"/>
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
       <c r="S12" s="9"/>
       <c r="T12" s="13"/>
-      <c r="U12" s="81"/>
-      <c r="V12" s="78"/>
-      <c r="W12" s="78"/>
-      <c r="X12" s="78"/>
-      <c r="Y12" s="78"/>
-      <c r="Z12" s="78"/>
-      <c r="AA12" s="78"/>
-      <c r="AB12" s="78"/>
-      <c r="AC12" s="78"/>
-      <c r="AD12" s="78"/>
-      <c r="AE12" s="78"/>
+      <c r="U12" s="75"/>
+      <c r="V12" s="74"/>
+      <c r="W12" s="74"/>
+      <c r="X12" s="74"/>
+      <c r="Y12" s="74"/>
+      <c r="Z12" s="74"/>
+      <c r="AA12" s="74"/>
+      <c r="AB12" s="74"/>
+      <c r="AC12" s="74"/>
+      <c r="AD12" s="74"/>
+      <c r="AE12" s="74"/>
       <c r="AF12" s="9"/>
-      <c r="AG12" s="78"/>
-      <c r="AH12" s="78"/>
+      <c r="AG12" s="74"/>
+      <c r="AH12" s="74"/>
       <c r="AI12" s="9"/>
-      <c r="AJ12" s="78"/>
-      <c r="AK12" s="78"/>
+      <c r="AJ12" s="74"/>
+      <c r="AK12" s="74"/>
       <c r="AL12" s="9"/>
       <c r="AM12" s="9"/>
       <c r="AN12" s="9"/>
@@ -6079,43 +6111,43 @@
       <c r="BI12" s="10"/>
     </row>
     <row r="13" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="78"/>
-      <c r="B13" s="78"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="78"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="78"/>
-      <c r="J13" s="78"/>
+      <c r="A13" s="74"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="74"/>
       <c r="K13" s="9"/>
-      <c r="L13" s="78"/>
-      <c r="M13" s="78"/>
+      <c r="L13" s="74"/>
+      <c r="M13" s="74"/>
       <c r="N13" s="9"/>
-      <c r="O13" s="78"/>
-      <c r="P13" s="78"/>
+      <c r="O13" s="74"/>
+      <c r="P13" s="74"/>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
       <c r="S13" s="9"/>
       <c r="T13" s="13"/>
-      <c r="U13" s="81"/>
-      <c r="V13" s="78"/>
-      <c r="W13" s="78"/>
-      <c r="X13" s="78"/>
-      <c r="Y13" s="78"/>
-      <c r="Z13" s="78"/>
-      <c r="AA13" s="78"/>
-      <c r="AB13" s="78"/>
-      <c r="AC13" s="78"/>
-      <c r="AD13" s="78"/>
-      <c r="AE13" s="78"/>
+      <c r="U13" s="75"/>
+      <c r="V13" s="74"/>
+      <c r="W13" s="74"/>
+      <c r="X13" s="74"/>
+      <c r="Y13" s="74"/>
+      <c r="Z13" s="74"/>
+      <c r="AA13" s="74"/>
+      <c r="AB13" s="74"/>
+      <c r="AC13" s="74"/>
+      <c r="AD13" s="74"/>
+      <c r="AE13" s="74"/>
       <c r="AF13" s="9"/>
-      <c r="AG13" s="78"/>
-      <c r="AH13" s="78"/>
+      <c r="AG13" s="74"/>
+      <c r="AH13" s="74"/>
       <c r="AI13" s="9"/>
-      <c r="AJ13" s="78"/>
-      <c r="AK13" s="78"/>
+      <c r="AJ13" s="74"/>
+      <c r="AK13" s="74"/>
       <c r="AL13" s="9"/>
       <c r="AM13" s="9"/>
       <c r="AN13" s="9"/>
@@ -6142,43 +6174,43 @@
       <c r="BI13" s="10"/>
     </row>
     <row r="14" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="78"/>
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="78"/>
-      <c r="G14" s="78"/>
-      <c r="H14" s="78"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="78"/>
+      <c r="A14" s="74"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="74"/>
       <c r="K14" s="9"/>
-      <c r="L14" s="78"/>
-      <c r="M14" s="78"/>
+      <c r="L14" s="74"/>
+      <c r="M14" s="74"/>
       <c r="N14" s="9"/>
-      <c r="O14" s="78"/>
-      <c r="P14" s="78"/>
+      <c r="O14" s="74"/>
+      <c r="P14" s="74"/>
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
       <c r="S14" s="9"/>
       <c r="T14" s="13"/>
-      <c r="U14" s="81"/>
-      <c r="V14" s="78"/>
-      <c r="W14" s="78"/>
-      <c r="X14" s="78"/>
-      <c r="Y14" s="78"/>
-      <c r="Z14" s="78"/>
-      <c r="AA14" s="78"/>
-      <c r="AB14" s="78"/>
-      <c r="AC14" s="78"/>
-      <c r="AD14" s="78"/>
-      <c r="AE14" s="78"/>
+      <c r="U14" s="75"/>
+      <c r="V14" s="74"/>
+      <c r="W14" s="74"/>
+      <c r="X14" s="74"/>
+      <c r="Y14" s="74"/>
+      <c r="Z14" s="74"/>
+      <c r="AA14" s="74"/>
+      <c r="AB14" s="74"/>
+      <c r="AC14" s="74"/>
+      <c r="AD14" s="74"/>
+      <c r="AE14" s="74"/>
       <c r="AF14" s="9"/>
-      <c r="AG14" s="78"/>
-      <c r="AH14" s="78"/>
+      <c r="AG14" s="74"/>
+      <c r="AH14" s="74"/>
       <c r="AI14" s="9"/>
-      <c r="AJ14" s="78"/>
-      <c r="AK14" s="78"/>
+      <c r="AJ14" s="74"/>
+      <c r="AK14" s="74"/>
       <c r="AL14" s="9"/>
       <c r="AM14" s="9"/>
       <c r="AN14" s="9"/>
@@ -6205,43 +6237,43 @@
       <c r="BI14" s="10"/>
     </row>
     <row r="15" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="78"/>
-      <c r="B15" s="78"/>
-      <c r="C15" s="78"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="78"/>
-      <c r="H15" s="78"/>
-      <c r="I15" s="78"/>
-      <c r="J15" s="78"/>
+      <c r="A15" s="74"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="74"/>
+      <c r="I15" s="74"/>
+      <c r="J15" s="74"/>
       <c r="K15" s="9"/>
-      <c r="L15" s="78"/>
-      <c r="M15" s="78"/>
+      <c r="L15" s="74"/>
+      <c r="M15" s="74"/>
       <c r="N15" s="9"/>
-      <c r="O15" s="78"/>
-      <c r="P15" s="78"/>
+      <c r="O15" s="74"/>
+      <c r="P15" s="74"/>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
       <c r="S15" s="9"/>
       <c r="T15" s="13"/>
-      <c r="U15" s="81"/>
-      <c r="V15" s="78"/>
-      <c r="W15" s="78"/>
-      <c r="X15" s="78"/>
-      <c r="Y15" s="78"/>
-      <c r="Z15" s="78"/>
-      <c r="AA15" s="78"/>
-      <c r="AB15" s="78"/>
-      <c r="AC15" s="78"/>
-      <c r="AD15" s="78"/>
-      <c r="AE15" s="78"/>
+      <c r="U15" s="75"/>
+      <c r="V15" s="74"/>
+      <c r="W15" s="74"/>
+      <c r="X15" s="74"/>
+      <c r="Y15" s="74"/>
+      <c r="Z15" s="74"/>
+      <c r="AA15" s="74"/>
+      <c r="AB15" s="74"/>
+      <c r="AC15" s="74"/>
+      <c r="AD15" s="74"/>
+      <c r="AE15" s="74"/>
       <c r="AF15" s="9"/>
-      <c r="AG15" s="78"/>
-      <c r="AH15" s="78"/>
+      <c r="AG15" s="74"/>
+      <c r="AH15" s="74"/>
       <c r="AI15" s="9"/>
-      <c r="AJ15" s="78"/>
-      <c r="AK15" s="78"/>
+      <c r="AJ15" s="74"/>
+      <c r="AK15" s="74"/>
       <c r="AL15" s="9"/>
       <c r="AM15" s="9"/>
       <c r="AN15" s="9"/>
@@ -6268,43 +6300,43 @@
       <c r="BI15" s="10"/>
     </row>
     <row r="16" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="78"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="78"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="78"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="78"/>
-      <c r="H16" s="78"/>
-      <c r="I16" s="78"/>
-      <c r="J16" s="78"/>
+      <c r="A16" s="74"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="74"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="74"/>
       <c r="K16" s="9"/>
-      <c r="L16" s="78"/>
-      <c r="M16" s="78"/>
+      <c r="L16" s="74"/>
+      <c r="M16" s="74"/>
       <c r="N16" s="9"/>
-      <c r="O16" s="78"/>
-      <c r="P16" s="78"/>
+      <c r="O16" s="74"/>
+      <c r="P16" s="74"/>
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
       <c r="S16" s="9"/>
       <c r="T16" s="13"/>
-      <c r="U16" s="81"/>
-      <c r="V16" s="78"/>
-      <c r="W16" s="78"/>
-      <c r="X16" s="78"/>
-      <c r="Y16" s="78"/>
-      <c r="Z16" s="78"/>
-      <c r="AA16" s="78"/>
-      <c r="AB16" s="78"/>
-      <c r="AC16" s="78"/>
-      <c r="AD16" s="78"/>
-      <c r="AE16" s="78"/>
+      <c r="U16" s="75"/>
+      <c r="V16" s="74"/>
+      <c r="W16" s="74"/>
+      <c r="X16" s="74"/>
+      <c r="Y16" s="74"/>
+      <c r="Z16" s="74"/>
+      <c r="AA16" s="74"/>
+      <c r="AB16" s="74"/>
+      <c r="AC16" s="74"/>
+      <c r="AD16" s="74"/>
+      <c r="AE16" s="74"/>
       <c r="AF16" s="9"/>
-      <c r="AG16" s="78"/>
-      <c r="AH16" s="78"/>
+      <c r="AG16" s="74"/>
+      <c r="AH16" s="74"/>
       <c r="AI16" s="9"/>
-      <c r="AJ16" s="78"/>
-      <c r="AK16" s="78"/>
+      <c r="AJ16" s="74"/>
+      <c r="AK16" s="74"/>
       <c r="AL16" s="9"/>
       <c r="AM16" s="9"/>
       <c r="AN16" s="9"/>
@@ -6331,43 +6363,43 @@
       <c r="BI16" s="10"/>
     </row>
     <row r="17" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="78"/>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="78"/>
-      <c r="J17" s="78"/>
+      <c r="A17" s="74"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="74"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="74"/>
+      <c r="I17" s="74"/>
+      <c r="J17" s="74"/>
       <c r="K17" s="9"/>
-      <c r="L17" s="78"/>
-      <c r="M17" s="78"/>
+      <c r="L17" s="74"/>
+      <c r="M17" s="74"/>
       <c r="N17" s="9"/>
-      <c r="O17" s="78"/>
-      <c r="P17" s="78"/>
+      <c r="O17" s="74"/>
+      <c r="P17" s="74"/>
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
       <c r="S17" s="9"/>
       <c r="T17" s="13"/>
-      <c r="U17" s="81"/>
-      <c r="V17" s="78"/>
-      <c r="W17" s="78"/>
-      <c r="X17" s="78"/>
-      <c r="Y17" s="78"/>
-      <c r="Z17" s="78"/>
-      <c r="AA17" s="78"/>
-      <c r="AB17" s="78"/>
-      <c r="AC17" s="78"/>
-      <c r="AD17" s="78"/>
-      <c r="AE17" s="78"/>
+      <c r="U17" s="75"/>
+      <c r="V17" s="74"/>
+      <c r="W17" s="74"/>
+      <c r="X17" s="74"/>
+      <c r="Y17" s="74"/>
+      <c r="Z17" s="74"/>
+      <c r="AA17" s="74"/>
+      <c r="AB17" s="74"/>
+      <c r="AC17" s="74"/>
+      <c r="AD17" s="74"/>
+      <c r="AE17" s="74"/>
       <c r="AF17" s="9"/>
-      <c r="AG17" s="78"/>
-      <c r="AH17" s="78"/>
+      <c r="AG17" s="74"/>
+      <c r="AH17" s="74"/>
       <c r="AI17" s="9"/>
-      <c r="AJ17" s="78"/>
-      <c r="AK17" s="78"/>
+      <c r="AJ17" s="74"/>
+      <c r="AK17" s="74"/>
       <c r="AL17" s="9"/>
       <c r="AM17" s="9"/>
       <c r="AN17" s="9"/>
@@ -6394,43 +6426,43 @@
       <c r="BI17" s="10"/>
     </row>
     <row r="18" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="78"/>
-      <c r="B18" s="78"/>
-      <c r="C18" s="78"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="78"/>
-      <c r="I18" s="78"/>
-      <c r="J18" s="78"/>
+      <c r="A18" s="74"/>
+      <c r="B18" s="74"/>
+      <c r="C18" s="74"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="74"/>
+      <c r="F18" s="74"/>
+      <c r="G18" s="74"/>
+      <c r="H18" s="74"/>
+      <c r="I18" s="74"/>
+      <c r="J18" s="74"/>
       <c r="K18" s="9"/>
-      <c r="L18" s="78"/>
-      <c r="M18" s="78"/>
+      <c r="L18" s="74"/>
+      <c r="M18" s="74"/>
       <c r="N18" s="9"/>
-      <c r="O18" s="78"/>
-      <c r="P18" s="78"/>
+      <c r="O18" s="74"/>
+      <c r="P18" s="74"/>
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
       <c r="S18" s="9"/>
       <c r="T18" s="13"/>
-      <c r="U18" s="81"/>
-      <c r="V18" s="78"/>
-      <c r="W18" s="78"/>
-      <c r="X18" s="78"/>
-      <c r="Y18" s="78"/>
-      <c r="Z18" s="78"/>
-      <c r="AA18" s="78"/>
-      <c r="AB18" s="78"/>
-      <c r="AC18" s="78"/>
-      <c r="AD18" s="78"/>
-      <c r="AE18" s="78"/>
+      <c r="U18" s="75"/>
+      <c r="V18" s="74"/>
+      <c r="W18" s="74"/>
+      <c r="X18" s="74"/>
+      <c r="Y18" s="74"/>
+      <c r="Z18" s="74"/>
+      <c r="AA18" s="74"/>
+      <c r="AB18" s="74"/>
+      <c r="AC18" s="74"/>
+      <c r="AD18" s="74"/>
+      <c r="AE18" s="74"/>
       <c r="AF18" s="9"/>
-      <c r="AG18" s="78"/>
-      <c r="AH18" s="78"/>
+      <c r="AG18" s="74"/>
+      <c r="AH18" s="74"/>
       <c r="AI18" s="9"/>
-      <c r="AJ18" s="78"/>
-      <c r="AK18" s="78"/>
+      <c r="AJ18" s="74"/>
+      <c r="AK18" s="74"/>
       <c r="AL18" s="9"/>
       <c r="AM18" s="9"/>
       <c r="AN18" s="9"/>
@@ -6457,43 +6489,43 @@
       <c r="BI18" s="10"/>
     </row>
     <row r="19" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="78"/>
-      <c r="B19" s="78"/>
-      <c r="C19" s="78"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="78"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="78"/>
-      <c r="I19" s="78"/>
-      <c r="J19" s="78"/>
+      <c r="A19" s="74"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="74"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="74"/>
       <c r="K19" s="9"/>
-      <c r="L19" s="78"/>
-      <c r="M19" s="78"/>
+      <c r="L19" s="74"/>
+      <c r="M19" s="74"/>
       <c r="N19" s="9"/>
-      <c r="O19" s="78"/>
-      <c r="P19" s="78"/>
+      <c r="O19" s="74"/>
+      <c r="P19" s="74"/>
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
       <c r="S19" s="9"/>
       <c r="T19" s="13"/>
-      <c r="U19" s="81"/>
-      <c r="V19" s="78"/>
-      <c r="W19" s="78"/>
-      <c r="X19" s="78"/>
-      <c r="Y19" s="78"/>
-      <c r="Z19" s="78"/>
-      <c r="AA19" s="78"/>
-      <c r="AB19" s="78"/>
-      <c r="AC19" s="78"/>
-      <c r="AD19" s="78"/>
-      <c r="AE19" s="78"/>
+      <c r="U19" s="75"/>
+      <c r="V19" s="74"/>
+      <c r="W19" s="74"/>
+      <c r="X19" s="74"/>
+      <c r="Y19" s="74"/>
+      <c r="Z19" s="74"/>
+      <c r="AA19" s="74"/>
+      <c r="AB19" s="74"/>
+      <c r="AC19" s="74"/>
+      <c r="AD19" s="74"/>
+      <c r="AE19" s="74"/>
       <c r="AF19" s="9"/>
-      <c r="AG19" s="78"/>
-      <c r="AH19" s="78"/>
+      <c r="AG19" s="74"/>
+      <c r="AH19" s="74"/>
       <c r="AI19" s="9"/>
-      <c r="AJ19" s="78"/>
-      <c r="AK19" s="78"/>
+      <c r="AJ19" s="74"/>
+      <c r="AK19" s="74"/>
       <c r="AL19" s="9"/>
       <c r="AM19" s="9"/>
       <c r="AN19" s="9"/>
@@ -6520,43 +6552,43 @@
       <c r="BI19" s="10"/>
     </row>
     <row r="20" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="78"/>
-      <c r="B20" s="78"/>
-      <c r="C20" s="78"/>
-      <c r="D20" s="78"/>
-      <c r="E20" s="78"/>
-      <c r="F20" s="78"/>
-      <c r="G20" s="78"/>
-      <c r="H20" s="78"/>
-      <c r="I20" s="78"/>
-      <c r="J20" s="78"/>
+      <c r="A20" s="74"/>
+      <c r="B20" s="74"/>
+      <c r="C20" s="74"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="74"/>
+      <c r="J20" s="74"/>
       <c r="K20" s="9"/>
-      <c r="L20" s="78"/>
-      <c r="M20" s="78"/>
+      <c r="L20" s="74"/>
+      <c r="M20" s="74"/>
       <c r="N20" s="9"/>
-      <c r="O20" s="78"/>
-      <c r="P20" s="78"/>
+      <c r="O20" s="74"/>
+      <c r="P20" s="74"/>
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
       <c r="S20" s="9"/>
       <c r="T20" s="13"/>
-      <c r="U20" s="81"/>
-      <c r="V20" s="78"/>
-      <c r="W20" s="78"/>
-      <c r="X20" s="78"/>
-      <c r="Y20" s="78"/>
-      <c r="Z20" s="78"/>
-      <c r="AA20" s="78"/>
-      <c r="AB20" s="78"/>
-      <c r="AC20" s="78"/>
-      <c r="AD20" s="78"/>
-      <c r="AE20" s="78"/>
+      <c r="U20" s="75"/>
+      <c r="V20" s="74"/>
+      <c r="W20" s="74"/>
+      <c r="X20" s="74"/>
+      <c r="Y20" s="74"/>
+      <c r="Z20" s="74"/>
+      <c r="AA20" s="74"/>
+      <c r="AB20" s="74"/>
+      <c r="AC20" s="74"/>
+      <c r="AD20" s="74"/>
+      <c r="AE20" s="74"/>
       <c r="AF20" s="9"/>
-      <c r="AG20" s="78"/>
-      <c r="AH20" s="78"/>
+      <c r="AG20" s="74"/>
+      <c r="AH20" s="74"/>
       <c r="AI20" s="9"/>
-      <c r="AJ20" s="78"/>
-      <c r="AK20" s="78"/>
+      <c r="AJ20" s="74"/>
+      <c r="AK20" s="74"/>
       <c r="AL20" s="9"/>
       <c r="AM20" s="9"/>
       <c r="AN20" s="9"/>
@@ -6583,43 +6615,43 @@
       <c r="BI20" s="10"/>
     </row>
     <row r="21" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="78"/>
-      <c r="B21" s="78"/>
-      <c r="C21" s="78"/>
-      <c r="D21" s="78"/>
-      <c r="E21" s="78"/>
-      <c r="F21" s="78"/>
-      <c r="G21" s="78"/>
-      <c r="H21" s="78"/>
-      <c r="I21" s="78"/>
-      <c r="J21" s="78"/>
+      <c r="A21" s="74"/>
+      <c r="B21" s="74"/>
+      <c r="C21" s="74"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="74"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="74"/>
       <c r="K21" s="9"/>
-      <c r="L21" s="78"/>
-      <c r="M21" s="78"/>
+      <c r="L21" s="74"/>
+      <c r="M21" s="74"/>
       <c r="N21" s="9"/>
-      <c r="O21" s="78"/>
-      <c r="P21" s="78"/>
+      <c r="O21" s="74"/>
+      <c r="P21" s="74"/>
       <c r="Q21" s="9"/>
       <c r="R21" s="9"/>
       <c r="S21" s="9"/>
       <c r="T21" s="13"/>
-      <c r="U21" s="81"/>
-      <c r="V21" s="78"/>
-      <c r="W21" s="78"/>
-      <c r="X21" s="78"/>
-      <c r="Y21" s="78"/>
-      <c r="Z21" s="78"/>
-      <c r="AA21" s="78"/>
-      <c r="AB21" s="78"/>
-      <c r="AC21" s="78"/>
-      <c r="AD21" s="78"/>
-      <c r="AE21" s="78"/>
+      <c r="U21" s="75"/>
+      <c r="V21" s="74"/>
+      <c r="W21" s="74"/>
+      <c r="X21" s="74"/>
+      <c r="Y21" s="74"/>
+      <c r="Z21" s="74"/>
+      <c r="AA21" s="74"/>
+      <c r="AB21" s="74"/>
+      <c r="AC21" s="74"/>
+      <c r="AD21" s="74"/>
+      <c r="AE21" s="74"/>
       <c r="AF21" s="9"/>
-      <c r="AG21" s="78"/>
-      <c r="AH21" s="78"/>
+      <c r="AG21" s="74"/>
+      <c r="AH21" s="74"/>
       <c r="AI21" s="9"/>
-      <c r="AJ21" s="78"/>
-      <c r="AK21" s="78"/>
+      <c r="AJ21" s="74"/>
+      <c r="AK21" s="74"/>
       <c r="AL21" s="9"/>
       <c r="AM21" s="9"/>
       <c r="AN21" s="9"/>
@@ -6646,43 +6678,43 @@
       <c r="BI21" s="10"/>
     </row>
     <row r="22" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="78"/>
-      <c r="B22" s="78"/>
-      <c r="C22" s="78"/>
-      <c r="D22" s="78"/>
-      <c r="E22" s="78"/>
-      <c r="F22" s="78"/>
-      <c r="G22" s="78"/>
-      <c r="H22" s="78"/>
-      <c r="I22" s="78"/>
-      <c r="J22" s="78"/>
+      <c r="A22" s="74"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="74"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="74"/>
+      <c r="I22" s="74"/>
+      <c r="J22" s="74"/>
       <c r="K22" s="9"/>
-      <c r="L22" s="78"/>
-      <c r="M22" s="78"/>
+      <c r="L22" s="74"/>
+      <c r="M22" s="74"/>
       <c r="N22" s="9"/>
-      <c r="O22" s="78"/>
-      <c r="P22" s="78"/>
+      <c r="O22" s="74"/>
+      <c r="P22" s="74"/>
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
       <c r="S22" s="9"/>
       <c r="T22" s="13"/>
-      <c r="U22" s="81"/>
-      <c r="V22" s="78"/>
-      <c r="W22" s="78"/>
-      <c r="X22" s="78"/>
-      <c r="Y22" s="78"/>
-      <c r="Z22" s="78"/>
-      <c r="AA22" s="78"/>
-      <c r="AB22" s="78"/>
-      <c r="AC22" s="78"/>
-      <c r="AD22" s="78"/>
-      <c r="AE22" s="78"/>
+      <c r="U22" s="75"/>
+      <c r="V22" s="74"/>
+      <c r="W22" s="74"/>
+      <c r="X22" s="74"/>
+      <c r="Y22" s="74"/>
+      <c r="Z22" s="74"/>
+      <c r="AA22" s="74"/>
+      <c r="AB22" s="74"/>
+      <c r="AC22" s="74"/>
+      <c r="AD22" s="74"/>
+      <c r="AE22" s="74"/>
       <c r="AF22" s="9"/>
-      <c r="AG22" s="78"/>
-      <c r="AH22" s="78"/>
+      <c r="AG22" s="74"/>
+      <c r="AH22" s="74"/>
       <c r="AI22" s="9"/>
-      <c r="AJ22" s="78"/>
-      <c r="AK22" s="78"/>
+      <c r="AJ22" s="74"/>
+      <c r="AK22" s="74"/>
       <c r="AL22" s="9"/>
       <c r="AM22" s="9"/>
       <c r="AN22" s="9"/>
@@ -6709,43 +6741,43 @@
       <c r="BI22" s="10"/>
     </row>
     <row r="23" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="78"/>
-      <c r="B23" s="78"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="78"/>
+      <c r="A23" s="74"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="74"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="74"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="74"/>
+      <c r="I23" s="74"/>
+      <c r="J23" s="74"/>
       <c r="K23" s="9"/>
-      <c r="L23" s="78"/>
-      <c r="M23" s="78"/>
+      <c r="L23" s="74"/>
+      <c r="M23" s="74"/>
       <c r="N23" s="9"/>
-      <c r="O23" s="78"/>
-      <c r="P23" s="78"/>
+      <c r="O23" s="74"/>
+      <c r="P23" s="74"/>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
       <c r="S23" s="9"/>
       <c r="T23" s="13"/>
-      <c r="U23" s="81"/>
-      <c r="V23" s="78"/>
-      <c r="W23" s="78"/>
-      <c r="X23" s="78"/>
-      <c r="Y23" s="78"/>
-      <c r="Z23" s="78"/>
-      <c r="AA23" s="78"/>
-      <c r="AB23" s="78"/>
-      <c r="AC23" s="78"/>
-      <c r="AD23" s="78"/>
-      <c r="AE23" s="78"/>
+      <c r="U23" s="75"/>
+      <c r="V23" s="74"/>
+      <c r="W23" s="74"/>
+      <c r="X23" s="74"/>
+      <c r="Y23" s="74"/>
+      <c r="Z23" s="74"/>
+      <c r="AA23" s="74"/>
+      <c r="AB23" s="74"/>
+      <c r="AC23" s="74"/>
+      <c r="AD23" s="74"/>
+      <c r="AE23" s="74"/>
       <c r="AF23" s="9"/>
-      <c r="AG23" s="78"/>
-      <c r="AH23" s="78"/>
+      <c r="AG23" s="74"/>
+      <c r="AH23" s="74"/>
       <c r="AI23" s="9"/>
-      <c r="AJ23" s="78"/>
-      <c r="AK23" s="78"/>
+      <c r="AJ23" s="74"/>
+      <c r="AK23" s="74"/>
       <c r="AL23" s="9"/>
       <c r="AM23" s="9"/>
       <c r="AN23" s="9"/>
@@ -6772,43 +6804,43 @@
       <c r="BI23" s="10"/>
     </row>
     <row r="24" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="78"/>
-      <c r="B24" s="78"/>
-      <c r="C24" s="78"/>
-      <c r="D24" s="78"/>
-      <c r="E24" s="78"/>
-      <c r="F24" s="78"/>
-      <c r="G24" s="78"/>
-      <c r="H24" s="78"/>
-      <c r="I24" s="78"/>
-      <c r="J24" s="78"/>
+      <c r="A24" s="74"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="74"/>
+      <c r="I24" s="74"/>
+      <c r="J24" s="74"/>
       <c r="K24" s="9"/>
-      <c r="L24" s="78"/>
-      <c r="M24" s="78"/>
+      <c r="L24" s="74"/>
+      <c r="M24" s="74"/>
       <c r="N24" s="9"/>
-      <c r="O24" s="78"/>
-      <c r="P24" s="78"/>
+      <c r="O24" s="74"/>
+      <c r="P24" s="74"/>
       <c r="Q24" s="9"/>
       <c r="R24" s="9"/>
       <c r="S24" s="9"/>
       <c r="T24" s="13"/>
-      <c r="U24" s="81"/>
-      <c r="V24" s="78"/>
-      <c r="W24" s="78"/>
-      <c r="X24" s="78"/>
-      <c r="Y24" s="78"/>
-      <c r="Z24" s="78"/>
-      <c r="AA24" s="78"/>
-      <c r="AB24" s="78"/>
-      <c r="AC24" s="78"/>
-      <c r="AD24" s="78"/>
-      <c r="AE24" s="78"/>
+      <c r="U24" s="75"/>
+      <c r="V24" s="74"/>
+      <c r="W24" s="74"/>
+      <c r="X24" s="74"/>
+      <c r="Y24" s="74"/>
+      <c r="Z24" s="74"/>
+      <c r="AA24" s="74"/>
+      <c r="AB24" s="74"/>
+      <c r="AC24" s="74"/>
+      <c r="AD24" s="74"/>
+      <c r="AE24" s="74"/>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="78"/>
-      <c r="AH24" s="78"/>
+      <c r="AG24" s="74"/>
+      <c r="AH24" s="74"/>
       <c r="AI24" s="9"/>
-      <c r="AJ24" s="78"/>
-      <c r="AK24" s="78"/>
+      <c r="AJ24" s="74"/>
+      <c r="AK24" s="74"/>
       <c r="AL24" s="9"/>
       <c r="AM24" s="9"/>
       <c r="AN24" s="9"/>
@@ -6835,43 +6867,43 @@
       <c r="BI24" s="10"/>
     </row>
     <row r="25" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="78"/>
-      <c r="B25" s="78"/>
-      <c r="C25" s="78"/>
-      <c r="D25" s="78"/>
-      <c r="E25" s="78"/>
-      <c r="F25" s="78"/>
-      <c r="G25" s="78"/>
-      <c r="H25" s="78"/>
-      <c r="I25" s="78"/>
-      <c r="J25" s="78"/>
+      <c r="A25" s="74"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="74"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="74"/>
+      <c r="F25" s="74"/>
+      <c r="G25" s="74"/>
+      <c r="H25" s="74"/>
+      <c r="I25" s="74"/>
+      <c r="J25" s="74"/>
       <c r="K25" s="9"/>
-      <c r="L25" s="78"/>
-      <c r="M25" s="78"/>
+      <c r="L25" s="74"/>
+      <c r="M25" s="74"/>
       <c r="N25" s="9"/>
-      <c r="O25" s="78"/>
-      <c r="P25" s="78"/>
+      <c r="O25" s="74"/>
+      <c r="P25" s="74"/>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
       <c r="S25" s="9"/>
       <c r="T25" s="13"/>
-      <c r="U25" s="81"/>
-      <c r="V25" s="78"/>
-      <c r="W25" s="78"/>
-      <c r="X25" s="78"/>
-      <c r="Y25" s="78"/>
-      <c r="Z25" s="78"/>
-      <c r="AA25" s="78"/>
-      <c r="AB25" s="78"/>
-      <c r="AC25" s="78"/>
-      <c r="AD25" s="78"/>
-      <c r="AE25" s="78"/>
+      <c r="U25" s="75"/>
+      <c r="V25" s="74"/>
+      <c r="W25" s="74"/>
+      <c r="X25" s="74"/>
+      <c r="Y25" s="74"/>
+      <c r="Z25" s="74"/>
+      <c r="AA25" s="74"/>
+      <c r="AB25" s="74"/>
+      <c r="AC25" s="74"/>
+      <c r="AD25" s="74"/>
+      <c r="AE25" s="74"/>
       <c r="AF25" s="9"/>
-      <c r="AG25" s="78"/>
-      <c r="AH25" s="78"/>
+      <c r="AG25" s="74"/>
+      <c r="AH25" s="74"/>
       <c r="AI25" s="9"/>
-      <c r="AJ25" s="78"/>
-      <c r="AK25" s="78"/>
+      <c r="AJ25" s="74"/>
+      <c r="AK25" s="74"/>
       <c r="AL25" s="9"/>
       <c r="AM25" s="9"/>
       <c r="AN25" s="9"/>
@@ -6898,43 +6930,43 @@
       <c r="BI25" s="10"/>
     </row>
     <row r="26" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="78"/>
-      <c r="B26" s="78"/>
-      <c r="C26" s="78"/>
-      <c r="D26" s="78"/>
-      <c r="E26" s="78"/>
-      <c r="F26" s="78"/>
-      <c r="G26" s="78"/>
-      <c r="H26" s="78"/>
-      <c r="I26" s="78"/>
-      <c r="J26" s="78"/>
+      <c r="A26" s="74"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="74"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="74"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="74"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="74"/>
       <c r="K26" s="9"/>
-      <c r="L26" s="78"/>
-      <c r="M26" s="78"/>
+      <c r="L26" s="74"/>
+      <c r="M26" s="74"/>
       <c r="N26" s="9"/>
-      <c r="O26" s="78"/>
-      <c r="P26" s="78"/>
+      <c r="O26" s="74"/>
+      <c r="P26" s="74"/>
       <c r="Q26" s="9"/>
       <c r="R26" s="9"/>
       <c r="S26" s="9"/>
       <c r="T26" s="13"/>
-      <c r="U26" s="81"/>
-      <c r="V26" s="78"/>
-      <c r="W26" s="78"/>
-      <c r="X26" s="78"/>
-      <c r="Y26" s="78"/>
-      <c r="Z26" s="78"/>
-      <c r="AA26" s="78"/>
-      <c r="AB26" s="78"/>
-      <c r="AC26" s="78"/>
-      <c r="AD26" s="78"/>
-      <c r="AE26" s="78"/>
+      <c r="U26" s="75"/>
+      <c r="V26" s="74"/>
+      <c r="W26" s="74"/>
+      <c r="X26" s="74"/>
+      <c r="Y26" s="74"/>
+      <c r="Z26" s="74"/>
+      <c r="AA26" s="74"/>
+      <c r="AB26" s="74"/>
+      <c r="AC26" s="74"/>
+      <c r="AD26" s="74"/>
+      <c r="AE26" s="74"/>
       <c r="AF26" s="9"/>
-      <c r="AG26" s="78"/>
-      <c r="AH26" s="78"/>
+      <c r="AG26" s="74"/>
+      <c r="AH26" s="74"/>
       <c r="AI26" s="9"/>
-      <c r="AJ26" s="78"/>
-      <c r="AK26" s="78"/>
+      <c r="AJ26" s="74"/>
+      <c r="AK26" s="74"/>
       <c r="AL26" s="9"/>
       <c r="AM26" s="9"/>
       <c r="AN26" s="9"/>
@@ -6961,43 +6993,43 @@
       <c r="BI26" s="10"/>
     </row>
     <row r="27" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="78"/>
-      <c r="B27" s="78"/>
-      <c r="C27" s="78"/>
-      <c r="D27" s="78"/>
-      <c r="E27" s="78"/>
-      <c r="F27" s="78"/>
-      <c r="G27" s="78"/>
-      <c r="H27" s="78"/>
-      <c r="I27" s="78"/>
-      <c r="J27" s="78"/>
+      <c r="A27" s="74"/>
+      <c r="B27" s="74"/>
+      <c r="C27" s="74"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="74"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="74"/>
+      <c r="H27" s="74"/>
+      <c r="I27" s="74"/>
+      <c r="J27" s="74"/>
       <c r="K27" s="9"/>
-      <c r="L27" s="78"/>
-      <c r="M27" s="78"/>
+      <c r="L27" s="74"/>
+      <c r="M27" s="74"/>
       <c r="N27" s="9"/>
-      <c r="O27" s="78"/>
-      <c r="P27" s="78"/>
+      <c r="O27" s="74"/>
+      <c r="P27" s="74"/>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="9"/>
       <c r="T27" s="13"/>
-      <c r="U27" s="81"/>
-      <c r="V27" s="78"/>
-      <c r="W27" s="78"/>
-      <c r="X27" s="78"/>
-      <c r="Y27" s="78"/>
-      <c r="Z27" s="78"/>
-      <c r="AA27" s="78"/>
-      <c r="AB27" s="78"/>
-      <c r="AC27" s="78"/>
-      <c r="AD27" s="78"/>
-      <c r="AE27" s="78"/>
+      <c r="U27" s="75"/>
+      <c r="V27" s="74"/>
+      <c r="W27" s="74"/>
+      <c r="X27" s="74"/>
+      <c r="Y27" s="74"/>
+      <c r="Z27" s="74"/>
+      <c r="AA27" s="74"/>
+      <c r="AB27" s="74"/>
+      <c r="AC27" s="74"/>
+      <c r="AD27" s="74"/>
+      <c r="AE27" s="74"/>
       <c r="AF27" s="9"/>
-      <c r="AG27" s="78"/>
-      <c r="AH27" s="78"/>
+      <c r="AG27" s="74"/>
+      <c r="AH27" s="74"/>
       <c r="AI27" s="9"/>
-      <c r="AJ27" s="78"/>
-      <c r="AK27" s="78"/>
+      <c r="AJ27" s="74"/>
+      <c r="AK27" s="74"/>
       <c r="AL27" s="9"/>
       <c r="AM27" s="9"/>
       <c r="AN27" s="9"/>
@@ -7024,43 +7056,43 @@
       <c r="BI27" s="10"/>
     </row>
     <row r="28" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="78"/>
-      <c r="B28" s="78"/>
-      <c r="C28" s="78"/>
-      <c r="D28" s="78"/>
-      <c r="E28" s="78"/>
-      <c r="F28" s="78"/>
-      <c r="G28" s="78"/>
-      <c r="H28" s="78"/>
-      <c r="I28" s="78"/>
-      <c r="J28" s="78"/>
+      <c r="A28" s="74"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="74"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="74"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="74"/>
+      <c r="H28" s="74"/>
+      <c r="I28" s="74"/>
+      <c r="J28" s="74"/>
       <c r="K28" s="9"/>
-      <c r="L28" s="78"/>
-      <c r="M28" s="78"/>
+      <c r="L28" s="74"/>
+      <c r="M28" s="74"/>
       <c r="N28" s="9"/>
-      <c r="O28" s="78"/>
-      <c r="P28" s="78"/>
+      <c r="O28" s="74"/>
+      <c r="P28" s="74"/>
       <c r="Q28" s="9"/>
       <c r="R28" s="9"/>
       <c r="S28" s="9"/>
       <c r="T28" s="13"/>
-      <c r="U28" s="81"/>
-      <c r="V28" s="78"/>
-      <c r="W28" s="78"/>
-      <c r="X28" s="78"/>
-      <c r="Y28" s="78"/>
-      <c r="Z28" s="78"/>
-      <c r="AA28" s="78"/>
-      <c r="AB28" s="78"/>
-      <c r="AC28" s="78"/>
-      <c r="AD28" s="78"/>
-      <c r="AE28" s="78"/>
+      <c r="U28" s="75"/>
+      <c r="V28" s="74"/>
+      <c r="W28" s="74"/>
+      <c r="X28" s="74"/>
+      <c r="Y28" s="74"/>
+      <c r="Z28" s="74"/>
+      <c r="AA28" s="74"/>
+      <c r="AB28" s="74"/>
+      <c r="AC28" s="74"/>
+      <c r="AD28" s="74"/>
+      <c r="AE28" s="74"/>
       <c r="AF28" s="9"/>
-      <c r="AG28" s="78"/>
-      <c r="AH28" s="78"/>
+      <c r="AG28" s="74"/>
+      <c r="AH28" s="74"/>
       <c r="AI28" s="9"/>
-      <c r="AJ28" s="78"/>
-      <c r="AK28" s="78"/>
+      <c r="AJ28" s="74"/>
+      <c r="AK28" s="74"/>
       <c r="AL28" s="9"/>
       <c r="AM28" s="9"/>
       <c r="AN28" s="9"/>
@@ -7087,43 +7119,43 @@
       <c r="BI28" s="10"/>
     </row>
     <row r="29" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="78"/>
-      <c r="B29" s="78"/>
-      <c r="C29" s="78"/>
-      <c r="D29" s="78"/>
-      <c r="E29" s="78"/>
-      <c r="F29" s="78"/>
-      <c r="G29" s="78"/>
-      <c r="H29" s="78"/>
-      <c r="I29" s="78"/>
-      <c r="J29" s="78"/>
+      <c r="A29" s="74"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="74"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="74"/>
+      <c r="F29" s="74"/>
+      <c r="G29" s="74"/>
+      <c r="H29" s="74"/>
+      <c r="I29" s="74"/>
+      <c r="J29" s="74"/>
       <c r="K29" s="9"/>
-      <c r="L29" s="78"/>
-      <c r="M29" s="78"/>
+      <c r="L29" s="74"/>
+      <c r="M29" s="74"/>
       <c r="N29" s="9"/>
-      <c r="O29" s="78"/>
-      <c r="P29" s="78"/>
+      <c r="O29" s="74"/>
+      <c r="P29" s="74"/>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="9"/>
       <c r="T29" s="13"/>
-      <c r="U29" s="81"/>
-      <c r="V29" s="78"/>
-      <c r="W29" s="78"/>
-      <c r="X29" s="78"/>
-      <c r="Y29" s="78"/>
-      <c r="Z29" s="78"/>
-      <c r="AA29" s="78"/>
-      <c r="AB29" s="78"/>
-      <c r="AC29" s="78"/>
-      <c r="AD29" s="78"/>
-      <c r="AE29" s="78"/>
+      <c r="U29" s="75"/>
+      <c r="V29" s="74"/>
+      <c r="W29" s="74"/>
+      <c r="X29" s="74"/>
+      <c r="Y29" s="74"/>
+      <c r="Z29" s="74"/>
+      <c r="AA29" s="74"/>
+      <c r="AB29" s="74"/>
+      <c r="AC29" s="74"/>
+      <c r="AD29" s="74"/>
+      <c r="AE29" s="74"/>
       <c r="AF29" s="9"/>
-      <c r="AG29" s="78"/>
-      <c r="AH29" s="78"/>
+      <c r="AG29" s="74"/>
+      <c r="AH29" s="74"/>
       <c r="AI29" s="9"/>
-      <c r="AJ29" s="78"/>
-      <c r="AK29" s="78"/>
+      <c r="AJ29" s="74"/>
+      <c r="AK29" s="74"/>
       <c r="AL29" s="9"/>
       <c r="AM29" s="9"/>
       <c r="AN29" s="9"/>
@@ -7150,43 +7182,43 @@
       <c r="BI29" s="10"/>
     </row>
     <row r="30" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="78"/>
-      <c r="B30" s="78"/>
-      <c r="C30" s="78"/>
-      <c r="D30" s="78"/>
-      <c r="E30" s="78"/>
-      <c r="F30" s="78"/>
-      <c r="G30" s="78"/>
-      <c r="H30" s="78"/>
-      <c r="I30" s="78"/>
-      <c r="J30" s="78"/>
+      <c r="A30" s="74"/>
+      <c r="B30" s="74"/>
+      <c r="C30" s="74"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="74"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="74"/>
+      <c r="H30" s="74"/>
+      <c r="I30" s="74"/>
+      <c r="J30" s="74"/>
       <c r="K30" s="9"/>
-      <c r="L30" s="78"/>
-      <c r="M30" s="78"/>
+      <c r="L30" s="74"/>
+      <c r="M30" s="74"/>
       <c r="N30" s="9"/>
-      <c r="O30" s="78"/>
-      <c r="P30" s="78"/>
+      <c r="O30" s="74"/>
+      <c r="P30" s="74"/>
       <c r="Q30" s="9"/>
       <c r="R30" s="9"/>
       <c r="S30" s="9"/>
       <c r="T30" s="13"/>
-      <c r="U30" s="81"/>
-      <c r="V30" s="78"/>
-      <c r="W30" s="78"/>
-      <c r="X30" s="78"/>
-      <c r="Y30" s="78"/>
-      <c r="Z30" s="78"/>
-      <c r="AA30" s="78"/>
-      <c r="AB30" s="78"/>
-      <c r="AC30" s="78"/>
-      <c r="AD30" s="78"/>
-      <c r="AE30" s="78"/>
+      <c r="U30" s="75"/>
+      <c r="V30" s="74"/>
+      <c r="W30" s="74"/>
+      <c r="X30" s="74"/>
+      <c r="Y30" s="74"/>
+      <c r="Z30" s="74"/>
+      <c r="AA30" s="74"/>
+      <c r="AB30" s="74"/>
+      <c r="AC30" s="74"/>
+      <c r="AD30" s="74"/>
+      <c r="AE30" s="74"/>
       <c r="AF30" s="9"/>
-      <c r="AG30" s="78"/>
-      <c r="AH30" s="78"/>
+      <c r="AG30" s="74"/>
+      <c r="AH30" s="74"/>
       <c r="AI30" s="9"/>
-      <c r="AJ30" s="78"/>
-      <c r="AK30" s="78"/>
+      <c r="AJ30" s="74"/>
+      <c r="AK30" s="74"/>
       <c r="AL30" s="9"/>
       <c r="AM30" s="9"/>
       <c r="AN30" s="9"/>
@@ -7213,43 +7245,43 @@
       <c r="BI30" s="10"/>
     </row>
     <row r="31" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="78"/>
-      <c r="B31" s="78"/>
-      <c r="C31" s="78"/>
-      <c r="D31" s="78"/>
-      <c r="E31" s="78"/>
-      <c r="F31" s="78"/>
-      <c r="G31" s="78"/>
-      <c r="H31" s="78"/>
-      <c r="I31" s="78"/>
-      <c r="J31" s="78"/>
+      <c r="A31" s="74"/>
+      <c r="B31" s="74"/>
+      <c r="C31" s="74"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="74"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="74"/>
+      <c r="J31" s="74"/>
       <c r="K31" s="9"/>
-      <c r="L31" s="78"/>
-      <c r="M31" s="78"/>
+      <c r="L31" s="74"/>
+      <c r="M31" s="74"/>
       <c r="N31" s="9"/>
-      <c r="O31" s="78"/>
-      <c r="P31" s="78"/>
+      <c r="O31" s="74"/>
+      <c r="P31" s="74"/>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
       <c r="S31" s="9"/>
       <c r="T31" s="13"/>
-      <c r="U31" s="81"/>
-      <c r="V31" s="78"/>
-      <c r="W31" s="78"/>
-      <c r="X31" s="78"/>
-      <c r="Y31" s="78"/>
-      <c r="Z31" s="78"/>
-      <c r="AA31" s="78"/>
-      <c r="AB31" s="78"/>
-      <c r="AC31" s="78"/>
-      <c r="AD31" s="78"/>
-      <c r="AE31" s="78"/>
+      <c r="U31" s="75"/>
+      <c r="V31" s="74"/>
+      <c r="W31" s="74"/>
+      <c r="X31" s="74"/>
+      <c r="Y31" s="74"/>
+      <c r="Z31" s="74"/>
+      <c r="AA31" s="74"/>
+      <c r="AB31" s="74"/>
+      <c r="AC31" s="74"/>
+      <c r="AD31" s="74"/>
+      <c r="AE31" s="74"/>
       <c r="AF31" s="9"/>
-      <c r="AG31" s="78"/>
-      <c r="AH31" s="78"/>
+      <c r="AG31" s="74"/>
+      <c r="AH31" s="74"/>
       <c r="AI31" s="9"/>
-      <c r="AJ31" s="78"/>
-      <c r="AK31" s="78"/>
+      <c r="AJ31" s="74"/>
+      <c r="AK31" s="74"/>
       <c r="AL31" s="9"/>
       <c r="AM31" s="9"/>
       <c r="AN31" s="9"/>
@@ -7276,43 +7308,43 @@
       <c r="BI31" s="10"/>
     </row>
     <row r="32" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="78"/>
-      <c r="B32" s="78"/>
-      <c r="C32" s="78"/>
-      <c r="D32" s="78"/>
-      <c r="E32" s="78"/>
-      <c r="F32" s="78"/>
-      <c r="G32" s="78"/>
-      <c r="H32" s="78"/>
-      <c r="I32" s="78"/>
-      <c r="J32" s="78"/>
+      <c r="A32" s="74"/>
+      <c r="B32" s="74"/>
+      <c r="C32" s="74"/>
+      <c r="D32" s="74"/>
+      <c r="E32" s="74"/>
+      <c r="F32" s="74"/>
+      <c r="G32" s="74"/>
+      <c r="H32" s="74"/>
+      <c r="I32" s="74"/>
+      <c r="J32" s="74"/>
       <c r="K32" s="9"/>
-      <c r="L32" s="78"/>
-      <c r="M32" s="78"/>
+      <c r="L32" s="74"/>
+      <c r="M32" s="74"/>
       <c r="N32" s="9"/>
-      <c r="O32" s="78"/>
-      <c r="P32" s="78"/>
+      <c r="O32" s="74"/>
+      <c r="P32" s="74"/>
       <c r="Q32" s="9"/>
       <c r="R32" s="9"/>
       <c r="S32" s="9"/>
       <c r="T32" s="13"/>
-      <c r="U32" s="81"/>
-      <c r="V32" s="78"/>
-      <c r="W32" s="78"/>
-      <c r="X32" s="78"/>
-      <c r="Y32" s="78"/>
-      <c r="Z32" s="78"/>
-      <c r="AA32" s="78"/>
-      <c r="AB32" s="78"/>
-      <c r="AC32" s="78"/>
-      <c r="AD32" s="78"/>
-      <c r="AE32" s="78"/>
+      <c r="U32" s="75"/>
+      <c r="V32" s="74"/>
+      <c r="W32" s="74"/>
+      <c r="X32" s="74"/>
+      <c r="Y32" s="74"/>
+      <c r="Z32" s="74"/>
+      <c r="AA32" s="74"/>
+      <c r="AB32" s="74"/>
+      <c r="AC32" s="74"/>
+      <c r="AD32" s="74"/>
+      <c r="AE32" s="74"/>
       <c r="AF32" s="9"/>
-      <c r="AG32" s="78"/>
-      <c r="AH32" s="78"/>
+      <c r="AG32" s="74"/>
+      <c r="AH32" s="74"/>
       <c r="AI32" s="9"/>
-      <c r="AJ32" s="78"/>
-      <c r="AK32" s="78"/>
+      <c r="AJ32" s="74"/>
+      <c r="AK32" s="74"/>
       <c r="AL32" s="9"/>
       <c r="AM32" s="9"/>
       <c r="AN32" s="9"/>
@@ -7339,43 +7371,43 @@
       <c r="BI32" s="10"/>
     </row>
     <row r="33" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="78"/>
-      <c r="B33" s="78"/>
-      <c r="C33" s="78"/>
-      <c r="D33" s="78"/>
-      <c r="E33" s="78"/>
-      <c r="F33" s="78"/>
-      <c r="G33" s="78"/>
-      <c r="H33" s="78"/>
-      <c r="I33" s="78"/>
-      <c r="J33" s="78"/>
+      <c r="A33" s="74"/>
+      <c r="B33" s="74"/>
+      <c r="C33" s="74"/>
+      <c r="D33" s="74"/>
+      <c r="E33" s="74"/>
+      <c r="F33" s="74"/>
+      <c r="G33" s="74"/>
+      <c r="H33" s="74"/>
+      <c r="I33" s="74"/>
+      <c r="J33" s="74"/>
       <c r="K33" s="9"/>
-      <c r="L33" s="78"/>
-      <c r="M33" s="78"/>
+      <c r="L33" s="74"/>
+      <c r="M33" s="74"/>
       <c r="N33" s="9"/>
-      <c r="O33" s="78"/>
-      <c r="P33" s="78"/>
+      <c r="O33" s="74"/>
+      <c r="P33" s="74"/>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="9"/>
       <c r="T33" s="13"/>
-      <c r="U33" s="81"/>
-      <c r="V33" s="78"/>
-      <c r="W33" s="78"/>
-      <c r="X33" s="78"/>
-      <c r="Y33" s="78"/>
-      <c r="Z33" s="78"/>
-      <c r="AA33" s="78"/>
-      <c r="AB33" s="78"/>
-      <c r="AC33" s="78"/>
-      <c r="AD33" s="78"/>
-      <c r="AE33" s="78"/>
+      <c r="U33" s="75"/>
+      <c r="V33" s="74"/>
+      <c r="W33" s="74"/>
+      <c r="X33" s="74"/>
+      <c r="Y33" s="74"/>
+      <c r="Z33" s="74"/>
+      <c r="AA33" s="74"/>
+      <c r="AB33" s="74"/>
+      <c r="AC33" s="74"/>
+      <c r="AD33" s="74"/>
+      <c r="AE33" s="74"/>
       <c r="AF33" s="9"/>
-      <c r="AG33" s="78"/>
-      <c r="AH33" s="78"/>
+      <c r="AG33" s="74"/>
+      <c r="AH33" s="74"/>
       <c r="AI33" s="9"/>
-      <c r="AJ33" s="78"/>
-      <c r="AK33" s="78"/>
+      <c r="AJ33" s="74"/>
+      <c r="AK33" s="74"/>
       <c r="AL33" s="9"/>
       <c r="AM33" s="9"/>
       <c r="AN33" s="9"/>
@@ -7402,43 +7434,43 @@
       <c r="BI33" s="10"/>
     </row>
     <row r="34" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="78"/>
-      <c r="B34" s="78"/>
-      <c r="C34" s="78"/>
-      <c r="D34" s="78"/>
-      <c r="E34" s="78"/>
-      <c r="F34" s="78"/>
-      <c r="G34" s="78"/>
-      <c r="H34" s="78"/>
-      <c r="I34" s="78"/>
-      <c r="J34" s="78"/>
+      <c r="A34" s="74"/>
+      <c r="B34" s="74"/>
+      <c r="C34" s="74"/>
+      <c r="D34" s="74"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="74"/>
+      <c r="H34" s="74"/>
+      <c r="I34" s="74"/>
+      <c r="J34" s="74"/>
       <c r="K34" s="9"/>
-      <c r="L34" s="78"/>
-      <c r="M34" s="78"/>
+      <c r="L34" s="74"/>
+      <c r="M34" s="74"/>
       <c r="N34" s="9"/>
-      <c r="O34" s="78"/>
-      <c r="P34" s="78"/>
+      <c r="O34" s="74"/>
+      <c r="P34" s="74"/>
       <c r="Q34" s="9"/>
       <c r="R34" s="9"/>
       <c r="S34" s="9"/>
       <c r="T34" s="13"/>
-      <c r="U34" s="81"/>
-      <c r="V34" s="78"/>
-      <c r="W34" s="78"/>
-      <c r="X34" s="78"/>
-      <c r="Y34" s="78"/>
-      <c r="Z34" s="78"/>
-      <c r="AA34" s="78"/>
-      <c r="AB34" s="78"/>
-      <c r="AC34" s="78"/>
-      <c r="AD34" s="78"/>
-      <c r="AE34" s="78"/>
+      <c r="U34" s="75"/>
+      <c r="V34" s="74"/>
+      <c r="W34" s="74"/>
+      <c r="X34" s="74"/>
+      <c r="Y34" s="74"/>
+      <c r="Z34" s="74"/>
+      <c r="AA34" s="74"/>
+      <c r="AB34" s="74"/>
+      <c r="AC34" s="74"/>
+      <c r="AD34" s="74"/>
+      <c r="AE34" s="74"/>
       <c r="AF34" s="9"/>
-      <c r="AG34" s="78"/>
-      <c r="AH34" s="78"/>
+      <c r="AG34" s="74"/>
+      <c r="AH34" s="74"/>
       <c r="AI34" s="9"/>
-      <c r="AJ34" s="78"/>
-      <c r="AK34" s="78"/>
+      <c r="AJ34" s="74"/>
+      <c r="AK34" s="74"/>
       <c r="AL34" s="9"/>
       <c r="AM34" s="9"/>
       <c r="AN34" s="9"/>
@@ -7465,43 +7497,43 @@
       <c r="BI34" s="10"/>
     </row>
     <row r="35" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="78"/>
-      <c r="B35" s="78"/>
-      <c r="C35" s="78"/>
-      <c r="D35" s="78"/>
-      <c r="E35" s="78"/>
-      <c r="F35" s="78"/>
-      <c r="G35" s="78"/>
-      <c r="H35" s="78"/>
-      <c r="I35" s="78"/>
-      <c r="J35" s="78"/>
+      <c r="A35" s="74"/>
+      <c r="B35" s="74"/>
+      <c r="C35" s="74"/>
+      <c r="D35" s="74"/>
+      <c r="E35" s="74"/>
+      <c r="F35" s="74"/>
+      <c r="G35" s="74"/>
+      <c r="H35" s="74"/>
+      <c r="I35" s="74"/>
+      <c r="J35" s="74"/>
       <c r="K35" s="9"/>
-      <c r="L35" s="78"/>
-      <c r="M35" s="78"/>
+      <c r="L35" s="74"/>
+      <c r="M35" s="74"/>
       <c r="N35" s="9"/>
-      <c r="O35" s="78"/>
-      <c r="P35" s="78"/>
+      <c r="O35" s="74"/>
+      <c r="P35" s="74"/>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
       <c r="S35" s="9"/>
       <c r="T35" s="13"/>
-      <c r="U35" s="81"/>
-      <c r="V35" s="78"/>
-      <c r="W35" s="78"/>
-      <c r="X35" s="78"/>
-      <c r="Y35" s="78"/>
-      <c r="Z35" s="78"/>
-      <c r="AA35" s="78"/>
-      <c r="AB35" s="78"/>
-      <c r="AC35" s="78"/>
-      <c r="AD35" s="78"/>
-      <c r="AE35" s="78"/>
+      <c r="U35" s="75"/>
+      <c r="V35" s="74"/>
+      <c r="W35" s="74"/>
+      <c r="X35" s="74"/>
+      <c r="Y35" s="74"/>
+      <c r="Z35" s="74"/>
+      <c r="AA35" s="74"/>
+      <c r="AB35" s="74"/>
+      <c r="AC35" s="74"/>
+      <c r="AD35" s="74"/>
+      <c r="AE35" s="74"/>
       <c r="AF35" s="9"/>
-      <c r="AG35" s="78"/>
-      <c r="AH35" s="78"/>
+      <c r="AG35" s="74"/>
+      <c r="AH35" s="74"/>
       <c r="AI35" s="9"/>
-      <c r="AJ35" s="78"/>
-      <c r="AK35" s="78"/>
+      <c r="AJ35" s="74"/>
+      <c r="AK35" s="74"/>
       <c r="AL35" s="9"/>
       <c r="AM35" s="9"/>
       <c r="AN35" s="9"/>
@@ -7528,43 +7560,43 @@
       <c r="BI35" s="10"/>
     </row>
     <row r="36" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="78"/>
-      <c r="B36" s="78"/>
-      <c r="C36" s="78"/>
-      <c r="D36" s="78"/>
-      <c r="E36" s="78"/>
-      <c r="F36" s="78"/>
-      <c r="G36" s="78"/>
-      <c r="H36" s="78"/>
-      <c r="I36" s="78"/>
-      <c r="J36" s="78"/>
+      <c r="A36" s="74"/>
+      <c r="B36" s="74"/>
+      <c r="C36" s="74"/>
+      <c r="D36" s="74"/>
+      <c r="E36" s="74"/>
+      <c r="F36" s="74"/>
+      <c r="G36" s="74"/>
+      <c r="H36" s="74"/>
+      <c r="I36" s="74"/>
+      <c r="J36" s="74"/>
       <c r="K36" s="9"/>
-      <c r="L36" s="78"/>
-      <c r="M36" s="78"/>
+      <c r="L36" s="74"/>
+      <c r="M36" s="74"/>
       <c r="N36" s="9"/>
-      <c r="O36" s="78"/>
-      <c r="P36" s="78"/>
+      <c r="O36" s="74"/>
+      <c r="P36" s="74"/>
       <c r="Q36" s="9"/>
       <c r="R36" s="9"/>
       <c r="S36" s="9"/>
       <c r="T36" s="13"/>
-      <c r="U36" s="81"/>
-      <c r="V36" s="78"/>
-      <c r="W36" s="78"/>
-      <c r="X36" s="78"/>
-      <c r="Y36" s="78"/>
-      <c r="Z36" s="78"/>
-      <c r="AA36" s="78"/>
-      <c r="AB36" s="78"/>
-      <c r="AC36" s="78"/>
-      <c r="AD36" s="78"/>
-      <c r="AE36" s="78"/>
+      <c r="U36" s="75"/>
+      <c r="V36" s="74"/>
+      <c r="W36" s="74"/>
+      <c r="X36" s="74"/>
+      <c r="Y36" s="74"/>
+      <c r="Z36" s="74"/>
+      <c r="AA36" s="74"/>
+      <c r="AB36" s="74"/>
+      <c r="AC36" s="74"/>
+      <c r="AD36" s="74"/>
+      <c r="AE36" s="74"/>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="78"/>
-      <c r="AH36" s="78"/>
+      <c r="AG36" s="74"/>
+      <c r="AH36" s="74"/>
       <c r="AI36" s="9"/>
-      <c r="AJ36" s="78"/>
-      <c r="AK36" s="78"/>
+      <c r="AJ36" s="74"/>
+      <c r="AK36" s="74"/>
       <c r="AL36" s="9"/>
       <c r="AM36" s="9"/>
       <c r="AN36" s="9"/>
@@ -7591,43 +7623,43 @@
       <c r="BI36" s="10"/>
     </row>
     <row r="37" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="78"/>
-      <c r="B37" s="78"/>
-      <c r="C37" s="78"/>
-      <c r="D37" s="78"/>
-      <c r="E37" s="78"/>
-      <c r="F37" s="78"/>
-      <c r="G37" s="78"/>
-      <c r="H37" s="78"/>
-      <c r="I37" s="78"/>
-      <c r="J37" s="78"/>
+      <c r="A37" s="74"/>
+      <c r="B37" s="74"/>
+      <c r="C37" s="74"/>
+      <c r="D37" s="74"/>
+      <c r="E37" s="74"/>
+      <c r="F37" s="74"/>
+      <c r="G37" s="74"/>
+      <c r="H37" s="74"/>
+      <c r="I37" s="74"/>
+      <c r="J37" s="74"/>
       <c r="K37" s="9"/>
-      <c r="L37" s="78"/>
-      <c r="M37" s="78"/>
+      <c r="L37" s="74"/>
+      <c r="M37" s="74"/>
       <c r="N37" s="9"/>
-      <c r="O37" s="78"/>
-      <c r="P37" s="78"/>
+      <c r="O37" s="74"/>
+      <c r="P37" s="74"/>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="9"/>
       <c r="T37" s="13"/>
-      <c r="U37" s="81"/>
-      <c r="V37" s="78"/>
-      <c r="W37" s="78"/>
-      <c r="X37" s="78"/>
-      <c r="Y37" s="78"/>
-      <c r="Z37" s="78"/>
-      <c r="AA37" s="78"/>
-      <c r="AB37" s="78"/>
-      <c r="AC37" s="78"/>
-      <c r="AD37" s="78"/>
-      <c r="AE37" s="78"/>
+      <c r="U37" s="75"/>
+      <c r="V37" s="74"/>
+      <c r="W37" s="74"/>
+      <c r="X37" s="74"/>
+      <c r="Y37" s="74"/>
+      <c r="Z37" s="74"/>
+      <c r="AA37" s="74"/>
+      <c r="AB37" s="74"/>
+      <c r="AC37" s="74"/>
+      <c r="AD37" s="74"/>
+      <c r="AE37" s="74"/>
       <c r="AF37" s="9"/>
-      <c r="AG37" s="78"/>
-      <c r="AH37" s="78"/>
+      <c r="AG37" s="74"/>
+      <c r="AH37" s="74"/>
       <c r="AI37" s="9"/>
-      <c r="AJ37" s="78"/>
-      <c r="AK37" s="78"/>
+      <c r="AJ37" s="74"/>
+      <c r="AK37" s="74"/>
       <c r="AL37" s="9"/>
       <c r="AM37" s="9"/>
       <c r="AN37" s="9"/>
@@ -7654,43 +7686,43 @@
       <c r="BI37" s="10"/>
     </row>
     <row r="38" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="78"/>
-      <c r="B38" s="78"/>
-      <c r="C38" s="78"/>
-      <c r="D38" s="78"/>
-      <c r="E38" s="78"/>
-      <c r="F38" s="78"/>
-      <c r="G38" s="78"/>
-      <c r="H38" s="78"/>
-      <c r="I38" s="78"/>
-      <c r="J38" s="78"/>
+      <c r="A38" s="74"/>
+      <c r="B38" s="74"/>
+      <c r="C38" s="74"/>
+      <c r="D38" s="74"/>
+      <c r="E38" s="74"/>
+      <c r="F38" s="74"/>
+      <c r="G38" s="74"/>
+      <c r="H38" s="74"/>
+      <c r="I38" s="74"/>
+      <c r="J38" s="74"/>
       <c r="K38" s="9"/>
-      <c r="L38" s="78"/>
-      <c r="M38" s="78"/>
+      <c r="L38" s="74"/>
+      <c r="M38" s="74"/>
       <c r="N38" s="9"/>
-      <c r="O38" s="78"/>
-      <c r="P38" s="78"/>
+      <c r="O38" s="74"/>
+      <c r="P38" s="74"/>
       <c r="Q38" s="9"/>
       <c r="R38" s="9"/>
       <c r="S38" s="9"/>
       <c r="T38" s="13"/>
-      <c r="U38" s="81"/>
-      <c r="V38" s="78"/>
-      <c r="W38" s="78"/>
-      <c r="X38" s="78"/>
-      <c r="Y38" s="78"/>
-      <c r="Z38" s="78"/>
-      <c r="AA38" s="78"/>
-      <c r="AB38" s="78"/>
-      <c r="AC38" s="78"/>
-      <c r="AD38" s="78"/>
-      <c r="AE38" s="78"/>
+      <c r="U38" s="75"/>
+      <c r="V38" s="74"/>
+      <c r="W38" s="74"/>
+      <c r="X38" s="74"/>
+      <c r="Y38" s="74"/>
+      <c r="Z38" s="74"/>
+      <c r="AA38" s="74"/>
+      <c r="AB38" s="74"/>
+      <c r="AC38" s="74"/>
+      <c r="AD38" s="74"/>
+      <c r="AE38" s="74"/>
       <c r="AF38" s="9"/>
-      <c r="AG38" s="78"/>
-      <c r="AH38" s="78"/>
+      <c r="AG38" s="74"/>
+      <c r="AH38" s="74"/>
       <c r="AI38" s="9"/>
-      <c r="AJ38" s="78"/>
-      <c r="AK38" s="78"/>
+      <c r="AJ38" s="74"/>
+      <c r="AK38" s="74"/>
       <c r="AL38" s="9"/>
       <c r="AM38" s="9"/>
       <c r="AN38" s="9"/>
@@ -7717,43 +7749,43 @@
       <c r="BI38" s="10"/>
     </row>
     <row r="39" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="78"/>
-      <c r="B39" s="78"/>
-      <c r="C39" s="78"/>
-      <c r="D39" s="78"/>
-      <c r="E39" s="78"/>
-      <c r="F39" s="78"/>
-      <c r="G39" s="78"/>
-      <c r="H39" s="78"/>
-      <c r="I39" s="78"/>
-      <c r="J39" s="78"/>
+      <c r="A39" s="74"/>
+      <c r="B39" s="74"/>
+      <c r="C39" s="74"/>
+      <c r="D39" s="74"/>
+      <c r="E39" s="74"/>
+      <c r="F39" s="74"/>
+      <c r="G39" s="74"/>
+      <c r="H39" s="74"/>
+      <c r="I39" s="74"/>
+      <c r="J39" s="74"/>
       <c r="K39" s="9"/>
-      <c r="L39" s="78"/>
-      <c r="M39" s="78"/>
+      <c r="L39" s="74"/>
+      <c r="M39" s="74"/>
       <c r="N39" s="9"/>
-      <c r="O39" s="78"/>
-      <c r="P39" s="78"/>
+      <c r="O39" s="74"/>
+      <c r="P39" s="74"/>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
       <c r="S39" s="9"/>
       <c r="T39" s="13"/>
-      <c r="U39" s="81"/>
-      <c r="V39" s="78"/>
-      <c r="W39" s="78"/>
-      <c r="X39" s="78"/>
-      <c r="Y39" s="78"/>
-      <c r="Z39" s="78"/>
-      <c r="AA39" s="78"/>
-      <c r="AB39" s="78"/>
-      <c r="AC39" s="78"/>
-      <c r="AD39" s="78"/>
-      <c r="AE39" s="78"/>
+      <c r="U39" s="75"/>
+      <c r="V39" s="74"/>
+      <c r="W39" s="74"/>
+      <c r="X39" s="74"/>
+      <c r="Y39" s="74"/>
+      <c r="Z39" s="74"/>
+      <c r="AA39" s="74"/>
+      <c r="AB39" s="74"/>
+      <c r="AC39" s="74"/>
+      <c r="AD39" s="74"/>
+      <c r="AE39" s="74"/>
       <c r="AF39" s="9"/>
-      <c r="AG39" s="78"/>
-      <c r="AH39" s="78"/>
+      <c r="AG39" s="74"/>
+      <c r="AH39" s="74"/>
       <c r="AI39" s="9"/>
-      <c r="AJ39" s="78"/>
-      <c r="AK39" s="78"/>
+      <c r="AJ39" s="74"/>
+      <c r="AK39" s="74"/>
       <c r="AL39" s="9"/>
       <c r="AM39" s="9"/>
       <c r="AN39" s="9"/>
@@ -7780,43 +7812,43 @@
       <c r="BI39" s="10"/>
     </row>
     <row r="40" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="78"/>
-      <c r="B40" s="78"/>
-      <c r="C40" s="78"/>
-      <c r="D40" s="78"/>
-      <c r="E40" s="78"/>
-      <c r="F40" s="78"/>
-      <c r="G40" s="78"/>
-      <c r="H40" s="78"/>
-      <c r="I40" s="78"/>
-      <c r="J40" s="78"/>
+      <c r="A40" s="74"/>
+      <c r="B40" s="74"/>
+      <c r="C40" s="74"/>
+      <c r="D40" s="74"/>
+      <c r="E40" s="74"/>
+      <c r="F40" s="74"/>
+      <c r="G40" s="74"/>
+      <c r="H40" s="74"/>
+      <c r="I40" s="74"/>
+      <c r="J40" s="74"/>
       <c r="K40" s="9"/>
-      <c r="L40" s="78"/>
-      <c r="M40" s="78"/>
+      <c r="L40" s="74"/>
+      <c r="M40" s="74"/>
       <c r="N40" s="9"/>
-      <c r="O40" s="78"/>
-      <c r="P40" s="78"/>
+      <c r="O40" s="74"/>
+      <c r="P40" s="74"/>
       <c r="Q40" s="9"/>
       <c r="R40" s="9"/>
       <c r="S40" s="9"/>
       <c r="T40" s="13"/>
-      <c r="U40" s="81"/>
-      <c r="V40" s="78"/>
-      <c r="W40" s="78"/>
-      <c r="X40" s="78"/>
-      <c r="Y40" s="78"/>
-      <c r="Z40" s="78"/>
-      <c r="AA40" s="78"/>
-      <c r="AB40" s="78"/>
-      <c r="AC40" s="78"/>
-      <c r="AD40" s="78"/>
-      <c r="AE40" s="78"/>
+      <c r="U40" s="75"/>
+      <c r="V40" s="74"/>
+      <c r="W40" s="74"/>
+      <c r="X40" s="74"/>
+      <c r="Y40" s="74"/>
+      <c r="Z40" s="74"/>
+      <c r="AA40" s="74"/>
+      <c r="AB40" s="74"/>
+      <c r="AC40" s="74"/>
+      <c r="AD40" s="74"/>
+      <c r="AE40" s="74"/>
       <c r="AF40" s="9"/>
-      <c r="AG40" s="78"/>
-      <c r="AH40" s="78"/>
+      <c r="AG40" s="74"/>
+      <c r="AH40" s="74"/>
       <c r="AI40" s="9"/>
-      <c r="AJ40" s="78"/>
-      <c r="AK40" s="78"/>
+      <c r="AJ40" s="74"/>
+      <c r="AK40" s="74"/>
       <c r="AL40" s="9"/>
       <c r="AM40" s="9"/>
       <c r="AN40" s="9"/>
@@ -8951,9 +8983,9 @@
       <c r="AI66" s="6"/>
       <c r="AJ66" s="6"/>
       <c r="AK66" s="6"/>
-      <c r="AL66" s="71"/>
-      <c r="AM66" s="71"/>
-      <c r="AN66" s="71"/>
+      <c r="AL66" s="16"/>
+      <c r="AM66" s="16"/>
+      <c r="AN66" s="16"/>
     </row>
     <row r="67" spans="1:41" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4"/>
@@ -9129,6 +9161,189 @@
     </row>
   </sheetData>
   <mergeCells count="207">
+    <mergeCell ref="AJ38:AK38"/>
+    <mergeCell ref="AJ39:AK39"/>
+    <mergeCell ref="AJ40:AK40"/>
+    <mergeCell ref="AP11:BA11"/>
+    <mergeCell ref="BC11:BI11"/>
+    <mergeCell ref="AJ33:AK33"/>
+    <mergeCell ref="AJ34:AK34"/>
+    <mergeCell ref="AJ35:AK35"/>
+    <mergeCell ref="AJ36:AK36"/>
+    <mergeCell ref="AJ37:AK37"/>
+    <mergeCell ref="AJ28:AK28"/>
+    <mergeCell ref="AJ29:AK29"/>
+    <mergeCell ref="AJ30:AK30"/>
+    <mergeCell ref="AJ31:AK31"/>
+    <mergeCell ref="AJ32:AK32"/>
+    <mergeCell ref="AJ12:AK12"/>
+    <mergeCell ref="AG40:AH40"/>
+    <mergeCell ref="AJ13:AK13"/>
+    <mergeCell ref="AJ14:AK14"/>
+    <mergeCell ref="AJ15:AK15"/>
+    <mergeCell ref="AJ16:AK16"/>
+    <mergeCell ref="AJ17:AK17"/>
+    <mergeCell ref="AJ18:AK18"/>
+    <mergeCell ref="AJ19:AK19"/>
+    <mergeCell ref="AJ20:AK20"/>
+    <mergeCell ref="AJ21:AK21"/>
+    <mergeCell ref="AJ22:AK22"/>
+    <mergeCell ref="AJ23:AK23"/>
+    <mergeCell ref="AJ24:AK24"/>
+    <mergeCell ref="AJ25:AK25"/>
+    <mergeCell ref="AJ26:AK26"/>
+    <mergeCell ref="AJ27:AK27"/>
+    <mergeCell ref="AG35:AH35"/>
+    <mergeCell ref="AG36:AH36"/>
+    <mergeCell ref="AG37:AH37"/>
+    <mergeCell ref="AG38:AH38"/>
+    <mergeCell ref="AG39:AH39"/>
+    <mergeCell ref="AG30:AH30"/>
+    <mergeCell ref="AG31:AH31"/>
+    <mergeCell ref="AG32:AH32"/>
+    <mergeCell ref="AG33:AH33"/>
+    <mergeCell ref="AG34:AH34"/>
+    <mergeCell ref="AG25:AH25"/>
+    <mergeCell ref="AG26:AH26"/>
+    <mergeCell ref="AG27:AH27"/>
+    <mergeCell ref="AG28:AH28"/>
+    <mergeCell ref="AG29:AH29"/>
+    <mergeCell ref="U37:AE37"/>
+    <mergeCell ref="U38:AE38"/>
+    <mergeCell ref="U39:AE39"/>
+    <mergeCell ref="U40:AE40"/>
+    <mergeCell ref="AG13:AH13"/>
+    <mergeCell ref="AG14:AH14"/>
+    <mergeCell ref="AG15:AH15"/>
+    <mergeCell ref="AG16:AH16"/>
+    <mergeCell ref="AG17:AH17"/>
+    <mergeCell ref="AG18:AH18"/>
+    <mergeCell ref="AG19:AH19"/>
+    <mergeCell ref="AG20:AH20"/>
+    <mergeCell ref="AG21:AH21"/>
+    <mergeCell ref="AG22:AH22"/>
+    <mergeCell ref="AG23:AH23"/>
+    <mergeCell ref="AG24:AH24"/>
+    <mergeCell ref="U32:AE32"/>
+    <mergeCell ref="U33:AE33"/>
+    <mergeCell ref="U34:AE34"/>
+    <mergeCell ref="U35:AE35"/>
+    <mergeCell ref="U36:AE36"/>
+    <mergeCell ref="U27:AE27"/>
+    <mergeCell ref="U28:AE28"/>
+    <mergeCell ref="U29:AE29"/>
+    <mergeCell ref="U30:AE30"/>
+    <mergeCell ref="U31:AE31"/>
+    <mergeCell ref="AG12:AH12"/>
+    <mergeCell ref="U13:AE13"/>
+    <mergeCell ref="U14:AE14"/>
+    <mergeCell ref="U15:AE15"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="U12:AE12"/>
+    <mergeCell ref="U16:AE16"/>
+    <mergeCell ref="U17:AE17"/>
+    <mergeCell ref="U18:AE18"/>
+    <mergeCell ref="U19:AE19"/>
+    <mergeCell ref="U20:AE20"/>
+    <mergeCell ref="U21:AE21"/>
+    <mergeCell ref="U22:AE22"/>
+    <mergeCell ref="U23:AE23"/>
+    <mergeCell ref="U24:AE24"/>
+    <mergeCell ref="U25:AE25"/>
+    <mergeCell ref="U26:AE26"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="AP9:BI9"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="AJ11:AK11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="AG11:AH11"/>
+    <mergeCell ref="U11:AE11"/>
+    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A19:J19"/>
     <mergeCell ref="AY1:BI1"/>
     <mergeCell ref="F1:J1"/>
     <mergeCell ref="K1:V1"/>
@@ -9153,189 +9368,6 @@
     <mergeCell ref="AN2:AR3"/>
     <mergeCell ref="A9:T9"/>
     <mergeCell ref="U9:AO9"/>
-    <mergeCell ref="AP9:BI9"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="A12:J12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="AJ11:AK11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="AG11:AH11"/>
-    <mergeCell ref="U11:AE11"/>
-    <mergeCell ref="A15:J15"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A38:J38"/>
-    <mergeCell ref="A39:J39"/>
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="A33:J33"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A35:J35"/>
-    <mergeCell ref="A36:J36"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="AG12:AH12"/>
-    <mergeCell ref="U13:AE13"/>
-    <mergeCell ref="U14:AE14"/>
-    <mergeCell ref="U15:AE15"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="U12:AE12"/>
-    <mergeCell ref="U16:AE16"/>
-    <mergeCell ref="U17:AE17"/>
-    <mergeCell ref="U18:AE18"/>
-    <mergeCell ref="U19:AE19"/>
-    <mergeCell ref="U20:AE20"/>
-    <mergeCell ref="U21:AE21"/>
-    <mergeCell ref="U22:AE22"/>
-    <mergeCell ref="U23:AE23"/>
-    <mergeCell ref="U24:AE24"/>
-    <mergeCell ref="U25:AE25"/>
-    <mergeCell ref="U26:AE26"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="U39:AE39"/>
-    <mergeCell ref="U40:AE40"/>
-    <mergeCell ref="AG13:AH13"/>
-    <mergeCell ref="AG14:AH14"/>
-    <mergeCell ref="AG15:AH15"/>
-    <mergeCell ref="AG16:AH16"/>
-    <mergeCell ref="AG17:AH17"/>
-    <mergeCell ref="AG18:AH18"/>
-    <mergeCell ref="AG19:AH19"/>
-    <mergeCell ref="AG20:AH20"/>
-    <mergeCell ref="AG21:AH21"/>
-    <mergeCell ref="AG22:AH22"/>
-    <mergeCell ref="AG23:AH23"/>
-    <mergeCell ref="AG24:AH24"/>
-    <mergeCell ref="U32:AE32"/>
-    <mergeCell ref="U33:AE33"/>
-    <mergeCell ref="U34:AE34"/>
-    <mergeCell ref="U35:AE35"/>
-    <mergeCell ref="U36:AE36"/>
-    <mergeCell ref="U27:AE27"/>
-    <mergeCell ref="U28:AE28"/>
-    <mergeCell ref="U29:AE29"/>
-    <mergeCell ref="U30:AE30"/>
-    <mergeCell ref="U31:AE31"/>
-    <mergeCell ref="AG33:AH33"/>
-    <mergeCell ref="AG34:AH34"/>
-    <mergeCell ref="AG25:AH25"/>
-    <mergeCell ref="AG26:AH26"/>
-    <mergeCell ref="AG27:AH27"/>
-    <mergeCell ref="AG28:AH28"/>
-    <mergeCell ref="AG29:AH29"/>
-    <mergeCell ref="U37:AE37"/>
-    <mergeCell ref="U38:AE38"/>
-    <mergeCell ref="AG40:AH40"/>
-    <mergeCell ref="AJ13:AK13"/>
-    <mergeCell ref="AJ14:AK14"/>
-    <mergeCell ref="AJ15:AK15"/>
-    <mergeCell ref="AJ16:AK16"/>
-    <mergeCell ref="AJ17:AK17"/>
-    <mergeCell ref="AJ18:AK18"/>
-    <mergeCell ref="AJ19:AK19"/>
-    <mergeCell ref="AJ20:AK20"/>
-    <mergeCell ref="AJ21:AK21"/>
-    <mergeCell ref="AJ22:AK22"/>
-    <mergeCell ref="AJ23:AK23"/>
-    <mergeCell ref="AJ24:AK24"/>
-    <mergeCell ref="AJ25:AK25"/>
-    <mergeCell ref="AJ26:AK26"/>
-    <mergeCell ref="AJ27:AK27"/>
-    <mergeCell ref="AG35:AH35"/>
-    <mergeCell ref="AG36:AH36"/>
-    <mergeCell ref="AG37:AH37"/>
-    <mergeCell ref="AG38:AH38"/>
-    <mergeCell ref="AG39:AH39"/>
-    <mergeCell ref="AG30:AH30"/>
-    <mergeCell ref="AG31:AH31"/>
-    <mergeCell ref="AG32:AH32"/>
-    <mergeCell ref="AJ38:AK38"/>
-    <mergeCell ref="AJ39:AK39"/>
-    <mergeCell ref="AJ40:AK40"/>
-    <mergeCell ref="AP11:BA11"/>
-    <mergeCell ref="BC11:BI11"/>
-    <mergeCell ref="AJ33:AK33"/>
-    <mergeCell ref="AJ34:AK34"/>
-    <mergeCell ref="AJ35:AK35"/>
-    <mergeCell ref="AJ36:AK36"/>
-    <mergeCell ref="AJ37:AK37"/>
-    <mergeCell ref="AJ28:AK28"/>
-    <mergeCell ref="AJ29:AK29"/>
-    <mergeCell ref="AJ30:AK30"/>
-    <mergeCell ref="AJ31:AK31"/>
-    <mergeCell ref="AJ32:AK32"/>
-    <mergeCell ref="AJ12:AK12"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -9346,12 +9378,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="bdc2d3d5-fc31-4d65-8e89-042f9aabae79" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="13b50d63-4097-4260-987b-0df3cda3515c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9556,20 +9590,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="bdc2d3d5-fc31-4d65-8e89-042f9aabae79" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="13b50d63-4097-4260-987b-0df3cda3515c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED9081D4-7DA8-4E8C-9299-427A52260533}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA865533-0B77-4147-AA92-F0C2FDB2E315}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bdc2d3d5-fc31-4d65-8e89-042f9aabae79"/>
+    <ds:schemaRef ds:uri="13b50d63-4097-4260-987b-0df3cda3515c"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9594,12 +9629,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA865533-0B77-4147-AA92-F0C2FDB2E315}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED9081D4-7DA8-4E8C-9299-427A52260533}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bdc2d3d5-fc31-4d65-8e89-042f9aabae79"/>
-    <ds:schemaRef ds:uri="13b50d63-4097-4260-987b-0df3cda3515c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/template_produzione.xlsx
+++ b/template_produzione.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maxporte.sharepoint.com/sites/MPCloud/Documenti condivisi/MPX/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="671" documentId="8_{CC15ACFE-ED8D-4D36-8DB1-DE3148A82591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B977DFE4-DF18-41AD-A5C5-B94323CA001B}"/>
+  <xr:revisionPtr revIDLastSave="673" documentId="8_{CC15ACFE-ED8D-4D36-8DB1-DE3148A82591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE974878-0D3C-4D22-B7F8-0D1607D337C3}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{2F1D62B1-3FD5-4D97-A455-0CD2ABF42920}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21820" activeTab="1" xr2:uid="{2F1D62B1-3FD5-4D97-A455-0CD2ABF42920}"/>
   </bookViews>
   <sheets>
     <sheet name="SCHEDA_PRODUZIONE" sheetId="2" r:id="rId1"/>
@@ -584,7 +584,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -621,8 +621,68 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
@@ -660,73 +720,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -760,75 +753,64 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1179,74 +1161,74 @@
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="45" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
-      <c r="S1" s="46"/>
-      <c r="T1" s="46"/>
-      <c r="U1" s="46"/>
-      <c r="V1" s="47"/>
-      <c r="W1" s="45" t="s">
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="46"/>
-      <c r="Z1" s="46"/>
-      <c r="AA1" s="46"/>
-      <c r="AB1" s="46"/>
-      <c r="AC1" s="46"/>
-      <c r="AD1" s="46"/>
-      <c r="AE1" s="46"/>
-      <c r="AF1" s="46"/>
-      <c r="AG1" s="46"/>
-      <c r="AH1" s="47"/>
-      <c r="AI1" s="45" t="s">
+      <c r="X1" s="33"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="33"/>
+      <c r="AB1" s="33"/>
+      <c r="AC1" s="33"/>
+      <c r="AD1" s="33"/>
+      <c r="AE1" s="33"/>
+      <c r="AF1" s="33"/>
+      <c r="AG1" s="33"/>
+      <c r="AH1" s="34"/>
+      <c r="AI1" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="AJ1" s="46"/>
-      <c r="AK1" s="46"/>
-      <c r="AL1" s="46"/>
-      <c r="AM1" s="47"/>
-      <c r="AN1" s="45" t="s">
+      <c r="AJ1" s="33"/>
+      <c r="AK1" s="33"/>
+      <c r="AL1" s="33"/>
+      <c r="AM1" s="34"/>
+      <c r="AN1" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="AO1" s="46"/>
-      <c r="AP1" s="46"/>
-      <c r="AQ1" s="46"/>
-      <c r="AR1" s="47"/>
+      <c r="AO1" s="33"/>
+      <c r="AP1" s="33"/>
+      <c r="AQ1" s="33"/>
+      <c r="AR1" s="34"/>
       <c r="AS1" s="7"/>
       <c r="AT1" s="7"/>
       <c r="AU1" s="7"/>
       <c r="AV1" s="7"/>
       <c r="AW1" s="7"/>
       <c r="AX1" s="7"/>
-      <c r="AY1" s="42" t="s">
+      <c r="AY1" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="AZ1" s="42"/>
-      <c r="BA1" s="42"/>
-      <c r="BB1" s="42"/>
-      <c r="BC1" s="42"/>
-      <c r="BD1" s="42"/>
-      <c r="BE1" s="42"/>
-      <c r="BF1" s="42"/>
-      <c r="BG1" s="42"/>
-      <c r="BH1" s="42"/>
-      <c r="BI1" s="42"/>
+      <c r="AZ1" s="29"/>
+      <c r="BA1" s="29"/>
+      <c r="BB1" s="29"/>
+      <c r="BC1" s="29"/>
+      <c r="BD1" s="29"/>
+      <c r="BE1" s="29"/>
+      <c r="BF1" s="29"/>
+      <c r="BG1" s="29"/>
+      <c r="BH1" s="29"/>
+      <c r="BI1" s="29"/>
     </row>
     <row r="2" spans="1:62" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
@@ -1254,68 +1236,68 @@
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="88" t="s">
+      <c r="F2" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="17" t="s">
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="18"/>
-      <c r="U2" s="18"/>
-      <c r="V2" s="19"/>
-      <c r="W2" s="17" t="s">
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="42"/>
+      <c r="P2" s="42"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="42"/>
+      <c r="S2" s="42"/>
+      <c r="T2" s="42"/>
+      <c r="U2" s="42"/>
+      <c r="V2" s="43"/>
+      <c r="W2" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="X2" s="18"/>
-      <c r="Y2" s="18"/>
-      <c r="Z2" s="18"/>
-      <c r="AA2" s="18"/>
-      <c r="AB2" s="18"/>
-      <c r="AC2" s="18"/>
-      <c r="AD2" s="18"/>
-      <c r="AE2" s="18"/>
-      <c r="AF2" s="18"/>
-      <c r="AG2" s="18"/>
-      <c r="AH2" s="19"/>
-      <c r="AI2" s="23" t="s">
+      <c r="X2" s="42"/>
+      <c r="Y2" s="42"/>
+      <c r="Z2" s="42"/>
+      <c r="AA2" s="42"/>
+      <c r="AB2" s="42"/>
+      <c r="AC2" s="42"/>
+      <c r="AD2" s="42"/>
+      <c r="AE2" s="42"/>
+      <c r="AF2" s="42"/>
+      <c r="AG2" s="42"/>
+      <c r="AH2" s="43"/>
+      <c r="AI2" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="AJ2" s="24"/>
-      <c r="AK2" s="24"/>
-      <c r="AL2" s="24"/>
-      <c r="AM2" s="25"/>
-      <c r="AN2" s="23" t="s">
+      <c r="AJ2" s="48"/>
+      <c r="AK2" s="48"/>
+      <c r="AL2" s="48"/>
+      <c r="AM2" s="49"/>
+      <c r="AN2" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="AO2" s="24"/>
-      <c r="AP2" s="24"/>
-      <c r="AQ2" s="24"/>
-      <c r="AR2" s="25"/>
-      <c r="AY2" s="43" t="s">
+      <c r="AO2" s="48"/>
+      <c r="AP2" s="48"/>
+      <c r="AQ2" s="48"/>
+      <c r="AR2" s="49"/>
+      <c r="AY2" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="AZ2" s="43"/>
-      <c r="BA2" s="43"/>
-      <c r="BB2" s="43"/>
-      <c r="BC2" s="43"/>
-      <c r="BD2" s="43"/>
-      <c r="BE2" s="43"/>
-      <c r="BF2" s="43"/>
-      <c r="BG2" s="43"/>
-      <c r="BH2" s="43"/>
-      <c r="BI2" s="43"/>
+      <c r="AZ2" s="30"/>
+      <c r="BA2" s="30"/>
+      <c r="BB2" s="30"/>
+      <c r="BC2" s="30"/>
+      <c r="BD2" s="30"/>
+      <c r="BE2" s="30"/>
+      <c r="BF2" s="30"/>
+      <c r="BG2" s="30"/>
+      <c r="BH2" s="30"/>
+      <c r="BI2" s="30"/>
     </row>
     <row r="3" spans="1:62" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4"/>
@@ -1323,56 +1305,56 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
-      <c r="I3" s="92"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="21"/>
-      <c r="S3" s="21"/>
-      <c r="T3" s="21"/>
-      <c r="U3" s="21"/>
-      <c r="V3" s="22"/>
-      <c r="W3" s="20"/>
-      <c r="X3" s="21"/>
-      <c r="Y3" s="21"/>
-      <c r="Z3" s="21"/>
-      <c r="AA3" s="21"/>
-      <c r="AB3" s="21"/>
-      <c r="AC3" s="21"/>
-      <c r="AD3" s="21"/>
-      <c r="AE3" s="21"/>
-      <c r="AF3" s="21"/>
-      <c r="AG3" s="21"/>
-      <c r="AH3" s="22"/>
-      <c r="AI3" s="26"/>
-      <c r="AJ3" s="27"/>
-      <c r="AK3" s="27"/>
-      <c r="AL3" s="27"/>
-      <c r="AM3" s="28"/>
-      <c r="AN3" s="26"/>
-      <c r="AO3" s="27"/>
-      <c r="AP3" s="27"/>
-      <c r="AQ3" s="27"/>
-      <c r="AR3" s="28"/>
-      <c r="AY3" s="44"/>
-      <c r="AZ3" s="44"/>
-      <c r="BA3" s="44"/>
-      <c r="BB3" s="44"/>
-      <c r="BC3" s="44"/>
-      <c r="BD3" s="44"/>
-      <c r="BE3" s="44"/>
-      <c r="BF3" s="44"/>
-      <c r="BG3" s="44"/>
-      <c r="BH3" s="44"/>
-      <c r="BI3" s="44"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="45"/>
+      <c r="Q3" s="45"/>
+      <c r="R3" s="45"/>
+      <c r="S3" s="45"/>
+      <c r="T3" s="45"/>
+      <c r="U3" s="45"/>
+      <c r="V3" s="46"/>
+      <c r="W3" s="44"/>
+      <c r="X3" s="45"/>
+      <c r="Y3" s="45"/>
+      <c r="Z3" s="45"/>
+      <c r="AA3" s="45"/>
+      <c r="AB3" s="45"/>
+      <c r="AC3" s="45"/>
+      <c r="AD3" s="45"/>
+      <c r="AE3" s="45"/>
+      <c r="AF3" s="45"/>
+      <c r="AG3" s="45"/>
+      <c r="AH3" s="46"/>
+      <c r="AI3" s="50"/>
+      <c r="AJ3" s="51"/>
+      <c r="AK3" s="51"/>
+      <c r="AL3" s="51"/>
+      <c r="AM3" s="52"/>
+      <c r="AN3" s="50"/>
+      <c r="AO3" s="51"/>
+      <c r="AP3" s="51"/>
+      <c r="AQ3" s="51"/>
+      <c r="AR3" s="52"/>
+      <c r="AY3" s="31"/>
+      <c r="AZ3" s="31"/>
+      <c r="BA3" s="31"/>
+      <c r="BB3" s="31"/>
+      <c r="BC3" s="31"/>
+      <c r="BD3" s="31"/>
+      <c r="BE3" s="31"/>
+      <c r="BF3" s="31"/>
+      <c r="BG3" s="31"/>
+      <c r="BH3" s="31"/>
+      <c r="BI3" s="31"/>
     </row>
     <row r="4" spans="1:62" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
@@ -1380,66 +1362,66 @@
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="54" t="s">
+      <c r="F4" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="54" t="s">
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="54" t="s">
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="Q4" s="55"/>
-      <c r="R4" s="55"/>
-      <c r="S4" s="55"/>
-      <c r="T4" s="56"/>
-      <c r="U4" s="54" t="s">
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="54"/>
+      <c r="T4" s="55"/>
+      <c r="U4" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="V4" s="55"/>
-      <c r="W4" s="55"/>
-      <c r="X4" s="55"/>
-      <c r="Y4" s="55"/>
-      <c r="Z4" s="55"/>
-      <c r="AA4" s="55"/>
-      <c r="AB4" s="55"/>
-      <c r="AC4" s="55"/>
-      <c r="AD4" s="55"/>
-      <c r="AE4" s="55"/>
-      <c r="AF4" s="55"/>
-      <c r="AG4" s="55"/>
-      <c r="AH4" s="56"/>
-      <c r="AI4" s="57" t="s">
+      <c r="V4" s="54"/>
+      <c r="W4" s="54"/>
+      <c r="X4" s="54"/>
+      <c r="Y4" s="54"/>
+      <c r="Z4" s="54"/>
+      <c r="AA4" s="54"/>
+      <c r="AB4" s="54"/>
+      <c r="AC4" s="54"/>
+      <c r="AD4" s="54"/>
+      <c r="AE4" s="54"/>
+      <c r="AF4" s="54"/>
+      <c r="AG4" s="54"/>
+      <c r="AH4" s="55"/>
+      <c r="AI4" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="AJ4" s="58"/>
-      <c r="AK4" s="58"/>
-      <c r="AL4" s="58"/>
-      <c r="AM4" s="58"/>
-      <c r="AN4" s="58"/>
-      <c r="AO4" s="58"/>
-      <c r="AP4" s="58"/>
-      <c r="AQ4" s="58"/>
-      <c r="AR4" s="59"/>
-      <c r="AY4" s="44"/>
-      <c r="AZ4" s="44"/>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44"/>
-      <c r="BC4" s="44"/>
-      <c r="BD4" s="44"/>
-      <c r="BE4" s="44"/>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="44"/>
-      <c r="BH4" s="44"/>
-      <c r="BI4" s="44"/>
+      <c r="AJ4" s="57"/>
+      <c r="AK4" s="57"/>
+      <c r="AL4" s="57"/>
+      <c r="AM4" s="57"/>
+      <c r="AN4" s="57"/>
+      <c r="AO4" s="57"/>
+      <c r="AP4" s="57"/>
+      <c r="AQ4" s="57"/>
+      <c r="AR4" s="58"/>
+      <c r="AY4" s="31"/>
+      <c r="AZ4" s="31"/>
+      <c r="BA4" s="31"/>
+      <c r="BB4" s="31"/>
+      <c r="BC4" s="31"/>
+      <c r="BD4" s="31"/>
+      <c r="BE4" s="31"/>
+      <c r="BF4" s="31"/>
+      <c r="BG4" s="31"/>
+      <c r="BH4" s="31"/>
+      <c r="BI4" s="31"/>
     </row>
     <row r="5" spans="1:62" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
@@ -1447,53 +1429,53 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="23" t="s">
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
-      <c r="N5" s="24"/>
-      <c r="O5" s="25"/>
-      <c r="P5" s="23" t="s">
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="24"/>
-      <c r="T5" s="25"/>
-      <c r="U5" s="29" t="s">
+      <c r="Q5" s="48"/>
+      <c r="R5" s="48"/>
+      <c r="S5" s="48"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30"/>
-      <c r="X5" s="30"/>
-      <c r="Y5" s="30"/>
-      <c r="Z5" s="30"/>
-      <c r="AA5" s="30"/>
-      <c r="AB5" s="30"/>
-      <c r="AC5" s="30"/>
-      <c r="AD5" s="30"/>
-      <c r="AE5" s="30"/>
-      <c r="AF5" s="30"/>
-      <c r="AG5" s="30"/>
-      <c r="AH5" s="31"/>
-      <c r="AI5" s="60"/>
-      <c r="AJ5" s="61"/>
-      <c r="AK5" s="61"/>
-      <c r="AL5" s="61"/>
-      <c r="AM5" s="61"/>
-      <c r="AN5" s="61"/>
-      <c r="AO5" s="61"/>
-      <c r="AP5" s="61"/>
-      <c r="AQ5" s="61"/>
-      <c r="AR5" s="62"/>
+      <c r="V5" s="68"/>
+      <c r="W5" s="68"/>
+      <c r="X5" s="68"/>
+      <c r="Y5" s="68"/>
+      <c r="Z5" s="68"/>
+      <c r="AA5" s="68"/>
+      <c r="AB5" s="68"/>
+      <c r="AC5" s="68"/>
+      <c r="AD5" s="68"/>
+      <c r="AE5" s="68"/>
+      <c r="AF5" s="68"/>
+      <c r="AG5" s="68"/>
+      <c r="AH5" s="69"/>
+      <c r="AI5" s="59"/>
+      <c r="AJ5" s="60"/>
+      <c r="AK5" s="60"/>
+      <c r="AL5" s="60"/>
+      <c r="AM5" s="60"/>
+      <c r="AN5" s="60"/>
+      <c r="AO5" s="60"/>
+      <c r="AP5" s="60"/>
+      <c r="AQ5" s="60"/>
+      <c r="AR5" s="61"/>
     </row>
     <row r="6" spans="1:62" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
@@ -1501,45 +1483,45 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="26"/>
-      <c r="Q6" s="27"/>
-      <c r="R6" s="27"/>
-      <c r="S6" s="27"/>
-      <c r="T6" s="28"/>
-      <c r="U6" s="32"/>
-      <c r="V6" s="33"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="33"/>
-      <c r="Y6" s="33"/>
-      <c r="Z6" s="33"/>
-      <c r="AA6" s="33"/>
-      <c r="AB6" s="33"/>
-      <c r="AC6" s="33"/>
-      <c r="AD6" s="33"/>
-      <c r="AE6" s="33"/>
-      <c r="AF6" s="33"/>
-      <c r="AG6" s="33"/>
-      <c r="AH6" s="34"/>
-      <c r="AI6" s="63"/>
-      <c r="AJ6" s="64"/>
-      <c r="AK6" s="64"/>
-      <c r="AL6" s="64"/>
-      <c r="AM6" s="64"/>
-      <c r="AN6" s="64"/>
-      <c r="AO6" s="64"/>
-      <c r="AP6" s="64"/>
-      <c r="AQ6" s="64"/>
-      <c r="AR6" s="65"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="50"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="51"/>
+      <c r="O6" s="52"/>
+      <c r="P6" s="50"/>
+      <c r="Q6" s="51"/>
+      <c r="R6" s="51"/>
+      <c r="S6" s="51"/>
+      <c r="T6" s="52"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
+      <c r="W6" s="71"/>
+      <c r="X6" s="71"/>
+      <c r="Y6" s="71"/>
+      <c r="Z6" s="71"/>
+      <c r="AA6" s="71"/>
+      <c r="AB6" s="71"/>
+      <c r="AC6" s="71"/>
+      <c r="AD6" s="71"/>
+      <c r="AE6" s="71"/>
+      <c r="AF6" s="71"/>
+      <c r="AG6" s="71"/>
+      <c r="AH6" s="72"/>
+      <c r="AI6" s="62"/>
+      <c r="AJ6" s="63"/>
+      <c r="AK6" s="63"/>
+      <c r="AL6" s="63"/>
+      <c r="AM6" s="63"/>
+      <c r="AN6" s="63"/>
+      <c r="AO6" s="63"/>
+      <c r="AP6" s="63"/>
+      <c r="AQ6" s="63"/>
+      <c r="AR6" s="64"/>
     </row>
     <row r="7" spans="1:62" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
@@ -1585,263 +1567,263 @@
       <c r="AO7" s="4"/>
     </row>
     <row r="8" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="20"/>
+      <c r="C8" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="35" t="s">
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="L8" s="37"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="36"/>
-      <c r="S8" s="38" t="s">
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="T8" s="39"/>
-      <c r="U8" s="38" t="s">
+      <c r="T8" s="28"/>
+      <c r="U8" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="V8" s="39"/>
-      <c r="W8" s="38" t="s">
+      <c r="V8" s="28"/>
+      <c r="W8" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="X8" s="39"/>
-      <c r="Y8" s="35" t="s">
+      <c r="X8" s="28"/>
+      <c r="Y8" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="Z8" s="36"/>
-      <c r="AA8" s="35" t="s">
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="AB8" s="36"/>
-      <c r="AC8" s="35" t="s">
+      <c r="AB8" s="20"/>
+      <c r="AC8" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="AD8" s="37"/>
-      <c r="AE8" s="37"/>
-      <c r="AF8" s="36"/>
-      <c r="AG8" s="35" t="s">
+      <c r="AD8" s="19"/>
+      <c r="AE8" s="19"/>
+      <c r="AF8" s="20"/>
+      <c r="AG8" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="AH8" s="37"/>
-      <c r="AI8" s="36"/>
-      <c r="AJ8" s="35" t="s">
+      <c r="AH8" s="19"/>
+      <c r="AI8" s="20"/>
+      <c r="AJ8" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="AK8" s="37"/>
-      <c r="AL8" s="36"/>
-      <c r="AM8" s="79" t="s">
+      <c r="AK8" s="19"/>
+      <c r="AL8" s="20"/>
+      <c r="AM8" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="AN8" s="80"/>
-      <c r="AO8" s="81"/>
-      <c r="AP8" s="35" t="s">
+      <c r="AN8" s="22"/>
+      <c r="AO8" s="23"/>
+      <c r="AP8" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="AQ8" s="37"/>
-      <c r="AR8" s="36"/>
-      <c r="AS8" s="35" t="s">
+      <c r="AQ8" s="19"/>
+      <c r="AR8" s="20"/>
+      <c r="AS8" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="AT8" s="37"/>
-      <c r="AU8" s="37"/>
-      <c r="AV8" s="37"/>
-      <c r="AW8" s="37"/>
-      <c r="AX8" s="37"/>
-      <c r="AY8" s="37"/>
-      <c r="AZ8" s="36"/>
-      <c r="BA8" s="35" t="s">
+      <c r="AT8" s="19"/>
+      <c r="AU8" s="19"/>
+      <c r="AV8" s="19"/>
+      <c r="AW8" s="19"/>
+      <c r="AX8" s="19"/>
+      <c r="AY8" s="19"/>
+      <c r="AZ8" s="20"/>
+      <c r="BA8" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="BB8" s="37"/>
-      <c r="BC8" s="36"/>
-      <c r="BD8" s="66" t="s">
+      <c r="BB8" s="19"/>
+      <c r="BC8" s="20"/>
+      <c r="BD8" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="BE8" s="66"/>
-      <c r="BF8" s="66"/>
-      <c r="BG8" s="66"/>
-      <c r="BH8" s="66"/>
-      <c r="BI8" s="66"/>
+      <c r="BE8" s="65"/>
+      <c r="BF8" s="65"/>
+      <c r="BG8" s="65"/>
+      <c r="BH8" s="65"/>
+      <c r="BI8" s="65"/>
       <c r="BJ8" s="8"/>
     </row>
     <row r="9" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="78"/>
-      <c r="C9" s="94" t="s">
+      <c r="B9" s="80"/>
+      <c r="C9" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="94"/>
-      <c r="E9" s="94"/>
-      <c r="F9" s="94"/>
-      <c r="G9" s="94"/>
-      <c r="H9" s="94"/>
-      <c r="I9" s="94"/>
-      <c r="J9" s="94"/>
-      <c r="K9" s="94" t="s">
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81"/>
+      <c r="J9" s="81"/>
+      <c r="K9" s="81" t="s">
         <v>31</v>
       </c>
-      <c r="L9" s="94"/>
-      <c r="M9" s="94"/>
-      <c r="N9" s="94"/>
-      <c r="O9" s="94"/>
-      <c r="P9" s="94"/>
-      <c r="Q9" s="94"/>
-      <c r="R9" s="94"/>
-      <c r="S9" s="83" t="s">
+      <c r="L9" s="81"/>
+      <c r="M9" s="81"/>
+      <c r="N9" s="81"/>
+      <c r="O9" s="81"/>
+      <c r="P9" s="81"/>
+      <c r="Q9" s="81"/>
+      <c r="R9" s="81"/>
+      <c r="S9" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="T9" s="83"/>
-      <c r="U9" s="83" t="s">
+      <c r="T9" s="82"/>
+      <c r="U9" s="82" t="s">
         <v>26</v>
       </c>
-      <c r="V9" s="83"/>
-      <c r="W9" s="83" t="s">
+      <c r="V9" s="82"/>
+      <c r="W9" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="X9" s="83"/>
-      <c r="Y9" s="83" t="s">
+      <c r="X9" s="82"/>
+      <c r="Y9" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="Z9" s="83"/>
-      <c r="AA9" s="84" t="s">
+      <c r="Z9" s="82"/>
+      <c r="AA9" s="83" t="s">
         <v>32</v>
       </c>
-      <c r="AB9" s="84"/>
-      <c r="AC9" s="85" t="s">
+      <c r="AB9" s="83"/>
+      <c r="AC9" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="AD9" s="86"/>
-      <c r="AE9" s="86"/>
-      <c r="AF9" s="87"/>
-      <c r="AG9" s="85" t="s">
+      <c r="AD9" s="85"/>
+      <c r="AE9" s="85"/>
+      <c r="AF9" s="86"/>
+      <c r="AG9" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="AH9" s="86"/>
-      <c r="AI9" s="87"/>
-      <c r="AJ9" s="82" t="s">
+      <c r="AH9" s="85"/>
+      <c r="AI9" s="86"/>
+      <c r="AJ9" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="AK9" s="82"/>
-      <c r="AL9" s="82"/>
-      <c r="AM9" s="82" t="s">
+      <c r="AK9" s="87"/>
+      <c r="AL9" s="87"/>
+      <c r="AM9" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="AN9" s="82"/>
-      <c r="AO9" s="82"/>
-      <c r="AP9" s="83" t="s">
+      <c r="AN9" s="87"/>
+      <c r="AO9" s="87"/>
+      <c r="AP9" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="AQ9" s="83"/>
-      <c r="AR9" s="83"/>
-      <c r="AS9" s="94" t="s">
+      <c r="AQ9" s="82"/>
+      <c r="AR9" s="82"/>
+      <c r="AS9" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="AT9" s="94"/>
-      <c r="AU9" s="94"/>
-      <c r="AV9" s="94"/>
-      <c r="AW9" s="94"/>
-      <c r="AX9" s="94"/>
-      <c r="AY9" s="94"/>
-      <c r="AZ9" s="94"/>
-      <c r="BA9" s="83" t="s">
+      <c r="AT9" s="81"/>
+      <c r="AU9" s="81"/>
+      <c r="AV9" s="81"/>
+      <c r="AW9" s="81"/>
+      <c r="AX9" s="81"/>
+      <c r="AY9" s="81"/>
+      <c r="AZ9" s="81"/>
+      <c r="BA9" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="BB9" s="83"/>
-      <c r="BC9" s="83"/>
-      <c r="BD9" s="67" t="s">
+      <c r="BB9" s="82"/>
+      <c r="BC9" s="82"/>
+      <c r="BD9" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="BE9" s="67"/>
-      <c r="BF9" s="67"/>
-      <c r="BG9" s="67"/>
-      <c r="BH9" s="67"/>
-      <c r="BI9" s="67"/>
+      <c r="BE9" s="88"/>
+      <c r="BF9" s="88"/>
+      <c r="BG9" s="88"/>
+      <c r="BH9" s="88"/>
+      <c r="BI9" s="88"/>
       <c r="BJ9" s="10"/>
     </row>
     <row r="10" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="69"/>
-      <c r="B10" s="69"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="68"/>
-      <c r="H10" s="68"/>
-      <c r="I10" s="68"/>
-      <c r="J10" s="68"/>
-      <c r="K10" s="68"/>
-      <c r="L10" s="68"/>
-      <c r="M10" s="68"/>
-      <c r="N10" s="68"/>
-      <c r="O10" s="68"/>
-      <c r="P10" s="68"/>
-      <c r="Q10" s="68"/>
-      <c r="R10" s="68"/>
-      <c r="S10" s="68"/>
-      <c r="T10" s="68"/>
-      <c r="U10" s="68"/>
-      <c r="V10" s="68"/>
-      <c r="W10" s="68"/>
-      <c r="X10" s="68"/>
-      <c r="Y10" s="68"/>
-      <c r="Z10" s="68"/>
-      <c r="AA10" s="70"/>
-      <c r="AB10" s="70"/>
-      <c r="AC10" s="68"/>
-      <c r="AD10" s="68"/>
-      <c r="AE10" s="68"/>
-      <c r="AF10" s="68"/>
-      <c r="AG10" s="68"/>
-      <c r="AH10" s="68"/>
-      <c r="AI10" s="68"/>
-      <c r="AJ10" s="68"/>
-      <c r="AK10" s="68"/>
-      <c r="AL10" s="68"/>
-      <c r="AM10" s="68"/>
-      <c r="AN10" s="68"/>
-      <c r="AO10" s="68"/>
-      <c r="AP10" s="68"/>
-      <c r="AQ10" s="68"/>
-      <c r="AR10" s="68"/>
-      <c r="AS10" s="68"/>
-      <c r="AT10" s="68"/>
-      <c r="AU10" s="68"/>
-      <c r="AV10" s="68"/>
-      <c r="AW10" s="68"/>
-      <c r="AX10" s="68"/>
-      <c r="AY10" s="68"/>
-      <c r="AZ10" s="68"/>
-      <c r="BA10" s="68"/>
-      <c r="BB10" s="68"/>
-      <c r="BC10" s="68"/>
-      <c r="BD10" s="68"/>
-      <c r="BE10" s="68"/>
-      <c r="BF10" s="68"/>
-      <c r="BG10" s="68"/>
-      <c r="BH10" s="68"/>
-      <c r="BI10" s="68"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="24"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="24"/>
+      <c r="V10" s="24"/>
+      <c r="W10" s="24"/>
+      <c r="X10" s="24"/>
+      <c r="Y10" s="24"/>
+      <c r="Z10" s="24"/>
+      <c r="AA10" s="26"/>
+      <c r="AB10" s="26"/>
+      <c r="AC10" s="24"/>
+      <c r="AD10" s="24"/>
+      <c r="AE10" s="24"/>
+      <c r="AF10" s="24"/>
+      <c r="AG10" s="24"/>
+      <c r="AH10" s="24"/>
+      <c r="AI10" s="24"/>
+      <c r="AJ10" s="24"/>
+      <c r="AK10" s="24"/>
+      <c r="AL10" s="24"/>
+      <c r="AM10" s="24"/>
+      <c r="AN10" s="24"/>
+      <c r="AO10" s="24"/>
+      <c r="AP10" s="24"/>
+      <c r="AQ10" s="24"/>
+      <c r="AR10" s="24"/>
+      <c r="AS10" s="24"/>
+      <c r="AT10" s="24"/>
+      <c r="AU10" s="24"/>
+      <c r="AV10" s="24"/>
+      <c r="AW10" s="24"/>
+      <c r="AX10" s="24"/>
+      <c r="AY10" s="24"/>
+      <c r="AZ10" s="24"/>
+      <c r="BA10" s="24"/>
+      <c r="BB10" s="24"/>
+      <c r="BC10" s="24"/>
+      <c r="BD10" s="24"/>
+      <c r="BE10" s="24"/>
+      <c r="BF10" s="24"/>
+      <c r="BG10" s="24"/>
+      <c r="BH10" s="24"/>
+      <c r="BI10" s="24"/>
     </row>
     <row r="11" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="40"/>
-      <c r="B11" s="40"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
@@ -1866,8 +1848,8 @@
       <c r="X11" s="15"/>
       <c r="Y11" s="15"/>
       <c r="Z11" s="15"/>
-      <c r="AA11" s="41"/>
-      <c r="AB11" s="41"/>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="17"/>
       <c r="AC11" s="15"/>
       <c r="AD11" s="15"/>
       <c r="AE11" s="15"/>
@@ -1903,8 +1885,8 @@
       <c r="BI11" s="15"/>
     </row>
     <row r="12" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="40"/>
-      <c r="B12" s="40"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
@@ -1929,8 +1911,8 @@
       <c r="X12" s="15"/>
       <c r="Y12" s="15"/>
       <c r="Z12" s="15"/>
-      <c r="AA12" s="41"/>
-      <c r="AB12" s="41"/>
+      <c r="AA12" s="17"/>
+      <c r="AB12" s="17"/>
       <c r="AC12" s="15"/>
       <c r="AD12" s="15"/>
       <c r="AE12" s="15"/>
@@ -1966,8 +1948,8 @@
       <c r="BI12" s="15"/>
     </row>
     <row r="13" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="40"/>
-      <c r="B13" s="40"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
@@ -1992,8 +1974,8 @@
       <c r="X13" s="15"/>
       <c r="Y13" s="15"/>
       <c r="Z13" s="15"/>
-      <c r="AA13" s="41"/>
-      <c r="AB13" s="41"/>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="17"/>
       <c r="AC13" s="15"/>
       <c r="AD13" s="15"/>
       <c r="AE13" s="15"/>
@@ -2029,8 +2011,8 @@
       <c r="BI13" s="15"/>
     </row>
     <row r="14" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="40"/>
-      <c r="B14" s="40"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
@@ -2055,8 +2037,8 @@
       <c r="X14" s="15"/>
       <c r="Y14" s="15"/>
       <c r="Z14" s="15"/>
-      <c r="AA14" s="41"/>
-      <c r="AB14" s="41"/>
+      <c r="AA14" s="17"/>
+      <c r="AB14" s="17"/>
       <c r="AC14" s="15"/>
       <c r="AD14" s="15"/>
       <c r="AE14" s="15"/>
@@ -2092,8 +2074,8 @@
       <c r="BI14" s="15"/>
     </row>
     <row r="15" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="40"/>
-      <c r="B15" s="40"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
@@ -2118,8 +2100,8 @@
       <c r="X15" s="15"/>
       <c r="Y15" s="15"/>
       <c r="Z15" s="15"/>
-      <c r="AA15" s="41"/>
-      <c r="AB15" s="41"/>
+      <c r="AA15" s="17"/>
+      <c r="AB15" s="17"/>
       <c r="AC15" s="15"/>
       <c r="AD15" s="15"/>
       <c r="AE15" s="15"/>
@@ -2155,8 +2137,8 @@
       <c r="BI15" s="15"/>
     </row>
     <row r="16" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="40"/>
-      <c r="B16" s="40"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
@@ -2181,8 +2163,8 @@
       <c r="X16" s="15"/>
       <c r="Y16" s="15"/>
       <c r="Z16" s="15"/>
-      <c r="AA16" s="41"/>
-      <c r="AB16" s="41"/>
+      <c r="AA16" s="17"/>
+      <c r="AB16" s="17"/>
       <c r="AC16" s="15"/>
       <c r="AD16" s="15"/>
       <c r="AE16" s="15"/>
@@ -2218,8 +2200,8 @@
       <c r="BI16" s="15"/>
     </row>
     <row r="17" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="40"/>
-      <c r="B17" s="40"/>
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
@@ -2244,8 +2226,8 @@
       <c r="X17" s="15"/>
       <c r="Y17" s="15"/>
       <c r="Z17" s="15"/>
-      <c r="AA17" s="41"/>
-      <c r="AB17" s="41"/>
+      <c r="AA17" s="17"/>
+      <c r="AB17" s="17"/>
       <c r="AC17" s="15"/>
       <c r="AD17" s="15"/>
       <c r="AE17" s="15"/>
@@ -2281,8 +2263,8 @@
       <c r="BI17" s="15"/>
     </row>
     <row r="18" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="40"/>
-      <c r="B18" s="40"/>
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
@@ -2307,8 +2289,8 @@
       <c r="X18" s="15"/>
       <c r="Y18" s="15"/>
       <c r="Z18" s="15"/>
-      <c r="AA18" s="41"/>
-      <c r="AB18" s="41"/>
+      <c r="AA18" s="17"/>
+      <c r="AB18" s="17"/>
       <c r="AC18" s="15"/>
       <c r="AD18" s="15"/>
       <c r="AE18" s="15"/>
@@ -2344,8 +2326,8 @@
       <c r="BI18" s="15"/>
     </row>
     <row r="19" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="40"/>
-      <c r="B19" s="40"/>
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
@@ -2370,8 +2352,8 @@
       <c r="X19" s="15"/>
       <c r="Y19" s="15"/>
       <c r="Z19" s="15"/>
-      <c r="AA19" s="41"/>
-      <c r="AB19" s="41"/>
+      <c r="AA19" s="17"/>
+      <c r="AB19" s="17"/>
       <c r="AC19" s="15"/>
       <c r="AD19" s="15"/>
       <c r="AE19" s="15"/>
@@ -2407,8 +2389,8 @@
       <c r="BI19" s="15"/>
     </row>
     <row r="20" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="40"/>
-      <c r="B20" s="40"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
@@ -2433,8 +2415,8 @@
       <c r="X20" s="15"/>
       <c r="Y20" s="15"/>
       <c r="Z20" s="15"/>
-      <c r="AA20" s="41"/>
-      <c r="AB20" s="41"/>
+      <c r="AA20" s="17"/>
+      <c r="AB20" s="17"/>
       <c r="AC20" s="15"/>
       <c r="AD20" s="15"/>
       <c r="AE20" s="15"/>
@@ -2470,8 +2452,8 @@
       <c r="BI20" s="15"/>
     </row>
     <row r="21" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="40"/>
-      <c r="B21" s="40"/>
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
@@ -2496,8 +2478,8 @@
       <c r="X21" s="15"/>
       <c r="Y21" s="15"/>
       <c r="Z21" s="15"/>
-      <c r="AA21" s="41"/>
-      <c r="AB21" s="41"/>
+      <c r="AA21" s="17"/>
+      <c r="AB21" s="17"/>
       <c r="AC21" s="15"/>
       <c r="AD21" s="15"/>
       <c r="AE21" s="15"/>
@@ -2533,8 +2515,8 @@
       <c r="BI21" s="15"/>
     </row>
     <row r="22" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="40"/>
-      <c r="B22" s="40"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
@@ -2559,8 +2541,8 @@
       <c r="X22" s="15"/>
       <c r="Y22" s="15"/>
       <c r="Z22" s="15"/>
-      <c r="AA22" s="41"/>
-      <c r="AB22" s="41"/>
+      <c r="AA22" s="17"/>
+      <c r="AB22" s="17"/>
       <c r="AC22" s="15"/>
       <c r="AD22" s="15"/>
       <c r="AE22" s="15"/>
@@ -2596,8 +2578,8 @@
       <c r="BI22" s="15"/>
     </row>
     <row r="23" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="40"/>
-      <c r="B23" s="40"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
@@ -2622,8 +2604,8 @@
       <c r="X23" s="15"/>
       <c r="Y23" s="15"/>
       <c r="Z23" s="15"/>
-      <c r="AA23" s="41"/>
-      <c r="AB23" s="41"/>
+      <c r="AA23" s="17"/>
+      <c r="AB23" s="17"/>
       <c r="AC23" s="15"/>
       <c r="AD23" s="15"/>
       <c r="AE23" s="15"/>
@@ -2659,8 +2641,8 @@
       <c r="BI23" s="15"/>
     </row>
     <row r="24" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="40"/>
-      <c r="B24" s="40"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
@@ -2685,8 +2667,8 @@
       <c r="X24" s="15"/>
       <c r="Y24" s="15"/>
       <c r="Z24" s="15"/>
-      <c r="AA24" s="41"/>
-      <c r="AB24" s="41"/>
+      <c r="AA24" s="17"/>
+      <c r="AB24" s="17"/>
       <c r="AC24" s="15"/>
       <c r="AD24" s="15"/>
       <c r="AE24" s="15"/>
@@ -2722,8 +2704,8 @@
       <c r="BI24" s="15"/>
     </row>
     <row r="25" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="40"/>
-      <c r="B25" s="40"/>
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
       <c r="C25" s="15"/>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
@@ -2748,8 +2730,8 @@
       <c r="X25" s="15"/>
       <c r="Y25" s="15"/>
       <c r="Z25" s="15"/>
-      <c r="AA25" s="41"/>
-      <c r="AB25" s="41"/>
+      <c r="AA25" s="17"/>
+      <c r="AB25" s="17"/>
       <c r="AC25" s="15"/>
       <c r="AD25" s="15"/>
       <c r="AE25" s="15"/>
@@ -2785,8 +2767,8 @@
       <c r="BI25" s="15"/>
     </row>
     <row r="26" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="40"/>
-      <c r="B26" s="40"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
       <c r="C26" s="15"/>
       <c r="D26" s="15"/>
       <c r="E26" s="15"/>
@@ -2811,8 +2793,8 @@
       <c r="X26" s="15"/>
       <c r="Y26" s="15"/>
       <c r="Z26" s="15"/>
-      <c r="AA26" s="41"/>
-      <c r="AB26" s="41"/>
+      <c r="AA26" s="17"/>
+      <c r="AB26" s="17"/>
       <c r="AC26" s="15"/>
       <c r="AD26" s="15"/>
       <c r="AE26" s="15"/>
@@ -2848,8 +2830,8 @@
       <c r="BI26" s="15"/>
     </row>
     <row r="27" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="40"/>
-      <c r="B27" s="40"/>
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
       <c r="C27" s="15"/>
       <c r="D27" s="15"/>
       <c r="E27" s="15"/>
@@ -2874,8 +2856,8 @@
       <c r="X27" s="15"/>
       <c r="Y27" s="15"/>
       <c r="Z27" s="15"/>
-      <c r="AA27" s="41"/>
-      <c r="AB27" s="41"/>
+      <c r="AA27" s="17"/>
+      <c r="AB27" s="17"/>
       <c r="AC27" s="15"/>
       <c r="AD27" s="15"/>
       <c r="AE27" s="15"/>
@@ -2911,8 +2893,8 @@
       <c r="BI27" s="15"/>
     </row>
     <row r="28" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="40"/>
-      <c r="B28" s="40"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
       <c r="C28" s="15"/>
       <c r="D28" s="15"/>
       <c r="E28" s="15"/>
@@ -2937,8 +2919,8 @@
       <c r="X28" s="15"/>
       <c r="Y28" s="15"/>
       <c r="Z28" s="15"/>
-      <c r="AA28" s="41"/>
-      <c r="AB28" s="41"/>
+      <c r="AA28" s="17"/>
+      <c r="AB28" s="17"/>
       <c r="AC28" s="15"/>
       <c r="AD28" s="15"/>
       <c r="AE28" s="15"/>
@@ -2974,8 +2956,8 @@
       <c r="BI28" s="15"/>
     </row>
     <row r="29" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="40"/>
-      <c r="B29" s="40"/>
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
       <c r="C29" s="15"/>
       <c r="D29" s="15"/>
       <c r="E29" s="15"/>
@@ -3000,8 +2982,8 @@
       <c r="X29" s="15"/>
       <c r="Y29" s="15"/>
       <c r="Z29" s="15"/>
-      <c r="AA29" s="41"/>
-      <c r="AB29" s="41"/>
+      <c r="AA29" s="17"/>
+      <c r="AB29" s="17"/>
       <c r="AC29" s="15"/>
       <c r="AD29" s="15"/>
       <c r="AE29" s="15"/>
@@ -3037,8 +3019,8 @@
       <c r="BI29" s="15"/>
     </row>
     <row r="30" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="40"/>
-      <c r="B30" s="40"/>
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
       <c r="C30" s="15"/>
       <c r="D30" s="15"/>
       <c r="E30" s="15"/>
@@ -3063,8 +3045,8 @@
       <c r="X30" s="15"/>
       <c r="Y30" s="15"/>
       <c r="Z30" s="15"/>
-      <c r="AA30" s="41"/>
-      <c r="AB30" s="41"/>
+      <c r="AA30" s="17"/>
+      <c r="AB30" s="17"/>
       <c r="AC30" s="15"/>
       <c r="AD30" s="15"/>
       <c r="AE30" s="15"/>
@@ -4775,9 +4757,9 @@
       <c r="AI65" s="6"/>
       <c r="AJ65" s="6"/>
       <c r="AK65" s="6"/>
-      <c r="AL65" s="16"/>
-      <c r="AM65" s="16"/>
-      <c r="AN65" s="16"/>
+      <c r="AL65" s="66"/>
+      <c r="AM65" s="66"/>
+      <c r="AN65" s="66"/>
     </row>
     <row r="66" spans="1:41" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4"/>
@@ -4953,6 +4935,372 @@
     </row>
   </sheetData>
   <mergeCells count="390">
+    <mergeCell ref="W30:X30"/>
+    <mergeCell ref="Y30:Z30"/>
+    <mergeCell ref="AL65:AN65"/>
+    <mergeCell ref="AG30:AI30"/>
+    <mergeCell ref="F5:J6"/>
+    <mergeCell ref="K5:O6"/>
+    <mergeCell ref="P5:T6"/>
+    <mergeCell ref="U5:AH6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="K8:R8"/>
+    <mergeCell ref="S8:T8"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:J21"/>
+    <mergeCell ref="K21:R21"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="U21:V21"/>
+    <mergeCell ref="W21:X21"/>
+    <mergeCell ref="Y21:Z21"/>
+    <mergeCell ref="AA21:AB21"/>
+    <mergeCell ref="AC21:AF21"/>
+    <mergeCell ref="AG21:AI21"/>
+    <mergeCell ref="AJ21:AL21"/>
+    <mergeCell ref="AS8:AZ8"/>
+    <mergeCell ref="W8:X8"/>
+    <mergeCell ref="Y8:Z8"/>
+    <mergeCell ref="AY1:BI1"/>
+    <mergeCell ref="AY2:BI4"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="F2:J3"/>
+    <mergeCell ref="K1:V1"/>
+    <mergeCell ref="K2:V3"/>
+    <mergeCell ref="W1:AH1"/>
+    <mergeCell ref="W2:AH3"/>
+    <mergeCell ref="AI1:AM1"/>
+    <mergeCell ref="AN1:AR1"/>
+    <mergeCell ref="AI2:AM3"/>
+    <mergeCell ref="AN2:AR3"/>
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="K4:O4"/>
+    <mergeCell ref="P4:T4"/>
+    <mergeCell ref="AI4:AR6"/>
+    <mergeCell ref="U4:AH4"/>
+    <mergeCell ref="BD8:BI8"/>
+    <mergeCell ref="AJ10:AL10"/>
+    <mergeCell ref="AM10:AO10"/>
+    <mergeCell ref="AP10:AR10"/>
+    <mergeCell ref="AS10:AZ10"/>
+    <mergeCell ref="BA10:BC10"/>
+    <mergeCell ref="BD10:BI10"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:J9"/>
+    <mergeCell ref="K9:R9"/>
+    <mergeCell ref="S9:T9"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="W9:X9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="K10:R10"/>
+    <mergeCell ref="S10:T10"/>
+    <mergeCell ref="U10:V10"/>
+    <mergeCell ref="W10:X10"/>
+    <mergeCell ref="Y10:Z10"/>
+    <mergeCell ref="AA10:AB10"/>
+    <mergeCell ref="AC10:AF10"/>
+    <mergeCell ref="BD9:BI9"/>
+    <mergeCell ref="AG10:AI10"/>
+    <mergeCell ref="C11:J11"/>
+    <mergeCell ref="K11:R11"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="W11:X11"/>
+    <mergeCell ref="Y11:Z11"/>
+    <mergeCell ref="AA11:AB11"/>
+    <mergeCell ref="AC11:AF11"/>
+    <mergeCell ref="BA8:BC8"/>
+    <mergeCell ref="Y9:Z9"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AJ9:AL9"/>
+    <mergeCell ref="AM9:AO9"/>
+    <mergeCell ref="AP9:AR9"/>
+    <mergeCell ref="AS9:AZ9"/>
+    <mergeCell ref="BA9:BC9"/>
+    <mergeCell ref="AG9:AI9"/>
+    <mergeCell ref="AC9:AF9"/>
+    <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="AC8:AF8"/>
+    <mergeCell ref="AG8:AI8"/>
+    <mergeCell ref="AJ8:AL8"/>
+    <mergeCell ref="AM8:AO8"/>
+    <mergeCell ref="AP8:AR8"/>
+    <mergeCell ref="AG11:AI11"/>
+    <mergeCell ref="AJ11:AL11"/>
+    <mergeCell ref="AM11:AO11"/>
+    <mergeCell ref="AP11:AR11"/>
+    <mergeCell ref="AS11:AZ11"/>
+    <mergeCell ref="BA11:BC11"/>
+    <mergeCell ref="BD11:BI11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="K12:R12"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="U12:V12"/>
+    <mergeCell ref="W12:X12"/>
+    <mergeCell ref="Y12:Z12"/>
+    <mergeCell ref="AA12:AB12"/>
+    <mergeCell ref="AC12:AF12"/>
+    <mergeCell ref="AG12:AI12"/>
+    <mergeCell ref="AJ12:AL12"/>
+    <mergeCell ref="AM12:AO12"/>
+    <mergeCell ref="AP12:AR12"/>
+    <mergeCell ref="AS12:AZ12"/>
+    <mergeCell ref="BA12:BC12"/>
+    <mergeCell ref="BD12:BI12"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="AJ13:AL13"/>
+    <mergeCell ref="AM13:AO13"/>
+    <mergeCell ref="AP13:AR13"/>
+    <mergeCell ref="AS13:AZ13"/>
+    <mergeCell ref="BA13:BC13"/>
+    <mergeCell ref="BD13:BI13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="K14:R14"/>
+    <mergeCell ref="S14:T14"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="W14:X14"/>
+    <mergeCell ref="Y14:Z14"/>
+    <mergeCell ref="AA14:AB14"/>
+    <mergeCell ref="AC14:AF14"/>
+    <mergeCell ref="AG14:AI14"/>
+    <mergeCell ref="AJ14:AL14"/>
+    <mergeCell ref="AM14:AO14"/>
+    <mergeCell ref="AP14:AR14"/>
+    <mergeCell ref="AS14:AZ14"/>
+    <mergeCell ref="BA14:BC14"/>
+    <mergeCell ref="BD14:BI14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:J13"/>
+    <mergeCell ref="K15:R15"/>
+    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="U15:V15"/>
+    <mergeCell ref="W15:X15"/>
+    <mergeCell ref="Y15:Z15"/>
+    <mergeCell ref="AA15:AB15"/>
+    <mergeCell ref="AC15:AF15"/>
+    <mergeCell ref="AG13:AI13"/>
+    <mergeCell ref="K13:R13"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="W13:X13"/>
+    <mergeCell ref="Y13:Z13"/>
+    <mergeCell ref="AA13:AB13"/>
+    <mergeCell ref="AC13:AF13"/>
+    <mergeCell ref="AG15:AI15"/>
+    <mergeCell ref="AJ15:AL15"/>
+    <mergeCell ref="AM15:AO15"/>
+    <mergeCell ref="AP15:AR15"/>
+    <mergeCell ref="AS15:AZ15"/>
+    <mergeCell ref="BA15:BC15"/>
+    <mergeCell ref="BD15:BI15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:J16"/>
+    <mergeCell ref="K16:R16"/>
+    <mergeCell ref="S16:T16"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="Y16:Z16"/>
+    <mergeCell ref="AA16:AB16"/>
+    <mergeCell ref="AC16:AF16"/>
+    <mergeCell ref="AG16:AI16"/>
+    <mergeCell ref="AJ16:AL16"/>
+    <mergeCell ref="AM16:AO16"/>
+    <mergeCell ref="AP16:AR16"/>
+    <mergeCell ref="AS16:AZ16"/>
+    <mergeCell ref="BA16:BC16"/>
+    <mergeCell ref="BD16:BI16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:J15"/>
+    <mergeCell ref="AJ17:AL17"/>
+    <mergeCell ref="AM17:AO17"/>
+    <mergeCell ref="AP17:AR17"/>
+    <mergeCell ref="AS17:AZ17"/>
+    <mergeCell ref="BA17:BC17"/>
+    <mergeCell ref="BD17:BI17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:J18"/>
+    <mergeCell ref="K18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="U18:V18"/>
+    <mergeCell ref="W18:X18"/>
+    <mergeCell ref="Y18:Z18"/>
+    <mergeCell ref="AA18:AB18"/>
+    <mergeCell ref="AC18:AF18"/>
+    <mergeCell ref="AG18:AI18"/>
+    <mergeCell ref="AJ18:AL18"/>
+    <mergeCell ref="AM18:AO18"/>
+    <mergeCell ref="AP18:AR18"/>
+    <mergeCell ref="AS18:AZ18"/>
+    <mergeCell ref="BA18:BC18"/>
+    <mergeCell ref="BD18:BI18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:J17"/>
+    <mergeCell ref="K19:R19"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="U19:V19"/>
+    <mergeCell ref="W19:X19"/>
+    <mergeCell ref="Y19:Z19"/>
+    <mergeCell ref="AA19:AB19"/>
+    <mergeCell ref="AC19:AF19"/>
+    <mergeCell ref="AG17:AI17"/>
+    <mergeCell ref="K17:R17"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="U17:V17"/>
+    <mergeCell ref="W17:X17"/>
+    <mergeCell ref="Y17:Z17"/>
+    <mergeCell ref="AA17:AB17"/>
+    <mergeCell ref="AC17:AF17"/>
+    <mergeCell ref="AG19:AI19"/>
+    <mergeCell ref="AJ19:AL19"/>
+    <mergeCell ref="AM19:AO19"/>
+    <mergeCell ref="AP19:AR19"/>
+    <mergeCell ref="AS19:AZ19"/>
+    <mergeCell ref="BA19:BC19"/>
+    <mergeCell ref="BD19:BI19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:J20"/>
+    <mergeCell ref="K20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="U20:V20"/>
+    <mergeCell ref="W20:X20"/>
+    <mergeCell ref="Y20:Z20"/>
+    <mergeCell ref="AA20:AB20"/>
+    <mergeCell ref="AC20:AF20"/>
+    <mergeCell ref="AG20:AI20"/>
+    <mergeCell ref="AJ20:AL20"/>
+    <mergeCell ref="AM20:AO20"/>
+    <mergeCell ref="AP20:AR20"/>
+    <mergeCell ref="AS20:AZ20"/>
+    <mergeCell ref="BA20:BC20"/>
+    <mergeCell ref="BD20:BI20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:J19"/>
+    <mergeCell ref="AC24:AF24"/>
+    <mergeCell ref="AP21:AR21"/>
+    <mergeCell ref="AS21:AZ21"/>
+    <mergeCell ref="BA21:BC21"/>
+    <mergeCell ref="BD21:BI21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:J22"/>
+    <mergeCell ref="K22:R22"/>
+    <mergeCell ref="S22:T22"/>
+    <mergeCell ref="U22:V22"/>
+    <mergeCell ref="W22:X22"/>
+    <mergeCell ref="Y22:Z22"/>
+    <mergeCell ref="AA22:AB22"/>
+    <mergeCell ref="AC22:AF22"/>
+    <mergeCell ref="AG22:AI22"/>
+    <mergeCell ref="AJ22:AL22"/>
+    <mergeCell ref="AM22:AO22"/>
+    <mergeCell ref="AP22:AR22"/>
+    <mergeCell ref="AS22:AZ22"/>
+    <mergeCell ref="BA22:BC22"/>
+    <mergeCell ref="BD22:BI22"/>
+    <mergeCell ref="AM21:AO21"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="W23:X23"/>
+    <mergeCell ref="Y23:Z23"/>
+    <mergeCell ref="AA23:AB23"/>
+    <mergeCell ref="W25:X25"/>
+    <mergeCell ref="Y25:Z25"/>
+    <mergeCell ref="AA25:AB25"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:J24"/>
+    <mergeCell ref="K24:R24"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="W24:X24"/>
+    <mergeCell ref="Y24:Z24"/>
+    <mergeCell ref="AA24:AB24"/>
+    <mergeCell ref="AP23:AR23"/>
+    <mergeCell ref="AC23:AF23"/>
+    <mergeCell ref="AG23:AI23"/>
+    <mergeCell ref="AJ23:AL23"/>
+    <mergeCell ref="AM23:AO23"/>
+    <mergeCell ref="AS25:AZ25"/>
+    <mergeCell ref="BA25:BC25"/>
+    <mergeCell ref="BD25:BI25"/>
+    <mergeCell ref="C23:J23"/>
+    <mergeCell ref="K23:R23"/>
+    <mergeCell ref="AG25:AI25"/>
+    <mergeCell ref="AJ25:AL25"/>
+    <mergeCell ref="AM25:AO25"/>
+    <mergeCell ref="AP25:AR25"/>
+    <mergeCell ref="AS23:AZ23"/>
+    <mergeCell ref="BA23:BC23"/>
+    <mergeCell ref="BD23:BI23"/>
+    <mergeCell ref="AG24:AI24"/>
+    <mergeCell ref="AJ24:AL24"/>
+    <mergeCell ref="AM24:AO24"/>
+    <mergeCell ref="AP24:AR24"/>
+    <mergeCell ref="AS24:AZ24"/>
+    <mergeCell ref="BA24:BC24"/>
+    <mergeCell ref="BD24:BI24"/>
+    <mergeCell ref="AG26:AI26"/>
+    <mergeCell ref="AJ26:AL26"/>
+    <mergeCell ref="AM26:AO26"/>
+    <mergeCell ref="AP26:AR26"/>
+    <mergeCell ref="AS26:AZ26"/>
+    <mergeCell ref="BA26:BC26"/>
+    <mergeCell ref="BD26:BI26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:J25"/>
+    <mergeCell ref="K25:R25"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:J26"/>
+    <mergeCell ref="K26:R26"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="W26:X26"/>
+    <mergeCell ref="Y26:Z26"/>
+    <mergeCell ref="AA26:AB26"/>
+    <mergeCell ref="AC26:AF26"/>
+    <mergeCell ref="AC25:AF25"/>
+    <mergeCell ref="AS27:AZ27"/>
+    <mergeCell ref="BA27:BC27"/>
+    <mergeCell ref="BD27:BI27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:J28"/>
+    <mergeCell ref="K28:R28"/>
+    <mergeCell ref="S28:T28"/>
+    <mergeCell ref="U28:V28"/>
+    <mergeCell ref="W28:X28"/>
+    <mergeCell ref="Y28:Z28"/>
+    <mergeCell ref="AA28:AB28"/>
+    <mergeCell ref="AC28:AF28"/>
+    <mergeCell ref="AG28:AI28"/>
+    <mergeCell ref="AJ28:AL28"/>
+    <mergeCell ref="AM28:AO28"/>
+    <mergeCell ref="AP28:AR28"/>
+    <mergeCell ref="AS28:AZ28"/>
+    <mergeCell ref="BA28:BC28"/>
+    <mergeCell ref="BD28:BI28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:J27"/>
+    <mergeCell ref="K27:R27"/>
+    <mergeCell ref="S27:T27"/>
+    <mergeCell ref="U27:V27"/>
+    <mergeCell ref="AC29:AF29"/>
+    <mergeCell ref="AG27:AI27"/>
+    <mergeCell ref="AJ27:AL27"/>
+    <mergeCell ref="AM27:AO27"/>
+    <mergeCell ref="AP27:AR27"/>
+    <mergeCell ref="W27:X27"/>
+    <mergeCell ref="Y27:Z27"/>
+    <mergeCell ref="AA27:AB27"/>
+    <mergeCell ref="AC27:AF27"/>
+    <mergeCell ref="AG29:AI29"/>
+    <mergeCell ref="AJ29:AL29"/>
+    <mergeCell ref="AM29:AO29"/>
+    <mergeCell ref="AP29:AR29"/>
     <mergeCell ref="AS29:AZ29"/>
     <mergeCell ref="BA29:BC29"/>
     <mergeCell ref="BD29:BI29"/>
@@ -4977,372 +5325,6 @@
     <mergeCell ref="W29:X29"/>
     <mergeCell ref="Y29:Z29"/>
     <mergeCell ref="AA29:AB29"/>
-    <mergeCell ref="AC29:AF29"/>
-    <mergeCell ref="AG27:AI27"/>
-    <mergeCell ref="AJ27:AL27"/>
-    <mergeCell ref="AM27:AO27"/>
-    <mergeCell ref="AP27:AR27"/>
-    <mergeCell ref="W27:X27"/>
-    <mergeCell ref="Y27:Z27"/>
-    <mergeCell ref="AA27:AB27"/>
-    <mergeCell ref="AC27:AF27"/>
-    <mergeCell ref="AG29:AI29"/>
-    <mergeCell ref="AJ29:AL29"/>
-    <mergeCell ref="AM29:AO29"/>
-    <mergeCell ref="AP29:AR29"/>
-    <mergeCell ref="AS27:AZ27"/>
-    <mergeCell ref="BA27:BC27"/>
-    <mergeCell ref="BD27:BI27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:J28"/>
-    <mergeCell ref="K28:R28"/>
-    <mergeCell ref="S28:T28"/>
-    <mergeCell ref="U28:V28"/>
-    <mergeCell ref="W28:X28"/>
-    <mergeCell ref="Y28:Z28"/>
-    <mergeCell ref="AA28:AB28"/>
-    <mergeCell ref="AC28:AF28"/>
-    <mergeCell ref="AG28:AI28"/>
-    <mergeCell ref="AJ28:AL28"/>
-    <mergeCell ref="AM28:AO28"/>
-    <mergeCell ref="AP28:AR28"/>
-    <mergeCell ref="AS28:AZ28"/>
-    <mergeCell ref="BA28:BC28"/>
-    <mergeCell ref="BD28:BI28"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:J27"/>
-    <mergeCell ref="K27:R27"/>
-    <mergeCell ref="S27:T27"/>
-    <mergeCell ref="U27:V27"/>
-    <mergeCell ref="AG26:AI26"/>
-    <mergeCell ref="AJ26:AL26"/>
-    <mergeCell ref="AM26:AO26"/>
-    <mergeCell ref="AP26:AR26"/>
-    <mergeCell ref="AS26:AZ26"/>
-    <mergeCell ref="BA26:BC26"/>
-    <mergeCell ref="BD26:BI26"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:J25"/>
-    <mergeCell ref="K25:R25"/>
-    <mergeCell ref="S25:T25"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:J26"/>
-    <mergeCell ref="K26:R26"/>
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="U26:V26"/>
-    <mergeCell ref="W26:X26"/>
-    <mergeCell ref="Y26:Z26"/>
-    <mergeCell ref="AA26:AB26"/>
-    <mergeCell ref="AC26:AF26"/>
-    <mergeCell ref="AC25:AF25"/>
-    <mergeCell ref="AP23:AR23"/>
-    <mergeCell ref="AC23:AF23"/>
-    <mergeCell ref="AG23:AI23"/>
-    <mergeCell ref="AJ23:AL23"/>
-    <mergeCell ref="AM23:AO23"/>
-    <mergeCell ref="AS25:AZ25"/>
-    <mergeCell ref="BA25:BC25"/>
-    <mergeCell ref="BD25:BI25"/>
-    <mergeCell ref="C23:J23"/>
-    <mergeCell ref="K23:R23"/>
-    <mergeCell ref="AG25:AI25"/>
-    <mergeCell ref="AJ25:AL25"/>
-    <mergeCell ref="AM25:AO25"/>
-    <mergeCell ref="AP25:AR25"/>
-    <mergeCell ref="AS23:AZ23"/>
-    <mergeCell ref="BA23:BC23"/>
-    <mergeCell ref="BD23:BI23"/>
-    <mergeCell ref="AG24:AI24"/>
-    <mergeCell ref="AJ24:AL24"/>
-    <mergeCell ref="AM24:AO24"/>
-    <mergeCell ref="AP24:AR24"/>
-    <mergeCell ref="AS24:AZ24"/>
-    <mergeCell ref="BA24:BC24"/>
-    <mergeCell ref="BD24:BI24"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="W23:X23"/>
-    <mergeCell ref="Y23:Z23"/>
-    <mergeCell ref="AA23:AB23"/>
-    <mergeCell ref="W25:X25"/>
-    <mergeCell ref="Y25:Z25"/>
-    <mergeCell ref="AA25:AB25"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:J24"/>
-    <mergeCell ref="K24:R24"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="W24:X24"/>
-    <mergeCell ref="Y24:Z24"/>
-    <mergeCell ref="AA24:AB24"/>
-    <mergeCell ref="AC24:AF24"/>
-    <mergeCell ref="AP21:AR21"/>
-    <mergeCell ref="AS21:AZ21"/>
-    <mergeCell ref="BA21:BC21"/>
-    <mergeCell ref="BD21:BI21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:J22"/>
-    <mergeCell ref="K22:R22"/>
-    <mergeCell ref="S22:T22"/>
-    <mergeCell ref="U22:V22"/>
-    <mergeCell ref="W22:X22"/>
-    <mergeCell ref="Y22:Z22"/>
-    <mergeCell ref="AA22:AB22"/>
-    <mergeCell ref="AC22:AF22"/>
-    <mergeCell ref="AG22:AI22"/>
-    <mergeCell ref="AJ22:AL22"/>
-    <mergeCell ref="AM22:AO22"/>
-    <mergeCell ref="AP22:AR22"/>
-    <mergeCell ref="AS22:AZ22"/>
-    <mergeCell ref="BA22:BC22"/>
-    <mergeCell ref="BD22:BI22"/>
-    <mergeCell ref="AM21:AO21"/>
-    <mergeCell ref="AJ19:AL19"/>
-    <mergeCell ref="AM19:AO19"/>
-    <mergeCell ref="AP19:AR19"/>
-    <mergeCell ref="AS19:AZ19"/>
-    <mergeCell ref="BA19:BC19"/>
-    <mergeCell ref="BD19:BI19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:J20"/>
-    <mergeCell ref="K20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="U20:V20"/>
-    <mergeCell ref="W20:X20"/>
-    <mergeCell ref="Y20:Z20"/>
-    <mergeCell ref="AA20:AB20"/>
-    <mergeCell ref="AC20:AF20"/>
-    <mergeCell ref="AG20:AI20"/>
-    <mergeCell ref="AJ20:AL20"/>
-    <mergeCell ref="AM20:AO20"/>
-    <mergeCell ref="AP20:AR20"/>
-    <mergeCell ref="AS20:AZ20"/>
-    <mergeCell ref="BA20:BC20"/>
-    <mergeCell ref="BD20:BI20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:J19"/>
-    <mergeCell ref="K19:R19"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="U19:V19"/>
-    <mergeCell ref="W19:X19"/>
-    <mergeCell ref="Y19:Z19"/>
-    <mergeCell ref="AA19:AB19"/>
-    <mergeCell ref="AC19:AF19"/>
-    <mergeCell ref="AG17:AI17"/>
-    <mergeCell ref="K17:R17"/>
-    <mergeCell ref="S17:T17"/>
-    <mergeCell ref="U17:V17"/>
-    <mergeCell ref="W17:X17"/>
-    <mergeCell ref="Y17:Z17"/>
-    <mergeCell ref="AA17:AB17"/>
-    <mergeCell ref="AC17:AF17"/>
-    <mergeCell ref="AG19:AI19"/>
-    <mergeCell ref="AJ17:AL17"/>
-    <mergeCell ref="AM17:AO17"/>
-    <mergeCell ref="AP17:AR17"/>
-    <mergeCell ref="AS17:AZ17"/>
-    <mergeCell ref="BA17:BC17"/>
-    <mergeCell ref="BD17:BI17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:J18"/>
-    <mergeCell ref="K18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="U18:V18"/>
-    <mergeCell ref="W18:X18"/>
-    <mergeCell ref="Y18:Z18"/>
-    <mergeCell ref="AA18:AB18"/>
-    <mergeCell ref="AC18:AF18"/>
-    <mergeCell ref="AG18:AI18"/>
-    <mergeCell ref="AJ18:AL18"/>
-    <mergeCell ref="AM18:AO18"/>
-    <mergeCell ref="AP18:AR18"/>
-    <mergeCell ref="AS18:AZ18"/>
-    <mergeCell ref="BA18:BC18"/>
-    <mergeCell ref="BD18:BI18"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:J17"/>
-    <mergeCell ref="AJ15:AL15"/>
-    <mergeCell ref="AM15:AO15"/>
-    <mergeCell ref="AP15:AR15"/>
-    <mergeCell ref="AS15:AZ15"/>
-    <mergeCell ref="BA15:BC15"/>
-    <mergeCell ref="BD15:BI15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:J16"/>
-    <mergeCell ref="K16:R16"/>
-    <mergeCell ref="S16:T16"/>
-    <mergeCell ref="U16:V16"/>
-    <mergeCell ref="W16:X16"/>
-    <mergeCell ref="Y16:Z16"/>
-    <mergeCell ref="AA16:AB16"/>
-    <mergeCell ref="AC16:AF16"/>
-    <mergeCell ref="AG16:AI16"/>
-    <mergeCell ref="AJ16:AL16"/>
-    <mergeCell ref="AM16:AO16"/>
-    <mergeCell ref="AP16:AR16"/>
-    <mergeCell ref="AS16:AZ16"/>
-    <mergeCell ref="BA16:BC16"/>
-    <mergeCell ref="BD16:BI16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:J15"/>
-    <mergeCell ref="K15:R15"/>
-    <mergeCell ref="S15:T15"/>
-    <mergeCell ref="U15:V15"/>
-    <mergeCell ref="W15:X15"/>
-    <mergeCell ref="Y15:Z15"/>
-    <mergeCell ref="AA15:AB15"/>
-    <mergeCell ref="AC15:AF15"/>
-    <mergeCell ref="AG13:AI13"/>
-    <mergeCell ref="K13:R13"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="W13:X13"/>
-    <mergeCell ref="Y13:Z13"/>
-    <mergeCell ref="AA13:AB13"/>
-    <mergeCell ref="AC13:AF13"/>
-    <mergeCell ref="AG15:AI15"/>
-    <mergeCell ref="AJ13:AL13"/>
-    <mergeCell ref="AM13:AO13"/>
-    <mergeCell ref="AP13:AR13"/>
-    <mergeCell ref="AS13:AZ13"/>
-    <mergeCell ref="BA13:BC13"/>
-    <mergeCell ref="BD13:BI13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:J14"/>
-    <mergeCell ref="K14:R14"/>
-    <mergeCell ref="S14:T14"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="W14:X14"/>
-    <mergeCell ref="Y14:Z14"/>
-    <mergeCell ref="AA14:AB14"/>
-    <mergeCell ref="AC14:AF14"/>
-    <mergeCell ref="AG14:AI14"/>
-    <mergeCell ref="AJ14:AL14"/>
-    <mergeCell ref="AM14:AO14"/>
-    <mergeCell ref="AP14:AR14"/>
-    <mergeCell ref="AS14:AZ14"/>
-    <mergeCell ref="BA14:BC14"/>
-    <mergeCell ref="BD14:BI14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="AG11:AI11"/>
-    <mergeCell ref="AJ11:AL11"/>
-    <mergeCell ref="AM11:AO11"/>
-    <mergeCell ref="AP11:AR11"/>
-    <mergeCell ref="AS11:AZ11"/>
-    <mergeCell ref="BA11:BC11"/>
-    <mergeCell ref="BD11:BI11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:J12"/>
-    <mergeCell ref="K12:R12"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="U12:V12"/>
-    <mergeCell ref="W12:X12"/>
-    <mergeCell ref="Y12:Z12"/>
-    <mergeCell ref="AA12:AB12"/>
-    <mergeCell ref="AC12:AF12"/>
-    <mergeCell ref="AG12:AI12"/>
-    <mergeCell ref="AJ12:AL12"/>
-    <mergeCell ref="AM12:AO12"/>
-    <mergeCell ref="AP12:AR12"/>
-    <mergeCell ref="AS12:AZ12"/>
-    <mergeCell ref="BA12:BC12"/>
-    <mergeCell ref="BD12:BI12"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:J11"/>
-    <mergeCell ref="K11:R11"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="W11:X11"/>
-    <mergeCell ref="Y11:Z11"/>
-    <mergeCell ref="AA11:AB11"/>
-    <mergeCell ref="AC11:AF11"/>
-    <mergeCell ref="BA8:BC8"/>
-    <mergeCell ref="Y9:Z9"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AJ9:AL9"/>
-    <mergeCell ref="AM9:AO9"/>
-    <mergeCell ref="AP9:AR9"/>
-    <mergeCell ref="AS9:AZ9"/>
-    <mergeCell ref="BA9:BC9"/>
-    <mergeCell ref="AG9:AI9"/>
-    <mergeCell ref="AC9:AF9"/>
-    <mergeCell ref="AA8:AB8"/>
-    <mergeCell ref="AC8:AF8"/>
-    <mergeCell ref="AG8:AI8"/>
-    <mergeCell ref="AJ8:AL8"/>
-    <mergeCell ref="AM8:AO8"/>
-    <mergeCell ref="AP8:AR8"/>
-    <mergeCell ref="AJ10:AL10"/>
-    <mergeCell ref="AM10:AO10"/>
-    <mergeCell ref="AP10:AR10"/>
-    <mergeCell ref="AS10:AZ10"/>
-    <mergeCell ref="BA10:BC10"/>
-    <mergeCell ref="BD10:BI10"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:J9"/>
-    <mergeCell ref="K9:R9"/>
-    <mergeCell ref="S9:T9"/>
-    <mergeCell ref="U9:V9"/>
-    <mergeCell ref="W9:X9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="K10:R10"/>
-    <mergeCell ref="S10:T10"/>
-    <mergeCell ref="U10:V10"/>
-    <mergeCell ref="W10:X10"/>
-    <mergeCell ref="Y10:Z10"/>
-    <mergeCell ref="AA10:AB10"/>
-    <mergeCell ref="AC10:AF10"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="AS8:AZ8"/>
-    <mergeCell ref="W8:X8"/>
-    <mergeCell ref="Y8:Z8"/>
-    <mergeCell ref="AY1:BI1"/>
-    <mergeCell ref="AY2:BI4"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="F2:J3"/>
-    <mergeCell ref="K1:V1"/>
-    <mergeCell ref="K2:V3"/>
-    <mergeCell ref="W1:AH1"/>
-    <mergeCell ref="W2:AH3"/>
-    <mergeCell ref="AI1:AM1"/>
-    <mergeCell ref="AN1:AR1"/>
-    <mergeCell ref="AI2:AM3"/>
-    <mergeCell ref="AN2:AR3"/>
-    <mergeCell ref="F4:J4"/>
-    <mergeCell ref="K4:O4"/>
-    <mergeCell ref="P4:T4"/>
-    <mergeCell ref="AI4:AR6"/>
-    <mergeCell ref="U4:AH4"/>
-    <mergeCell ref="BD8:BI8"/>
-    <mergeCell ref="BD9:BI9"/>
-    <mergeCell ref="AG10:AI10"/>
-    <mergeCell ref="W30:X30"/>
-    <mergeCell ref="Y30:Z30"/>
-    <mergeCell ref="AL65:AN65"/>
-    <mergeCell ref="AG30:AI30"/>
-    <mergeCell ref="F5:J6"/>
-    <mergeCell ref="K5:O6"/>
-    <mergeCell ref="P5:T6"/>
-    <mergeCell ref="U5:AH6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:J8"/>
-    <mergeCell ref="K8:R8"/>
-    <mergeCell ref="S8:T8"/>
-    <mergeCell ref="U8:V8"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:J21"/>
-    <mergeCell ref="K21:R21"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="U21:V21"/>
-    <mergeCell ref="W21:X21"/>
-    <mergeCell ref="Y21:Z21"/>
-    <mergeCell ref="AA21:AB21"/>
-    <mergeCell ref="AC21:AF21"/>
-    <mergeCell ref="AG21:AI21"/>
-    <mergeCell ref="AJ21:AL21"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -5370,74 +5352,74 @@
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="45" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
-      <c r="S1" s="46"/>
-      <c r="T1" s="46"/>
-      <c r="U1" s="46"/>
-      <c r="V1" s="47"/>
-      <c r="W1" s="45" t="s">
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="46"/>
-      <c r="Z1" s="46"/>
-      <c r="AA1" s="46"/>
-      <c r="AB1" s="46"/>
-      <c r="AC1" s="46"/>
-      <c r="AD1" s="46"/>
-      <c r="AE1" s="46"/>
-      <c r="AF1" s="46"/>
-      <c r="AG1" s="46"/>
-      <c r="AH1" s="47"/>
-      <c r="AI1" s="45" t="s">
+      <c r="X1" s="33"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="33"/>
+      <c r="AB1" s="33"/>
+      <c r="AC1" s="33"/>
+      <c r="AD1" s="33"/>
+      <c r="AE1" s="33"/>
+      <c r="AF1" s="33"/>
+      <c r="AG1" s="33"/>
+      <c r="AH1" s="34"/>
+      <c r="AI1" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="AJ1" s="46"/>
-      <c r="AK1" s="46"/>
-      <c r="AL1" s="46"/>
-      <c r="AM1" s="47"/>
-      <c r="AN1" s="45" t="s">
+      <c r="AJ1" s="33"/>
+      <c r="AK1" s="33"/>
+      <c r="AL1" s="33"/>
+      <c r="AM1" s="34"/>
+      <c r="AN1" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="AO1" s="46"/>
-      <c r="AP1" s="46"/>
-      <c r="AQ1" s="46"/>
-      <c r="AR1" s="47"/>
+      <c r="AO1" s="33"/>
+      <c r="AP1" s="33"/>
+      <c r="AQ1" s="33"/>
+      <c r="AR1" s="34"/>
       <c r="AS1" s="7"/>
       <c r="AT1" s="7"/>
       <c r="AU1" s="7"/>
       <c r="AV1" s="7"/>
       <c r="AW1" s="7"/>
       <c r="AX1" s="7"/>
-      <c r="AY1" s="42" t="s">
+      <c r="AY1" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="AZ1" s="42"/>
-      <c r="BA1" s="42"/>
-      <c r="BB1" s="42"/>
-      <c r="BC1" s="42"/>
-      <c r="BD1" s="42"/>
-      <c r="BE1" s="42"/>
-      <c r="BF1" s="42"/>
-      <c r="BG1" s="42"/>
-      <c r="BH1" s="42"/>
-      <c r="BI1" s="42"/>
+      <c r="AZ1" s="29"/>
+      <c r="BA1" s="29"/>
+      <c r="BB1" s="29"/>
+      <c r="BC1" s="29"/>
+      <c r="BD1" s="29"/>
+      <c r="BE1" s="29"/>
+      <c r="BF1" s="29"/>
+      <c r="BG1" s="29"/>
+      <c r="BH1" s="29"/>
+      <c r="BI1" s="29"/>
     </row>
     <row r="2" spans="1:61" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
@@ -5445,68 +5427,68 @@
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="48" t="s">
+      <c r="F2" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="17" t="s">
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="18"/>
-      <c r="U2" s="18"/>
-      <c r="V2" s="19"/>
-      <c r="W2" s="17" t="s">
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="42"/>
+      <c r="P2" s="42"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="42"/>
+      <c r="S2" s="42"/>
+      <c r="T2" s="42"/>
+      <c r="U2" s="42"/>
+      <c r="V2" s="43"/>
+      <c r="W2" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="X2" s="18"/>
-      <c r="Y2" s="18"/>
-      <c r="Z2" s="18"/>
-      <c r="AA2" s="18"/>
-      <c r="AB2" s="18"/>
-      <c r="AC2" s="18"/>
-      <c r="AD2" s="18"/>
-      <c r="AE2" s="18"/>
-      <c r="AF2" s="18"/>
-      <c r="AG2" s="18"/>
-      <c r="AH2" s="19"/>
-      <c r="AI2" s="23" t="s">
+      <c r="X2" s="42"/>
+      <c r="Y2" s="42"/>
+      <c r="Z2" s="42"/>
+      <c r="AA2" s="42"/>
+      <c r="AB2" s="42"/>
+      <c r="AC2" s="42"/>
+      <c r="AD2" s="42"/>
+      <c r="AE2" s="42"/>
+      <c r="AF2" s="42"/>
+      <c r="AG2" s="42"/>
+      <c r="AH2" s="43"/>
+      <c r="AI2" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="AJ2" s="24"/>
-      <c r="AK2" s="24"/>
-      <c r="AL2" s="24"/>
-      <c r="AM2" s="25"/>
-      <c r="AN2" s="23" t="s">
+      <c r="AJ2" s="48"/>
+      <c r="AK2" s="48"/>
+      <c r="AL2" s="48"/>
+      <c r="AM2" s="49"/>
+      <c r="AN2" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="AO2" s="24"/>
-      <c r="AP2" s="24"/>
-      <c r="AQ2" s="24"/>
-      <c r="AR2" s="25"/>
-      <c r="AY2" s="43" t="s">
+      <c r="AO2" s="48"/>
+      <c r="AP2" s="48"/>
+      <c r="AQ2" s="48"/>
+      <c r="AR2" s="49"/>
+      <c r="AY2" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="AZ2" s="43"/>
-      <c r="BA2" s="43"/>
-      <c r="BB2" s="43"/>
-      <c r="BC2" s="43"/>
-      <c r="BD2" s="43"/>
-      <c r="BE2" s="43"/>
-      <c r="BF2" s="43"/>
-      <c r="BG2" s="43"/>
-      <c r="BH2" s="43"/>
-      <c r="BI2" s="43"/>
+      <c r="AZ2" s="30"/>
+      <c r="BA2" s="30"/>
+      <c r="BB2" s="30"/>
+      <c r="BC2" s="30"/>
+      <c r="BD2" s="30"/>
+      <c r="BE2" s="30"/>
+      <c r="BF2" s="30"/>
+      <c r="BG2" s="30"/>
+      <c r="BH2" s="30"/>
+      <c r="BI2" s="30"/>
     </row>
     <row r="3" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4"/>
@@ -5514,56 +5496,56 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="21"/>
-      <c r="S3" s="21"/>
-      <c r="T3" s="21"/>
-      <c r="U3" s="21"/>
-      <c r="V3" s="22"/>
-      <c r="W3" s="20"/>
-      <c r="X3" s="21"/>
-      <c r="Y3" s="21"/>
-      <c r="Z3" s="21"/>
-      <c r="AA3" s="21"/>
-      <c r="AB3" s="21"/>
-      <c r="AC3" s="21"/>
-      <c r="AD3" s="21"/>
-      <c r="AE3" s="21"/>
-      <c r="AF3" s="21"/>
-      <c r="AG3" s="21"/>
-      <c r="AH3" s="22"/>
-      <c r="AI3" s="26"/>
-      <c r="AJ3" s="27"/>
-      <c r="AK3" s="27"/>
-      <c r="AL3" s="27"/>
-      <c r="AM3" s="28"/>
-      <c r="AN3" s="26"/>
-      <c r="AO3" s="27"/>
-      <c r="AP3" s="27"/>
-      <c r="AQ3" s="27"/>
-      <c r="AR3" s="28"/>
-      <c r="AY3" s="44"/>
-      <c r="AZ3" s="44"/>
-      <c r="BA3" s="44"/>
-      <c r="BB3" s="44"/>
-      <c r="BC3" s="44"/>
-      <c r="BD3" s="44"/>
-      <c r="BE3" s="44"/>
-      <c r="BF3" s="44"/>
-      <c r="BG3" s="44"/>
-      <c r="BH3" s="44"/>
-      <c r="BI3" s="44"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="45"/>
+      <c r="Q3" s="45"/>
+      <c r="R3" s="45"/>
+      <c r="S3" s="45"/>
+      <c r="T3" s="45"/>
+      <c r="U3" s="45"/>
+      <c r="V3" s="46"/>
+      <c r="W3" s="44"/>
+      <c r="X3" s="45"/>
+      <c r="Y3" s="45"/>
+      <c r="Z3" s="45"/>
+      <c r="AA3" s="45"/>
+      <c r="AB3" s="45"/>
+      <c r="AC3" s="45"/>
+      <c r="AD3" s="45"/>
+      <c r="AE3" s="45"/>
+      <c r="AF3" s="45"/>
+      <c r="AG3" s="45"/>
+      <c r="AH3" s="46"/>
+      <c r="AI3" s="50"/>
+      <c r="AJ3" s="51"/>
+      <c r="AK3" s="51"/>
+      <c r="AL3" s="51"/>
+      <c r="AM3" s="52"/>
+      <c r="AN3" s="50"/>
+      <c r="AO3" s="51"/>
+      <c r="AP3" s="51"/>
+      <c r="AQ3" s="51"/>
+      <c r="AR3" s="52"/>
+      <c r="AY3" s="31"/>
+      <c r="AZ3" s="31"/>
+      <c r="BA3" s="31"/>
+      <c r="BB3" s="31"/>
+      <c r="BC3" s="31"/>
+      <c r="BD3" s="31"/>
+      <c r="BE3" s="31"/>
+      <c r="BF3" s="31"/>
+      <c r="BG3" s="31"/>
+      <c r="BH3" s="31"/>
+      <c r="BI3" s="31"/>
     </row>
     <row r="4" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
@@ -5571,66 +5553,66 @@
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="54" t="s">
+      <c r="F4" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="54" t="s">
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="54" t="s">
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="Q4" s="55"/>
-      <c r="R4" s="55"/>
-      <c r="S4" s="55"/>
-      <c r="T4" s="56"/>
-      <c r="U4" s="54" t="s">
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="54"/>
+      <c r="T4" s="55"/>
+      <c r="U4" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="V4" s="55"/>
-      <c r="W4" s="55"/>
-      <c r="X4" s="55"/>
-      <c r="Y4" s="55"/>
-      <c r="Z4" s="55"/>
-      <c r="AA4" s="55"/>
-      <c r="AB4" s="55"/>
-      <c r="AC4" s="55"/>
-      <c r="AD4" s="55"/>
-      <c r="AE4" s="55"/>
-      <c r="AF4" s="55"/>
-      <c r="AG4" s="55"/>
-      <c r="AH4" s="56"/>
-      <c r="AI4" s="57" t="s">
+      <c r="V4" s="54"/>
+      <c r="W4" s="54"/>
+      <c r="X4" s="54"/>
+      <c r="Y4" s="54"/>
+      <c r="Z4" s="54"/>
+      <c r="AA4" s="54"/>
+      <c r="AB4" s="54"/>
+      <c r="AC4" s="54"/>
+      <c r="AD4" s="54"/>
+      <c r="AE4" s="54"/>
+      <c r="AF4" s="54"/>
+      <c r="AG4" s="54"/>
+      <c r="AH4" s="55"/>
+      <c r="AI4" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="AJ4" s="58"/>
-      <c r="AK4" s="58"/>
-      <c r="AL4" s="58"/>
-      <c r="AM4" s="58"/>
-      <c r="AN4" s="58"/>
-      <c r="AO4" s="58"/>
-      <c r="AP4" s="58"/>
-      <c r="AQ4" s="58"/>
-      <c r="AR4" s="59"/>
-      <c r="AY4" s="44"/>
-      <c r="AZ4" s="44"/>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44"/>
-      <c r="BC4" s="44"/>
-      <c r="BD4" s="44"/>
-      <c r="BE4" s="44"/>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="44"/>
-      <c r="BH4" s="44"/>
-      <c r="BI4" s="44"/>
+      <c r="AJ4" s="57"/>
+      <c r="AK4" s="57"/>
+      <c r="AL4" s="57"/>
+      <c r="AM4" s="57"/>
+      <c r="AN4" s="57"/>
+      <c r="AO4" s="57"/>
+      <c r="AP4" s="57"/>
+      <c r="AQ4" s="57"/>
+      <c r="AR4" s="58"/>
+      <c r="AY4" s="31"/>
+      <c r="AZ4" s="31"/>
+      <c r="BA4" s="31"/>
+      <c r="BB4" s="31"/>
+      <c r="BC4" s="31"/>
+      <c r="BD4" s="31"/>
+      <c r="BE4" s="31"/>
+      <c r="BF4" s="31"/>
+      <c r="BG4" s="31"/>
+      <c r="BH4" s="31"/>
+      <c r="BI4" s="31"/>
     </row>
     <row r="5" spans="1:61" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
@@ -5638,53 +5620,53 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="23" t="s">
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
-      <c r="N5" s="24"/>
-      <c r="O5" s="25"/>
-      <c r="P5" s="23" t="s">
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="24"/>
-      <c r="T5" s="25"/>
-      <c r="U5" s="29" t="s">
+      <c r="Q5" s="48"/>
+      <c r="R5" s="48"/>
+      <c r="S5" s="48"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30"/>
-      <c r="X5" s="30"/>
-      <c r="Y5" s="30"/>
-      <c r="Z5" s="30"/>
-      <c r="AA5" s="30"/>
-      <c r="AB5" s="30"/>
-      <c r="AC5" s="30"/>
-      <c r="AD5" s="30"/>
-      <c r="AE5" s="30"/>
-      <c r="AF5" s="30"/>
-      <c r="AG5" s="30"/>
-      <c r="AH5" s="31"/>
-      <c r="AI5" s="60"/>
-      <c r="AJ5" s="61"/>
-      <c r="AK5" s="61"/>
-      <c r="AL5" s="61"/>
-      <c r="AM5" s="61"/>
-      <c r="AN5" s="61"/>
-      <c r="AO5" s="61"/>
-      <c r="AP5" s="61"/>
-      <c r="AQ5" s="61"/>
-      <c r="AR5" s="62"/>
+      <c r="V5" s="68"/>
+      <c r="W5" s="68"/>
+      <c r="X5" s="68"/>
+      <c r="Y5" s="68"/>
+      <c r="Z5" s="68"/>
+      <c r="AA5" s="68"/>
+      <c r="AB5" s="68"/>
+      <c r="AC5" s="68"/>
+      <c r="AD5" s="68"/>
+      <c r="AE5" s="68"/>
+      <c r="AF5" s="68"/>
+      <c r="AG5" s="68"/>
+      <c r="AH5" s="69"/>
+      <c r="AI5" s="59"/>
+      <c r="AJ5" s="60"/>
+      <c r="AK5" s="60"/>
+      <c r="AL5" s="60"/>
+      <c r="AM5" s="60"/>
+      <c r="AN5" s="60"/>
+      <c r="AO5" s="60"/>
+      <c r="AP5" s="60"/>
+      <c r="AQ5" s="60"/>
+      <c r="AR5" s="61"/>
     </row>
     <row r="6" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
@@ -5692,45 +5674,45 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="26"/>
-      <c r="Q6" s="27"/>
-      <c r="R6" s="27"/>
-      <c r="S6" s="27"/>
-      <c r="T6" s="28"/>
-      <c r="U6" s="32"/>
-      <c r="V6" s="33"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="33"/>
-      <c r="Y6" s="33"/>
-      <c r="Z6" s="33"/>
-      <c r="AA6" s="33"/>
-      <c r="AB6" s="33"/>
-      <c r="AC6" s="33"/>
-      <c r="AD6" s="33"/>
-      <c r="AE6" s="33"/>
-      <c r="AF6" s="33"/>
-      <c r="AG6" s="33"/>
-      <c r="AH6" s="34"/>
-      <c r="AI6" s="63"/>
-      <c r="AJ6" s="64"/>
-      <c r="AK6" s="64"/>
-      <c r="AL6" s="64"/>
-      <c r="AM6" s="64"/>
-      <c r="AN6" s="64"/>
-      <c r="AO6" s="64"/>
-      <c r="AP6" s="64"/>
-      <c r="AQ6" s="64"/>
-      <c r="AR6" s="65"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="50"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="51"/>
+      <c r="O6" s="52"/>
+      <c r="P6" s="50"/>
+      <c r="Q6" s="51"/>
+      <c r="R6" s="51"/>
+      <c r="S6" s="51"/>
+      <c r="T6" s="52"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
+      <c r="W6" s="71"/>
+      <c r="X6" s="71"/>
+      <c r="Y6" s="71"/>
+      <c r="Z6" s="71"/>
+      <c r="AA6" s="71"/>
+      <c r="AB6" s="71"/>
+      <c r="AC6" s="71"/>
+      <c r="AD6" s="71"/>
+      <c r="AE6" s="71"/>
+      <c r="AF6" s="71"/>
+      <c r="AG6" s="71"/>
+      <c r="AH6" s="72"/>
+      <c r="AI6" s="62"/>
+      <c r="AJ6" s="63"/>
+      <c r="AK6" s="63"/>
+      <c r="AL6" s="63"/>
+      <c r="AM6" s="63"/>
+      <c r="AN6" s="63"/>
+      <c r="AO6" s="63"/>
+      <c r="AP6" s="63"/>
+      <c r="AQ6" s="63"/>
+      <c r="AR6" s="64"/>
     </row>
     <row r="7" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
@@ -5839,73 +5821,73 @@
       <c r="BI8" s="8"/>
     </row>
     <row r="9" spans="1:61" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="71"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="71"/>
-      <c r="K9" s="71"/>
-      <c r="L9" s="71"/>
-      <c r="M9" s="71"/>
-      <c r="N9" s="71"/>
-      <c r="O9" s="71"/>
-      <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
-      <c r="R9" s="71"/>
-      <c r="S9" s="71"/>
-      <c r="T9" s="72"/>
-      <c r="U9" s="73" t="s">
+      <c r="B9" s="78"/>
+      <c r="C9" s="78"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="78"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="78"/>
+      <c r="I9" s="78"/>
+      <c r="J9" s="78"/>
+      <c r="K9" s="78"/>
+      <c r="L9" s="78"/>
+      <c r="M9" s="78"/>
+      <c r="N9" s="78"/>
+      <c r="O9" s="78"/>
+      <c r="P9" s="78"/>
+      <c r="Q9" s="78"/>
+      <c r="R9" s="78"/>
+      <c r="S9" s="78"/>
+      <c r="T9" s="79"/>
+      <c r="U9" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="V9" s="71"/>
-      <c r="W9" s="71"/>
-      <c r="X9" s="71"/>
-      <c r="Y9" s="71"/>
-      <c r="Z9" s="71"/>
-      <c r="AA9" s="71"/>
-      <c r="AB9" s="71"/>
-      <c r="AC9" s="71"/>
-      <c r="AD9" s="71"/>
-      <c r="AE9" s="71"/>
-      <c r="AF9" s="71"/>
-      <c r="AG9" s="71"/>
-      <c r="AH9" s="71"/>
-      <c r="AI9" s="71"/>
-      <c r="AJ9" s="71"/>
-      <c r="AK9" s="71"/>
-      <c r="AL9" s="71"/>
-      <c r="AM9" s="71"/>
-      <c r="AN9" s="71"/>
-      <c r="AO9" s="72"/>
-      <c r="AP9" s="73" t="s">
+      <c r="V9" s="78"/>
+      <c r="W9" s="78"/>
+      <c r="X9" s="78"/>
+      <c r="Y9" s="78"/>
+      <c r="Z9" s="78"/>
+      <c r="AA9" s="78"/>
+      <c r="AB9" s="78"/>
+      <c r="AC9" s="78"/>
+      <c r="AD9" s="78"/>
+      <c r="AE9" s="78"/>
+      <c r="AF9" s="78"/>
+      <c r="AG9" s="78"/>
+      <c r="AH9" s="78"/>
+      <c r="AI9" s="78"/>
+      <c r="AJ9" s="78"/>
+      <c r="AK9" s="78"/>
+      <c r="AL9" s="78"/>
+      <c r="AM9" s="78"/>
+      <c r="AN9" s="78"/>
+      <c r="AO9" s="79"/>
+      <c r="AP9" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="AQ9" s="71"/>
-      <c r="AR9" s="71"/>
-      <c r="AS9" s="71"/>
-      <c r="AT9" s="71"/>
-      <c r="AU9" s="71"/>
-      <c r="AV9" s="71"/>
-      <c r="AW9" s="71"/>
-      <c r="AX9" s="71"/>
-      <c r="AY9" s="71"/>
-      <c r="AZ9" s="71"/>
-      <c r="BA9" s="71"/>
-      <c r="BB9" s="71"/>
-      <c r="BC9" s="71"/>
-      <c r="BD9" s="71"/>
-      <c r="BE9" s="71"/>
-      <c r="BF9" s="71"/>
-      <c r="BG9" s="71"/>
-      <c r="BH9" s="71"/>
-      <c r="BI9" s="71"/>
+      <c r="AQ9" s="78"/>
+      <c r="AR9" s="78"/>
+      <c r="AS9" s="78"/>
+      <c r="AT9" s="78"/>
+      <c r="AU9" s="78"/>
+      <c r="AV9" s="78"/>
+      <c r="AW9" s="78"/>
+      <c r="AX9" s="78"/>
+      <c r="AY9" s="78"/>
+      <c r="AZ9" s="78"/>
+      <c r="BA9" s="78"/>
+      <c r="BB9" s="78"/>
+      <c r="BC9" s="78"/>
+      <c r="BD9" s="78"/>
+      <c r="BE9" s="78"/>
+      <c r="BF9" s="78"/>
+      <c r="BG9" s="78"/>
+      <c r="BH9" s="78"/>
+      <c r="BI9" s="78"/>
     </row>
     <row r="10" spans="1:61" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="11"/>
@@ -5970,121 +5952,121 @@
       <c r="BI10" s="10"/>
     </row>
     <row r="11" spans="1:61" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="74" t="s">
+      <c r="A11" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="74"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="74"/>
-      <c r="J11" s="74"/>
+      <c r="B11" s="73"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73"/>
+      <c r="J11" s="73"/>
       <c r="K11" s="9"/>
-      <c r="L11" s="74" t="s">
+      <c r="L11" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="M11" s="74"/>
-      <c r="O11" s="74" t="s">
+      <c r="M11" s="73"/>
+      <c r="O11" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="P11" s="74"/>
+      <c r="P11" s="73"/>
       <c r="Q11" s="9"/>
       <c r="R11" s="14"/>
       <c r="S11" s="9"/>
       <c r="T11" s="13"/>
-      <c r="U11" s="75" t="s">
+      <c r="U11" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="V11" s="74"/>
-      <c r="W11" s="74"/>
-      <c r="X11" s="74"/>
-      <c r="Y11" s="74"/>
-      <c r="Z11" s="74"/>
-      <c r="AA11" s="74"/>
-      <c r="AB11" s="74"/>
-      <c r="AC11" s="74"/>
-      <c r="AD11" s="74"/>
-      <c r="AE11" s="74"/>
+      <c r="V11" s="73"/>
+      <c r="W11" s="73"/>
+      <c r="X11" s="73"/>
+      <c r="Y11" s="73"/>
+      <c r="Z11" s="73"/>
+      <c r="AA11" s="73"/>
+      <c r="AB11" s="73"/>
+      <c r="AC11" s="73"/>
+      <c r="AD11" s="73"/>
+      <c r="AE11" s="73"/>
       <c r="AF11" s="9"/>
-      <c r="AG11" s="74" t="s">
+      <c r="AG11" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="AH11" s="74"/>
+      <c r="AH11" s="73"/>
       <c r="AI11" s="9"/>
-      <c r="AJ11" s="74" t="s">
+      <c r="AJ11" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="AK11" s="74"/>
+      <c r="AK11" s="73"/>
       <c r="AL11" s="9"/>
       <c r="AM11" s="14"/>
       <c r="AN11" s="9"/>
       <c r="AO11" s="13"/>
-      <c r="AP11" s="76" t="s">
+      <c r="AP11" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="AQ11" s="77"/>
-      <c r="AR11" s="77"/>
-      <c r="AS11" s="77"/>
-      <c r="AT11" s="77"/>
-      <c r="AU11" s="77"/>
-      <c r="AV11" s="77"/>
-      <c r="AW11" s="77"/>
-      <c r="AX11" s="77"/>
-      <c r="AY11" s="77"/>
-      <c r="AZ11" s="77"/>
-      <c r="BA11" s="77"/>
+      <c r="AQ11" s="75"/>
+      <c r="AR11" s="75"/>
+      <c r="AS11" s="75"/>
+      <c r="AT11" s="75"/>
+      <c r="AU11" s="75"/>
+      <c r="AV11" s="75"/>
+      <c r="AW11" s="75"/>
+      <c r="AX11" s="75"/>
+      <c r="AY11" s="75"/>
+      <c r="AZ11" s="75"/>
+      <c r="BA11" s="75"/>
       <c r="BB11" s="10"/>
-      <c r="BC11" s="77" t="s">
+      <c r="BC11" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="BD11" s="77"/>
-      <c r="BE11" s="77"/>
-      <c r="BF11" s="77"/>
-      <c r="BG11" s="77"/>
-      <c r="BH11" s="77"/>
-      <c r="BI11" s="77"/>
+      <c r="BD11" s="75"/>
+      <c r="BE11" s="75"/>
+      <c r="BF11" s="75"/>
+      <c r="BG11" s="75"/>
+      <c r="BH11" s="75"/>
+      <c r="BI11" s="75"/>
     </row>
     <row r="12" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="74"/>
-      <c r="B12" s="74"/>
-      <c r="C12" s="74"/>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="74"/>
-      <c r="J12" s="74"/>
+      <c r="A12" s="73"/>
+      <c r="B12" s="73"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73"/>
+      <c r="J12" s="73"/>
       <c r="K12" s="9"/>
-      <c r="L12" s="74"/>
-      <c r="M12" s="74"/>
+      <c r="L12" s="73"/>
+      <c r="M12" s="73"/>
       <c r="N12" s="9"/>
-      <c r="O12" s="74"/>
-      <c r="P12" s="74"/>
+      <c r="O12" s="73"/>
+      <c r="P12" s="73"/>
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
       <c r="S12" s="9"/>
       <c r="T12" s="13"/>
-      <c r="U12" s="75"/>
-      <c r="V12" s="74"/>
-      <c r="W12" s="74"/>
-      <c r="X12" s="74"/>
-      <c r="Y12" s="74"/>
-      <c r="Z12" s="74"/>
-      <c r="AA12" s="74"/>
-      <c r="AB12" s="74"/>
-      <c r="AC12" s="74"/>
-      <c r="AD12" s="74"/>
-      <c r="AE12" s="74"/>
+      <c r="U12" s="76"/>
+      <c r="V12" s="73"/>
+      <c r="W12" s="73"/>
+      <c r="X12" s="73"/>
+      <c r="Y12" s="73"/>
+      <c r="Z12" s="73"/>
+      <c r="AA12" s="73"/>
+      <c r="AB12" s="73"/>
+      <c r="AC12" s="73"/>
+      <c r="AD12" s="73"/>
+      <c r="AE12" s="73"/>
       <c r="AF12" s="9"/>
-      <c r="AG12" s="74"/>
-      <c r="AH12" s="74"/>
+      <c r="AG12" s="73"/>
+      <c r="AH12" s="73"/>
       <c r="AI12" s="9"/>
-      <c r="AJ12" s="74"/>
-      <c r="AK12" s="74"/>
+      <c r="AJ12" s="73"/>
+      <c r="AK12" s="73"/>
       <c r="AL12" s="9"/>
       <c r="AM12" s="9"/>
       <c r="AN12" s="9"/>
@@ -6111,43 +6093,43 @@
       <c r="BI12" s="10"/>
     </row>
     <row r="13" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="74"/>
-      <c r="B13" s="74"/>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="74"/>
+      <c r="A13" s="73"/>
+      <c r="B13" s="73"/>
+      <c r="C13" s="73"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="73"/>
+      <c r="J13" s="73"/>
       <c r="K13" s="9"/>
-      <c r="L13" s="74"/>
-      <c r="M13" s="74"/>
+      <c r="L13" s="73"/>
+      <c r="M13" s="73"/>
       <c r="N13" s="9"/>
-      <c r="O13" s="74"/>
-      <c r="P13" s="74"/>
+      <c r="O13" s="73"/>
+      <c r="P13" s="73"/>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
       <c r="S13" s="9"/>
       <c r="T13" s="13"/>
-      <c r="U13" s="75"/>
-      <c r="V13" s="74"/>
-      <c r="W13" s="74"/>
-      <c r="X13" s="74"/>
-      <c r="Y13" s="74"/>
-      <c r="Z13" s="74"/>
-      <c r="AA13" s="74"/>
-      <c r="AB13" s="74"/>
-      <c r="AC13" s="74"/>
-      <c r="AD13" s="74"/>
-      <c r="AE13" s="74"/>
+      <c r="U13" s="76"/>
+      <c r="V13" s="73"/>
+      <c r="W13" s="73"/>
+      <c r="X13" s="73"/>
+      <c r="Y13" s="73"/>
+      <c r="Z13" s="73"/>
+      <c r="AA13" s="73"/>
+      <c r="AB13" s="73"/>
+      <c r="AC13" s="73"/>
+      <c r="AD13" s="73"/>
+      <c r="AE13" s="73"/>
       <c r="AF13" s="9"/>
-      <c r="AG13" s="74"/>
-      <c r="AH13" s="74"/>
+      <c r="AG13" s="73"/>
+      <c r="AH13" s="73"/>
       <c r="AI13" s="9"/>
-      <c r="AJ13" s="74"/>
-      <c r="AK13" s="74"/>
+      <c r="AJ13" s="73"/>
+      <c r="AK13" s="73"/>
       <c r="AL13" s="9"/>
       <c r="AM13" s="9"/>
       <c r="AN13" s="9"/>
@@ -6174,43 +6156,43 @@
       <c r="BI13" s="10"/>
     </row>
     <row r="14" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="74"/>
-      <c r="B14" s="74"/>
-      <c r="C14" s="74"/>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="74"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="74"/>
-      <c r="I14" s="74"/>
-      <c r="J14" s="74"/>
+      <c r="A14" s="73"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="73"/>
       <c r="K14" s="9"/>
-      <c r="L14" s="74"/>
-      <c r="M14" s="74"/>
+      <c r="L14" s="73"/>
+      <c r="M14" s="73"/>
       <c r="N14" s="9"/>
-      <c r="O14" s="74"/>
-      <c r="P14" s="74"/>
+      <c r="O14" s="73"/>
+      <c r="P14" s="73"/>
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
       <c r="S14" s="9"/>
       <c r="T14" s="13"/>
-      <c r="U14" s="75"/>
-      <c r="V14" s="74"/>
-      <c r="W14" s="74"/>
-      <c r="X14" s="74"/>
-      <c r="Y14" s="74"/>
-      <c r="Z14" s="74"/>
-      <c r="AA14" s="74"/>
-      <c r="AB14" s="74"/>
-      <c r="AC14" s="74"/>
-      <c r="AD14" s="74"/>
-      <c r="AE14" s="74"/>
+      <c r="U14" s="76"/>
+      <c r="V14" s="73"/>
+      <c r="W14" s="73"/>
+      <c r="X14" s="73"/>
+      <c r="Y14" s="73"/>
+      <c r="Z14" s="73"/>
+      <c r="AA14" s="73"/>
+      <c r="AB14" s="73"/>
+      <c r="AC14" s="73"/>
+      <c r="AD14" s="73"/>
+      <c r="AE14" s="73"/>
       <c r="AF14" s="9"/>
-      <c r="AG14" s="74"/>
-      <c r="AH14" s="74"/>
+      <c r="AG14" s="73"/>
+      <c r="AH14" s="73"/>
       <c r="AI14" s="9"/>
-      <c r="AJ14" s="74"/>
-      <c r="AK14" s="74"/>
+      <c r="AJ14" s="73"/>
+      <c r="AK14" s="73"/>
       <c r="AL14" s="9"/>
       <c r="AM14" s="9"/>
       <c r="AN14" s="9"/>
@@ -6237,43 +6219,43 @@
       <c r="BI14" s="10"/>
     </row>
     <row r="15" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="74"/>
-      <c r="B15" s="74"/>
-      <c r="C15" s="74"/>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="74"/>
-      <c r="H15" s="74"/>
-      <c r="I15" s="74"/>
-      <c r="J15" s="74"/>
+      <c r="A15" s="73"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73"/>
+      <c r="J15" s="73"/>
       <c r="K15" s="9"/>
-      <c r="L15" s="74"/>
-      <c r="M15" s="74"/>
+      <c r="L15" s="73"/>
+      <c r="M15" s="73"/>
       <c r="N15" s="9"/>
-      <c r="O15" s="74"/>
-      <c r="P15" s="74"/>
+      <c r="O15" s="73"/>
+      <c r="P15" s="73"/>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
       <c r="S15" s="9"/>
       <c r="T15" s="13"/>
-      <c r="U15" s="75"/>
-      <c r="V15" s="74"/>
-      <c r="W15" s="74"/>
-      <c r="X15" s="74"/>
-      <c r="Y15" s="74"/>
-      <c r="Z15" s="74"/>
-      <c r="AA15" s="74"/>
-      <c r="AB15" s="74"/>
-      <c r="AC15" s="74"/>
-      <c r="AD15" s="74"/>
-      <c r="AE15" s="74"/>
+      <c r="U15" s="76"/>
+      <c r="V15" s="73"/>
+      <c r="W15" s="73"/>
+      <c r="X15" s="73"/>
+      <c r="Y15" s="73"/>
+      <c r="Z15" s="73"/>
+      <c r="AA15" s="73"/>
+      <c r="AB15" s="73"/>
+      <c r="AC15" s="73"/>
+      <c r="AD15" s="73"/>
+      <c r="AE15" s="73"/>
       <c r="AF15" s="9"/>
-      <c r="AG15" s="74"/>
-      <c r="AH15" s="74"/>
+      <c r="AG15" s="73"/>
+      <c r="AH15" s="73"/>
       <c r="AI15" s="9"/>
-      <c r="AJ15" s="74"/>
-      <c r="AK15" s="74"/>
+      <c r="AJ15" s="73"/>
+      <c r="AK15" s="73"/>
       <c r="AL15" s="9"/>
       <c r="AM15" s="9"/>
       <c r="AN15" s="9"/>
@@ -6300,43 +6282,43 @@
       <c r="BI15" s="10"/>
     </row>
     <row r="16" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="74"/>
-      <c r="B16" s="74"/>
-      <c r="C16" s="74"/>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="74"/>
-      <c r="I16" s="74"/>
-      <c r="J16" s="74"/>
+      <c r="A16" s="73"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="73"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="73"/>
+      <c r="G16" s="73"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73"/>
+      <c r="J16" s="73"/>
       <c r="K16" s="9"/>
-      <c r="L16" s="74"/>
-      <c r="M16" s="74"/>
+      <c r="L16" s="73"/>
+      <c r="M16" s="73"/>
       <c r="N16" s="9"/>
-      <c r="O16" s="74"/>
-      <c r="P16" s="74"/>
+      <c r="O16" s="73"/>
+      <c r="P16" s="73"/>
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
       <c r="S16" s="9"/>
       <c r="T16" s="13"/>
-      <c r="U16" s="75"/>
-      <c r="V16" s="74"/>
-      <c r="W16" s="74"/>
-      <c r="X16" s="74"/>
-      <c r="Y16" s="74"/>
-      <c r="Z16" s="74"/>
-      <c r="AA16" s="74"/>
-      <c r="AB16" s="74"/>
-      <c r="AC16" s="74"/>
-      <c r="AD16" s="74"/>
-      <c r="AE16" s="74"/>
+      <c r="U16" s="76"/>
+      <c r="V16" s="73"/>
+      <c r="W16" s="73"/>
+      <c r="X16" s="73"/>
+      <c r="Y16" s="73"/>
+      <c r="Z16" s="73"/>
+      <c r="AA16" s="73"/>
+      <c r="AB16" s="73"/>
+      <c r="AC16" s="73"/>
+      <c r="AD16" s="73"/>
+      <c r="AE16" s="73"/>
       <c r="AF16" s="9"/>
-      <c r="AG16" s="74"/>
-      <c r="AH16" s="74"/>
+      <c r="AG16" s="73"/>
+      <c r="AH16" s="73"/>
       <c r="AI16" s="9"/>
-      <c r="AJ16" s="74"/>
-      <c r="AK16" s="74"/>
+      <c r="AJ16" s="73"/>
+      <c r="AK16" s="73"/>
       <c r="AL16" s="9"/>
       <c r="AM16" s="9"/>
       <c r="AN16" s="9"/>
@@ -6363,43 +6345,43 @@
       <c r="BI16" s="10"/>
     </row>
     <row r="17" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="74"/>
-      <c r="B17" s="74"/>
-      <c r="C17" s="74"/>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="74"/>
-      <c r="H17" s="74"/>
-      <c r="I17" s="74"/>
-      <c r="J17" s="74"/>
+      <c r="A17" s="73"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="73"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="73"/>
       <c r="K17" s="9"/>
-      <c r="L17" s="74"/>
-      <c r="M17" s="74"/>
+      <c r="L17" s="73"/>
+      <c r="M17" s="73"/>
       <c r="N17" s="9"/>
-      <c r="O17" s="74"/>
-      <c r="P17" s="74"/>
+      <c r="O17" s="73"/>
+      <c r="P17" s="73"/>
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
       <c r="S17" s="9"/>
       <c r="T17" s="13"/>
-      <c r="U17" s="75"/>
-      <c r="V17" s="74"/>
-      <c r="W17" s="74"/>
-      <c r="X17" s="74"/>
-      <c r="Y17" s="74"/>
-      <c r="Z17" s="74"/>
-      <c r="AA17" s="74"/>
-      <c r="AB17" s="74"/>
-      <c r="AC17" s="74"/>
-      <c r="AD17" s="74"/>
-      <c r="AE17" s="74"/>
+      <c r="U17" s="76"/>
+      <c r="V17" s="73"/>
+      <c r="W17" s="73"/>
+      <c r="X17" s="73"/>
+      <c r="Y17" s="73"/>
+      <c r="Z17" s="73"/>
+      <c r="AA17" s="73"/>
+      <c r="AB17" s="73"/>
+      <c r="AC17" s="73"/>
+      <c r="AD17" s="73"/>
+      <c r="AE17" s="73"/>
       <c r="AF17" s="9"/>
-      <c r="AG17" s="74"/>
-      <c r="AH17" s="74"/>
+      <c r="AG17" s="73"/>
+      <c r="AH17" s="73"/>
       <c r="AI17" s="9"/>
-      <c r="AJ17" s="74"/>
-      <c r="AK17" s="74"/>
+      <c r="AJ17" s="73"/>
+      <c r="AK17" s="73"/>
       <c r="AL17" s="9"/>
       <c r="AM17" s="9"/>
       <c r="AN17" s="9"/>
@@ -6426,43 +6408,43 @@
       <c r="BI17" s="10"/>
     </row>
     <row r="18" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="74"/>
-      <c r="B18" s="74"/>
-      <c r="C18" s="74"/>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74"/>
-      <c r="G18" s="74"/>
-      <c r="H18" s="74"/>
-      <c r="I18" s="74"/>
-      <c r="J18" s="74"/>
+      <c r="A18" s="73"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="73"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73"/>
+      <c r="J18" s="73"/>
       <c r="K18" s="9"/>
-      <c r="L18" s="74"/>
-      <c r="M18" s="74"/>
+      <c r="L18" s="73"/>
+      <c r="M18" s="73"/>
       <c r="N18" s="9"/>
-      <c r="O18" s="74"/>
-      <c r="P18" s="74"/>
+      <c r="O18" s="73"/>
+      <c r="P18" s="73"/>
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
       <c r="S18" s="9"/>
       <c r="T18" s="13"/>
-      <c r="U18" s="75"/>
-      <c r="V18" s="74"/>
-      <c r="W18" s="74"/>
-      <c r="X18" s="74"/>
-      <c r="Y18" s="74"/>
-      <c r="Z18" s="74"/>
-      <c r="AA18" s="74"/>
-      <c r="AB18" s="74"/>
-      <c r="AC18" s="74"/>
-      <c r="AD18" s="74"/>
-      <c r="AE18" s="74"/>
+      <c r="U18" s="76"/>
+      <c r="V18" s="73"/>
+      <c r="W18" s="73"/>
+      <c r="X18" s="73"/>
+      <c r="Y18" s="73"/>
+      <c r="Z18" s="73"/>
+      <c r="AA18" s="73"/>
+      <c r="AB18" s="73"/>
+      <c r="AC18" s="73"/>
+      <c r="AD18" s="73"/>
+      <c r="AE18" s="73"/>
       <c r="AF18" s="9"/>
-      <c r="AG18" s="74"/>
-      <c r="AH18" s="74"/>
+      <c r="AG18" s="73"/>
+      <c r="AH18" s="73"/>
       <c r="AI18" s="9"/>
-      <c r="AJ18" s="74"/>
-      <c r="AK18" s="74"/>
+      <c r="AJ18" s="73"/>
+      <c r="AK18" s="73"/>
       <c r="AL18" s="9"/>
       <c r="AM18" s="9"/>
       <c r="AN18" s="9"/>
@@ -6489,43 +6471,43 @@
       <c r="BI18" s="10"/>
     </row>
     <row r="19" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="74"/>
-      <c r="B19" s="74"/>
-      <c r="C19" s="74"/>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="74"/>
-      <c r="J19" s="74"/>
+      <c r="A19" s="73"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="73"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="73"/>
+      <c r="G19" s="73"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73"/>
+      <c r="J19" s="73"/>
       <c r="K19" s="9"/>
-      <c r="L19" s="74"/>
-      <c r="M19" s="74"/>
+      <c r="L19" s="73"/>
+      <c r="M19" s="73"/>
       <c r="N19" s="9"/>
-      <c r="O19" s="74"/>
-      <c r="P19" s="74"/>
+      <c r="O19" s="73"/>
+      <c r="P19" s="73"/>
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
       <c r="S19" s="9"/>
       <c r="T19" s="13"/>
-      <c r="U19" s="75"/>
-      <c r="V19" s="74"/>
-      <c r="W19" s="74"/>
-      <c r="X19" s="74"/>
-      <c r="Y19" s="74"/>
-      <c r="Z19" s="74"/>
-      <c r="AA19" s="74"/>
-      <c r="AB19" s="74"/>
-      <c r="AC19" s="74"/>
-      <c r="AD19" s="74"/>
-      <c r="AE19" s="74"/>
+      <c r="U19" s="76"/>
+      <c r="V19" s="73"/>
+      <c r="W19" s="73"/>
+      <c r="X19" s="73"/>
+      <c r="Y19" s="73"/>
+      <c r="Z19" s="73"/>
+      <c r="AA19" s="73"/>
+      <c r="AB19" s="73"/>
+      <c r="AC19" s="73"/>
+      <c r="AD19" s="73"/>
+      <c r="AE19" s="73"/>
       <c r="AF19" s="9"/>
-      <c r="AG19" s="74"/>
-      <c r="AH19" s="74"/>
+      <c r="AG19" s="73"/>
+      <c r="AH19" s="73"/>
       <c r="AI19" s="9"/>
-      <c r="AJ19" s="74"/>
-      <c r="AK19" s="74"/>
+      <c r="AJ19" s="73"/>
+      <c r="AK19" s="73"/>
       <c r="AL19" s="9"/>
       <c r="AM19" s="9"/>
       <c r="AN19" s="9"/>
@@ -6552,43 +6534,43 @@
       <c r="BI19" s="10"/>
     </row>
     <row r="20" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="74"/>
-      <c r="B20" s="74"/>
-      <c r="C20" s="74"/>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="74"/>
-      <c r="J20" s="74"/>
+      <c r="A20" s="73"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73"/>
+      <c r="J20" s="73"/>
       <c r="K20" s="9"/>
-      <c r="L20" s="74"/>
-      <c r="M20" s="74"/>
+      <c r="L20" s="73"/>
+      <c r="M20" s="73"/>
       <c r="N20" s="9"/>
-      <c r="O20" s="74"/>
-      <c r="P20" s="74"/>
+      <c r="O20" s="73"/>
+      <c r="P20" s="73"/>
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
       <c r="S20" s="9"/>
       <c r="T20" s="13"/>
-      <c r="U20" s="75"/>
-      <c r="V20" s="74"/>
-      <c r="W20" s="74"/>
-      <c r="X20" s="74"/>
-      <c r="Y20" s="74"/>
-      <c r="Z20" s="74"/>
-      <c r="AA20" s="74"/>
-      <c r="AB20" s="74"/>
-      <c r="AC20" s="74"/>
-      <c r="AD20" s="74"/>
-      <c r="AE20" s="74"/>
+      <c r="U20" s="76"/>
+      <c r="V20" s="73"/>
+      <c r="W20" s="73"/>
+      <c r="X20" s="73"/>
+      <c r="Y20" s="73"/>
+      <c r="Z20" s="73"/>
+      <c r="AA20" s="73"/>
+      <c r="AB20" s="73"/>
+      <c r="AC20" s="73"/>
+      <c r="AD20" s="73"/>
+      <c r="AE20" s="73"/>
       <c r="AF20" s="9"/>
-      <c r="AG20" s="74"/>
-      <c r="AH20" s="74"/>
+      <c r="AG20" s="73"/>
+      <c r="AH20" s="73"/>
       <c r="AI20" s="9"/>
-      <c r="AJ20" s="74"/>
-      <c r="AK20" s="74"/>
+      <c r="AJ20" s="73"/>
+      <c r="AK20" s="73"/>
       <c r="AL20" s="9"/>
       <c r="AM20" s="9"/>
       <c r="AN20" s="9"/>
@@ -6615,43 +6597,43 @@
       <c r="BI20" s="10"/>
     </row>
     <row r="21" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="74"/>
-      <c r="B21" s="74"/>
-      <c r="C21" s="74"/>
-      <c r="D21" s="74"/>
-      <c r="E21" s="74"/>
-      <c r="F21" s="74"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="74"/>
-      <c r="I21" s="74"/>
-      <c r="J21" s="74"/>
+      <c r="A21" s="73"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="73"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73"/>
+      <c r="J21" s="73"/>
       <c r="K21" s="9"/>
-      <c r="L21" s="74"/>
-      <c r="M21" s="74"/>
+      <c r="L21" s="73"/>
+      <c r="M21" s="73"/>
       <c r="N21" s="9"/>
-      <c r="O21" s="74"/>
-      <c r="P21" s="74"/>
+      <c r="O21" s="73"/>
+      <c r="P21" s="73"/>
       <c r="Q21" s="9"/>
       <c r="R21" s="9"/>
       <c r="S21" s="9"/>
       <c r="T21" s="13"/>
-      <c r="U21" s="75"/>
-      <c r="V21" s="74"/>
-      <c r="W21" s="74"/>
-      <c r="X21" s="74"/>
-      <c r="Y21" s="74"/>
-      <c r="Z21" s="74"/>
-      <c r="AA21" s="74"/>
-      <c r="AB21" s="74"/>
-      <c r="AC21" s="74"/>
-      <c r="AD21" s="74"/>
-      <c r="AE21" s="74"/>
+      <c r="U21" s="76"/>
+      <c r="V21" s="73"/>
+      <c r="W21" s="73"/>
+      <c r="X21" s="73"/>
+      <c r="Y21" s="73"/>
+      <c r="Z21" s="73"/>
+      <c r="AA21" s="73"/>
+      <c r="AB21" s="73"/>
+      <c r="AC21" s="73"/>
+      <c r="AD21" s="73"/>
+      <c r="AE21" s="73"/>
       <c r="AF21" s="9"/>
-      <c r="AG21" s="74"/>
-      <c r="AH21" s="74"/>
+      <c r="AG21" s="73"/>
+      <c r="AH21" s="73"/>
       <c r="AI21" s="9"/>
-      <c r="AJ21" s="74"/>
-      <c r="AK21" s="74"/>
+      <c r="AJ21" s="73"/>
+      <c r="AK21" s="73"/>
       <c r="AL21" s="9"/>
       <c r="AM21" s="9"/>
       <c r="AN21" s="9"/>
@@ -6678,43 +6660,43 @@
       <c r="BI21" s="10"/>
     </row>
     <row r="22" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="74"/>
-      <c r="B22" s="74"/>
-      <c r="C22" s="74"/>
-      <c r="D22" s="74"/>
-      <c r="E22" s="74"/>
-      <c r="F22" s="74"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="74"/>
-      <c r="I22" s="74"/>
-      <c r="J22" s="74"/>
+      <c r="A22" s="73"/>
+      <c r="B22" s="73"/>
+      <c r="C22" s="73"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="73"/>
       <c r="K22" s="9"/>
-      <c r="L22" s="74"/>
-      <c r="M22" s="74"/>
+      <c r="L22" s="73"/>
+      <c r="M22" s="73"/>
       <c r="N22" s="9"/>
-      <c r="O22" s="74"/>
-      <c r="P22" s="74"/>
+      <c r="O22" s="73"/>
+      <c r="P22" s="73"/>
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
       <c r="S22" s="9"/>
       <c r="T22" s="13"/>
-      <c r="U22" s="75"/>
-      <c r="V22" s="74"/>
-      <c r="W22" s="74"/>
-      <c r="X22" s="74"/>
-      <c r="Y22" s="74"/>
-      <c r="Z22" s="74"/>
-      <c r="AA22" s="74"/>
-      <c r="AB22" s="74"/>
-      <c r="AC22" s="74"/>
-      <c r="AD22" s="74"/>
-      <c r="AE22" s="74"/>
+      <c r="U22" s="76"/>
+      <c r="V22" s="73"/>
+      <c r="W22" s="73"/>
+      <c r="X22" s="73"/>
+      <c r="Y22" s="73"/>
+      <c r="Z22" s="73"/>
+      <c r="AA22" s="73"/>
+      <c r="AB22" s="73"/>
+      <c r="AC22" s="73"/>
+      <c r="AD22" s="73"/>
+      <c r="AE22" s="73"/>
       <c r="AF22" s="9"/>
-      <c r="AG22" s="74"/>
-      <c r="AH22" s="74"/>
+      <c r="AG22" s="73"/>
+      <c r="AH22" s="73"/>
       <c r="AI22" s="9"/>
-      <c r="AJ22" s="74"/>
-      <c r="AK22" s="74"/>
+      <c r="AJ22" s="73"/>
+      <c r="AK22" s="73"/>
       <c r="AL22" s="9"/>
       <c r="AM22" s="9"/>
       <c r="AN22" s="9"/>
@@ -6741,43 +6723,43 @@
       <c r="BI22" s="10"/>
     </row>
     <row r="23" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="74"/>
-      <c r="B23" s="74"/>
-      <c r="C23" s="74"/>
-      <c r="D23" s="74"/>
-      <c r="E23" s="74"/>
-      <c r="F23" s="74"/>
-      <c r="G23" s="74"/>
-      <c r="H23" s="74"/>
-      <c r="I23" s="74"/>
-      <c r="J23" s="74"/>
+      <c r="A23" s="73"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="73"/>
       <c r="K23" s="9"/>
-      <c r="L23" s="74"/>
-      <c r="M23" s="74"/>
+      <c r="L23" s="73"/>
+      <c r="M23" s="73"/>
       <c r="N23" s="9"/>
-      <c r="O23" s="74"/>
-      <c r="P23" s="74"/>
+      <c r="O23" s="73"/>
+      <c r="P23" s="73"/>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
       <c r="S23" s="9"/>
       <c r="T23" s="13"/>
-      <c r="U23" s="75"/>
-      <c r="V23" s="74"/>
-      <c r="W23" s="74"/>
-      <c r="X23" s="74"/>
-      <c r="Y23" s="74"/>
-      <c r="Z23" s="74"/>
-      <c r="AA23" s="74"/>
-      <c r="AB23" s="74"/>
-      <c r="AC23" s="74"/>
-      <c r="AD23" s="74"/>
-      <c r="AE23" s="74"/>
+      <c r="U23" s="76"/>
+      <c r="V23" s="73"/>
+      <c r="W23" s="73"/>
+      <c r="X23" s="73"/>
+      <c r="Y23" s="73"/>
+      <c r="Z23" s="73"/>
+      <c r="AA23" s="73"/>
+      <c r="AB23" s="73"/>
+      <c r="AC23" s="73"/>
+      <c r="AD23" s="73"/>
+      <c r="AE23" s="73"/>
       <c r="AF23" s="9"/>
-      <c r="AG23" s="74"/>
-      <c r="AH23" s="74"/>
+      <c r="AG23" s="73"/>
+      <c r="AH23" s="73"/>
       <c r="AI23" s="9"/>
-      <c r="AJ23" s="74"/>
-      <c r="AK23" s="74"/>
+      <c r="AJ23" s="73"/>
+      <c r="AK23" s="73"/>
       <c r="AL23" s="9"/>
       <c r="AM23" s="9"/>
       <c r="AN23" s="9"/>
@@ -6804,43 +6786,43 @@
       <c r="BI23" s="10"/>
     </row>
     <row r="24" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="74"/>
-      <c r="B24" s="74"/>
-      <c r="C24" s="74"/>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="74"/>
-      <c r="H24" s="74"/>
-      <c r="I24" s="74"/>
-      <c r="J24" s="74"/>
+      <c r="A24" s="73"/>
+      <c r="B24" s="73"/>
+      <c r="C24" s="73"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73"/>
+      <c r="J24" s="73"/>
       <c r="K24" s="9"/>
-      <c r="L24" s="74"/>
-      <c r="M24" s="74"/>
+      <c r="L24" s="73"/>
+      <c r="M24" s="73"/>
       <c r="N24" s="9"/>
-      <c r="O24" s="74"/>
-      <c r="P24" s="74"/>
+      <c r="O24" s="73"/>
+      <c r="P24" s="73"/>
       <c r="Q24" s="9"/>
       <c r="R24" s="9"/>
       <c r="S24" s="9"/>
       <c r="T24" s="13"/>
-      <c r="U24" s="75"/>
-      <c r="V24" s="74"/>
-      <c r="W24" s="74"/>
-      <c r="X24" s="74"/>
-      <c r="Y24" s="74"/>
-      <c r="Z24" s="74"/>
-      <c r="AA24" s="74"/>
-      <c r="AB24" s="74"/>
-      <c r="AC24" s="74"/>
-      <c r="AD24" s="74"/>
-      <c r="AE24" s="74"/>
+      <c r="U24" s="76"/>
+      <c r="V24" s="73"/>
+      <c r="W24" s="73"/>
+      <c r="X24" s="73"/>
+      <c r="Y24" s="73"/>
+      <c r="Z24" s="73"/>
+      <c r="AA24" s="73"/>
+      <c r="AB24" s="73"/>
+      <c r="AC24" s="73"/>
+      <c r="AD24" s="73"/>
+      <c r="AE24" s="73"/>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="74"/>
-      <c r="AH24" s="74"/>
+      <c r="AG24" s="73"/>
+      <c r="AH24" s="73"/>
       <c r="AI24" s="9"/>
-      <c r="AJ24" s="74"/>
-      <c r="AK24" s="74"/>
+      <c r="AJ24" s="73"/>
+      <c r="AK24" s="73"/>
       <c r="AL24" s="9"/>
       <c r="AM24" s="9"/>
       <c r="AN24" s="9"/>
@@ -6867,43 +6849,43 @@
       <c r="BI24" s="10"/>
     </row>
     <row r="25" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="74"/>
-      <c r="B25" s="74"/>
-      <c r="C25" s="74"/>
-      <c r="D25" s="74"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="74"/>
-      <c r="G25" s="74"/>
-      <c r="H25" s="74"/>
-      <c r="I25" s="74"/>
-      <c r="J25" s="74"/>
+      <c r="A25" s="73"/>
+      <c r="B25" s="73"/>
+      <c r="C25" s="73"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73"/>
+      <c r="J25" s="73"/>
       <c r="K25" s="9"/>
-      <c r="L25" s="74"/>
-      <c r="M25" s="74"/>
+      <c r="L25" s="73"/>
+      <c r="M25" s="73"/>
       <c r="N25" s="9"/>
-      <c r="O25" s="74"/>
-      <c r="P25" s="74"/>
+      <c r="O25" s="73"/>
+      <c r="P25" s="73"/>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
       <c r="S25" s="9"/>
       <c r="T25" s="13"/>
-      <c r="U25" s="75"/>
-      <c r="V25" s="74"/>
-      <c r="W25" s="74"/>
-      <c r="X25" s="74"/>
-      <c r="Y25" s="74"/>
-      <c r="Z25" s="74"/>
-      <c r="AA25" s="74"/>
-      <c r="AB25" s="74"/>
-      <c r="AC25" s="74"/>
-      <c r="AD25" s="74"/>
-      <c r="AE25" s="74"/>
+      <c r="U25" s="76"/>
+      <c r="V25" s="73"/>
+      <c r="W25" s="73"/>
+      <c r="X25" s="73"/>
+      <c r="Y25" s="73"/>
+      <c r="Z25" s="73"/>
+      <c r="AA25" s="73"/>
+      <c r="AB25" s="73"/>
+      <c r="AC25" s="73"/>
+      <c r="AD25" s="73"/>
+      <c r="AE25" s="73"/>
       <c r="AF25" s="9"/>
-      <c r="AG25" s="74"/>
-      <c r="AH25" s="74"/>
+      <c r="AG25" s="73"/>
+      <c r="AH25" s="73"/>
       <c r="AI25" s="9"/>
-      <c r="AJ25" s="74"/>
-      <c r="AK25" s="74"/>
+      <c r="AJ25" s="73"/>
+      <c r="AK25" s="73"/>
       <c r="AL25" s="9"/>
       <c r="AM25" s="9"/>
       <c r="AN25" s="9"/>
@@ -6930,43 +6912,43 @@
       <c r="BI25" s="10"/>
     </row>
     <row r="26" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="74"/>
-      <c r="B26" s="74"/>
-      <c r="C26" s="74"/>
-      <c r="D26" s="74"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="74"/>
-      <c r="H26" s="74"/>
-      <c r="I26" s="74"/>
-      <c r="J26" s="74"/>
+      <c r="A26" s="73"/>
+      <c r="B26" s="73"/>
+      <c r="C26" s="73"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="73"/>
+      <c r="G26" s="73"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73"/>
+      <c r="J26" s="73"/>
       <c r="K26" s="9"/>
-      <c r="L26" s="74"/>
-      <c r="M26" s="74"/>
+      <c r="L26" s="73"/>
+      <c r="M26" s="73"/>
       <c r="N26" s="9"/>
-      <c r="O26" s="74"/>
-      <c r="P26" s="74"/>
+      <c r="O26" s="73"/>
+      <c r="P26" s="73"/>
       <c r="Q26" s="9"/>
       <c r="R26" s="9"/>
       <c r="S26" s="9"/>
       <c r="T26" s="13"/>
-      <c r="U26" s="75"/>
-      <c r="V26" s="74"/>
-      <c r="W26" s="74"/>
-      <c r="X26" s="74"/>
-      <c r="Y26" s="74"/>
-      <c r="Z26" s="74"/>
-      <c r="AA26" s="74"/>
-      <c r="AB26" s="74"/>
-      <c r="AC26" s="74"/>
-      <c r="AD26" s="74"/>
-      <c r="AE26" s="74"/>
+      <c r="U26" s="76"/>
+      <c r="V26" s="73"/>
+      <c r="W26" s="73"/>
+      <c r="X26" s="73"/>
+      <c r="Y26" s="73"/>
+      <c r="Z26" s="73"/>
+      <c r="AA26" s="73"/>
+      <c r="AB26" s="73"/>
+      <c r="AC26" s="73"/>
+      <c r="AD26" s="73"/>
+      <c r="AE26" s="73"/>
       <c r="AF26" s="9"/>
-      <c r="AG26" s="74"/>
-      <c r="AH26" s="74"/>
+      <c r="AG26" s="73"/>
+      <c r="AH26" s="73"/>
       <c r="AI26" s="9"/>
-      <c r="AJ26" s="74"/>
-      <c r="AK26" s="74"/>
+      <c r="AJ26" s="73"/>
+      <c r="AK26" s="73"/>
       <c r="AL26" s="9"/>
       <c r="AM26" s="9"/>
       <c r="AN26" s="9"/>
@@ -6993,43 +6975,43 @@
       <c r="BI26" s="10"/>
     </row>
     <row r="27" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="74"/>
-      <c r="B27" s="74"/>
-      <c r="C27" s="74"/>
-      <c r="D27" s="74"/>
-      <c r="E27" s="74"/>
-      <c r="F27" s="74"/>
-      <c r="G27" s="74"/>
-      <c r="H27" s="74"/>
-      <c r="I27" s="74"/>
-      <c r="J27" s="74"/>
+      <c r="A27" s="73"/>
+      <c r="B27" s="73"/>
+      <c r="C27" s="73"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="73"/>
+      <c r="G27" s="73"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73"/>
+      <c r="J27" s="73"/>
       <c r="K27" s="9"/>
-      <c r="L27" s="74"/>
-      <c r="M27" s="74"/>
+      <c r="L27" s="73"/>
+      <c r="M27" s="73"/>
       <c r="N27" s="9"/>
-      <c r="O27" s="74"/>
-      <c r="P27" s="74"/>
+      <c r="O27" s="73"/>
+      <c r="P27" s="73"/>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="9"/>
       <c r="T27" s="13"/>
-      <c r="U27" s="75"/>
-      <c r="V27" s="74"/>
-      <c r="W27" s="74"/>
-      <c r="X27" s="74"/>
-      <c r="Y27" s="74"/>
-      <c r="Z27" s="74"/>
-      <c r="AA27" s="74"/>
-      <c r="AB27" s="74"/>
-      <c r="AC27" s="74"/>
-      <c r="AD27" s="74"/>
-      <c r="AE27" s="74"/>
+      <c r="U27" s="76"/>
+      <c r="V27" s="73"/>
+      <c r="W27" s="73"/>
+      <c r="X27" s="73"/>
+      <c r="Y27" s="73"/>
+      <c r="Z27" s="73"/>
+      <c r="AA27" s="73"/>
+      <c r="AB27" s="73"/>
+      <c r="AC27" s="73"/>
+      <c r="AD27" s="73"/>
+      <c r="AE27" s="73"/>
       <c r="AF27" s="9"/>
-      <c r="AG27" s="74"/>
-      <c r="AH27" s="74"/>
+      <c r="AG27" s="73"/>
+      <c r="AH27" s="73"/>
       <c r="AI27" s="9"/>
-      <c r="AJ27" s="74"/>
-      <c r="AK27" s="74"/>
+      <c r="AJ27" s="73"/>
+      <c r="AK27" s="73"/>
       <c r="AL27" s="9"/>
       <c r="AM27" s="9"/>
       <c r="AN27" s="9"/>
@@ -7056,43 +7038,43 @@
       <c r="BI27" s="10"/>
     </row>
     <row r="28" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="74"/>
-      <c r="B28" s="74"/>
-      <c r="C28" s="74"/>
-      <c r="D28" s="74"/>
-      <c r="E28" s="74"/>
-      <c r="F28" s="74"/>
-      <c r="G28" s="74"/>
-      <c r="H28" s="74"/>
-      <c r="I28" s="74"/>
-      <c r="J28" s="74"/>
+      <c r="A28" s="73"/>
+      <c r="B28" s="73"/>
+      <c r="C28" s="73"/>
+      <c r="D28" s="73"/>
+      <c r="E28" s="73"/>
+      <c r="F28" s="73"/>
+      <c r="G28" s="73"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73"/>
+      <c r="J28" s="73"/>
       <c r="K28" s="9"/>
-      <c r="L28" s="74"/>
-      <c r="M28" s="74"/>
+      <c r="L28" s="73"/>
+      <c r="M28" s="73"/>
       <c r="N28" s="9"/>
-      <c r="O28" s="74"/>
-      <c r="P28" s="74"/>
+      <c r="O28" s="73"/>
+      <c r="P28" s="73"/>
       <c r="Q28" s="9"/>
       <c r="R28" s="9"/>
       <c r="S28" s="9"/>
       <c r="T28" s="13"/>
-      <c r="U28" s="75"/>
-      <c r="V28" s="74"/>
-      <c r="W28" s="74"/>
-      <c r="X28" s="74"/>
-      <c r="Y28" s="74"/>
-      <c r="Z28" s="74"/>
-      <c r="AA28" s="74"/>
-      <c r="AB28" s="74"/>
-      <c r="AC28" s="74"/>
-      <c r="AD28" s="74"/>
-      <c r="AE28" s="74"/>
+      <c r="U28" s="76"/>
+      <c r="V28" s="73"/>
+      <c r="W28" s="73"/>
+      <c r="X28" s="73"/>
+      <c r="Y28" s="73"/>
+      <c r="Z28" s="73"/>
+      <c r="AA28" s="73"/>
+      <c r="AB28" s="73"/>
+      <c r="AC28" s="73"/>
+      <c r="AD28" s="73"/>
+      <c r="AE28" s="73"/>
       <c r="AF28" s="9"/>
-      <c r="AG28" s="74"/>
-      <c r="AH28" s="74"/>
+      <c r="AG28" s="73"/>
+      <c r="AH28" s="73"/>
       <c r="AI28" s="9"/>
-      <c r="AJ28" s="74"/>
-      <c r="AK28" s="74"/>
+      <c r="AJ28" s="73"/>
+      <c r="AK28" s="73"/>
       <c r="AL28" s="9"/>
       <c r="AM28" s="9"/>
       <c r="AN28" s="9"/>
@@ -7119,43 +7101,43 @@
       <c r="BI28" s="10"/>
     </row>
     <row r="29" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="74"/>
-      <c r="B29" s="74"/>
-      <c r="C29" s="74"/>
-      <c r="D29" s="74"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="74"/>
-      <c r="G29" s="74"/>
-      <c r="H29" s="74"/>
-      <c r="I29" s="74"/>
-      <c r="J29" s="74"/>
+      <c r="A29" s="73"/>
+      <c r="B29" s="73"/>
+      <c r="C29" s="73"/>
+      <c r="D29" s="73"/>
+      <c r="E29" s="73"/>
+      <c r="F29" s="73"/>
+      <c r="G29" s="73"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73"/>
+      <c r="J29" s="73"/>
       <c r="K29" s="9"/>
-      <c r="L29" s="74"/>
-      <c r="M29" s="74"/>
+      <c r="L29" s="73"/>
+      <c r="M29" s="73"/>
       <c r="N29" s="9"/>
-      <c r="O29" s="74"/>
-      <c r="P29" s="74"/>
+      <c r="O29" s="73"/>
+      <c r="P29" s="73"/>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="9"/>
       <c r="T29" s="13"/>
-      <c r="U29" s="75"/>
-      <c r="V29" s="74"/>
-      <c r="W29" s="74"/>
-      <c r="X29" s="74"/>
-      <c r="Y29" s="74"/>
-      <c r="Z29" s="74"/>
-      <c r="AA29" s="74"/>
-      <c r="AB29" s="74"/>
-      <c r="AC29" s="74"/>
-      <c r="AD29" s="74"/>
-      <c r="AE29" s="74"/>
+      <c r="U29" s="76"/>
+      <c r="V29" s="73"/>
+      <c r="W29" s="73"/>
+      <c r="X29" s="73"/>
+      <c r="Y29" s="73"/>
+      <c r="Z29" s="73"/>
+      <c r="AA29" s="73"/>
+      <c r="AB29" s="73"/>
+      <c r="AC29" s="73"/>
+      <c r="AD29" s="73"/>
+      <c r="AE29" s="73"/>
       <c r="AF29" s="9"/>
-      <c r="AG29" s="74"/>
-      <c r="AH29" s="74"/>
+      <c r="AG29" s="73"/>
+      <c r="AH29" s="73"/>
       <c r="AI29" s="9"/>
-      <c r="AJ29" s="74"/>
-      <c r="AK29" s="74"/>
+      <c r="AJ29" s="73"/>
+      <c r="AK29" s="73"/>
       <c r="AL29" s="9"/>
       <c r="AM29" s="9"/>
       <c r="AN29" s="9"/>
@@ -7182,43 +7164,43 @@
       <c r="BI29" s="10"/>
     </row>
     <row r="30" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="74"/>
-      <c r="B30" s="74"/>
-      <c r="C30" s="74"/>
-      <c r="D30" s="74"/>
-      <c r="E30" s="74"/>
-      <c r="F30" s="74"/>
-      <c r="G30" s="74"/>
-      <c r="H30" s="74"/>
-      <c r="I30" s="74"/>
-      <c r="J30" s="74"/>
+      <c r="A30" s="73"/>
+      <c r="B30" s="73"/>
+      <c r="C30" s="73"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="73"/>
+      <c r="F30" s="73"/>
+      <c r="G30" s="73"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73"/>
+      <c r="J30" s="73"/>
       <c r="K30" s="9"/>
-      <c r="L30" s="74"/>
-      <c r="M30" s="74"/>
+      <c r="L30" s="73"/>
+      <c r="M30" s="73"/>
       <c r="N30" s="9"/>
-      <c r="O30" s="74"/>
-      <c r="P30" s="74"/>
+      <c r="O30" s="73"/>
+      <c r="P30" s="73"/>
       <c r="Q30" s="9"/>
       <c r="R30" s="9"/>
       <c r="S30" s="9"/>
       <c r="T30" s="13"/>
-      <c r="U30" s="75"/>
-      <c r="V30" s="74"/>
-      <c r="W30" s="74"/>
-      <c r="X30" s="74"/>
-      <c r="Y30" s="74"/>
-      <c r="Z30" s="74"/>
-      <c r="AA30" s="74"/>
-      <c r="AB30" s="74"/>
-      <c r="AC30" s="74"/>
-      <c r="AD30" s="74"/>
-      <c r="AE30" s="74"/>
+      <c r="U30" s="76"/>
+      <c r="V30" s="73"/>
+      <c r="W30" s="73"/>
+      <c r="X30" s="73"/>
+      <c r="Y30" s="73"/>
+      <c r="Z30" s="73"/>
+      <c r="AA30" s="73"/>
+      <c r="AB30" s="73"/>
+      <c r="AC30" s="73"/>
+      <c r="AD30" s="73"/>
+      <c r="AE30" s="73"/>
       <c r="AF30" s="9"/>
-      <c r="AG30" s="74"/>
-      <c r="AH30" s="74"/>
+      <c r="AG30" s="73"/>
+      <c r="AH30" s="73"/>
       <c r="AI30" s="9"/>
-      <c r="AJ30" s="74"/>
-      <c r="AK30" s="74"/>
+      <c r="AJ30" s="73"/>
+      <c r="AK30" s="73"/>
       <c r="AL30" s="9"/>
       <c r="AM30" s="9"/>
       <c r="AN30" s="9"/>
@@ -7245,43 +7227,43 @@
       <c r="BI30" s="10"/>
     </row>
     <row r="31" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="74"/>
-      <c r="B31" s="74"/>
-      <c r="C31" s="74"/>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="74"/>
-      <c r="H31" s="74"/>
-      <c r="I31" s="74"/>
-      <c r="J31" s="74"/>
+      <c r="A31" s="73"/>
+      <c r="B31" s="73"/>
+      <c r="C31" s="73"/>
+      <c r="D31" s="73"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="73"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73"/>
+      <c r="J31" s="73"/>
       <c r="K31" s="9"/>
-      <c r="L31" s="74"/>
-      <c r="M31" s="74"/>
+      <c r="L31" s="73"/>
+      <c r="M31" s="73"/>
       <c r="N31" s="9"/>
-      <c r="O31" s="74"/>
-      <c r="P31" s="74"/>
+      <c r="O31" s="73"/>
+      <c r="P31" s="73"/>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
       <c r="S31" s="9"/>
       <c r="T31" s="13"/>
-      <c r="U31" s="75"/>
-      <c r="V31" s="74"/>
-      <c r="W31" s="74"/>
-      <c r="X31" s="74"/>
-      <c r="Y31" s="74"/>
-      <c r="Z31" s="74"/>
-      <c r="AA31" s="74"/>
-      <c r="AB31" s="74"/>
-      <c r="AC31" s="74"/>
-      <c r="AD31" s="74"/>
-      <c r="AE31" s="74"/>
+      <c r="U31" s="76"/>
+      <c r="V31" s="73"/>
+      <c r="W31" s="73"/>
+      <c r="X31" s="73"/>
+      <c r="Y31" s="73"/>
+      <c r="Z31" s="73"/>
+      <c r="AA31" s="73"/>
+      <c r="AB31" s="73"/>
+      <c r="AC31" s="73"/>
+      <c r="AD31" s="73"/>
+      <c r="AE31" s="73"/>
       <c r="AF31" s="9"/>
-      <c r="AG31" s="74"/>
-      <c r="AH31" s="74"/>
+      <c r="AG31" s="73"/>
+      <c r="AH31" s="73"/>
       <c r="AI31" s="9"/>
-      <c r="AJ31" s="74"/>
-      <c r="AK31" s="74"/>
+      <c r="AJ31" s="73"/>
+      <c r="AK31" s="73"/>
       <c r="AL31" s="9"/>
       <c r="AM31" s="9"/>
       <c r="AN31" s="9"/>
@@ -7308,43 +7290,43 @@
       <c r="BI31" s="10"/>
     </row>
     <row r="32" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="74"/>
-      <c r="B32" s="74"/>
-      <c r="C32" s="74"/>
-      <c r="D32" s="74"/>
-      <c r="E32" s="74"/>
-      <c r="F32" s="74"/>
-      <c r="G32" s="74"/>
-      <c r="H32" s="74"/>
-      <c r="I32" s="74"/>
-      <c r="J32" s="74"/>
+      <c r="A32" s="73"/>
+      <c r="B32" s="73"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="73"/>
+      <c r="E32" s="73"/>
+      <c r="F32" s="73"/>
+      <c r="G32" s="73"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73"/>
+      <c r="J32" s="73"/>
       <c r="K32" s="9"/>
-      <c r="L32" s="74"/>
-      <c r="M32" s="74"/>
+      <c r="L32" s="73"/>
+      <c r="M32" s="73"/>
       <c r="N32" s="9"/>
-      <c r="O32" s="74"/>
-      <c r="P32" s="74"/>
+      <c r="O32" s="73"/>
+      <c r="P32" s="73"/>
       <c r="Q32" s="9"/>
       <c r="R32" s="9"/>
       <c r="S32" s="9"/>
       <c r="T32" s="13"/>
-      <c r="U32" s="75"/>
-      <c r="V32" s="74"/>
-      <c r="W32" s="74"/>
-      <c r="X32" s="74"/>
-      <c r="Y32" s="74"/>
-      <c r="Z32" s="74"/>
-      <c r="AA32" s="74"/>
-      <c r="AB32" s="74"/>
-      <c r="AC32" s="74"/>
-      <c r="AD32" s="74"/>
-      <c r="AE32" s="74"/>
+      <c r="U32" s="76"/>
+      <c r="V32" s="73"/>
+      <c r="W32" s="73"/>
+      <c r="X32" s="73"/>
+      <c r="Y32" s="73"/>
+      <c r="Z32" s="73"/>
+      <c r="AA32" s="73"/>
+      <c r="AB32" s="73"/>
+      <c r="AC32" s="73"/>
+      <c r="AD32" s="73"/>
+      <c r="AE32" s="73"/>
       <c r="AF32" s="9"/>
-      <c r="AG32" s="74"/>
-      <c r="AH32" s="74"/>
+      <c r="AG32" s="73"/>
+      <c r="AH32" s="73"/>
       <c r="AI32" s="9"/>
-      <c r="AJ32" s="74"/>
-      <c r="AK32" s="74"/>
+      <c r="AJ32" s="73"/>
+      <c r="AK32" s="73"/>
       <c r="AL32" s="9"/>
       <c r="AM32" s="9"/>
       <c r="AN32" s="9"/>
@@ -7371,43 +7353,43 @@
       <c r="BI32" s="10"/>
     </row>
     <row r="33" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="74"/>
-      <c r="B33" s="74"/>
-      <c r="C33" s="74"/>
-      <c r="D33" s="74"/>
-      <c r="E33" s="74"/>
-      <c r="F33" s="74"/>
-      <c r="G33" s="74"/>
-      <c r="H33" s="74"/>
-      <c r="I33" s="74"/>
-      <c r="J33" s="74"/>
+      <c r="A33" s="73"/>
+      <c r="B33" s="73"/>
+      <c r="C33" s="73"/>
+      <c r="D33" s="73"/>
+      <c r="E33" s="73"/>
+      <c r="F33" s="73"/>
+      <c r="G33" s="73"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73"/>
+      <c r="J33" s="73"/>
       <c r="K33" s="9"/>
-      <c r="L33" s="74"/>
-      <c r="M33" s="74"/>
+      <c r="L33" s="73"/>
+      <c r="M33" s="73"/>
       <c r="N33" s="9"/>
-      <c r="O33" s="74"/>
-      <c r="P33" s="74"/>
+      <c r="O33" s="73"/>
+      <c r="P33" s="73"/>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="9"/>
       <c r="T33" s="13"/>
-      <c r="U33" s="75"/>
-      <c r="V33" s="74"/>
-      <c r="W33" s="74"/>
-      <c r="X33" s="74"/>
-      <c r="Y33" s="74"/>
-      <c r="Z33" s="74"/>
-      <c r="AA33" s="74"/>
-      <c r="AB33" s="74"/>
-      <c r="AC33" s="74"/>
-      <c r="AD33" s="74"/>
-      <c r="AE33" s="74"/>
+      <c r="U33" s="76"/>
+      <c r="V33" s="73"/>
+      <c r="W33" s="73"/>
+      <c r="X33" s="73"/>
+      <c r="Y33" s="73"/>
+      <c r="Z33" s="73"/>
+      <c r="AA33" s="73"/>
+      <c r="AB33" s="73"/>
+      <c r="AC33" s="73"/>
+      <c r="AD33" s="73"/>
+      <c r="AE33" s="73"/>
       <c r="AF33" s="9"/>
-      <c r="AG33" s="74"/>
-      <c r="AH33" s="74"/>
+      <c r="AG33" s="73"/>
+      <c r="AH33" s="73"/>
       <c r="AI33" s="9"/>
-      <c r="AJ33" s="74"/>
-      <c r="AK33" s="74"/>
+      <c r="AJ33" s="73"/>
+      <c r="AK33" s="73"/>
       <c r="AL33" s="9"/>
       <c r="AM33" s="9"/>
       <c r="AN33" s="9"/>
@@ -7434,43 +7416,43 @@
       <c r="BI33" s="10"/>
     </row>
     <row r="34" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="74"/>
-      <c r="B34" s="74"/>
-      <c r="C34" s="74"/>
-      <c r="D34" s="74"/>
-      <c r="E34" s="74"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="74"/>
-      <c r="H34" s="74"/>
-      <c r="I34" s="74"/>
-      <c r="J34" s="74"/>
+      <c r="A34" s="73"/>
+      <c r="B34" s="73"/>
+      <c r="C34" s="73"/>
+      <c r="D34" s="73"/>
+      <c r="E34" s="73"/>
+      <c r="F34" s="73"/>
+      <c r="G34" s="73"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73"/>
+      <c r="J34" s="73"/>
       <c r="K34" s="9"/>
-      <c r="L34" s="74"/>
-      <c r="M34" s="74"/>
+      <c r="L34" s="73"/>
+      <c r="M34" s="73"/>
       <c r="N34" s="9"/>
-      <c r="O34" s="74"/>
-      <c r="P34" s="74"/>
+      <c r="O34" s="73"/>
+      <c r="P34" s="73"/>
       <c r="Q34" s="9"/>
       <c r="R34" s="9"/>
       <c r="S34" s="9"/>
       <c r="T34" s="13"/>
-      <c r="U34" s="75"/>
-      <c r="V34" s="74"/>
-      <c r="W34" s="74"/>
-      <c r="X34" s="74"/>
-      <c r="Y34" s="74"/>
-      <c r="Z34" s="74"/>
-      <c r="AA34" s="74"/>
-      <c r="AB34" s="74"/>
-      <c r="AC34" s="74"/>
-      <c r="AD34" s="74"/>
-      <c r="AE34" s="74"/>
+      <c r="U34" s="76"/>
+      <c r="V34" s="73"/>
+      <c r="W34" s="73"/>
+      <c r="X34" s="73"/>
+      <c r="Y34" s="73"/>
+      <c r="Z34" s="73"/>
+      <c r="AA34" s="73"/>
+      <c r="AB34" s="73"/>
+      <c r="AC34" s="73"/>
+      <c r="AD34" s="73"/>
+      <c r="AE34" s="73"/>
       <c r="AF34" s="9"/>
-      <c r="AG34" s="74"/>
-      <c r="AH34" s="74"/>
+      <c r="AG34" s="73"/>
+      <c r="AH34" s="73"/>
       <c r="AI34" s="9"/>
-      <c r="AJ34" s="74"/>
-      <c r="AK34" s="74"/>
+      <c r="AJ34" s="73"/>
+      <c r="AK34" s="73"/>
       <c r="AL34" s="9"/>
       <c r="AM34" s="9"/>
       <c r="AN34" s="9"/>
@@ -7497,43 +7479,43 @@
       <c r="BI34" s="10"/>
     </row>
     <row r="35" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="74"/>
-      <c r="B35" s="74"/>
-      <c r="C35" s="74"/>
-      <c r="D35" s="74"/>
-      <c r="E35" s="74"/>
-      <c r="F35" s="74"/>
-      <c r="G35" s="74"/>
-      <c r="H35" s="74"/>
-      <c r="I35" s="74"/>
-      <c r="J35" s="74"/>
+      <c r="A35" s="73"/>
+      <c r="B35" s="73"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="73"/>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73"/>
+      <c r="J35" s="73"/>
       <c r="K35" s="9"/>
-      <c r="L35" s="74"/>
-      <c r="M35" s="74"/>
+      <c r="L35" s="73"/>
+      <c r="M35" s="73"/>
       <c r="N35" s="9"/>
-      <c r="O35" s="74"/>
-      <c r="P35" s="74"/>
+      <c r="O35" s="73"/>
+      <c r="P35" s="73"/>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
       <c r="S35" s="9"/>
       <c r="T35" s="13"/>
-      <c r="U35" s="75"/>
-      <c r="V35" s="74"/>
-      <c r="W35" s="74"/>
-      <c r="X35" s="74"/>
-      <c r="Y35" s="74"/>
-      <c r="Z35" s="74"/>
-      <c r="AA35" s="74"/>
-      <c r="AB35" s="74"/>
-      <c r="AC35" s="74"/>
-      <c r="AD35" s="74"/>
-      <c r="AE35" s="74"/>
+      <c r="U35" s="76"/>
+      <c r="V35" s="73"/>
+      <c r="W35" s="73"/>
+      <c r="X35" s="73"/>
+      <c r="Y35" s="73"/>
+      <c r="Z35" s="73"/>
+      <c r="AA35" s="73"/>
+      <c r="AB35" s="73"/>
+      <c r="AC35" s="73"/>
+      <c r="AD35" s="73"/>
+      <c r="AE35" s="73"/>
       <c r="AF35" s="9"/>
-      <c r="AG35" s="74"/>
-      <c r="AH35" s="74"/>
+      <c r="AG35" s="73"/>
+      <c r="AH35" s="73"/>
       <c r="AI35" s="9"/>
-      <c r="AJ35" s="74"/>
-      <c r="AK35" s="74"/>
+      <c r="AJ35" s="73"/>
+      <c r="AK35" s="73"/>
       <c r="AL35" s="9"/>
       <c r="AM35" s="9"/>
       <c r="AN35" s="9"/>
@@ -7560,43 +7542,43 @@
       <c r="BI35" s="10"/>
     </row>
     <row r="36" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="74"/>
-      <c r="B36" s="74"/>
-      <c r="C36" s="74"/>
-      <c r="D36" s="74"/>
-      <c r="E36" s="74"/>
-      <c r="F36" s="74"/>
-      <c r="G36" s="74"/>
-      <c r="H36" s="74"/>
-      <c r="I36" s="74"/>
-      <c r="J36" s="74"/>
+      <c r="A36" s="73"/>
+      <c r="B36" s="73"/>
+      <c r="C36" s="73"/>
+      <c r="D36" s="73"/>
+      <c r="E36" s="73"/>
+      <c r="F36" s="73"/>
+      <c r="G36" s="73"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73"/>
+      <c r="J36" s="73"/>
       <c r="K36" s="9"/>
-      <c r="L36" s="74"/>
-      <c r="M36" s="74"/>
+      <c r="L36" s="73"/>
+      <c r="M36" s="73"/>
       <c r="N36" s="9"/>
-      <c r="O36" s="74"/>
-      <c r="P36" s="74"/>
+      <c r="O36" s="73"/>
+      <c r="P36" s="73"/>
       <c r="Q36" s="9"/>
       <c r="R36" s="9"/>
       <c r="S36" s="9"/>
       <c r="T36" s="13"/>
-      <c r="U36" s="75"/>
-      <c r="V36" s="74"/>
-      <c r="W36" s="74"/>
-      <c r="X36" s="74"/>
-      <c r="Y36" s="74"/>
-      <c r="Z36" s="74"/>
-      <c r="AA36" s="74"/>
-      <c r="AB36" s="74"/>
-      <c r="AC36" s="74"/>
-      <c r="AD36" s="74"/>
-      <c r="AE36" s="74"/>
+      <c r="U36" s="76"/>
+      <c r="V36" s="73"/>
+      <c r="W36" s="73"/>
+      <c r="X36" s="73"/>
+      <c r="Y36" s="73"/>
+      <c r="Z36" s="73"/>
+      <c r="AA36" s="73"/>
+      <c r="AB36" s="73"/>
+      <c r="AC36" s="73"/>
+      <c r="AD36" s="73"/>
+      <c r="AE36" s="73"/>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="74"/>
-      <c r="AH36" s="74"/>
+      <c r="AG36" s="73"/>
+      <c r="AH36" s="73"/>
       <c r="AI36" s="9"/>
-      <c r="AJ36" s="74"/>
-      <c r="AK36" s="74"/>
+      <c r="AJ36" s="73"/>
+      <c r="AK36" s="73"/>
       <c r="AL36" s="9"/>
       <c r="AM36" s="9"/>
       <c r="AN36" s="9"/>
@@ -7623,43 +7605,43 @@
       <c r="BI36" s="10"/>
     </row>
     <row r="37" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="74"/>
-      <c r="B37" s="74"/>
-      <c r="C37" s="74"/>
-      <c r="D37" s="74"/>
-      <c r="E37" s="74"/>
-      <c r="F37" s="74"/>
-      <c r="G37" s="74"/>
-      <c r="H37" s="74"/>
-      <c r="I37" s="74"/>
-      <c r="J37" s="74"/>
+      <c r="A37" s="73"/>
+      <c r="B37" s="73"/>
+      <c r="C37" s="73"/>
+      <c r="D37" s="73"/>
+      <c r="E37" s="73"/>
+      <c r="F37" s="73"/>
+      <c r="G37" s="73"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73"/>
+      <c r="J37" s="73"/>
       <c r="K37" s="9"/>
-      <c r="L37" s="74"/>
-      <c r="M37" s="74"/>
+      <c r="L37" s="73"/>
+      <c r="M37" s="73"/>
       <c r="N37" s="9"/>
-      <c r="O37" s="74"/>
-      <c r="P37" s="74"/>
+      <c r="O37" s="73"/>
+      <c r="P37" s="73"/>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="9"/>
       <c r="T37" s="13"/>
-      <c r="U37" s="75"/>
-      <c r="V37" s="74"/>
-      <c r="W37" s="74"/>
-      <c r="X37" s="74"/>
-      <c r="Y37" s="74"/>
-      <c r="Z37" s="74"/>
-      <c r="AA37" s="74"/>
-      <c r="AB37" s="74"/>
-      <c r="AC37" s="74"/>
-      <c r="AD37" s="74"/>
-      <c r="AE37" s="74"/>
+      <c r="U37" s="76"/>
+      <c r="V37" s="73"/>
+      <c r="W37" s="73"/>
+      <c r="X37" s="73"/>
+      <c r="Y37" s="73"/>
+      <c r="Z37" s="73"/>
+      <c r="AA37" s="73"/>
+      <c r="AB37" s="73"/>
+      <c r="AC37" s="73"/>
+      <c r="AD37" s="73"/>
+      <c r="AE37" s="73"/>
       <c r="AF37" s="9"/>
-      <c r="AG37" s="74"/>
-      <c r="AH37" s="74"/>
+      <c r="AG37" s="73"/>
+      <c r="AH37" s="73"/>
       <c r="AI37" s="9"/>
-      <c r="AJ37" s="74"/>
-      <c r="AK37" s="74"/>
+      <c r="AJ37" s="73"/>
+      <c r="AK37" s="73"/>
       <c r="AL37" s="9"/>
       <c r="AM37" s="9"/>
       <c r="AN37" s="9"/>
@@ -7686,43 +7668,43 @@
       <c r="BI37" s="10"/>
     </row>
     <row r="38" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="74"/>
-      <c r="B38" s="74"/>
-      <c r="C38" s="74"/>
-      <c r="D38" s="74"/>
-      <c r="E38" s="74"/>
-      <c r="F38" s="74"/>
-      <c r="G38" s="74"/>
-      <c r="H38" s="74"/>
-      <c r="I38" s="74"/>
-      <c r="J38" s="74"/>
+      <c r="A38" s="73"/>
+      <c r="B38" s="73"/>
+      <c r="C38" s="73"/>
+      <c r="D38" s="73"/>
+      <c r="E38" s="73"/>
+      <c r="F38" s="73"/>
+      <c r="G38" s="73"/>
+      <c r="H38" s="73"/>
+      <c r="I38" s="73"/>
+      <c r="J38" s="73"/>
       <c r="K38" s="9"/>
-      <c r="L38" s="74"/>
-      <c r="M38" s="74"/>
+      <c r="L38" s="73"/>
+      <c r="M38" s="73"/>
       <c r="N38" s="9"/>
-      <c r="O38" s="74"/>
-      <c r="P38" s="74"/>
+      <c r="O38" s="73"/>
+      <c r="P38" s="73"/>
       <c r="Q38" s="9"/>
       <c r="R38" s="9"/>
       <c r="S38" s="9"/>
       <c r="T38" s="13"/>
-      <c r="U38" s="75"/>
-      <c r="V38" s="74"/>
-      <c r="W38" s="74"/>
-      <c r="X38" s="74"/>
-      <c r="Y38" s="74"/>
-      <c r="Z38" s="74"/>
-      <c r="AA38" s="74"/>
-      <c r="AB38" s="74"/>
-      <c r="AC38" s="74"/>
-      <c r="AD38" s="74"/>
-      <c r="AE38" s="74"/>
+      <c r="U38" s="76"/>
+      <c r="V38" s="73"/>
+      <c r="W38" s="73"/>
+      <c r="X38" s="73"/>
+      <c r="Y38" s="73"/>
+      <c r="Z38" s="73"/>
+      <c r="AA38" s="73"/>
+      <c r="AB38" s="73"/>
+      <c r="AC38" s="73"/>
+      <c r="AD38" s="73"/>
+      <c r="AE38" s="73"/>
       <c r="AF38" s="9"/>
-      <c r="AG38" s="74"/>
-      <c r="AH38" s="74"/>
+      <c r="AG38" s="73"/>
+      <c r="AH38" s="73"/>
       <c r="AI38" s="9"/>
-      <c r="AJ38" s="74"/>
-      <c r="AK38" s="74"/>
+      <c r="AJ38" s="73"/>
+      <c r="AK38" s="73"/>
       <c r="AL38" s="9"/>
       <c r="AM38" s="9"/>
       <c r="AN38" s="9"/>
@@ -7749,43 +7731,43 @@
       <c r="BI38" s="10"/>
     </row>
     <row r="39" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="74"/>
-      <c r="B39" s="74"/>
-      <c r="C39" s="74"/>
-      <c r="D39" s="74"/>
-      <c r="E39" s="74"/>
-      <c r="F39" s="74"/>
-      <c r="G39" s="74"/>
-      <c r="H39" s="74"/>
-      <c r="I39" s="74"/>
-      <c r="J39" s="74"/>
+      <c r="A39" s="73"/>
+      <c r="B39" s="73"/>
+      <c r="C39" s="73"/>
+      <c r="D39" s="73"/>
+      <c r="E39" s="73"/>
+      <c r="F39" s="73"/>
+      <c r="G39" s="73"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="73"/>
+      <c r="J39" s="73"/>
       <c r="K39" s="9"/>
-      <c r="L39" s="74"/>
-      <c r="M39" s="74"/>
+      <c r="L39" s="73"/>
+      <c r="M39" s="73"/>
       <c r="N39" s="9"/>
-      <c r="O39" s="74"/>
-      <c r="P39" s="74"/>
+      <c r="O39" s="73"/>
+      <c r="P39" s="73"/>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
       <c r="S39" s="9"/>
       <c r="T39" s="13"/>
-      <c r="U39" s="75"/>
-      <c r="V39" s="74"/>
-      <c r="W39" s="74"/>
-      <c r="X39" s="74"/>
-      <c r="Y39" s="74"/>
-      <c r="Z39" s="74"/>
-      <c r="AA39" s="74"/>
-      <c r="AB39" s="74"/>
-      <c r="AC39" s="74"/>
-      <c r="AD39" s="74"/>
-      <c r="AE39" s="74"/>
+      <c r="U39" s="76"/>
+      <c r="V39" s="73"/>
+      <c r="W39" s="73"/>
+      <c r="X39" s="73"/>
+      <c r="Y39" s="73"/>
+      <c r="Z39" s="73"/>
+      <c r="AA39" s="73"/>
+      <c r="AB39" s="73"/>
+      <c r="AC39" s="73"/>
+      <c r="AD39" s="73"/>
+      <c r="AE39" s="73"/>
       <c r="AF39" s="9"/>
-      <c r="AG39" s="74"/>
-      <c r="AH39" s="74"/>
+      <c r="AG39" s="73"/>
+      <c r="AH39" s="73"/>
       <c r="AI39" s="9"/>
-      <c r="AJ39" s="74"/>
-      <c r="AK39" s="74"/>
+      <c r="AJ39" s="73"/>
+      <c r="AK39" s="73"/>
       <c r="AL39" s="9"/>
       <c r="AM39" s="9"/>
       <c r="AN39" s="9"/>
@@ -7812,43 +7794,43 @@
       <c r="BI39" s="10"/>
     </row>
     <row r="40" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="74"/>
-      <c r="B40" s="74"/>
-      <c r="C40" s="74"/>
-      <c r="D40" s="74"/>
-      <c r="E40" s="74"/>
-      <c r="F40" s="74"/>
-      <c r="G40" s="74"/>
-      <c r="H40" s="74"/>
-      <c r="I40" s="74"/>
-      <c r="J40" s="74"/>
+      <c r="A40" s="73"/>
+      <c r="B40" s="73"/>
+      <c r="C40" s="73"/>
+      <c r="D40" s="73"/>
+      <c r="E40" s="73"/>
+      <c r="F40" s="73"/>
+      <c r="G40" s="73"/>
+      <c r="H40" s="73"/>
+      <c r="I40" s="73"/>
+      <c r="J40" s="73"/>
       <c r="K40" s="9"/>
-      <c r="L40" s="74"/>
-      <c r="M40" s="74"/>
+      <c r="L40" s="73"/>
+      <c r="M40" s="73"/>
       <c r="N40" s="9"/>
-      <c r="O40" s="74"/>
-      <c r="P40" s="74"/>
+      <c r="O40" s="73"/>
+      <c r="P40" s="73"/>
       <c r="Q40" s="9"/>
       <c r="R40" s="9"/>
       <c r="S40" s="9"/>
       <c r="T40" s="13"/>
-      <c r="U40" s="75"/>
-      <c r="V40" s="74"/>
-      <c r="W40" s="74"/>
-      <c r="X40" s="74"/>
-      <c r="Y40" s="74"/>
-      <c r="Z40" s="74"/>
-      <c r="AA40" s="74"/>
-      <c r="AB40" s="74"/>
-      <c r="AC40" s="74"/>
-      <c r="AD40" s="74"/>
-      <c r="AE40" s="74"/>
+      <c r="U40" s="76"/>
+      <c r="V40" s="73"/>
+      <c r="W40" s="73"/>
+      <c r="X40" s="73"/>
+      <c r="Y40" s="73"/>
+      <c r="Z40" s="73"/>
+      <c r="AA40" s="73"/>
+      <c r="AB40" s="73"/>
+      <c r="AC40" s="73"/>
+      <c r="AD40" s="73"/>
+      <c r="AE40" s="73"/>
       <c r="AF40" s="9"/>
-      <c r="AG40" s="74"/>
-      <c r="AH40" s="74"/>
+      <c r="AG40" s="73"/>
+      <c r="AH40" s="73"/>
       <c r="AI40" s="9"/>
-      <c r="AJ40" s="74"/>
-      <c r="AK40" s="74"/>
+      <c r="AJ40" s="73"/>
+      <c r="AK40" s="73"/>
       <c r="AL40" s="9"/>
       <c r="AM40" s="9"/>
       <c r="AN40" s="9"/>
@@ -8983,9 +8965,9 @@
       <c r="AI66" s="6"/>
       <c r="AJ66" s="6"/>
       <c r="AK66" s="6"/>
-      <c r="AL66" s="16"/>
-      <c r="AM66" s="16"/>
-      <c r="AN66" s="16"/>
+      <c r="AL66" s="66"/>
+      <c r="AM66" s="66"/>
+      <c r="AN66" s="66"/>
     </row>
     <row r="67" spans="1:41" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4"/>
@@ -9161,22 +9143,173 @@
     </row>
   </sheetData>
   <mergeCells count="207">
-    <mergeCell ref="AJ38:AK38"/>
-    <mergeCell ref="AJ39:AK39"/>
-    <mergeCell ref="AJ40:AK40"/>
-    <mergeCell ref="AP11:BA11"/>
-    <mergeCell ref="BC11:BI11"/>
-    <mergeCell ref="AJ33:AK33"/>
-    <mergeCell ref="AJ34:AK34"/>
-    <mergeCell ref="AJ35:AK35"/>
-    <mergeCell ref="AJ36:AK36"/>
-    <mergeCell ref="AJ37:AK37"/>
-    <mergeCell ref="AJ28:AK28"/>
-    <mergeCell ref="AJ29:AK29"/>
-    <mergeCell ref="AJ30:AK30"/>
-    <mergeCell ref="AJ31:AK31"/>
-    <mergeCell ref="AJ32:AK32"/>
-    <mergeCell ref="AJ12:AK12"/>
+    <mergeCell ref="AY1:BI1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="K1:V1"/>
+    <mergeCell ref="W1:AH1"/>
+    <mergeCell ref="AI1:AM1"/>
+    <mergeCell ref="AN1:AR1"/>
+    <mergeCell ref="AL66:AN66"/>
+    <mergeCell ref="AI4:AR6"/>
+    <mergeCell ref="F5:J6"/>
+    <mergeCell ref="K5:O6"/>
+    <mergeCell ref="P5:T6"/>
+    <mergeCell ref="U5:AH6"/>
+    <mergeCell ref="AY2:BI4"/>
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="K4:O4"/>
+    <mergeCell ref="P4:T4"/>
+    <mergeCell ref="U4:AH4"/>
+    <mergeCell ref="F2:J3"/>
+    <mergeCell ref="K2:V3"/>
+    <mergeCell ref="W2:AH3"/>
+    <mergeCell ref="AI2:AM3"/>
+    <mergeCell ref="AN2:AR3"/>
+    <mergeCell ref="A9:T9"/>
+    <mergeCell ref="U9:AO9"/>
+    <mergeCell ref="AP9:BI9"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="AJ11:AK11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="AG11:AH11"/>
+    <mergeCell ref="U11:AE11"/>
+    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="AG12:AH12"/>
+    <mergeCell ref="U13:AE13"/>
+    <mergeCell ref="U14:AE14"/>
+    <mergeCell ref="U15:AE15"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="U12:AE12"/>
+    <mergeCell ref="U16:AE16"/>
+    <mergeCell ref="U17:AE17"/>
+    <mergeCell ref="U18:AE18"/>
+    <mergeCell ref="U19:AE19"/>
+    <mergeCell ref="U20:AE20"/>
+    <mergeCell ref="U21:AE21"/>
+    <mergeCell ref="U22:AE22"/>
+    <mergeCell ref="U23:AE23"/>
+    <mergeCell ref="U24:AE24"/>
+    <mergeCell ref="U25:AE25"/>
+    <mergeCell ref="U26:AE26"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="U39:AE39"/>
+    <mergeCell ref="U40:AE40"/>
+    <mergeCell ref="AG13:AH13"/>
+    <mergeCell ref="AG14:AH14"/>
+    <mergeCell ref="AG15:AH15"/>
+    <mergeCell ref="AG16:AH16"/>
+    <mergeCell ref="AG17:AH17"/>
+    <mergeCell ref="AG18:AH18"/>
+    <mergeCell ref="AG19:AH19"/>
+    <mergeCell ref="AG20:AH20"/>
+    <mergeCell ref="AG21:AH21"/>
+    <mergeCell ref="AG22:AH22"/>
+    <mergeCell ref="AG23:AH23"/>
+    <mergeCell ref="AG24:AH24"/>
+    <mergeCell ref="U32:AE32"/>
+    <mergeCell ref="U33:AE33"/>
+    <mergeCell ref="U34:AE34"/>
+    <mergeCell ref="U35:AE35"/>
+    <mergeCell ref="U36:AE36"/>
+    <mergeCell ref="U27:AE27"/>
+    <mergeCell ref="U28:AE28"/>
+    <mergeCell ref="U29:AE29"/>
+    <mergeCell ref="U30:AE30"/>
+    <mergeCell ref="U31:AE31"/>
+    <mergeCell ref="AG33:AH33"/>
+    <mergeCell ref="AG34:AH34"/>
+    <mergeCell ref="AG25:AH25"/>
+    <mergeCell ref="AG26:AH26"/>
+    <mergeCell ref="AG27:AH27"/>
+    <mergeCell ref="AG28:AH28"/>
+    <mergeCell ref="AG29:AH29"/>
+    <mergeCell ref="U37:AE37"/>
+    <mergeCell ref="U38:AE38"/>
     <mergeCell ref="AG40:AH40"/>
     <mergeCell ref="AJ13:AK13"/>
     <mergeCell ref="AJ14:AK14"/>
@@ -9201,173 +9334,22 @@
     <mergeCell ref="AG30:AH30"/>
     <mergeCell ref="AG31:AH31"/>
     <mergeCell ref="AG32:AH32"/>
-    <mergeCell ref="AG33:AH33"/>
-    <mergeCell ref="AG34:AH34"/>
-    <mergeCell ref="AG25:AH25"/>
-    <mergeCell ref="AG26:AH26"/>
-    <mergeCell ref="AG27:AH27"/>
-    <mergeCell ref="AG28:AH28"/>
-    <mergeCell ref="AG29:AH29"/>
-    <mergeCell ref="U37:AE37"/>
-    <mergeCell ref="U38:AE38"/>
-    <mergeCell ref="U39:AE39"/>
-    <mergeCell ref="U40:AE40"/>
-    <mergeCell ref="AG13:AH13"/>
-    <mergeCell ref="AG14:AH14"/>
-    <mergeCell ref="AG15:AH15"/>
-    <mergeCell ref="AG16:AH16"/>
-    <mergeCell ref="AG17:AH17"/>
-    <mergeCell ref="AG18:AH18"/>
-    <mergeCell ref="AG19:AH19"/>
-    <mergeCell ref="AG20:AH20"/>
-    <mergeCell ref="AG21:AH21"/>
-    <mergeCell ref="AG22:AH22"/>
-    <mergeCell ref="AG23:AH23"/>
-    <mergeCell ref="AG24:AH24"/>
-    <mergeCell ref="U32:AE32"/>
-    <mergeCell ref="U33:AE33"/>
-    <mergeCell ref="U34:AE34"/>
-    <mergeCell ref="U35:AE35"/>
-    <mergeCell ref="U36:AE36"/>
-    <mergeCell ref="U27:AE27"/>
-    <mergeCell ref="U28:AE28"/>
-    <mergeCell ref="U29:AE29"/>
-    <mergeCell ref="U30:AE30"/>
-    <mergeCell ref="U31:AE31"/>
-    <mergeCell ref="AG12:AH12"/>
-    <mergeCell ref="U13:AE13"/>
-    <mergeCell ref="U14:AE14"/>
-    <mergeCell ref="U15:AE15"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="U12:AE12"/>
-    <mergeCell ref="U16:AE16"/>
-    <mergeCell ref="U17:AE17"/>
-    <mergeCell ref="U18:AE18"/>
-    <mergeCell ref="U19:AE19"/>
-    <mergeCell ref="U20:AE20"/>
-    <mergeCell ref="U21:AE21"/>
-    <mergeCell ref="U22:AE22"/>
-    <mergeCell ref="U23:AE23"/>
-    <mergeCell ref="U24:AE24"/>
-    <mergeCell ref="U25:AE25"/>
-    <mergeCell ref="U26:AE26"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="A33:J33"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A35:J35"/>
-    <mergeCell ref="A36:J36"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A38:J38"/>
-    <mergeCell ref="A39:J39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="AP9:BI9"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="A12:J12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="AJ11:AK11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="AG11:AH11"/>
-    <mergeCell ref="U11:AE11"/>
-    <mergeCell ref="A15:J15"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="AY1:BI1"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="K1:V1"/>
-    <mergeCell ref="W1:AH1"/>
-    <mergeCell ref="AI1:AM1"/>
-    <mergeCell ref="AN1:AR1"/>
-    <mergeCell ref="AL66:AN66"/>
-    <mergeCell ref="AI4:AR6"/>
-    <mergeCell ref="F5:J6"/>
-    <mergeCell ref="K5:O6"/>
-    <mergeCell ref="P5:T6"/>
-    <mergeCell ref="U5:AH6"/>
-    <mergeCell ref="AY2:BI4"/>
-    <mergeCell ref="F4:J4"/>
-    <mergeCell ref="K4:O4"/>
-    <mergeCell ref="P4:T4"/>
-    <mergeCell ref="U4:AH4"/>
-    <mergeCell ref="F2:J3"/>
-    <mergeCell ref="K2:V3"/>
-    <mergeCell ref="W2:AH3"/>
-    <mergeCell ref="AI2:AM3"/>
-    <mergeCell ref="AN2:AR3"/>
-    <mergeCell ref="A9:T9"/>
-    <mergeCell ref="U9:AO9"/>
+    <mergeCell ref="AJ38:AK38"/>
+    <mergeCell ref="AJ39:AK39"/>
+    <mergeCell ref="AJ40:AK40"/>
+    <mergeCell ref="AP11:BA11"/>
+    <mergeCell ref="BC11:BI11"/>
+    <mergeCell ref="AJ33:AK33"/>
+    <mergeCell ref="AJ34:AK34"/>
+    <mergeCell ref="AJ35:AK35"/>
+    <mergeCell ref="AJ36:AK36"/>
+    <mergeCell ref="AJ37:AK37"/>
+    <mergeCell ref="AJ28:AK28"/>
+    <mergeCell ref="AJ29:AK29"/>
+    <mergeCell ref="AJ30:AK30"/>
+    <mergeCell ref="AJ31:AK31"/>
+    <mergeCell ref="AJ32:AK32"/>
+    <mergeCell ref="AJ12:AK12"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -9378,14 +9360,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="bdc2d3d5-fc31-4d65-8e89-042f9aabae79" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="13b50d63-4097-4260-987b-0df3cda3515c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9590,21 +9570,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="bdc2d3d5-fc31-4d65-8e89-042f9aabae79" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="13b50d63-4097-4260-987b-0df3cda3515c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA865533-0B77-4147-AA92-F0C2FDB2E315}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED9081D4-7DA8-4E8C-9299-427A52260533}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bdc2d3d5-fc31-4d65-8e89-042f9aabae79"/>
-    <ds:schemaRef ds:uri="13b50d63-4097-4260-987b-0df3cda3515c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9629,9 +9608,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED9081D4-7DA8-4E8C-9299-427A52260533}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA865533-0B77-4147-AA92-F0C2FDB2E315}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bdc2d3d5-fc31-4d65-8e89-042f9aabae79"/>
+    <ds:schemaRef ds:uri="13b50d63-4097-4260-987b-0df3cda3515c"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/template_produzione.xlsx
+++ b/template_produzione.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maxporte.sharepoint.com/sites/MPCloud/Documenti condivisi/MPX/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="673" documentId="8_{CC15ACFE-ED8D-4D36-8DB1-DE3148A82591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE974878-0D3C-4D22-B7F8-0D1607D337C3}"/>
+  <xr:revisionPtr revIDLastSave="674" documentId="8_{CC15ACFE-ED8D-4D36-8DB1-DE3148A82591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC1D2BCB-B6C7-459A-8AD0-3EB0A19A9C25}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21820" activeTab="1" xr2:uid="{2F1D62B1-3FD5-4D97-A455-0CD2ABF42920}"/>
   </bookViews>
@@ -584,7 +584,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -620,42 +620,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -666,23 +632,35 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
@@ -720,42 +698,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -774,17 +716,61 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -794,8 +780,18 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
@@ -806,11 +802,26 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1161,74 +1172,74 @@
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="32" t="s">
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="32" t="s">
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="33"/>
-      <c r="AA1" s="33"/>
-      <c r="AB1" s="33"/>
-      <c r="AC1" s="33"/>
-      <c r="AD1" s="33"/>
-      <c r="AE1" s="33"/>
-      <c r="AF1" s="33"/>
-      <c r="AG1" s="33"/>
-      <c r="AH1" s="34"/>
-      <c r="AI1" s="32" t="s">
+      <c r="X1" s="17"/>
+      <c r="Y1" s="17"/>
+      <c r="Z1" s="17"/>
+      <c r="AA1" s="17"/>
+      <c r="AB1" s="17"/>
+      <c r="AC1" s="17"/>
+      <c r="AD1" s="17"/>
+      <c r="AE1" s="17"/>
+      <c r="AF1" s="17"/>
+      <c r="AG1" s="17"/>
+      <c r="AH1" s="18"/>
+      <c r="AI1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="AJ1" s="33"/>
-      <c r="AK1" s="33"/>
-      <c r="AL1" s="33"/>
-      <c r="AM1" s="34"/>
-      <c r="AN1" s="32" t="s">
+      <c r="AJ1" s="17"/>
+      <c r="AK1" s="17"/>
+      <c r="AL1" s="17"/>
+      <c r="AM1" s="18"/>
+      <c r="AN1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="AO1" s="33"/>
-      <c r="AP1" s="33"/>
-      <c r="AQ1" s="33"/>
-      <c r="AR1" s="34"/>
+      <c r="AO1" s="17"/>
+      <c r="AP1" s="17"/>
+      <c r="AQ1" s="17"/>
+      <c r="AR1" s="18"/>
       <c r="AS1" s="7"/>
       <c r="AT1" s="7"/>
       <c r="AU1" s="7"/>
       <c r="AV1" s="7"/>
       <c r="AW1" s="7"/>
       <c r="AX1" s="7"/>
-      <c r="AY1" s="29" t="s">
+      <c r="AY1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="AZ1" s="29"/>
-      <c r="BA1" s="29"/>
-      <c r="BB1" s="29"/>
-      <c r="BC1" s="29"/>
-      <c r="BD1" s="29"/>
-      <c r="BE1" s="29"/>
-      <c r="BF1" s="29"/>
-      <c r="BG1" s="29"/>
-      <c r="BH1" s="29"/>
-      <c r="BI1" s="29"/>
+      <c r="AZ1" s="15"/>
+      <c r="BA1" s="15"/>
+      <c r="BB1" s="15"/>
+      <c r="BC1" s="15"/>
+      <c r="BD1" s="15"/>
+      <c r="BE1" s="15"/>
+      <c r="BF1" s="15"/>
+      <c r="BG1" s="15"/>
+      <c r="BH1" s="15"/>
+      <c r="BI1" s="15"/>
     </row>
     <row r="2" spans="1:62" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
@@ -1236,68 +1247,68 @@
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="41" t="s">
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
-      <c r="T2" s="42"/>
-      <c r="U2" s="42"/>
-      <c r="V2" s="43"/>
-      <c r="W2" s="41" t="s">
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="X2" s="42"/>
-      <c r="Y2" s="42"/>
-      <c r="Z2" s="42"/>
-      <c r="AA2" s="42"/>
-      <c r="AB2" s="42"/>
-      <c r="AC2" s="42"/>
-      <c r="AD2" s="42"/>
-      <c r="AE2" s="42"/>
-      <c r="AF2" s="42"/>
-      <c r="AG2" s="42"/>
-      <c r="AH2" s="43"/>
-      <c r="AI2" s="47" t="s">
+      <c r="X2" s="30"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="30"/>
+      <c r="AB2" s="30"/>
+      <c r="AC2" s="30"/>
+      <c r="AD2" s="30"/>
+      <c r="AE2" s="30"/>
+      <c r="AF2" s="30"/>
+      <c r="AG2" s="30"/>
+      <c r="AH2" s="31"/>
+      <c r="AI2" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="AJ2" s="48"/>
-      <c r="AK2" s="48"/>
-      <c r="AL2" s="48"/>
-      <c r="AM2" s="49"/>
-      <c r="AN2" s="47" t="s">
+      <c r="AJ2" s="36"/>
+      <c r="AK2" s="36"/>
+      <c r="AL2" s="36"/>
+      <c r="AM2" s="37"/>
+      <c r="AN2" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="AO2" s="48"/>
-      <c r="AP2" s="48"/>
-      <c r="AQ2" s="48"/>
-      <c r="AR2" s="49"/>
-      <c r="AY2" s="30" t="s">
+      <c r="AO2" s="36"/>
+      <c r="AP2" s="36"/>
+      <c r="AQ2" s="36"/>
+      <c r="AR2" s="37"/>
+      <c r="AY2" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="AZ2" s="30"/>
-      <c r="BA2" s="30"/>
-      <c r="BB2" s="30"/>
-      <c r="BC2" s="30"/>
-      <c r="BD2" s="30"/>
-      <c r="BE2" s="30"/>
-      <c r="BF2" s="30"/>
-      <c r="BG2" s="30"/>
-      <c r="BH2" s="30"/>
-      <c r="BI2" s="30"/>
+      <c r="AZ2" s="47"/>
+      <c r="BA2" s="47"/>
+      <c r="BB2" s="47"/>
+      <c r="BC2" s="47"/>
+      <c r="BD2" s="47"/>
+      <c r="BE2" s="47"/>
+      <c r="BF2" s="47"/>
+      <c r="BG2" s="47"/>
+      <c r="BH2" s="47"/>
+      <c r="BI2" s="47"/>
     </row>
     <row r="3" spans="1:62" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4"/>
@@ -1305,56 +1316,56 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
-      <c r="V3" s="46"/>
-      <c r="W3" s="44"/>
-      <c r="X3" s="45"/>
-      <c r="Y3" s="45"/>
-      <c r="Z3" s="45"/>
-      <c r="AA3" s="45"/>
-      <c r="AB3" s="45"/>
-      <c r="AC3" s="45"/>
-      <c r="AD3" s="45"/>
-      <c r="AE3" s="45"/>
-      <c r="AF3" s="45"/>
-      <c r="AG3" s="45"/>
-      <c r="AH3" s="46"/>
-      <c r="AI3" s="50"/>
-      <c r="AJ3" s="51"/>
-      <c r="AK3" s="51"/>
-      <c r="AL3" s="51"/>
-      <c r="AM3" s="52"/>
-      <c r="AN3" s="50"/>
-      <c r="AO3" s="51"/>
-      <c r="AP3" s="51"/>
-      <c r="AQ3" s="51"/>
-      <c r="AR3" s="52"/>
-      <c r="AY3" s="31"/>
-      <c r="AZ3" s="31"/>
-      <c r="BA3" s="31"/>
-      <c r="BB3" s="31"/>
-      <c r="BC3" s="31"/>
-      <c r="BD3" s="31"/>
-      <c r="BE3" s="31"/>
-      <c r="BF3" s="31"/>
-      <c r="BG3" s="31"/>
-      <c r="BH3" s="31"/>
-      <c r="BI3" s="31"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="33"/>
+      <c r="O3" s="33"/>
+      <c r="P3" s="33"/>
+      <c r="Q3" s="33"/>
+      <c r="R3" s="33"/>
+      <c r="S3" s="33"/>
+      <c r="T3" s="33"/>
+      <c r="U3" s="33"/>
+      <c r="V3" s="34"/>
+      <c r="W3" s="32"/>
+      <c r="X3" s="33"/>
+      <c r="Y3" s="33"/>
+      <c r="Z3" s="33"/>
+      <c r="AA3" s="33"/>
+      <c r="AB3" s="33"/>
+      <c r="AC3" s="33"/>
+      <c r="AD3" s="33"/>
+      <c r="AE3" s="33"/>
+      <c r="AF3" s="33"/>
+      <c r="AG3" s="33"/>
+      <c r="AH3" s="34"/>
+      <c r="AI3" s="38"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="39"/>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="40"/>
+      <c r="AN3" s="38"/>
+      <c r="AO3" s="39"/>
+      <c r="AP3" s="39"/>
+      <c r="AQ3" s="39"/>
+      <c r="AR3" s="40"/>
+      <c r="AY3" s="48"/>
+      <c r="AZ3" s="48"/>
+      <c r="BA3" s="48"/>
+      <c r="BB3" s="48"/>
+      <c r="BC3" s="48"/>
+      <c r="BD3" s="48"/>
+      <c r="BE3" s="48"/>
+      <c r="BF3" s="48"/>
+      <c r="BG3" s="48"/>
+      <c r="BH3" s="48"/>
+      <c r="BI3" s="48"/>
     </row>
     <row r="4" spans="1:62" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
@@ -1362,66 +1373,66 @@
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="53" t="s">
+      <c r="F4" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="53" t="s">
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="53" t="s">
+      <c r="L4" s="50"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="50"/>
+      <c r="O4" s="51"/>
+      <c r="P4" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="54"/>
-      <c r="T4" s="55"/>
-      <c r="U4" s="53" t="s">
+      <c r="Q4" s="50"/>
+      <c r="R4" s="50"/>
+      <c r="S4" s="50"/>
+      <c r="T4" s="51"/>
+      <c r="U4" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="V4" s="54"/>
-      <c r="W4" s="54"/>
-      <c r="X4" s="54"/>
-      <c r="Y4" s="54"/>
-      <c r="Z4" s="54"/>
-      <c r="AA4" s="54"/>
-      <c r="AB4" s="54"/>
-      <c r="AC4" s="54"/>
-      <c r="AD4" s="54"/>
-      <c r="AE4" s="54"/>
-      <c r="AF4" s="54"/>
-      <c r="AG4" s="54"/>
-      <c r="AH4" s="55"/>
-      <c r="AI4" s="56" t="s">
+      <c r="V4" s="50"/>
+      <c r="W4" s="50"/>
+      <c r="X4" s="50"/>
+      <c r="Y4" s="50"/>
+      <c r="Z4" s="50"/>
+      <c r="AA4" s="50"/>
+      <c r="AB4" s="50"/>
+      <c r="AC4" s="50"/>
+      <c r="AD4" s="50"/>
+      <c r="AE4" s="50"/>
+      <c r="AF4" s="50"/>
+      <c r="AG4" s="50"/>
+      <c r="AH4" s="51"/>
+      <c r="AI4" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="AJ4" s="57"/>
-      <c r="AK4" s="57"/>
-      <c r="AL4" s="57"/>
-      <c r="AM4" s="57"/>
-      <c r="AN4" s="57"/>
-      <c r="AO4" s="57"/>
-      <c r="AP4" s="57"/>
-      <c r="AQ4" s="57"/>
-      <c r="AR4" s="58"/>
-      <c r="AY4" s="31"/>
-      <c r="AZ4" s="31"/>
-      <c r="BA4" s="31"/>
-      <c r="BB4" s="31"/>
-      <c r="BC4" s="31"/>
-      <c r="BD4" s="31"/>
-      <c r="BE4" s="31"/>
-      <c r="BF4" s="31"/>
-      <c r="BG4" s="31"/>
-      <c r="BH4" s="31"/>
-      <c r="BI4" s="31"/>
+      <c r="AJ4" s="21"/>
+      <c r="AK4" s="21"/>
+      <c r="AL4" s="21"/>
+      <c r="AM4" s="21"/>
+      <c r="AN4" s="21"/>
+      <c r="AO4" s="21"/>
+      <c r="AP4" s="21"/>
+      <c r="AQ4" s="21"/>
+      <c r="AR4" s="22"/>
+      <c r="AY4" s="48"/>
+      <c r="AZ4" s="48"/>
+      <c r="BA4" s="48"/>
+      <c r="BB4" s="48"/>
+      <c r="BC4" s="48"/>
+      <c r="BD4" s="48"/>
+      <c r="BE4" s="48"/>
+      <c r="BF4" s="48"/>
+      <c r="BG4" s="48"/>
+      <c r="BH4" s="48"/>
+      <c r="BI4" s="48"/>
     </row>
     <row r="5" spans="1:62" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
@@ -1429,53 +1440,53 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
-      <c r="F5" s="41" t="s">
+      <c r="F5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="47" t="s">
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="L5" s="48"/>
-      <c r="M5" s="48"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="47" t="s">
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="67" t="s">
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="37"/>
+      <c r="U5" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="V5" s="68"/>
-      <c r="W5" s="68"/>
-      <c r="X5" s="68"/>
-      <c r="Y5" s="68"/>
-      <c r="Z5" s="68"/>
-      <c r="AA5" s="68"/>
-      <c r="AB5" s="68"/>
-      <c r="AC5" s="68"/>
-      <c r="AD5" s="68"/>
-      <c r="AE5" s="68"/>
-      <c r="AF5" s="68"/>
-      <c r="AG5" s="68"/>
-      <c r="AH5" s="69"/>
-      <c r="AI5" s="59"/>
-      <c r="AJ5" s="60"/>
-      <c r="AK5" s="60"/>
-      <c r="AL5" s="60"/>
-      <c r="AM5" s="60"/>
-      <c r="AN5" s="60"/>
-      <c r="AO5" s="60"/>
-      <c r="AP5" s="60"/>
-      <c r="AQ5" s="60"/>
-      <c r="AR5" s="61"/>
+      <c r="V5" s="42"/>
+      <c r="W5" s="42"/>
+      <c r="X5" s="42"/>
+      <c r="Y5" s="42"/>
+      <c r="Z5" s="42"/>
+      <c r="AA5" s="42"/>
+      <c r="AB5" s="42"/>
+      <c r="AC5" s="42"/>
+      <c r="AD5" s="42"/>
+      <c r="AE5" s="42"/>
+      <c r="AF5" s="42"/>
+      <c r="AG5" s="42"/>
+      <c r="AH5" s="43"/>
+      <c r="AI5" s="23"/>
+      <c r="AJ5" s="24"/>
+      <c r="AK5" s="24"/>
+      <c r="AL5" s="24"/>
+      <c r="AM5" s="24"/>
+      <c r="AN5" s="24"/>
+      <c r="AO5" s="24"/>
+      <c r="AP5" s="24"/>
+      <c r="AQ5" s="24"/>
+      <c r="AR5" s="25"/>
     </row>
     <row r="6" spans="1:62" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
@@ -1483,45 +1494,45 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="52"/>
-      <c r="P6" s="50"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="51"/>
-      <c r="S6" s="51"/>
-      <c r="T6" s="52"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
-      <c r="W6" s="71"/>
-      <c r="X6" s="71"/>
-      <c r="Y6" s="71"/>
-      <c r="Z6" s="71"/>
-      <c r="AA6" s="71"/>
-      <c r="AB6" s="71"/>
-      <c r="AC6" s="71"/>
-      <c r="AD6" s="71"/>
-      <c r="AE6" s="71"/>
-      <c r="AF6" s="71"/>
-      <c r="AG6" s="71"/>
-      <c r="AH6" s="72"/>
-      <c r="AI6" s="62"/>
-      <c r="AJ6" s="63"/>
-      <c r="AK6" s="63"/>
-      <c r="AL6" s="63"/>
-      <c r="AM6" s="63"/>
-      <c r="AN6" s="63"/>
-      <c r="AO6" s="63"/>
-      <c r="AP6" s="63"/>
-      <c r="AQ6" s="63"/>
-      <c r="AR6" s="64"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="38"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="39"/>
+      <c r="T6" s="40"/>
+      <c r="U6" s="44"/>
+      <c r="V6" s="45"/>
+      <c r="W6" s="45"/>
+      <c r="X6" s="45"/>
+      <c r="Y6" s="45"/>
+      <c r="Z6" s="45"/>
+      <c r="AA6" s="45"/>
+      <c r="AB6" s="45"/>
+      <c r="AC6" s="45"/>
+      <c r="AD6" s="45"/>
+      <c r="AE6" s="45"/>
+      <c r="AF6" s="45"/>
+      <c r="AG6" s="45"/>
+      <c r="AH6" s="46"/>
+      <c r="AI6" s="26"/>
+      <c r="AJ6" s="27"/>
+      <c r="AK6" s="27"/>
+      <c r="AL6" s="27"/>
+      <c r="AM6" s="27"/>
+      <c r="AN6" s="27"/>
+      <c r="AO6" s="27"/>
+      <c r="AP6" s="27"/>
+      <c r="AQ6" s="27"/>
+      <c r="AR6" s="28"/>
     </row>
     <row r="7" spans="1:62" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
@@ -1567,1519 +1578,1519 @@
       <c r="AO7" s="4"/>
     </row>
     <row r="8" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="18" t="s">
+      <c r="B8" s="66"/>
+      <c r="C8" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="18" t="s">
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="27" t="s">
+      <c r="L8" s="67"/>
+      <c r="M8" s="67"/>
+      <c r="N8" s="67"/>
+      <c r="O8" s="67"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="66"/>
+      <c r="S8" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="T8" s="28"/>
-      <c r="U8" s="27" t="s">
+      <c r="T8" s="69"/>
+      <c r="U8" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="V8" s="28"/>
-      <c r="W8" s="27" t="s">
+      <c r="V8" s="69"/>
+      <c r="W8" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="X8" s="28"/>
-      <c r="Y8" s="18" t="s">
+      <c r="X8" s="69"/>
+      <c r="Y8" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="Z8" s="20"/>
-      <c r="AA8" s="18" t="s">
+      <c r="Z8" s="66"/>
+      <c r="AA8" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="AB8" s="20"/>
-      <c r="AC8" s="18" t="s">
+      <c r="AB8" s="66"/>
+      <c r="AC8" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="AD8" s="19"/>
-      <c r="AE8" s="19"/>
-      <c r="AF8" s="20"/>
-      <c r="AG8" s="18" t="s">
+      <c r="AD8" s="67"/>
+      <c r="AE8" s="67"/>
+      <c r="AF8" s="66"/>
+      <c r="AG8" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="AH8" s="19"/>
-      <c r="AI8" s="20"/>
-      <c r="AJ8" s="18" t="s">
+      <c r="AH8" s="67"/>
+      <c r="AI8" s="66"/>
+      <c r="AJ8" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="AK8" s="19"/>
-      <c r="AL8" s="20"/>
-      <c r="AM8" s="21" t="s">
+      <c r="AK8" s="67"/>
+      <c r="AL8" s="66"/>
+      <c r="AM8" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="AN8" s="22"/>
-      <c r="AO8" s="23"/>
-      <c r="AP8" s="18" t="s">
+      <c r="AN8" s="86"/>
+      <c r="AO8" s="87"/>
+      <c r="AP8" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="AQ8" s="19"/>
-      <c r="AR8" s="20"/>
-      <c r="AS8" s="18" t="s">
+      <c r="AQ8" s="67"/>
+      <c r="AR8" s="66"/>
+      <c r="AS8" s="65" t="s">
         <v>60</v>
       </c>
-      <c r="AT8" s="19"/>
-      <c r="AU8" s="19"/>
-      <c r="AV8" s="19"/>
-      <c r="AW8" s="19"/>
-      <c r="AX8" s="19"/>
-      <c r="AY8" s="19"/>
-      <c r="AZ8" s="20"/>
-      <c r="BA8" s="18" t="s">
+      <c r="AT8" s="67"/>
+      <c r="AU8" s="67"/>
+      <c r="AV8" s="67"/>
+      <c r="AW8" s="67"/>
+      <c r="AX8" s="67"/>
+      <c r="AY8" s="67"/>
+      <c r="AZ8" s="66"/>
+      <c r="BA8" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="BB8" s="19"/>
-      <c r="BC8" s="20"/>
-      <c r="BD8" s="65" t="s">
+      <c r="BB8" s="67"/>
+      <c r="BC8" s="66"/>
+      <c r="BD8" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="BE8" s="65"/>
-      <c r="BF8" s="65"/>
-      <c r="BG8" s="65"/>
-      <c r="BH8" s="65"/>
-      <c r="BI8" s="65"/>
+      <c r="BE8" s="72"/>
+      <c r="BF8" s="72"/>
+      <c r="BG8" s="72"/>
+      <c r="BH8" s="72"/>
+      <c r="BI8" s="72"/>
       <c r="BJ8" s="8"/>
     </row>
     <row r="9" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="80" t="s">
+      <c r="A9" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="80"/>
-      <c r="C9" s="81" t="s">
+      <c r="B9" s="74"/>
+      <c r="C9" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
-      <c r="G9" s="81"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="81"/>
-      <c r="J9" s="81"/>
-      <c r="K9" s="81" t="s">
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
+      <c r="I9" s="75"/>
+      <c r="J9" s="75"/>
+      <c r="K9" s="75" t="s">
         <v>31</v>
       </c>
-      <c r="L9" s="81"/>
-      <c r="M9" s="81"/>
-      <c r="N9" s="81"/>
-      <c r="O9" s="81"/>
-      <c r="P9" s="81"/>
-      <c r="Q9" s="81"/>
-      <c r="R9" s="81"/>
-      <c r="S9" s="82" t="s">
+      <c r="L9" s="75"/>
+      <c r="M9" s="75"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="75"/>
+      <c r="P9" s="75"/>
+      <c r="Q9" s="75"/>
+      <c r="R9" s="75"/>
+      <c r="S9" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="T9" s="82"/>
-      <c r="U9" s="82" t="s">
+      <c r="T9" s="76"/>
+      <c r="U9" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="V9" s="82"/>
-      <c r="W9" s="82" t="s">
+      <c r="V9" s="76"/>
+      <c r="W9" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="X9" s="82"/>
-      <c r="Y9" s="82" t="s">
+      <c r="X9" s="76"/>
+      <c r="Y9" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="Z9" s="82"/>
-      <c r="AA9" s="83" t="s">
+      <c r="Z9" s="76"/>
+      <c r="AA9" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="AB9" s="83"/>
-      <c r="AC9" s="84" t="s">
+      <c r="AB9" s="80"/>
+      <c r="AC9" s="82" t="s">
         <v>33</v>
       </c>
-      <c r="AD9" s="85"/>
-      <c r="AE9" s="85"/>
-      <c r="AF9" s="86"/>
-      <c r="AG9" s="84" t="s">
+      <c r="AD9" s="83"/>
+      <c r="AE9" s="83"/>
+      <c r="AF9" s="84"/>
+      <c r="AG9" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="AH9" s="85"/>
-      <c r="AI9" s="86"/>
-      <c r="AJ9" s="87" t="s">
+      <c r="AH9" s="83"/>
+      <c r="AI9" s="84"/>
+      <c r="AJ9" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="AK9" s="87"/>
-      <c r="AL9" s="87"/>
-      <c r="AM9" s="87" t="s">
+      <c r="AK9" s="81"/>
+      <c r="AL9" s="81"/>
+      <c r="AM9" s="81" t="s">
         <v>36</v>
       </c>
-      <c r="AN9" s="87"/>
-      <c r="AO9" s="87"/>
-      <c r="AP9" s="82" t="s">
+      <c r="AN9" s="81"/>
+      <c r="AO9" s="81"/>
+      <c r="AP9" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="AQ9" s="82"/>
-      <c r="AR9" s="82"/>
-      <c r="AS9" s="81" t="s">
+      <c r="AQ9" s="76"/>
+      <c r="AR9" s="76"/>
+      <c r="AS9" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="AT9" s="81"/>
-      <c r="AU9" s="81"/>
-      <c r="AV9" s="81"/>
-      <c r="AW9" s="81"/>
-      <c r="AX9" s="81"/>
-      <c r="AY9" s="81"/>
-      <c r="AZ9" s="81"/>
-      <c r="BA9" s="82" t="s">
+      <c r="AT9" s="75"/>
+      <c r="AU9" s="75"/>
+      <c r="AV9" s="75"/>
+      <c r="AW9" s="75"/>
+      <c r="AX9" s="75"/>
+      <c r="AY9" s="75"/>
+      <c r="AZ9" s="75"/>
+      <c r="BA9" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="BB9" s="82"/>
-      <c r="BC9" s="82"/>
-      <c r="BD9" s="88" t="s">
+      <c r="BB9" s="76"/>
+      <c r="BC9" s="76"/>
+      <c r="BD9" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="BE9" s="88"/>
-      <c r="BF9" s="88"/>
-      <c r="BG9" s="88"/>
-      <c r="BH9" s="88"/>
-      <c r="BI9" s="88"/>
+      <c r="BE9" s="79"/>
+      <c r="BF9" s="79"/>
+      <c r="BG9" s="79"/>
+      <c r="BH9" s="79"/>
+      <c r="BI9" s="79"/>
       <c r="BJ9" s="10"/>
     </row>
     <row r="10" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="24"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="24"/>
-      <c r="R10" s="24"/>
-      <c r="S10" s="24"/>
-      <c r="T10" s="24"/>
-      <c r="U10" s="24"/>
-      <c r="V10" s="24"/>
-      <c r="W10" s="24"/>
-      <c r="X10" s="24"/>
-      <c r="Y10" s="24"/>
-      <c r="Z10" s="24"/>
-      <c r="AA10" s="26"/>
-      <c r="AB10" s="26"/>
-      <c r="AC10" s="24"/>
-      <c r="AD10" s="24"/>
-      <c r="AE10" s="24"/>
-      <c r="AF10" s="24"/>
-      <c r="AG10" s="24"/>
-      <c r="AH10" s="24"/>
-      <c r="AI10" s="24"/>
-      <c r="AJ10" s="24"/>
-      <c r="AK10" s="24"/>
-      <c r="AL10" s="24"/>
-      <c r="AM10" s="24"/>
-      <c r="AN10" s="24"/>
-      <c r="AO10" s="24"/>
-      <c r="AP10" s="24"/>
-      <c r="AQ10" s="24"/>
-      <c r="AR10" s="24"/>
-      <c r="AS10" s="24"/>
-      <c r="AT10" s="24"/>
-      <c r="AU10" s="24"/>
-      <c r="AV10" s="24"/>
-      <c r="AW10" s="24"/>
-      <c r="AX10" s="24"/>
-      <c r="AY10" s="24"/>
-      <c r="AZ10" s="24"/>
-      <c r="BA10" s="24"/>
-      <c r="BB10" s="24"/>
-      <c r="BC10" s="24"/>
-      <c r="BD10" s="24"/>
-      <c r="BE10" s="24"/>
-      <c r="BF10" s="24"/>
-      <c r="BG10" s="24"/>
-      <c r="BH10" s="24"/>
-      <c r="BI10" s="24"/>
+      <c r="A10" s="77"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73"/>
+      <c r="J10" s="73"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="73"/>
+      <c r="O10" s="73"/>
+      <c r="P10" s="73"/>
+      <c r="Q10" s="73"/>
+      <c r="R10" s="73"/>
+      <c r="S10" s="73"/>
+      <c r="T10" s="73"/>
+      <c r="U10" s="73"/>
+      <c r="V10" s="73"/>
+      <c r="W10" s="73"/>
+      <c r="X10" s="73"/>
+      <c r="Y10" s="73"/>
+      <c r="Z10" s="73"/>
+      <c r="AA10" s="78"/>
+      <c r="AB10" s="78"/>
+      <c r="AC10" s="73"/>
+      <c r="AD10" s="73"/>
+      <c r="AE10" s="73"/>
+      <c r="AF10" s="73"/>
+      <c r="AG10" s="73"/>
+      <c r="AH10" s="73"/>
+      <c r="AI10" s="73"/>
+      <c r="AJ10" s="73"/>
+      <c r="AK10" s="73"/>
+      <c r="AL10" s="73"/>
+      <c r="AM10" s="73"/>
+      <c r="AN10" s="73"/>
+      <c r="AO10" s="73"/>
+      <c r="AP10" s="73"/>
+      <c r="AQ10" s="73"/>
+      <c r="AR10" s="73"/>
+      <c r="AS10" s="73"/>
+      <c r="AT10" s="73"/>
+      <c r="AU10" s="73"/>
+      <c r="AV10" s="73"/>
+      <c r="AW10" s="73"/>
+      <c r="AX10" s="73"/>
+      <c r="AY10" s="73"/>
+      <c r="AZ10" s="73"/>
+      <c r="BA10" s="73"/>
+      <c r="BB10" s="73"/>
+      <c r="BC10" s="73"/>
+      <c r="BD10" s="73"/>
+      <c r="BE10" s="73"/>
+      <c r="BF10" s="73"/>
+      <c r="BG10" s="73"/>
+      <c r="BH10" s="73"/>
+      <c r="BI10" s="73"/>
     </row>
     <row r="11" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="15"/>
-      <c r="T11" s="15"/>
-      <c r="U11" s="15"/>
-      <c r="V11" s="15"/>
-      <c r="W11" s="15"/>
-      <c r="X11" s="15"/>
-      <c r="Y11" s="15"/>
-      <c r="Z11" s="15"/>
-      <c r="AA11" s="17"/>
-      <c r="AB11" s="17"/>
-      <c r="AC11" s="15"/>
-      <c r="AD11" s="15"/>
-      <c r="AE11" s="15"/>
-      <c r="AF11" s="15"/>
-      <c r="AG11" s="15"/>
-      <c r="AH11" s="15"/>
-      <c r="AI11" s="15"/>
-      <c r="AJ11" s="15"/>
-      <c r="AK11" s="15"/>
-      <c r="AL11" s="15"/>
-      <c r="AM11" s="15"/>
-      <c r="AN11" s="15"/>
-      <c r="AO11" s="15"/>
-      <c r="AP11" s="15"/>
-      <c r="AQ11" s="15"/>
-      <c r="AR11" s="15"/>
-      <c r="AS11" s="15"/>
-      <c r="AT11" s="15"/>
-      <c r="AU11" s="15"/>
-      <c r="AV11" s="15"/>
-      <c r="AW11" s="15"/>
-      <c r="AX11" s="15"/>
-      <c r="AY11" s="15"/>
-      <c r="AZ11" s="15"/>
-      <c r="BA11" s="15"/>
-      <c r="BB11" s="15"/>
-      <c r="BC11" s="15"/>
-      <c r="BD11" s="15"/>
-      <c r="BE11" s="15"/>
-      <c r="BF11" s="15"/>
-      <c r="BG11" s="15"/>
-      <c r="BH11" s="15"/>
-      <c r="BI11" s="15"/>
+      <c r="A11" s="70"/>
+      <c r="B11" s="70"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="64"/>
+      <c r="K11" s="64"/>
+      <c r="L11" s="64"/>
+      <c r="M11" s="64"/>
+      <c r="N11" s="64"/>
+      <c r="O11" s="64"/>
+      <c r="P11" s="64"/>
+      <c r="Q11" s="64"/>
+      <c r="R11" s="64"/>
+      <c r="S11" s="64"/>
+      <c r="T11" s="64"/>
+      <c r="U11" s="64"/>
+      <c r="V11" s="64"/>
+      <c r="W11" s="64"/>
+      <c r="X11" s="64"/>
+      <c r="Y11" s="64"/>
+      <c r="Z11" s="64"/>
+      <c r="AA11" s="71"/>
+      <c r="AB11" s="71"/>
+      <c r="AC11" s="64"/>
+      <c r="AD11" s="64"/>
+      <c r="AE11" s="64"/>
+      <c r="AF11" s="64"/>
+      <c r="AG11" s="64"/>
+      <c r="AH11" s="64"/>
+      <c r="AI11" s="64"/>
+      <c r="AJ11" s="64"/>
+      <c r="AK11" s="64"/>
+      <c r="AL11" s="64"/>
+      <c r="AM11" s="64"/>
+      <c r="AN11" s="64"/>
+      <c r="AO11" s="64"/>
+      <c r="AP11" s="64"/>
+      <c r="AQ11" s="64"/>
+      <c r="AR11" s="64"/>
+      <c r="AS11" s="64"/>
+      <c r="AT11" s="64"/>
+      <c r="AU11" s="64"/>
+      <c r="AV11" s="64"/>
+      <c r="AW11" s="64"/>
+      <c r="AX11" s="64"/>
+      <c r="AY11" s="64"/>
+      <c r="AZ11" s="64"/>
+      <c r="BA11" s="64"/>
+      <c r="BB11" s="64"/>
+      <c r="BC11" s="64"/>
+      <c r="BD11" s="64"/>
+      <c r="BE11" s="64"/>
+      <c r="BF11" s="64"/>
+      <c r="BG11" s="64"/>
+      <c r="BH11" s="64"/>
+      <c r="BI11" s="64"/>
     </row>
     <row r="12" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="15"/>
-      <c r="T12" s="15"/>
-      <c r="U12" s="15"/>
-      <c r="V12" s="15"/>
-      <c r="W12" s="15"/>
-      <c r="X12" s="15"/>
-      <c r="Y12" s="15"/>
-      <c r="Z12" s="15"/>
-      <c r="AA12" s="17"/>
-      <c r="AB12" s="17"/>
-      <c r="AC12" s="15"/>
-      <c r="AD12" s="15"/>
-      <c r="AE12" s="15"/>
-      <c r="AF12" s="15"/>
-      <c r="AG12" s="15"/>
-      <c r="AH12" s="15"/>
-      <c r="AI12" s="15"/>
-      <c r="AJ12" s="15"/>
-      <c r="AK12" s="15"/>
-      <c r="AL12" s="15"/>
-      <c r="AM12" s="15"/>
-      <c r="AN12" s="15"/>
-      <c r="AO12" s="15"/>
-      <c r="AP12" s="15"/>
-      <c r="AQ12" s="15"/>
-      <c r="AR12" s="15"/>
-      <c r="AS12" s="15"/>
-      <c r="AT12" s="15"/>
-      <c r="AU12" s="15"/>
-      <c r="AV12" s="15"/>
-      <c r="AW12" s="15"/>
-      <c r="AX12" s="15"/>
-      <c r="AY12" s="15"/>
-      <c r="AZ12" s="15"/>
-      <c r="BA12" s="15"/>
-      <c r="BB12" s="15"/>
-      <c r="BC12" s="15"/>
-      <c r="BD12" s="15"/>
-      <c r="BE12" s="15"/>
-      <c r="BF12" s="15"/>
-      <c r="BG12" s="15"/>
-      <c r="BH12" s="15"/>
-      <c r="BI12" s="15"/>
+      <c r="A12" s="70"/>
+      <c r="B12" s="70"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="64"/>
+      <c r="L12" s="64"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="64"/>
+      <c r="O12" s="64"/>
+      <c r="P12" s="64"/>
+      <c r="Q12" s="64"/>
+      <c r="R12" s="64"/>
+      <c r="S12" s="64"/>
+      <c r="T12" s="64"/>
+      <c r="U12" s="64"/>
+      <c r="V12" s="64"/>
+      <c r="W12" s="64"/>
+      <c r="X12" s="64"/>
+      <c r="Y12" s="64"/>
+      <c r="Z12" s="64"/>
+      <c r="AA12" s="71"/>
+      <c r="AB12" s="71"/>
+      <c r="AC12" s="64"/>
+      <c r="AD12" s="64"/>
+      <c r="AE12" s="64"/>
+      <c r="AF12" s="64"/>
+      <c r="AG12" s="64"/>
+      <c r="AH12" s="64"/>
+      <c r="AI12" s="64"/>
+      <c r="AJ12" s="64"/>
+      <c r="AK12" s="64"/>
+      <c r="AL12" s="64"/>
+      <c r="AM12" s="64"/>
+      <c r="AN12" s="64"/>
+      <c r="AO12" s="64"/>
+      <c r="AP12" s="64"/>
+      <c r="AQ12" s="64"/>
+      <c r="AR12" s="64"/>
+      <c r="AS12" s="64"/>
+      <c r="AT12" s="64"/>
+      <c r="AU12" s="64"/>
+      <c r="AV12" s="64"/>
+      <c r="AW12" s="64"/>
+      <c r="AX12" s="64"/>
+      <c r="AY12" s="64"/>
+      <c r="AZ12" s="64"/>
+      <c r="BA12" s="64"/>
+      <c r="BB12" s="64"/>
+      <c r="BC12" s="64"/>
+      <c r="BD12" s="64"/>
+      <c r="BE12" s="64"/>
+      <c r="BF12" s="64"/>
+      <c r="BG12" s="64"/>
+      <c r="BH12" s="64"/>
+      <c r="BI12" s="64"/>
     </row>
     <row r="13" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="15"/>
-      <c r="T13" s="15"/>
-      <c r="U13" s="15"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="15"/>
-      <c r="X13" s="15"/>
-      <c r="Y13" s="15"/>
-      <c r="Z13" s="15"/>
-      <c r="AA13" s="17"/>
-      <c r="AB13" s="17"/>
-      <c r="AC13" s="15"/>
-      <c r="AD13" s="15"/>
-      <c r="AE13" s="15"/>
-      <c r="AF13" s="15"/>
-      <c r="AG13" s="15"/>
-      <c r="AH13" s="15"/>
-      <c r="AI13" s="15"/>
-      <c r="AJ13" s="15"/>
-      <c r="AK13" s="15"/>
-      <c r="AL13" s="15"/>
-      <c r="AM13" s="15"/>
-      <c r="AN13" s="15"/>
-      <c r="AO13" s="15"/>
-      <c r="AP13" s="15"/>
-      <c r="AQ13" s="15"/>
-      <c r="AR13" s="15"/>
-      <c r="AS13" s="15"/>
-      <c r="AT13" s="15"/>
-      <c r="AU13" s="15"/>
-      <c r="AV13" s="15"/>
-      <c r="AW13" s="15"/>
-      <c r="AX13" s="15"/>
-      <c r="AY13" s="15"/>
-      <c r="AZ13" s="15"/>
-      <c r="BA13" s="15"/>
-      <c r="BB13" s="15"/>
-      <c r="BC13" s="15"/>
-      <c r="BD13" s="15"/>
-      <c r="BE13" s="15"/>
-      <c r="BF13" s="15"/>
-      <c r="BG13" s="15"/>
-      <c r="BH13" s="15"/>
-      <c r="BI13" s="15"/>
+      <c r="A13" s="70"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="64"/>
+      <c r="K13" s="64"/>
+      <c r="L13" s="64"/>
+      <c r="M13" s="64"/>
+      <c r="N13" s="64"/>
+      <c r="O13" s="64"/>
+      <c r="P13" s="64"/>
+      <c r="Q13" s="64"/>
+      <c r="R13" s="64"/>
+      <c r="S13" s="64"/>
+      <c r="T13" s="64"/>
+      <c r="U13" s="64"/>
+      <c r="V13" s="64"/>
+      <c r="W13" s="64"/>
+      <c r="X13" s="64"/>
+      <c r="Y13" s="64"/>
+      <c r="Z13" s="64"/>
+      <c r="AA13" s="71"/>
+      <c r="AB13" s="71"/>
+      <c r="AC13" s="64"/>
+      <c r="AD13" s="64"/>
+      <c r="AE13" s="64"/>
+      <c r="AF13" s="64"/>
+      <c r="AG13" s="64"/>
+      <c r="AH13" s="64"/>
+      <c r="AI13" s="64"/>
+      <c r="AJ13" s="64"/>
+      <c r="AK13" s="64"/>
+      <c r="AL13" s="64"/>
+      <c r="AM13" s="64"/>
+      <c r="AN13" s="64"/>
+      <c r="AO13" s="64"/>
+      <c r="AP13" s="64"/>
+      <c r="AQ13" s="64"/>
+      <c r="AR13" s="64"/>
+      <c r="AS13" s="64"/>
+      <c r="AT13" s="64"/>
+      <c r="AU13" s="64"/>
+      <c r="AV13" s="64"/>
+      <c r="AW13" s="64"/>
+      <c r="AX13" s="64"/>
+      <c r="AY13" s="64"/>
+      <c r="AZ13" s="64"/>
+      <c r="BA13" s="64"/>
+      <c r="BB13" s="64"/>
+      <c r="BC13" s="64"/>
+      <c r="BD13" s="64"/>
+      <c r="BE13" s="64"/>
+      <c r="BF13" s="64"/>
+      <c r="BG13" s="64"/>
+      <c r="BH13" s="64"/>
+      <c r="BI13" s="64"/>
     </row>
     <row r="14" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="15"/>
-      <c r="S14" s="15"/>
-      <c r="T14" s="15"/>
-      <c r="U14" s="15"/>
-      <c r="V14" s="15"/>
-      <c r="W14" s="15"/>
-      <c r="X14" s="15"/>
-      <c r="Y14" s="15"/>
-      <c r="Z14" s="15"/>
-      <c r="AA14" s="17"/>
-      <c r="AB14" s="17"/>
-      <c r="AC14" s="15"/>
-      <c r="AD14" s="15"/>
-      <c r="AE14" s="15"/>
-      <c r="AF14" s="15"/>
-      <c r="AG14" s="15"/>
-      <c r="AH14" s="15"/>
-      <c r="AI14" s="15"/>
-      <c r="AJ14" s="15"/>
-      <c r="AK14" s="15"/>
-      <c r="AL14" s="15"/>
-      <c r="AM14" s="15"/>
-      <c r="AN14" s="15"/>
-      <c r="AO14" s="15"/>
-      <c r="AP14" s="15"/>
-      <c r="AQ14" s="15"/>
-      <c r="AR14" s="15"/>
-      <c r="AS14" s="15"/>
-      <c r="AT14" s="15"/>
-      <c r="AU14" s="15"/>
-      <c r="AV14" s="15"/>
-      <c r="AW14" s="15"/>
-      <c r="AX14" s="15"/>
-      <c r="AY14" s="15"/>
-      <c r="AZ14" s="15"/>
-      <c r="BA14" s="15"/>
-      <c r="BB14" s="15"/>
-      <c r="BC14" s="15"/>
-      <c r="BD14" s="15"/>
-      <c r="BE14" s="15"/>
-      <c r="BF14" s="15"/>
-      <c r="BG14" s="15"/>
-      <c r="BH14" s="15"/>
-      <c r="BI14" s="15"/>
+      <c r="A14" s="70"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="64"/>
+      <c r="L14" s="64"/>
+      <c r="M14" s="64"/>
+      <c r="N14" s="64"/>
+      <c r="O14" s="64"/>
+      <c r="P14" s="64"/>
+      <c r="Q14" s="64"/>
+      <c r="R14" s="64"/>
+      <c r="S14" s="64"/>
+      <c r="T14" s="64"/>
+      <c r="U14" s="64"/>
+      <c r="V14" s="64"/>
+      <c r="W14" s="64"/>
+      <c r="X14" s="64"/>
+      <c r="Y14" s="64"/>
+      <c r="Z14" s="64"/>
+      <c r="AA14" s="71"/>
+      <c r="AB14" s="71"/>
+      <c r="AC14" s="64"/>
+      <c r="AD14" s="64"/>
+      <c r="AE14" s="64"/>
+      <c r="AF14" s="64"/>
+      <c r="AG14" s="64"/>
+      <c r="AH14" s="64"/>
+      <c r="AI14" s="64"/>
+      <c r="AJ14" s="64"/>
+      <c r="AK14" s="64"/>
+      <c r="AL14" s="64"/>
+      <c r="AM14" s="64"/>
+      <c r="AN14" s="64"/>
+      <c r="AO14" s="64"/>
+      <c r="AP14" s="64"/>
+      <c r="AQ14" s="64"/>
+      <c r="AR14" s="64"/>
+      <c r="AS14" s="64"/>
+      <c r="AT14" s="64"/>
+      <c r="AU14" s="64"/>
+      <c r="AV14" s="64"/>
+      <c r="AW14" s="64"/>
+      <c r="AX14" s="64"/>
+      <c r="AY14" s="64"/>
+      <c r="AZ14" s="64"/>
+      <c r="BA14" s="64"/>
+      <c r="BB14" s="64"/>
+      <c r="BC14" s="64"/>
+      <c r="BD14" s="64"/>
+      <c r="BE14" s="64"/>
+      <c r="BF14" s="64"/>
+      <c r="BG14" s="64"/>
+      <c r="BH14" s="64"/>
+      <c r="BI14" s="64"/>
     </row>
     <row r="15" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="15"/>
-      <c r="S15" s="15"/>
-      <c r="T15" s="15"/>
-      <c r="U15" s="15"/>
-      <c r="V15" s="15"/>
-      <c r="W15" s="15"/>
-      <c r="X15" s="15"/>
-      <c r="Y15" s="15"/>
-      <c r="Z15" s="15"/>
-      <c r="AA15" s="17"/>
-      <c r="AB15" s="17"/>
-      <c r="AC15" s="15"/>
-      <c r="AD15" s="15"/>
-      <c r="AE15" s="15"/>
-      <c r="AF15" s="15"/>
-      <c r="AG15" s="15"/>
-      <c r="AH15" s="15"/>
-      <c r="AI15" s="15"/>
-      <c r="AJ15" s="15"/>
-      <c r="AK15" s="15"/>
-      <c r="AL15" s="15"/>
-      <c r="AM15" s="15"/>
-      <c r="AN15" s="15"/>
-      <c r="AO15" s="15"/>
-      <c r="AP15" s="15"/>
-      <c r="AQ15" s="15"/>
-      <c r="AR15" s="15"/>
-      <c r="AS15" s="15"/>
-      <c r="AT15" s="15"/>
-      <c r="AU15" s="15"/>
-      <c r="AV15" s="15"/>
-      <c r="AW15" s="15"/>
-      <c r="AX15" s="15"/>
-      <c r="AY15" s="15"/>
-      <c r="AZ15" s="15"/>
-      <c r="BA15" s="15"/>
-      <c r="BB15" s="15"/>
-      <c r="BC15" s="15"/>
-      <c r="BD15" s="15"/>
-      <c r="BE15" s="15"/>
-      <c r="BF15" s="15"/>
-      <c r="BG15" s="15"/>
-      <c r="BH15" s="15"/>
-      <c r="BI15" s="15"/>
+      <c r="A15" s="70"/>
+      <c r="B15" s="70"/>
+      <c r="C15" s="64"/>
+      <c r="D15" s="64"/>
+      <c r="E15" s="64"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="64"/>
+      <c r="J15" s="64"/>
+      <c r="K15" s="64"/>
+      <c r="L15" s="64"/>
+      <c r="M15" s="64"/>
+      <c r="N15" s="64"/>
+      <c r="O15" s="64"/>
+      <c r="P15" s="64"/>
+      <c r="Q15" s="64"/>
+      <c r="R15" s="64"/>
+      <c r="S15" s="64"/>
+      <c r="T15" s="64"/>
+      <c r="U15" s="64"/>
+      <c r="V15" s="64"/>
+      <c r="W15" s="64"/>
+      <c r="X15" s="64"/>
+      <c r="Y15" s="64"/>
+      <c r="Z15" s="64"/>
+      <c r="AA15" s="71"/>
+      <c r="AB15" s="71"/>
+      <c r="AC15" s="64"/>
+      <c r="AD15" s="64"/>
+      <c r="AE15" s="64"/>
+      <c r="AF15" s="64"/>
+      <c r="AG15" s="64"/>
+      <c r="AH15" s="64"/>
+      <c r="AI15" s="64"/>
+      <c r="AJ15" s="64"/>
+      <c r="AK15" s="64"/>
+      <c r="AL15" s="64"/>
+      <c r="AM15" s="64"/>
+      <c r="AN15" s="64"/>
+      <c r="AO15" s="64"/>
+      <c r="AP15" s="64"/>
+      <c r="AQ15" s="64"/>
+      <c r="AR15" s="64"/>
+      <c r="AS15" s="64"/>
+      <c r="AT15" s="64"/>
+      <c r="AU15" s="64"/>
+      <c r="AV15" s="64"/>
+      <c r="AW15" s="64"/>
+      <c r="AX15" s="64"/>
+      <c r="AY15" s="64"/>
+      <c r="AZ15" s="64"/>
+      <c r="BA15" s="64"/>
+      <c r="BB15" s="64"/>
+      <c r="BC15" s="64"/>
+      <c r="BD15" s="64"/>
+      <c r="BE15" s="64"/>
+      <c r="BF15" s="64"/>
+      <c r="BG15" s="64"/>
+      <c r="BH15" s="64"/>
+      <c r="BI15" s="64"/>
     </row>
     <row r="16" spans="1:62" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="15"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="15"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="15"/>
-      <c r="X16" s="15"/>
-      <c r="Y16" s="15"/>
-      <c r="Z16" s="15"/>
-      <c r="AA16" s="17"/>
-      <c r="AB16" s="17"/>
-      <c r="AC16" s="15"/>
-      <c r="AD16" s="15"/>
-      <c r="AE16" s="15"/>
-      <c r="AF16" s="15"/>
-      <c r="AG16" s="15"/>
-      <c r="AH16" s="15"/>
-      <c r="AI16" s="15"/>
-      <c r="AJ16" s="15"/>
-      <c r="AK16" s="15"/>
-      <c r="AL16" s="15"/>
-      <c r="AM16" s="15"/>
-      <c r="AN16" s="15"/>
-      <c r="AO16" s="15"/>
-      <c r="AP16" s="15"/>
-      <c r="AQ16" s="15"/>
-      <c r="AR16" s="15"/>
-      <c r="AS16" s="15"/>
-      <c r="AT16" s="15"/>
-      <c r="AU16" s="15"/>
-      <c r="AV16" s="15"/>
-      <c r="AW16" s="15"/>
-      <c r="AX16" s="15"/>
-      <c r="AY16" s="15"/>
-      <c r="AZ16" s="15"/>
-      <c r="BA16" s="15"/>
-      <c r="BB16" s="15"/>
-      <c r="BC16" s="15"/>
-      <c r="BD16" s="15"/>
-      <c r="BE16" s="15"/>
-      <c r="BF16" s="15"/>
-      <c r="BG16" s="15"/>
-      <c r="BH16" s="15"/>
-      <c r="BI16" s="15"/>
+      <c r="A16" s="70"/>
+      <c r="B16" s="70"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="64"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="64"/>
+      <c r="G16" s="64"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="64"/>
+      <c r="K16" s="64"/>
+      <c r="L16" s="64"/>
+      <c r="M16" s="64"/>
+      <c r="N16" s="64"/>
+      <c r="O16" s="64"/>
+      <c r="P16" s="64"/>
+      <c r="Q16" s="64"/>
+      <c r="R16" s="64"/>
+      <c r="S16" s="64"/>
+      <c r="T16" s="64"/>
+      <c r="U16" s="64"/>
+      <c r="V16" s="64"/>
+      <c r="W16" s="64"/>
+      <c r="X16" s="64"/>
+      <c r="Y16" s="64"/>
+      <c r="Z16" s="64"/>
+      <c r="AA16" s="71"/>
+      <c r="AB16" s="71"/>
+      <c r="AC16" s="64"/>
+      <c r="AD16" s="64"/>
+      <c r="AE16" s="64"/>
+      <c r="AF16" s="64"/>
+      <c r="AG16" s="64"/>
+      <c r="AH16" s="64"/>
+      <c r="AI16" s="64"/>
+      <c r="AJ16" s="64"/>
+      <c r="AK16" s="64"/>
+      <c r="AL16" s="64"/>
+      <c r="AM16" s="64"/>
+      <c r="AN16" s="64"/>
+      <c r="AO16" s="64"/>
+      <c r="AP16" s="64"/>
+      <c r="AQ16" s="64"/>
+      <c r="AR16" s="64"/>
+      <c r="AS16" s="64"/>
+      <c r="AT16" s="64"/>
+      <c r="AU16" s="64"/>
+      <c r="AV16" s="64"/>
+      <c r="AW16" s="64"/>
+      <c r="AX16" s="64"/>
+      <c r="AY16" s="64"/>
+      <c r="AZ16" s="64"/>
+      <c r="BA16" s="64"/>
+      <c r="BB16" s="64"/>
+      <c r="BC16" s="64"/>
+      <c r="BD16" s="64"/>
+      <c r="BE16" s="64"/>
+      <c r="BF16" s="64"/>
+      <c r="BG16" s="64"/>
+      <c r="BH16" s="64"/>
+      <c r="BI16" s="64"/>
     </row>
     <row r="17" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="15"/>
-      <c r="S17" s="15"/>
-      <c r="T17" s="15"/>
-      <c r="U17" s="15"/>
-      <c r="V17" s="15"/>
-      <c r="W17" s="15"/>
-      <c r="X17" s="15"/>
-      <c r="Y17" s="15"/>
-      <c r="Z17" s="15"/>
-      <c r="AA17" s="17"/>
-      <c r="AB17" s="17"/>
-      <c r="AC17" s="15"/>
-      <c r="AD17" s="15"/>
-      <c r="AE17" s="15"/>
-      <c r="AF17" s="15"/>
-      <c r="AG17" s="15"/>
-      <c r="AH17" s="15"/>
-      <c r="AI17" s="15"/>
-      <c r="AJ17" s="15"/>
-      <c r="AK17" s="15"/>
-      <c r="AL17" s="15"/>
-      <c r="AM17" s="15"/>
-      <c r="AN17" s="15"/>
-      <c r="AO17" s="15"/>
-      <c r="AP17" s="15"/>
-      <c r="AQ17" s="15"/>
-      <c r="AR17" s="15"/>
-      <c r="AS17" s="15"/>
-      <c r="AT17" s="15"/>
-      <c r="AU17" s="15"/>
-      <c r="AV17" s="15"/>
-      <c r="AW17" s="15"/>
-      <c r="AX17" s="15"/>
-      <c r="AY17" s="15"/>
-      <c r="AZ17" s="15"/>
-      <c r="BA17" s="15"/>
-      <c r="BB17" s="15"/>
-      <c r="BC17" s="15"/>
-      <c r="BD17" s="15"/>
-      <c r="BE17" s="15"/>
-      <c r="BF17" s="15"/>
-      <c r="BG17" s="15"/>
-      <c r="BH17" s="15"/>
-      <c r="BI17" s="15"/>
+      <c r="A17" s="70"/>
+      <c r="B17" s="70"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="64"/>
+      <c r="G17" s="64"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="64"/>
+      <c r="K17" s="64"/>
+      <c r="L17" s="64"/>
+      <c r="M17" s="64"/>
+      <c r="N17" s="64"/>
+      <c r="O17" s="64"/>
+      <c r="P17" s="64"/>
+      <c r="Q17" s="64"/>
+      <c r="R17" s="64"/>
+      <c r="S17" s="64"/>
+      <c r="T17" s="64"/>
+      <c r="U17" s="64"/>
+      <c r="V17" s="64"/>
+      <c r="W17" s="64"/>
+      <c r="X17" s="64"/>
+      <c r="Y17" s="64"/>
+      <c r="Z17" s="64"/>
+      <c r="AA17" s="71"/>
+      <c r="AB17" s="71"/>
+      <c r="AC17" s="64"/>
+      <c r="AD17" s="64"/>
+      <c r="AE17" s="64"/>
+      <c r="AF17" s="64"/>
+      <c r="AG17" s="64"/>
+      <c r="AH17" s="64"/>
+      <c r="AI17" s="64"/>
+      <c r="AJ17" s="64"/>
+      <c r="AK17" s="64"/>
+      <c r="AL17" s="64"/>
+      <c r="AM17" s="64"/>
+      <c r="AN17" s="64"/>
+      <c r="AO17" s="64"/>
+      <c r="AP17" s="64"/>
+      <c r="AQ17" s="64"/>
+      <c r="AR17" s="64"/>
+      <c r="AS17" s="64"/>
+      <c r="AT17" s="64"/>
+      <c r="AU17" s="64"/>
+      <c r="AV17" s="64"/>
+      <c r="AW17" s="64"/>
+      <c r="AX17" s="64"/>
+      <c r="AY17" s="64"/>
+      <c r="AZ17" s="64"/>
+      <c r="BA17" s="64"/>
+      <c r="BB17" s="64"/>
+      <c r="BC17" s="64"/>
+      <c r="BD17" s="64"/>
+      <c r="BE17" s="64"/>
+      <c r="BF17" s="64"/>
+      <c r="BG17" s="64"/>
+      <c r="BH17" s="64"/>
+      <c r="BI17" s="64"/>
     </row>
     <row r="18" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="15"/>
-      <c r="S18" s="15"/>
-      <c r="T18" s="15"/>
-      <c r="U18" s="15"/>
-      <c r="V18" s="15"/>
-      <c r="W18" s="15"/>
-      <c r="X18" s="15"/>
-      <c r="Y18" s="15"/>
-      <c r="Z18" s="15"/>
-      <c r="AA18" s="17"/>
-      <c r="AB18" s="17"/>
-      <c r="AC18" s="15"/>
-      <c r="AD18" s="15"/>
-      <c r="AE18" s="15"/>
-      <c r="AF18" s="15"/>
-      <c r="AG18" s="15"/>
-      <c r="AH18" s="15"/>
-      <c r="AI18" s="15"/>
-      <c r="AJ18" s="15"/>
-      <c r="AK18" s="15"/>
-      <c r="AL18" s="15"/>
-      <c r="AM18" s="15"/>
-      <c r="AN18" s="15"/>
-      <c r="AO18" s="15"/>
-      <c r="AP18" s="15"/>
-      <c r="AQ18" s="15"/>
-      <c r="AR18" s="15"/>
-      <c r="AS18" s="15"/>
-      <c r="AT18" s="15"/>
-      <c r="AU18" s="15"/>
-      <c r="AV18" s="15"/>
-      <c r="AW18" s="15"/>
-      <c r="AX18" s="15"/>
-      <c r="AY18" s="15"/>
-      <c r="AZ18" s="15"/>
-      <c r="BA18" s="15"/>
-      <c r="BB18" s="15"/>
-      <c r="BC18" s="15"/>
-      <c r="BD18" s="15"/>
-      <c r="BE18" s="15"/>
-      <c r="BF18" s="15"/>
-      <c r="BG18" s="15"/>
-      <c r="BH18" s="15"/>
-      <c r="BI18" s="15"/>
+      <c r="A18" s="70"/>
+      <c r="B18" s="70"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="64"/>
+      <c r="G18" s="64"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="64"/>
+      <c r="K18" s="64"/>
+      <c r="L18" s="64"/>
+      <c r="M18" s="64"/>
+      <c r="N18" s="64"/>
+      <c r="O18" s="64"/>
+      <c r="P18" s="64"/>
+      <c r="Q18" s="64"/>
+      <c r="R18" s="64"/>
+      <c r="S18" s="64"/>
+      <c r="T18" s="64"/>
+      <c r="U18" s="64"/>
+      <c r="V18" s="64"/>
+      <c r="W18" s="64"/>
+      <c r="X18" s="64"/>
+      <c r="Y18" s="64"/>
+      <c r="Z18" s="64"/>
+      <c r="AA18" s="71"/>
+      <c r="AB18" s="71"/>
+      <c r="AC18" s="64"/>
+      <c r="AD18" s="64"/>
+      <c r="AE18" s="64"/>
+      <c r="AF18" s="64"/>
+      <c r="AG18" s="64"/>
+      <c r="AH18" s="64"/>
+      <c r="AI18" s="64"/>
+      <c r="AJ18" s="64"/>
+      <c r="AK18" s="64"/>
+      <c r="AL18" s="64"/>
+      <c r="AM18" s="64"/>
+      <c r="AN18" s="64"/>
+      <c r="AO18" s="64"/>
+      <c r="AP18" s="64"/>
+      <c r="AQ18" s="64"/>
+      <c r="AR18" s="64"/>
+      <c r="AS18" s="64"/>
+      <c r="AT18" s="64"/>
+      <c r="AU18" s="64"/>
+      <c r="AV18" s="64"/>
+      <c r="AW18" s="64"/>
+      <c r="AX18" s="64"/>
+      <c r="AY18" s="64"/>
+      <c r="AZ18" s="64"/>
+      <c r="BA18" s="64"/>
+      <c r="BB18" s="64"/>
+      <c r="BC18" s="64"/>
+      <c r="BD18" s="64"/>
+      <c r="BE18" s="64"/>
+      <c r="BF18" s="64"/>
+      <c r="BG18" s="64"/>
+      <c r="BH18" s="64"/>
+      <c r="BI18" s="64"/>
     </row>
     <row r="19" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="15"/>
-      <c r="R19" s="15"/>
-      <c r="S19" s="15"/>
-      <c r="T19" s="15"/>
-      <c r="U19" s="15"/>
-      <c r="V19" s="15"/>
-      <c r="W19" s="15"/>
-      <c r="X19" s="15"/>
-      <c r="Y19" s="15"/>
-      <c r="Z19" s="15"/>
-      <c r="AA19" s="17"/>
-      <c r="AB19" s="17"/>
-      <c r="AC19" s="15"/>
-      <c r="AD19" s="15"/>
-      <c r="AE19" s="15"/>
-      <c r="AF19" s="15"/>
-      <c r="AG19" s="15"/>
-      <c r="AH19" s="15"/>
-      <c r="AI19" s="15"/>
-      <c r="AJ19" s="15"/>
-      <c r="AK19" s="15"/>
-      <c r="AL19" s="15"/>
-      <c r="AM19" s="15"/>
-      <c r="AN19" s="15"/>
-      <c r="AO19" s="15"/>
-      <c r="AP19" s="15"/>
-      <c r="AQ19" s="15"/>
-      <c r="AR19" s="15"/>
-      <c r="AS19" s="15"/>
-      <c r="AT19" s="15"/>
-      <c r="AU19" s="15"/>
-      <c r="AV19" s="15"/>
-      <c r="AW19" s="15"/>
-      <c r="AX19" s="15"/>
-      <c r="AY19" s="15"/>
-      <c r="AZ19" s="15"/>
-      <c r="BA19" s="15"/>
-      <c r="BB19" s="15"/>
-      <c r="BC19" s="15"/>
-      <c r="BD19" s="15"/>
-      <c r="BE19" s="15"/>
-      <c r="BF19" s="15"/>
-      <c r="BG19" s="15"/>
-      <c r="BH19" s="15"/>
-      <c r="BI19" s="15"/>
+      <c r="A19" s="70"/>
+      <c r="B19" s="70"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="64"/>
+      <c r="F19" s="64"/>
+      <c r="G19" s="64"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="64"/>
+      <c r="J19" s="64"/>
+      <c r="K19" s="64"/>
+      <c r="L19" s="64"/>
+      <c r="M19" s="64"/>
+      <c r="N19" s="64"/>
+      <c r="O19" s="64"/>
+      <c r="P19" s="64"/>
+      <c r="Q19" s="64"/>
+      <c r="R19" s="64"/>
+      <c r="S19" s="64"/>
+      <c r="T19" s="64"/>
+      <c r="U19" s="64"/>
+      <c r="V19" s="64"/>
+      <c r="W19" s="64"/>
+      <c r="X19" s="64"/>
+      <c r="Y19" s="64"/>
+      <c r="Z19" s="64"/>
+      <c r="AA19" s="71"/>
+      <c r="AB19" s="71"/>
+      <c r="AC19" s="64"/>
+      <c r="AD19" s="64"/>
+      <c r="AE19" s="64"/>
+      <c r="AF19" s="64"/>
+      <c r="AG19" s="64"/>
+      <c r="AH19" s="64"/>
+      <c r="AI19" s="64"/>
+      <c r="AJ19" s="64"/>
+      <c r="AK19" s="64"/>
+      <c r="AL19" s="64"/>
+      <c r="AM19" s="64"/>
+      <c r="AN19" s="64"/>
+      <c r="AO19" s="64"/>
+      <c r="AP19" s="64"/>
+      <c r="AQ19" s="64"/>
+      <c r="AR19" s="64"/>
+      <c r="AS19" s="64"/>
+      <c r="AT19" s="64"/>
+      <c r="AU19" s="64"/>
+      <c r="AV19" s="64"/>
+      <c r="AW19" s="64"/>
+      <c r="AX19" s="64"/>
+      <c r="AY19" s="64"/>
+      <c r="AZ19" s="64"/>
+      <c r="BA19" s="64"/>
+      <c r="BB19" s="64"/>
+      <c r="BC19" s="64"/>
+      <c r="BD19" s="64"/>
+      <c r="BE19" s="64"/>
+      <c r="BF19" s="64"/>
+      <c r="BG19" s="64"/>
+      <c r="BH19" s="64"/>
+      <c r="BI19" s="64"/>
     </row>
     <row r="20" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="15"/>
-      <c r="O20" s="15"/>
-      <c r="P20" s="15"/>
-      <c r="Q20" s="15"/>
-      <c r="R20" s="15"/>
-      <c r="S20" s="15"/>
-      <c r="T20" s="15"/>
-      <c r="U20" s="15"/>
-      <c r="V20" s="15"/>
-      <c r="W20" s="15"/>
-      <c r="X20" s="15"/>
-      <c r="Y20" s="15"/>
-      <c r="Z20" s="15"/>
-      <c r="AA20" s="17"/>
-      <c r="AB20" s="17"/>
-      <c r="AC20" s="15"/>
-      <c r="AD20" s="15"/>
-      <c r="AE20" s="15"/>
-      <c r="AF20" s="15"/>
-      <c r="AG20" s="15"/>
-      <c r="AH20" s="15"/>
-      <c r="AI20" s="15"/>
-      <c r="AJ20" s="15"/>
-      <c r="AK20" s="15"/>
-      <c r="AL20" s="15"/>
-      <c r="AM20" s="15"/>
-      <c r="AN20" s="15"/>
-      <c r="AO20" s="15"/>
-      <c r="AP20" s="15"/>
-      <c r="AQ20" s="15"/>
-      <c r="AR20" s="15"/>
-      <c r="AS20" s="15"/>
-      <c r="AT20" s="15"/>
-      <c r="AU20" s="15"/>
-      <c r="AV20" s="15"/>
-      <c r="AW20" s="15"/>
-      <c r="AX20" s="15"/>
-      <c r="AY20" s="15"/>
-      <c r="AZ20" s="15"/>
-      <c r="BA20" s="15"/>
-      <c r="BB20" s="15"/>
-      <c r="BC20" s="15"/>
-      <c r="BD20" s="15"/>
-      <c r="BE20" s="15"/>
-      <c r="BF20" s="15"/>
-      <c r="BG20" s="15"/>
-      <c r="BH20" s="15"/>
-      <c r="BI20" s="15"/>
+      <c r="A20" s="70"/>
+      <c r="B20" s="70"/>
+      <c r="C20" s="64"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="64"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="64"/>
+      <c r="K20" s="64"/>
+      <c r="L20" s="64"/>
+      <c r="M20" s="64"/>
+      <c r="N20" s="64"/>
+      <c r="O20" s="64"/>
+      <c r="P20" s="64"/>
+      <c r="Q20" s="64"/>
+      <c r="R20" s="64"/>
+      <c r="S20" s="64"/>
+      <c r="T20" s="64"/>
+      <c r="U20" s="64"/>
+      <c r="V20" s="64"/>
+      <c r="W20" s="64"/>
+      <c r="X20" s="64"/>
+      <c r="Y20" s="64"/>
+      <c r="Z20" s="64"/>
+      <c r="AA20" s="71"/>
+      <c r="AB20" s="71"/>
+      <c r="AC20" s="64"/>
+      <c r="AD20" s="64"/>
+      <c r="AE20" s="64"/>
+      <c r="AF20" s="64"/>
+      <c r="AG20" s="64"/>
+      <c r="AH20" s="64"/>
+      <c r="AI20" s="64"/>
+      <c r="AJ20" s="64"/>
+      <c r="AK20" s="64"/>
+      <c r="AL20" s="64"/>
+      <c r="AM20" s="64"/>
+      <c r="AN20" s="64"/>
+      <c r="AO20" s="64"/>
+      <c r="AP20" s="64"/>
+      <c r="AQ20" s="64"/>
+      <c r="AR20" s="64"/>
+      <c r="AS20" s="64"/>
+      <c r="AT20" s="64"/>
+      <c r="AU20" s="64"/>
+      <c r="AV20" s="64"/>
+      <c r="AW20" s="64"/>
+      <c r="AX20" s="64"/>
+      <c r="AY20" s="64"/>
+      <c r="AZ20" s="64"/>
+      <c r="BA20" s="64"/>
+      <c r="BB20" s="64"/>
+      <c r="BC20" s="64"/>
+      <c r="BD20" s="64"/>
+      <c r="BE20" s="64"/>
+      <c r="BF20" s="64"/>
+      <c r="BG20" s="64"/>
+      <c r="BH20" s="64"/>
+      <c r="BI20" s="64"/>
     </row>
     <row r="21" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="15"/>
-      <c r="R21" s="15"/>
-      <c r="S21" s="15"/>
-      <c r="T21" s="15"/>
-      <c r="U21" s="15"/>
-      <c r="V21" s="15"/>
-      <c r="W21" s="15"/>
-      <c r="X21" s="15"/>
-      <c r="Y21" s="15"/>
-      <c r="Z21" s="15"/>
-      <c r="AA21" s="17"/>
-      <c r="AB21" s="17"/>
-      <c r="AC21" s="15"/>
-      <c r="AD21" s="15"/>
-      <c r="AE21" s="15"/>
-      <c r="AF21" s="15"/>
-      <c r="AG21" s="15"/>
-      <c r="AH21" s="15"/>
-      <c r="AI21" s="15"/>
-      <c r="AJ21" s="15"/>
-      <c r="AK21" s="15"/>
-      <c r="AL21" s="15"/>
-      <c r="AM21" s="15"/>
-      <c r="AN21" s="15"/>
-      <c r="AO21" s="15"/>
-      <c r="AP21" s="15"/>
-      <c r="AQ21" s="15"/>
-      <c r="AR21" s="15"/>
-      <c r="AS21" s="15"/>
-      <c r="AT21" s="15"/>
-      <c r="AU21" s="15"/>
-      <c r="AV21" s="15"/>
-      <c r="AW21" s="15"/>
-      <c r="AX21" s="15"/>
-      <c r="AY21" s="15"/>
-      <c r="AZ21" s="15"/>
-      <c r="BA21" s="15"/>
-      <c r="BB21" s="15"/>
-      <c r="BC21" s="15"/>
-      <c r="BD21" s="15"/>
-      <c r="BE21" s="15"/>
-      <c r="BF21" s="15"/>
-      <c r="BG21" s="15"/>
-      <c r="BH21" s="15"/>
-      <c r="BI21" s="15"/>
+      <c r="A21" s="70"/>
+      <c r="B21" s="70"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="64"/>
+      <c r="K21" s="64"/>
+      <c r="L21" s="64"/>
+      <c r="M21" s="64"/>
+      <c r="N21" s="64"/>
+      <c r="O21" s="64"/>
+      <c r="P21" s="64"/>
+      <c r="Q21" s="64"/>
+      <c r="R21" s="64"/>
+      <c r="S21" s="64"/>
+      <c r="T21" s="64"/>
+      <c r="U21" s="64"/>
+      <c r="V21" s="64"/>
+      <c r="W21" s="64"/>
+      <c r="X21" s="64"/>
+      <c r="Y21" s="64"/>
+      <c r="Z21" s="64"/>
+      <c r="AA21" s="71"/>
+      <c r="AB21" s="71"/>
+      <c r="AC21" s="64"/>
+      <c r="AD21" s="64"/>
+      <c r="AE21" s="64"/>
+      <c r="AF21" s="64"/>
+      <c r="AG21" s="64"/>
+      <c r="AH21" s="64"/>
+      <c r="AI21" s="64"/>
+      <c r="AJ21" s="64"/>
+      <c r="AK21" s="64"/>
+      <c r="AL21" s="64"/>
+      <c r="AM21" s="64"/>
+      <c r="AN21" s="64"/>
+      <c r="AO21" s="64"/>
+      <c r="AP21" s="64"/>
+      <c r="AQ21" s="64"/>
+      <c r="AR21" s="64"/>
+      <c r="AS21" s="64"/>
+      <c r="AT21" s="64"/>
+      <c r="AU21" s="64"/>
+      <c r="AV21" s="64"/>
+      <c r="AW21" s="64"/>
+      <c r="AX21" s="64"/>
+      <c r="AY21" s="64"/>
+      <c r="AZ21" s="64"/>
+      <c r="BA21" s="64"/>
+      <c r="BB21" s="64"/>
+      <c r="BC21" s="64"/>
+      <c r="BD21" s="64"/>
+      <c r="BE21" s="64"/>
+      <c r="BF21" s="64"/>
+      <c r="BG21" s="64"/>
+      <c r="BH21" s="64"/>
+      <c r="BI21" s="64"/>
     </row>
     <row r="22" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
-      <c r="P22" s="15"/>
-      <c r="Q22" s="15"/>
-      <c r="R22" s="15"/>
-      <c r="S22" s="15"/>
-      <c r="T22" s="15"/>
-      <c r="U22" s="15"/>
-      <c r="V22" s="15"/>
-      <c r="W22" s="15"/>
-      <c r="X22" s="15"/>
-      <c r="Y22" s="15"/>
-      <c r="Z22" s="15"/>
-      <c r="AA22" s="17"/>
-      <c r="AB22" s="17"/>
-      <c r="AC22" s="15"/>
-      <c r="AD22" s="15"/>
-      <c r="AE22" s="15"/>
-      <c r="AF22" s="15"/>
-      <c r="AG22" s="15"/>
-      <c r="AH22" s="15"/>
-      <c r="AI22" s="15"/>
-      <c r="AJ22" s="15"/>
-      <c r="AK22" s="15"/>
-      <c r="AL22" s="15"/>
-      <c r="AM22" s="15"/>
-      <c r="AN22" s="15"/>
-      <c r="AO22" s="15"/>
-      <c r="AP22" s="15"/>
-      <c r="AQ22" s="15"/>
-      <c r="AR22" s="15"/>
-      <c r="AS22" s="15"/>
-      <c r="AT22" s="15"/>
-      <c r="AU22" s="15"/>
-      <c r="AV22" s="15"/>
-      <c r="AW22" s="15"/>
-      <c r="AX22" s="15"/>
-      <c r="AY22" s="15"/>
-      <c r="AZ22" s="15"/>
-      <c r="BA22" s="15"/>
-      <c r="BB22" s="15"/>
-      <c r="BC22" s="15"/>
-      <c r="BD22" s="15"/>
-      <c r="BE22" s="15"/>
-      <c r="BF22" s="15"/>
-      <c r="BG22" s="15"/>
-      <c r="BH22" s="15"/>
-      <c r="BI22" s="15"/>
+      <c r="A22" s="70"/>
+      <c r="B22" s="70"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="64"/>
+      <c r="F22" s="64"/>
+      <c r="G22" s="64"/>
+      <c r="H22" s="64"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="64"/>
+      <c r="K22" s="64"/>
+      <c r="L22" s="64"/>
+      <c r="M22" s="64"/>
+      <c r="N22" s="64"/>
+      <c r="O22" s="64"/>
+      <c r="P22" s="64"/>
+      <c r="Q22" s="64"/>
+      <c r="R22" s="64"/>
+      <c r="S22" s="64"/>
+      <c r="T22" s="64"/>
+      <c r="U22" s="64"/>
+      <c r="V22" s="64"/>
+      <c r="W22" s="64"/>
+      <c r="X22" s="64"/>
+      <c r="Y22" s="64"/>
+      <c r="Z22" s="64"/>
+      <c r="AA22" s="71"/>
+      <c r="AB22" s="71"/>
+      <c r="AC22" s="64"/>
+      <c r="AD22" s="64"/>
+      <c r="AE22" s="64"/>
+      <c r="AF22" s="64"/>
+      <c r="AG22" s="64"/>
+      <c r="AH22" s="64"/>
+      <c r="AI22" s="64"/>
+      <c r="AJ22" s="64"/>
+      <c r="AK22" s="64"/>
+      <c r="AL22" s="64"/>
+      <c r="AM22" s="64"/>
+      <c r="AN22" s="64"/>
+      <c r="AO22" s="64"/>
+      <c r="AP22" s="64"/>
+      <c r="AQ22" s="64"/>
+      <c r="AR22" s="64"/>
+      <c r="AS22" s="64"/>
+      <c r="AT22" s="64"/>
+      <c r="AU22" s="64"/>
+      <c r="AV22" s="64"/>
+      <c r="AW22" s="64"/>
+      <c r="AX22" s="64"/>
+      <c r="AY22" s="64"/>
+      <c r="AZ22" s="64"/>
+      <c r="BA22" s="64"/>
+      <c r="BB22" s="64"/>
+      <c r="BC22" s="64"/>
+      <c r="BD22" s="64"/>
+      <c r="BE22" s="64"/>
+      <c r="BF22" s="64"/>
+      <c r="BG22" s="64"/>
+      <c r="BH22" s="64"/>
+      <c r="BI22" s="64"/>
     </row>
     <row r="23" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="15"/>
-      <c r="R23" s="15"/>
-      <c r="S23" s="15"/>
-      <c r="T23" s="15"/>
-      <c r="U23" s="15"/>
-      <c r="V23" s="15"/>
-      <c r="W23" s="15"/>
-      <c r="X23" s="15"/>
-      <c r="Y23" s="15"/>
-      <c r="Z23" s="15"/>
-      <c r="AA23" s="17"/>
-      <c r="AB23" s="17"/>
-      <c r="AC23" s="15"/>
-      <c r="AD23" s="15"/>
-      <c r="AE23" s="15"/>
-      <c r="AF23" s="15"/>
-      <c r="AG23" s="15"/>
-      <c r="AH23" s="15"/>
-      <c r="AI23" s="15"/>
-      <c r="AJ23" s="15"/>
-      <c r="AK23" s="15"/>
-      <c r="AL23" s="15"/>
-      <c r="AM23" s="15"/>
-      <c r="AN23" s="15"/>
-      <c r="AO23" s="15"/>
-      <c r="AP23" s="15"/>
-      <c r="AQ23" s="15"/>
-      <c r="AR23" s="15"/>
-      <c r="AS23" s="15"/>
-      <c r="AT23" s="15"/>
-      <c r="AU23" s="15"/>
-      <c r="AV23" s="15"/>
-      <c r="AW23" s="15"/>
-      <c r="AX23" s="15"/>
-      <c r="AY23" s="15"/>
-      <c r="AZ23" s="15"/>
-      <c r="BA23" s="15"/>
-      <c r="BB23" s="15"/>
-      <c r="BC23" s="15"/>
-      <c r="BD23" s="15"/>
-      <c r="BE23" s="15"/>
-      <c r="BF23" s="15"/>
-      <c r="BG23" s="15"/>
-      <c r="BH23" s="15"/>
-      <c r="BI23" s="15"/>
+      <c r="A23" s="70"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="64"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="64"/>
+      <c r="J23" s="64"/>
+      <c r="K23" s="64"/>
+      <c r="L23" s="64"/>
+      <c r="M23" s="64"/>
+      <c r="N23" s="64"/>
+      <c r="O23" s="64"/>
+      <c r="P23" s="64"/>
+      <c r="Q23" s="64"/>
+      <c r="R23" s="64"/>
+      <c r="S23" s="64"/>
+      <c r="T23" s="64"/>
+      <c r="U23" s="64"/>
+      <c r="V23" s="64"/>
+      <c r="W23" s="64"/>
+      <c r="X23" s="64"/>
+      <c r="Y23" s="64"/>
+      <c r="Z23" s="64"/>
+      <c r="AA23" s="71"/>
+      <c r="AB23" s="71"/>
+      <c r="AC23" s="64"/>
+      <c r="AD23" s="64"/>
+      <c r="AE23" s="64"/>
+      <c r="AF23" s="64"/>
+      <c r="AG23" s="64"/>
+      <c r="AH23" s="64"/>
+      <c r="AI23" s="64"/>
+      <c r="AJ23" s="64"/>
+      <c r="AK23" s="64"/>
+      <c r="AL23" s="64"/>
+      <c r="AM23" s="64"/>
+      <c r="AN23" s="64"/>
+      <c r="AO23" s="64"/>
+      <c r="AP23" s="64"/>
+      <c r="AQ23" s="64"/>
+      <c r="AR23" s="64"/>
+      <c r="AS23" s="64"/>
+      <c r="AT23" s="64"/>
+      <c r="AU23" s="64"/>
+      <c r="AV23" s="64"/>
+      <c r="AW23" s="64"/>
+      <c r="AX23" s="64"/>
+      <c r="AY23" s="64"/>
+      <c r="AZ23" s="64"/>
+      <c r="BA23" s="64"/>
+      <c r="BB23" s="64"/>
+      <c r="BC23" s="64"/>
+      <c r="BD23" s="64"/>
+      <c r="BE23" s="64"/>
+      <c r="BF23" s="64"/>
+      <c r="BG23" s="64"/>
+      <c r="BH23" s="64"/>
+      <c r="BI23" s="64"/>
     </row>
     <row r="24" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="15"/>
-      <c r="O24" s="15"/>
-      <c r="P24" s="15"/>
-      <c r="Q24" s="15"/>
-      <c r="R24" s="15"/>
-      <c r="S24" s="15"/>
-      <c r="T24" s="15"/>
-      <c r="U24" s="15"/>
-      <c r="V24" s="15"/>
-      <c r="W24" s="15"/>
-      <c r="X24" s="15"/>
-      <c r="Y24" s="15"/>
-      <c r="Z24" s="15"/>
-      <c r="AA24" s="17"/>
-      <c r="AB24" s="17"/>
-      <c r="AC24" s="15"/>
-      <c r="AD24" s="15"/>
-      <c r="AE24" s="15"/>
-      <c r="AF24" s="15"/>
-      <c r="AG24" s="15"/>
-      <c r="AH24" s="15"/>
-      <c r="AI24" s="15"/>
-      <c r="AJ24" s="15"/>
-      <c r="AK24" s="15"/>
-      <c r="AL24" s="15"/>
-      <c r="AM24" s="15"/>
-      <c r="AN24" s="15"/>
-      <c r="AO24" s="15"/>
-      <c r="AP24" s="15"/>
-      <c r="AQ24" s="15"/>
-      <c r="AR24" s="15"/>
-      <c r="AS24" s="15"/>
-      <c r="AT24" s="15"/>
-      <c r="AU24" s="15"/>
-      <c r="AV24" s="15"/>
-      <c r="AW24" s="15"/>
-      <c r="AX24" s="15"/>
-      <c r="AY24" s="15"/>
-      <c r="AZ24" s="15"/>
-      <c r="BA24" s="15"/>
-      <c r="BB24" s="15"/>
-      <c r="BC24" s="15"/>
-      <c r="BD24" s="15"/>
-      <c r="BE24" s="15"/>
-      <c r="BF24" s="15"/>
-      <c r="BG24" s="15"/>
-      <c r="BH24" s="15"/>
-      <c r="BI24" s="15"/>
+      <c r="A24" s="70"/>
+      <c r="B24" s="70"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="64"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="64"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="64"/>
+      <c r="K24" s="64"/>
+      <c r="L24" s="64"/>
+      <c r="M24" s="64"/>
+      <c r="N24" s="64"/>
+      <c r="O24" s="64"/>
+      <c r="P24" s="64"/>
+      <c r="Q24" s="64"/>
+      <c r="R24" s="64"/>
+      <c r="S24" s="64"/>
+      <c r="T24" s="64"/>
+      <c r="U24" s="64"/>
+      <c r="V24" s="64"/>
+      <c r="W24" s="64"/>
+      <c r="X24" s="64"/>
+      <c r="Y24" s="64"/>
+      <c r="Z24" s="64"/>
+      <c r="AA24" s="71"/>
+      <c r="AB24" s="71"/>
+      <c r="AC24" s="64"/>
+      <c r="AD24" s="64"/>
+      <c r="AE24" s="64"/>
+      <c r="AF24" s="64"/>
+      <c r="AG24" s="64"/>
+      <c r="AH24" s="64"/>
+      <c r="AI24" s="64"/>
+      <c r="AJ24" s="64"/>
+      <c r="AK24" s="64"/>
+      <c r="AL24" s="64"/>
+      <c r="AM24" s="64"/>
+      <c r="AN24" s="64"/>
+      <c r="AO24" s="64"/>
+      <c r="AP24" s="64"/>
+      <c r="AQ24" s="64"/>
+      <c r="AR24" s="64"/>
+      <c r="AS24" s="64"/>
+      <c r="AT24" s="64"/>
+      <c r="AU24" s="64"/>
+      <c r="AV24" s="64"/>
+      <c r="AW24" s="64"/>
+      <c r="AX24" s="64"/>
+      <c r="AY24" s="64"/>
+      <c r="AZ24" s="64"/>
+      <c r="BA24" s="64"/>
+      <c r="BB24" s="64"/>
+      <c r="BC24" s="64"/>
+      <c r="BD24" s="64"/>
+      <c r="BE24" s="64"/>
+      <c r="BF24" s="64"/>
+      <c r="BG24" s="64"/>
+      <c r="BH24" s="64"/>
+      <c r="BI24" s="64"/>
     </row>
     <row r="25" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="15"/>
-      <c r="S25" s="15"/>
-      <c r="T25" s="15"/>
-      <c r="U25" s="15"/>
-      <c r="V25" s="15"/>
-      <c r="W25" s="15"/>
-      <c r="X25" s="15"/>
-      <c r="Y25" s="15"/>
-      <c r="Z25" s="15"/>
-      <c r="AA25" s="17"/>
-      <c r="AB25" s="17"/>
-      <c r="AC25" s="15"/>
-      <c r="AD25" s="15"/>
-      <c r="AE25" s="15"/>
-      <c r="AF25" s="15"/>
-      <c r="AG25" s="15"/>
-      <c r="AH25" s="15"/>
-      <c r="AI25" s="15"/>
-      <c r="AJ25" s="15"/>
-      <c r="AK25" s="15"/>
-      <c r="AL25" s="15"/>
-      <c r="AM25" s="15"/>
-      <c r="AN25" s="15"/>
-      <c r="AO25" s="15"/>
-      <c r="AP25" s="15"/>
-      <c r="AQ25" s="15"/>
-      <c r="AR25" s="15"/>
-      <c r="AS25" s="15"/>
-      <c r="AT25" s="15"/>
-      <c r="AU25" s="15"/>
-      <c r="AV25" s="15"/>
-      <c r="AW25" s="15"/>
-      <c r="AX25" s="15"/>
-      <c r="AY25" s="15"/>
-      <c r="AZ25" s="15"/>
-      <c r="BA25" s="15"/>
-      <c r="BB25" s="15"/>
-      <c r="BC25" s="15"/>
-      <c r="BD25" s="15"/>
-      <c r="BE25" s="15"/>
-      <c r="BF25" s="15"/>
-      <c r="BG25" s="15"/>
-      <c r="BH25" s="15"/>
-      <c r="BI25" s="15"/>
+      <c r="A25" s="70"/>
+      <c r="B25" s="70"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="64"/>
+      <c r="F25" s="64"/>
+      <c r="G25" s="64"/>
+      <c r="H25" s="64"/>
+      <c r="I25" s="64"/>
+      <c r="J25" s="64"/>
+      <c r="K25" s="64"/>
+      <c r="L25" s="64"/>
+      <c r="M25" s="64"/>
+      <c r="N25" s="64"/>
+      <c r="O25" s="64"/>
+      <c r="P25" s="64"/>
+      <c r="Q25" s="64"/>
+      <c r="R25" s="64"/>
+      <c r="S25" s="64"/>
+      <c r="T25" s="64"/>
+      <c r="U25" s="64"/>
+      <c r="V25" s="64"/>
+      <c r="W25" s="64"/>
+      <c r="X25" s="64"/>
+      <c r="Y25" s="64"/>
+      <c r="Z25" s="64"/>
+      <c r="AA25" s="71"/>
+      <c r="AB25" s="71"/>
+      <c r="AC25" s="64"/>
+      <c r="AD25" s="64"/>
+      <c r="AE25" s="64"/>
+      <c r="AF25" s="64"/>
+      <c r="AG25" s="64"/>
+      <c r="AH25" s="64"/>
+      <c r="AI25" s="64"/>
+      <c r="AJ25" s="64"/>
+      <c r="AK25" s="64"/>
+      <c r="AL25" s="64"/>
+      <c r="AM25" s="64"/>
+      <c r="AN25" s="64"/>
+      <c r="AO25" s="64"/>
+      <c r="AP25" s="64"/>
+      <c r="AQ25" s="64"/>
+      <c r="AR25" s="64"/>
+      <c r="AS25" s="64"/>
+      <c r="AT25" s="64"/>
+      <c r="AU25" s="64"/>
+      <c r="AV25" s="64"/>
+      <c r="AW25" s="64"/>
+      <c r="AX25" s="64"/>
+      <c r="AY25" s="64"/>
+      <c r="AZ25" s="64"/>
+      <c r="BA25" s="64"/>
+      <c r="BB25" s="64"/>
+      <c r="BC25" s="64"/>
+      <c r="BD25" s="64"/>
+      <c r="BE25" s="64"/>
+      <c r="BF25" s="64"/>
+      <c r="BG25" s="64"/>
+      <c r="BH25" s="64"/>
+      <c r="BI25" s="64"/>
     </row>
     <row r="26" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
-      <c r="O26" s="15"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="15"/>
-      <c r="R26" s="15"/>
-      <c r="S26" s="15"/>
-      <c r="T26" s="15"/>
-      <c r="U26" s="15"/>
-      <c r="V26" s="15"/>
-      <c r="W26" s="15"/>
-      <c r="X26" s="15"/>
-      <c r="Y26" s="15"/>
-      <c r="Z26" s="15"/>
-      <c r="AA26" s="17"/>
-      <c r="AB26" s="17"/>
-      <c r="AC26" s="15"/>
-      <c r="AD26" s="15"/>
-      <c r="AE26" s="15"/>
-      <c r="AF26" s="15"/>
-      <c r="AG26" s="15"/>
-      <c r="AH26" s="15"/>
-      <c r="AI26" s="15"/>
-      <c r="AJ26" s="15"/>
-      <c r="AK26" s="15"/>
-      <c r="AL26" s="15"/>
-      <c r="AM26" s="15"/>
-      <c r="AN26" s="15"/>
-      <c r="AO26" s="15"/>
-      <c r="AP26" s="15"/>
-      <c r="AQ26" s="15"/>
-      <c r="AR26" s="15"/>
-      <c r="AS26" s="15"/>
-      <c r="AT26" s="15"/>
-      <c r="AU26" s="15"/>
-      <c r="AV26" s="15"/>
-      <c r="AW26" s="15"/>
-      <c r="AX26" s="15"/>
-      <c r="AY26" s="15"/>
-      <c r="AZ26" s="15"/>
-      <c r="BA26" s="15"/>
-      <c r="BB26" s="15"/>
-      <c r="BC26" s="15"/>
-      <c r="BD26" s="15"/>
-      <c r="BE26" s="15"/>
-      <c r="BF26" s="15"/>
-      <c r="BG26" s="15"/>
-      <c r="BH26" s="15"/>
-      <c r="BI26" s="15"/>
+      <c r="A26" s="70"/>
+      <c r="B26" s="70"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64"/>
+      <c r="F26" s="64"/>
+      <c r="G26" s="64"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="64"/>
+      <c r="J26" s="64"/>
+      <c r="K26" s="64"/>
+      <c r="L26" s="64"/>
+      <c r="M26" s="64"/>
+      <c r="N26" s="64"/>
+      <c r="O26" s="64"/>
+      <c r="P26" s="64"/>
+      <c r="Q26" s="64"/>
+      <c r="R26" s="64"/>
+      <c r="S26" s="64"/>
+      <c r="T26" s="64"/>
+      <c r="U26" s="64"/>
+      <c r="V26" s="64"/>
+      <c r="W26" s="64"/>
+      <c r="X26" s="64"/>
+      <c r="Y26" s="64"/>
+      <c r="Z26" s="64"/>
+      <c r="AA26" s="71"/>
+      <c r="AB26" s="71"/>
+      <c r="AC26" s="64"/>
+      <c r="AD26" s="64"/>
+      <c r="AE26" s="64"/>
+      <c r="AF26" s="64"/>
+      <c r="AG26" s="64"/>
+      <c r="AH26" s="64"/>
+      <c r="AI26" s="64"/>
+      <c r="AJ26" s="64"/>
+      <c r="AK26" s="64"/>
+      <c r="AL26" s="64"/>
+      <c r="AM26" s="64"/>
+      <c r="AN26" s="64"/>
+      <c r="AO26" s="64"/>
+      <c r="AP26" s="64"/>
+      <c r="AQ26" s="64"/>
+      <c r="AR26" s="64"/>
+      <c r="AS26" s="64"/>
+      <c r="AT26" s="64"/>
+      <c r="AU26" s="64"/>
+      <c r="AV26" s="64"/>
+      <c r="AW26" s="64"/>
+      <c r="AX26" s="64"/>
+      <c r="AY26" s="64"/>
+      <c r="AZ26" s="64"/>
+      <c r="BA26" s="64"/>
+      <c r="BB26" s="64"/>
+      <c r="BC26" s="64"/>
+      <c r="BD26" s="64"/>
+      <c r="BE26" s="64"/>
+      <c r="BF26" s="64"/>
+      <c r="BG26" s="64"/>
+      <c r="BH26" s="64"/>
+      <c r="BI26" s="64"/>
     </row>
     <row r="27" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="15"/>
-      <c r="R27" s="15"/>
-      <c r="S27" s="15"/>
-      <c r="T27" s="15"/>
-      <c r="U27" s="15"/>
-      <c r="V27" s="15"/>
-      <c r="W27" s="15"/>
-      <c r="X27" s="15"/>
-      <c r="Y27" s="15"/>
-      <c r="Z27" s="15"/>
-      <c r="AA27" s="17"/>
-      <c r="AB27" s="17"/>
-      <c r="AC27" s="15"/>
-      <c r="AD27" s="15"/>
-      <c r="AE27" s="15"/>
-      <c r="AF27" s="15"/>
-      <c r="AG27" s="15"/>
-      <c r="AH27" s="15"/>
-      <c r="AI27" s="15"/>
-      <c r="AJ27" s="15"/>
-      <c r="AK27" s="15"/>
-      <c r="AL27" s="15"/>
-      <c r="AM27" s="15"/>
-      <c r="AN27" s="15"/>
-      <c r="AO27" s="15"/>
-      <c r="AP27" s="15"/>
-      <c r="AQ27" s="15"/>
-      <c r="AR27" s="15"/>
-      <c r="AS27" s="15"/>
-      <c r="AT27" s="15"/>
-      <c r="AU27" s="15"/>
-      <c r="AV27" s="15"/>
-      <c r="AW27" s="15"/>
-      <c r="AX27" s="15"/>
-      <c r="AY27" s="15"/>
-      <c r="AZ27" s="15"/>
-      <c r="BA27" s="15"/>
-      <c r="BB27" s="15"/>
-      <c r="BC27" s="15"/>
-      <c r="BD27" s="15"/>
-      <c r="BE27" s="15"/>
-      <c r="BF27" s="15"/>
-      <c r="BG27" s="15"/>
-      <c r="BH27" s="15"/>
-      <c r="BI27" s="15"/>
+      <c r="A27" s="70"/>
+      <c r="B27" s="70"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="64"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="64"/>
+      <c r="J27" s="64"/>
+      <c r="K27" s="64"/>
+      <c r="L27" s="64"/>
+      <c r="M27" s="64"/>
+      <c r="N27" s="64"/>
+      <c r="O27" s="64"/>
+      <c r="P27" s="64"/>
+      <c r="Q27" s="64"/>
+      <c r="R27" s="64"/>
+      <c r="S27" s="64"/>
+      <c r="T27" s="64"/>
+      <c r="U27" s="64"/>
+      <c r="V27" s="64"/>
+      <c r="W27" s="64"/>
+      <c r="X27" s="64"/>
+      <c r="Y27" s="64"/>
+      <c r="Z27" s="64"/>
+      <c r="AA27" s="71"/>
+      <c r="AB27" s="71"/>
+      <c r="AC27" s="64"/>
+      <c r="AD27" s="64"/>
+      <c r="AE27" s="64"/>
+      <c r="AF27" s="64"/>
+      <c r="AG27" s="64"/>
+      <c r="AH27" s="64"/>
+      <c r="AI27" s="64"/>
+      <c r="AJ27" s="64"/>
+      <c r="AK27" s="64"/>
+      <c r="AL27" s="64"/>
+      <c r="AM27" s="64"/>
+      <c r="AN27" s="64"/>
+      <c r="AO27" s="64"/>
+      <c r="AP27" s="64"/>
+      <c r="AQ27" s="64"/>
+      <c r="AR27" s="64"/>
+      <c r="AS27" s="64"/>
+      <c r="AT27" s="64"/>
+      <c r="AU27" s="64"/>
+      <c r="AV27" s="64"/>
+      <c r="AW27" s="64"/>
+      <c r="AX27" s="64"/>
+      <c r="AY27" s="64"/>
+      <c r="AZ27" s="64"/>
+      <c r="BA27" s="64"/>
+      <c r="BB27" s="64"/>
+      <c r="BC27" s="64"/>
+      <c r="BD27" s="64"/>
+      <c r="BE27" s="64"/>
+      <c r="BF27" s="64"/>
+      <c r="BG27" s="64"/>
+      <c r="BH27" s="64"/>
+      <c r="BI27" s="64"/>
     </row>
     <row r="28" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15"/>
-      <c r="O28" s="15"/>
-      <c r="P28" s="15"/>
-      <c r="Q28" s="15"/>
-      <c r="R28" s="15"/>
-      <c r="S28" s="15"/>
-      <c r="T28" s="15"/>
-      <c r="U28" s="15"/>
-      <c r="V28" s="15"/>
-      <c r="W28" s="15"/>
-      <c r="X28" s="15"/>
-      <c r="Y28" s="15"/>
-      <c r="Z28" s="15"/>
-      <c r="AA28" s="17"/>
-      <c r="AB28" s="17"/>
-      <c r="AC28" s="15"/>
-      <c r="AD28" s="15"/>
-      <c r="AE28" s="15"/>
-      <c r="AF28" s="15"/>
-      <c r="AG28" s="15"/>
-      <c r="AH28" s="15"/>
-      <c r="AI28" s="15"/>
-      <c r="AJ28" s="15"/>
-      <c r="AK28" s="15"/>
-      <c r="AL28" s="15"/>
-      <c r="AM28" s="15"/>
-      <c r="AN28" s="15"/>
-      <c r="AO28" s="15"/>
-      <c r="AP28" s="15"/>
-      <c r="AQ28" s="15"/>
-      <c r="AR28" s="15"/>
-      <c r="AS28" s="15"/>
-      <c r="AT28" s="15"/>
-      <c r="AU28" s="15"/>
-      <c r="AV28" s="15"/>
-      <c r="AW28" s="15"/>
-      <c r="AX28" s="15"/>
-      <c r="AY28" s="15"/>
-      <c r="AZ28" s="15"/>
-      <c r="BA28" s="15"/>
-      <c r="BB28" s="15"/>
-      <c r="BC28" s="15"/>
-      <c r="BD28" s="15"/>
-      <c r="BE28" s="15"/>
-      <c r="BF28" s="15"/>
-      <c r="BG28" s="15"/>
-      <c r="BH28" s="15"/>
-      <c r="BI28" s="15"/>
+      <c r="A28" s="70"/>
+      <c r="B28" s="70"/>
+      <c r="C28" s="64"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="64"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="64"/>
+      <c r="J28" s="64"/>
+      <c r="K28" s="64"/>
+      <c r="L28" s="64"/>
+      <c r="M28" s="64"/>
+      <c r="N28" s="64"/>
+      <c r="O28" s="64"/>
+      <c r="P28" s="64"/>
+      <c r="Q28" s="64"/>
+      <c r="R28" s="64"/>
+      <c r="S28" s="64"/>
+      <c r="T28" s="64"/>
+      <c r="U28" s="64"/>
+      <c r="V28" s="64"/>
+      <c r="W28" s="64"/>
+      <c r="X28" s="64"/>
+      <c r="Y28" s="64"/>
+      <c r="Z28" s="64"/>
+      <c r="AA28" s="71"/>
+      <c r="AB28" s="71"/>
+      <c r="AC28" s="64"/>
+      <c r="AD28" s="64"/>
+      <c r="AE28" s="64"/>
+      <c r="AF28" s="64"/>
+      <c r="AG28" s="64"/>
+      <c r="AH28" s="64"/>
+      <c r="AI28" s="64"/>
+      <c r="AJ28" s="64"/>
+      <c r="AK28" s="64"/>
+      <c r="AL28" s="64"/>
+      <c r="AM28" s="64"/>
+      <c r="AN28" s="64"/>
+      <c r="AO28" s="64"/>
+      <c r="AP28" s="64"/>
+      <c r="AQ28" s="64"/>
+      <c r="AR28" s="64"/>
+      <c r="AS28" s="64"/>
+      <c r="AT28" s="64"/>
+      <c r="AU28" s="64"/>
+      <c r="AV28" s="64"/>
+      <c r="AW28" s="64"/>
+      <c r="AX28" s="64"/>
+      <c r="AY28" s="64"/>
+      <c r="AZ28" s="64"/>
+      <c r="BA28" s="64"/>
+      <c r="BB28" s="64"/>
+      <c r="BC28" s="64"/>
+      <c r="BD28" s="64"/>
+      <c r="BE28" s="64"/>
+      <c r="BF28" s="64"/>
+      <c r="BG28" s="64"/>
+      <c r="BH28" s="64"/>
+      <c r="BI28" s="64"/>
     </row>
     <row r="29" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="16"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="15"/>
-      <c r="O29" s="15"/>
-      <c r="P29" s="15"/>
-      <c r="Q29" s="15"/>
-      <c r="R29" s="15"/>
-      <c r="S29" s="15"/>
-      <c r="T29" s="15"/>
-      <c r="U29" s="15"/>
-      <c r="V29" s="15"/>
-      <c r="W29" s="15"/>
-      <c r="X29" s="15"/>
-      <c r="Y29" s="15"/>
-      <c r="Z29" s="15"/>
-      <c r="AA29" s="17"/>
-      <c r="AB29" s="17"/>
-      <c r="AC29" s="15"/>
-      <c r="AD29" s="15"/>
-      <c r="AE29" s="15"/>
-      <c r="AF29" s="15"/>
-      <c r="AG29" s="15"/>
-      <c r="AH29" s="15"/>
-      <c r="AI29" s="15"/>
-      <c r="AJ29" s="15"/>
-      <c r="AK29" s="15"/>
-      <c r="AL29" s="15"/>
-      <c r="AM29" s="15"/>
-      <c r="AN29" s="15"/>
-      <c r="AO29" s="15"/>
-      <c r="AP29" s="15"/>
-      <c r="AQ29" s="15"/>
-      <c r="AR29" s="15"/>
-      <c r="AS29" s="15"/>
-      <c r="AT29" s="15"/>
-      <c r="AU29" s="15"/>
-      <c r="AV29" s="15"/>
-      <c r="AW29" s="15"/>
-      <c r="AX29" s="15"/>
-      <c r="AY29" s="15"/>
-      <c r="AZ29" s="15"/>
-      <c r="BA29" s="15"/>
-      <c r="BB29" s="15"/>
-      <c r="BC29" s="15"/>
-      <c r="BD29" s="15"/>
-      <c r="BE29" s="15"/>
-      <c r="BF29" s="15"/>
-      <c r="BG29" s="15"/>
-      <c r="BH29" s="15"/>
-      <c r="BI29" s="15"/>
+      <c r="A29" s="70"/>
+      <c r="B29" s="70"/>
+      <c r="C29" s="64"/>
+      <c r="D29" s="64"/>
+      <c r="E29" s="64"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="64"/>
+      <c r="J29" s="64"/>
+      <c r="K29" s="64"/>
+      <c r="L29" s="64"/>
+      <c r="M29" s="64"/>
+      <c r="N29" s="64"/>
+      <c r="O29" s="64"/>
+      <c r="P29" s="64"/>
+      <c r="Q29" s="64"/>
+      <c r="R29" s="64"/>
+      <c r="S29" s="64"/>
+      <c r="T29" s="64"/>
+      <c r="U29" s="64"/>
+      <c r="V29" s="64"/>
+      <c r="W29" s="64"/>
+      <c r="X29" s="64"/>
+      <c r="Y29" s="64"/>
+      <c r="Z29" s="64"/>
+      <c r="AA29" s="71"/>
+      <c r="AB29" s="71"/>
+      <c r="AC29" s="64"/>
+      <c r="AD29" s="64"/>
+      <c r="AE29" s="64"/>
+      <c r="AF29" s="64"/>
+      <c r="AG29" s="64"/>
+      <c r="AH29" s="64"/>
+      <c r="AI29" s="64"/>
+      <c r="AJ29" s="64"/>
+      <c r="AK29" s="64"/>
+      <c r="AL29" s="64"/>
+      <c r="AM29" s="64"/>
+      <c r="AN29" s="64"/>
+      <c r="AO29" s="64"/>
+      <c r="AP29" s="64"/>
+      <c r="AQ29" s="64"/>
+      <c r="AR29" s="64"/>
+      <c r="AS29" s="64"/>
+      <c r="AT29" s="64"/>
+      <c r="AU29" s="64"/>
+      <c r="AV29" s="64"/>
+      <c r="AW29" s="64"/>
+      <c r="AX29" s="64"/>
+      <c r="AY29" s="64"/>
+      <c r="AZ29" s="64"/>
+      <c r="BA29" s="64"/>
+      <c r="BB29" s="64"/>
+      <c r="BC29" s="64"/>
+      <c r="BD29" s="64"/>
+      <c r="BE29" s="64"/>
+      <c r="BF29" s="64"/>
+      <c r="BG29" s="64"/>
+      <c r="BH29" s="64"/>
+      <c r="BI29" s="64"/>
     </row>
     <row r="30" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="16"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="15"/>
-      <c r="O30" s="15"/>
-      <c r="P30" s="15"/>
-      <c r="Q30" s="15"/>
-      <c r="R30" s="15"/>
-      <c r="S30" s="15"/>
-      <c r="T30" s="15"/>
-      <c r="U30" s="15"/>
-      <c r="V30" s="15"/>
-      <c r="W30" s="15"/>
-      <c r="X30" s="15"/>
-      <c r="Y30" s="15"/>
-      <c r="Z30" s="15"/>
-      <c r="AA30" s="17"/>
-      <c r="AB30" s="17"/>
-      <c r="AC30" s="15"/>
-      <c r="AD30" s="15"/>
-      <c r="AE30" s="15"/>
-      <c r="AF30" s="15"/>
-      <c r="AG30" s="15"/>
-      <c r="AH30" s="15"/>
-      <c r="AI30" s="15"/>
-      <c r="AJ30" s="15"/>
-      <c r="AK30" s="15"/>
-      <c r="AL30" s="15"/>
-      <c r="AM30" s="15"/>
-      <c r="AN30" s="15"/>
-      <c r="AO30" s="15"/>
-      <c r="AP30" s="15"/>
-      <c r="AQ30" s="15"/>
-      <c r="AR30" s="15"/>
-      <c r="AS30" s="15"/>
-      <c r="AT30" s="15"/>
-      <c r="AU30" s="15"/>
-      <c r="AV30" s="15"/>
-      <c r="AW30" s="15"/>
-      <c r="AX30" s="15"/>
-      <c r="AY30" s="15"/>
-      <c r="AZ30" s="15"/>
-      <c r="BA30" s="15"/>
-      <c r="BB30" s="15"/>
-      <c r="BC30" s="15"/>
-      <c r="BD30" s="15"/>
-      <c r="BE30" s="15"/>
-      <c r="BF30" s="15"/>
-      <c r="BG30" s="15"/>
-      <c r="BH30" s="15"/>
-      <c r="BI30" s="15"/>
+      <c r="A30" s="70"/>
+      <c r="B30" s="70"/>
+      <c r="C30" s="64"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="64"/>
+      <c r="F30" s="64"/>
+      <c r="G30" s="64"/>
+      <c r="H30" s="64"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="64"/>
+      <c r="K30" s="64"/>
+      <c r="L30" s="64"/>
+      <c r="M30" s="64"/>
+      <c r="N30" s="64"/>
+      <c r="O30" s="64"/>
+      <c r="P30" s="64"/>
+      <c r="Q30" s="64"/>
+      <c r="R30" s="64"/>
+      <c r="S30" s="64"/>
+      <c r="T30" s="64"/>
+      <c r="U30" s="64"/>
+      <c r="V30" s="64"/>
+      <c r="W30" s="64"/>
+      <c r="X30" s="64"/>
+      <c r="Y30" s="64"/>
+      <c r="Z30" s="64"/>
+      <c r="AA30" s="71"/>
+      <c r="AB30" s="71"/>
+      <c r="AC30" s="64"/>
+      <c r="AD30" s="64"/>
+      <c r="AE30" s="64"/>
+      <c r="AF30" s="64"/>
+      <c r="AG30" s="64"/>
+      <c r="AH30" s="64"/>
+      <c r="AI30" s="64"/>
+      <c r="AJ30" s="64"/>
+      <c r="AK30" s="64"/>
+      <c r="AL30" s="64"/>
+      <c r="AM30" s="64"/>
+      <c r="AN30" s="64"/>
+      <c r="AO30" s="64"/>
+      <c r="AP30" s="64"/>
+      <c r="AQ30" s="64"/>
+      <c r="AR30" s="64"/>
+      <c r="AS30" s="64"/>
+      <c r="AT30" s="64"/>
+      <c r="AU30" s="64"/>
+      <c r="AV30" s="64"/>
+      <c r="AW30" s="64"/>
+      <c r="AX30" s="64"/>
+      <c r="AY30" s="64"/>
+      <c r="AZ30" s="64"/>
+      <c r="BA30" s="64"/>
+      <c r="BB30" s="64"/>
+      <c r="BC30" s="64"/>
+      <c r="BD30" s="64"/>
+      <c r="BE30" s="64"/>
+      <c r="BF30" s="64"/>
+      <c r="BG30" s="64"/>
+      <c r="BH30" s="64"/>
+      <c r="BI30" s="64"/>
     </row>
     <row r="31" spans="1:61" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9"/>
@@ -4757,9 +4768,9 @@
       <c r="AI65" s="6"/>
       <c r="AJ65" s="6"/>
       <c r="AK65" s="6"/>
-      <c r="AL65" s="66"/>
-      <c r="AM65" s="66"/>
-      <c r="AN65" s="66"/>
+      <c r="AL65" s="19"/>
+      <c r="AM65" s="19"/>
+      <c r="AN65" s="19"/>
     </row>
     <row r="66" spans="1:41" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4"/>
@@ -4935,6 +4946,372 @@
     </row>
   </sheetData>
   <mergeCells count="390">
+    <mergeCell ref="AS29:AZ29"/>
+    <mergeCell ref="BA29:BC29"/>
+    <mergeCell ref="BD29:BI29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:J30"/>
+    <mergeCell ref="K30:R30"/>
+    <mergeCell ref="S30:T30"/>
+    <mergeCell ref="U30:V30"/>
+    <mergeCell ref="AA30:AB30"/>
+    <mergeCell ref="AC30:AF30"/>
+    <mergeCell ref="AJ30:AL30"/>
+    <mergeCell ref="AM30:AO30"/>
+    <mergeCell ref="AP30:AR30"/>
+    <mergeCell ref="AS30:AZ30"/>
+    <mergeCell ref="BA30:BC30"/>
+    <mergeCell ref="BD30:BI30"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:J29"/>
+    <mergeCell ref="K29:R29"/>
+    <mergeCell ref="S29:T29"/>
+    <mergeCell ref="U29:V29"/>
+    <mergeCell ref="W29:X29"/>
+    <mergeCell ref="Y29:Z29"/>
+    <mergeCell ref="AA29:AB29"/>
+    <mergeCell ref="AC29:AF29"/>
+    <mergeCell ref="AG27:AI27"/>
+    <mergeCell ref="AJ27:AL27"/>
+    <mergeCell ref="AM27:AO27"/>
+    <mergeCell ref="AP27:AR27"/>
+    <mergeCell ref="W27:X27"/>
+    <mergeCell ref="Y27:Z27"/>
+    <mergeCell ref="AA27:AB27"/>
+    <mergeCell ref="AC27:AF27"/>
+    <mergeCell ref="AG29:AI29"/>
+    <mergeCell ref="AJ29:AL29"/>
+    <mergeCell ref="AM29:AO29"/>
+    <mergeCell ref="AP29:AR29"/>
+    <mergeCell ref="AS27:AZ27"/>
+    <mergeCell ref="BA27:BC27"/>
+    <mergeCell ref="BD27:BI27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:J28"/>
+    <mergeCell ref="K28:R28"/>
+    <mergeCell ref="S28:T28"/>
+    <mergeCell ref="U28:V28"/>
+    <mergeCell ref="W28:X28"/>
+    <mergeCell ref="Y28:Z28"/>
+    <mergeCell ref="AA28:AB28"/>
+    <mergeCell ref="AC28:AF28"/>
+    <mergeCell ref="AG28:AI28"/>
+    <mergeCell ref="AJ28:AL28"/>
+    <mergeCell ref="AM28:AO28"/>
+    <mergeCell ref="AP28:AR28"/>
+    <mergeCell ref="AS28:AZ28"/>
+    <mergeCell ref="BA28:BC28"/>
+    <mergeCell ref="BD28:BI28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:J27"/>
+    <mergeCell ref="K27:R27"/>
+    <mergeCell ref="S27:T27"/>
+    <mergeCell ref="U27:V27"/>
+    <mergeCell ref="AG26:AI26"/>
+    <mergeCell ref="AJ26:AL26"/>
+    <mergeCell ref="AM26:AO26"/>
+    <mergeCell ref="AP26:AR26"/>
+    <mergeCell ref="AS26:AZ26"/>
+    <mergeCell ref="BA26:BC26"/>
+    <mergeCell ref="BD26:BI26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:J25"/>
+    <mergeCell ref="K25:R25"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:J26"/>
+    <mergeCell ref="K26:R26"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="W26:X26"/>
+    <mergeCell ref="Y26:Z26"/>
+    <mergeCell ref="AA26:AB26"/>
+    <mergeCell ref="AC26:AF26"/>
+    <mergeCell ref="AC25:AF25"/>
+    <mergeCell ref="AP23:AR23"/>
+    <mergeCell ref="AC23:AF23"/>
+    <mergeCell ref="AG23:AI23"/>
+    <mergeCell ref="AJ23:AL23"/>
+    <mergeCell ref="AM23:AO23"/>
+    <mergeCell ref="AS25:AZ25"/>
+    <mergeCell ref="BA25:BC25"/>
+    <mergeCell ref="BD25:BI25"/>
+    <mergeCell ref="C23:J23"/>
+    <mergeCell ref="K23:R23"/>
+    <mergeCell ref="AG25:AI25"/>
+    <mergeCell ref="AJ25:AL25"/>
+    <mergeCell ref="AM25:AO25"/>
+    <mergeCell ref="AP25:AR25"/>
+    <mergeCell ref="AS23:AZ23"/>
+    <mergeCell ref="BA23:BC23"/>
+    <mergeCell ref="BD23:BI23"/>
+    <mergeCell ref="AG24:AI24"/>
+    <mergeCell ref="AJ24:AL24"/>
+    <mergeCell ref="AM24:AO24"/>
+    <mergeCell ref="AP24:AR24"/>
+    <mergeCell ref="AS24:AZ24"/>
+    <mergeCell ref="BA24:BC24"/>
+    <mergeCell ref="BD24:BI24"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="W23:X23"/>
+    <mergeCell ref="Y23:Z23"/>
+    <mergeCell ref="AA23:AB23"/>
+    <mergeCell ref="W25:X25"/>
+    <mergeCell ref="Y25:Z25"/>
+    <mergeCell ref="AA25:AB25"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:J24"/>
+    <mergeCell ref="K24:R24"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="W24:X24"/>
+    <mergeCell ref="Y24:Z24"/>
+    <mergeCell ref="AA24:AB24"/>
+    <mergeCell ref="AC24:AF24"/>
+    <mergeCell ref="AP21:AR21"/>
+    <mergeCell ref="AS21:AZ21"/>
+    <mergeCell ref="BA21:BC21"/>
+    <mergeCell ref="BD21:BI21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:J22"/>
+    <mergeCell ref="K22:R22"/>
+    <mergeCell ref="S22:T22"/>
+    <mergeCell ref="U22:V22"/>
+    <mergeCell ref="W22:X22"/>
+    <mergeCell ref="Y22:Z22"/>
+    <mergeCell ref="AA22:AB22"/>
+    <mergeCell ref="AC22:AF22"/>
+    <mergeCell ref="AG22:AI22"/>
+    <mergeCell ref="AJ22:AL22"/>
+    <mergeCell ref="AM22:AO22"/>
+    <mergeCell ref="AP22:AR22"/>
+    <mergeCell ref="AS22:AZ22"/>
+    <mergeCell ref="BA22:BC22"/>
+    <mergeCell ref="BD22:BI22"/>
+    <mergeCell ref="AM21:AO21"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="AJ19:AL19"/>
+    <mergeCell ref="AM19:AO19"/>
+    <mergeCell ref="AP19:AR19"/>
+    <mergeCell ref="AS19:AZ19"/>
+    <mergeCell ref="BA19:BC19"/>
+    <mergeCell ref="BD19:BI19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:J20"/>
+    <mergeCell ref="K20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="U20:V20"/>
+    <mergeCell ref="W20:X20"/>
+    <mergeCell ref="Y20:Z20"/>
+    <mergeCell ref="AA20:AB20"/>
+    <mergeCell ref="AC20:AF20"/>
+    <mergeCell ref="AG20:AI20"/>
+    <mergeCell ref="AJ20:AL20"/>
+    <mergeCell ref="AM20:AO20"/>
+    <mergeCell ref="AP20:AR20"/>
+    <mergeCell ref="AS20:AZ20"/>
+    <mergeCell ref="BA20:BC20"/>
+    <mergeCell ref="BD20:BI20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:J19"/>
+    <mergeCell ref="K19:R19"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="U19:V19"/>
+    <mergeCell ref="W19:X19"/>
+    <mergeCell ref="Y19:Z19"/>
+    <mergeCell ref="AA19:AB19"/>
+    <mergeCell ref="AC19:AF19"/>
+    <mergeCell ref="AG17:AI17"/>
+    <mergeCell ref="K17:R17"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="U17:V17"/>
+    <mergeCell ref="W17:X17"/>
+    <mergeCell ref="Y17:Z17"/>
+    <mergeCell ref="AA17:AB17"/>
+    <mergeCell ref="AC17:AF17"/>
+    <mergeCell ref="AG19:AI19"/>
+    <mergeCell ref="AJ17:AL17"/>
+    <mergeCell ref="AM17:AO17"/>
+    <mergeCell ref="AP17:AR17"/>
+    <mergeCell ref="AS17:AZ17"/>
+    <mergeCell ref="BA17:BC17"/>
+    <mergeCell ref="BD17:BI17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:J18"/>
+    <mergeCell ref="K18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="U18:V18"/>
+    <mergeCell ref="W18:X18"/>
+    <mergeCell ref="Y18:Z18"/>
+    <mergeCell ref="AA18:AB18"/>
+    <mergeCell ref="AC18:AF18"/>
+    <mergeCell ref="AG18:AI18"/>
+    <mergeCell ref="AJ18:AL18"/>
+    <mergeCell ref="AM18:AO18"/>
+    <mergeCell ref="AP18:AR18"/>
+    <mergeCell ref="AS18:AZ18"/>
+    <mergeCell ref="BA18:BC18"/>
+    <mergeCell ref="BD18:BI18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:J17"/>
+    <mergeCell ref="AJ15:AL15"/>
+    <mergeCell ref="AM15:AO15"/>
+    <mergeCell ref="AP15:AR15"/>
+    <mergeCell ref="AS15:AZ15"/>
+    <mergeCell ref="BA15:BC15"/>
+    <mergeCell ref="BD15:BI15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:J16"/>
+    <mergeCell ref="K16:R16"/>
+    <mergeCell ref="S16:T16"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="Y16:Z16"/>
+    <mergeCell ref="AA16:AB16"/>
+    <mergeCell ref="AC16:AF16"/>
+    <mergeCell ref="AG16:AI16"/>
+    <mergeCell ref="AJ16:AL16"/>
+    <mergeCell ref="AM16:AO16"/>
+    <mergeCell ref="AP16:AR16"/>
+    <mergeCell ref="AS16:AZ16"/>
+    <mergeCell ref="BA16:BC16"/>
+    <mergeCell ref="BD16:BI16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:J15"/>
+    <mergeCell ref="K15:R15"/>
+    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="U15:V15"/>
+    <mergeCell ref="W15:X15"/>
+    <mergeCell ref="Y15:Z15"/>
+    <mergeCell ref="AA15:AB15"/>
+    <mergeCell ref="AC15:AF15"/>
+    <mergeCell ref="AG13:AI13"/>
+    <mergeCell ref="K13:R13"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="W13:X13"/>
+    <mergeCell ref="Y13:Z13"/>
+    <mergeCell ref="AA13:AB13"/>
+    <mergeCell ref="AC13:AF13"/>
+    <mergeCell ref="AG15:AI15"/>
+    <mergeCell ref="AJ13:AL13"/>
+    <mergeCell ref="AM13:AO13"/>
+    <mergeCell ref="AP13:AR13"/>
+    <mergeCell ref="AS13:AZ13"/>
+    <mergeCell ref="BA13:BC13"/>
+    <mergeCell ref="BD13:BI13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="K14:R14"/>
+    <mergeCell ref="S14:T14"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="W14:X14"/>
+    <mergeCell ref="Y14:Z14"/>
+    <mergeCell ref="AA14:AB14"/>
+    <mergeCell ref="AC14:AF14"/>
+    <mergeCell ref="AG14:AI14"/>
+    <mergeCell ref="AJ14:AL14"/>
+    <mergeCell ref="AM14:AO14"/>
+    <mergeCell ref="AP14:AR14"/>
+    <mergeCell ref="AS14:AZ14"/>
+    <mergeCell ref="BA14:BC14"/>
+    <mergeCell ref="BD14:BI14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:J13"/>
+    <mergeCell ref="AG11:AI11"/>
+    <mergeCell ref="AJ11:AL11"/>
+    <mergeCell ref="AM11:AO11"/>
+    <mergeCell ref="AP11:AR11"/>
+    <mergeCell ref="AS11:AZ11"/>
+    <mergeCell ref="BA11:BC11"/>
+    <mergeCell ref="BD11:BI11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="K12:R12"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="U12:V12"/>
+    <mergeCell ref="W12:X12"/>
+    <mergeCell ref="Y12:Z12"/>
+    <mergeCell ref="AA12:AB12"/>
+    <mergeCell ref="AC12:AF12"/>
+    <mergeCell ref="AG12:AI12"/>
+    <mergeCell ref="AJ12:AL12"/>
+    <mergeCell ref="AM12:AO12"/>
+    <mergeCell ref="AP12:AR12"/>
+    <mergeCell ref="AS12:AZ12"/>
+    <mergeCell ref="BA12:BC12"/>
+    <mergeCell ref="BD12:BI12"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:J11"/>
+    <mergeCell ref="K11:R11"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="W11:X11"/>
+    <mergeCell ref="Y11:Z11"/>
+    <mergeCell ref="AA11:AB11"/>
+    <mergeCell ref="AC11:AF11"/>
+    <mergeCell ref="BA8:BC8"/>
+    <mergeCell ref="Y9:Z9"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AJ9:AL9"/>
+    <mergeCell ref="AM9:AO9"/>
+    <mergeCell ref="AP9:AR9"/>
+    <mergeCell ref="AS9:AZ9"/>
+    <mergeCell ref="BA9:BC9"/>
+    <mergeCell ref="AG9:AI9"/>
+    <mergeCell ref="AC9:AF9"/>
+    <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="AC8:AF8"/>
+    <mergeCell ref="AG8:AI8"/>
+    <mergeCell ref="AJ8:AL8"/>
+    <mergeCell ref="AM8:AO8"/>
+    <mergeCell ref="AP8:AR8"/>
+    <mergeCell ref="AJ10:AL10"/>
+    <mergeCell ref="AM10:AO10"/>
+    <mergeCell ref="AP10:AR10"/>
+    <mergeCell ref="AS10:AZ10"/>
+    <mergeCell ref="BA10:BC10"/>
+    <mergeCell ref="BD10:BI10"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:J9"/>
+    <mergeCell ref="K9:R9"/>
+    <mergeCell ref="S9:T9"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="W9:X9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="K10:R10"/>
+    <mergeCell ref="S10:T10"/>
+    <mergeCell ref="U10:V10"/>
+    <mergeCell ref="W10:X10"/>
+    <mergeCell ref="Y10:Z10"/>
+    <mergeCell ref="AA10:AB10"/>
+    <mergeCell ref="AC10:AF10"/>
+    <mergeCell ref="BD9:BI9"/>
+    <mergeCell ref="AG10:AI10"/>
+    <mergeCell ref="AS8:AZ8"/>
+    <mergeCell ref="W8:X8"/>
+    <mergeCell ref="Y8:Z8"/>
+    <mergeCell ref="AY1:BI1"/>
+    <mergeCell ref="AY2:BI4"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="F2:J3"/>
+    <mergeCell ref="K1:V1"/>
+    <mergeCell ref="K2:V3"/>
+    <mergeCell ref="W1:AH1"/>
+    <mergeCell ref="W2:AH3"/>
+    <mergeCell ref="AI1:AM1"/>
+    <mergeCell ref="AN1:AR1"/>
+    <mergeCell ref="AI2:AM3"/>
+    <mergeCell ref="AN2:AR3"/>
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="K4:O4"/>
+    <mergeCell ref="P4:T4"/>
+    <mergeCell ref="AI4:AR6"/>
+    <mergeCell ref="U4:AH4"/>
+    <mergeCell ref="BD8:BI8"/>
     <mergeCell ref="W30:X30"/>
     <mergeCell ref="Y30:Z30"/>
     <mergeCell ref="AL65:AN65"/>
@@ -4959,372 +5336,6 @@
     <mergeCell ref="AC21:AF21"/>
     <mergeCell ref="AG21:AI21"/>
     <mergeCell ref="AJ21:AL21"/>
-    <mergeCell ref="AS8:AZ8"/>
-    <mergeCell ref="W8:X8"/>
-    <mergeCell ref="Y8:Z8"/>
-    <mergeCell ref="AY1:BI1"/>
-    <mergeCell ref="AY2:BI4"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="F2:J3"/>
-    <mergeCell ref="K1:V1"/>
-    <mergeCell ref="K2:V3"/>
-    <mergeCell ref="W1:AH1"/>
-    <mergeCell ref="W2:AH3"/>
-    <mergeCell ref="AI1:AM1"/>
-    <mergeCell ref="AN1:AR1"/>
-    <mergeCell ref="AI2:AM3"/>
-    <mergeCell ref="AN2:AR3"/>
-    <mergeCell ref="F4:J4"/>
-    <mergeCell ref="K4:O4"/>
-    <mergeCell ref="P4:T4"/>
-    <mergeCell ref="AI4:AR6"/>
-    <mergeCell ref="U4:AH4"/>
-    <mergeCell ref="BD8:BI8"/>
-    <mergeCell ref="AJ10:AL10"/>
-    <mergeCell ref="AM10:AO10"/>
-    <mergeCell ref="AP10:AR10"/>
-    <mergeCell ref="AS10:AZ10"/>
-    <mergeCell ref="BA10:BC10"/>
-    <mergeCell ref="BD10:BI10"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:J9"/>
-    <mergeCell ref="K9:R9"/>
-    <mergeCell ref="S9:T9"/>
-    <mergeCell ref="U9:V9"/>
-    <mergeCell ref="W9:X9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="K10:R10"/>
-    <mergeCell ref="S10:T10"/>
-    <mergeCell ref="U10:V10"/>
-    <mergeCell ref="W10:X10"/>
-    <mergeCell ref="Y10:Z10"/>
-    <mergeCell ref="AA10:AB10"/>
-    <mergeCell ref="AC10:AF10"/>
-    <mergeCell ref="BD9:BI9"/>
-    <mergeCell ref="AG10:AI10"/>
-    <mergeCell ref="C11:J11"/>
-    <mergeCell ref="K11:R11"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="W11:X11"/>
-    <mergeCell ref="Y11:Z11"/>
-    <mergeCell ref="AA11:AB11"/>
-    <mergeCell ref="AC11:AF11"/>
-    <mergeCell ref="BA8:BC8"/>
-    <mergeCell ref="Y9:Z9"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AJ9:AL9"/>
-    <mergeCell ref="AM9:AO9"/>
-    <mergeCell ref="AP9:AR9"/>
-    <mergeCell ref="AS9:AZ9"/>
-    <mergeCell ref="BA9:BC9"/>
-    <mergeCell ref="AG9:AI9"/>
-    <mergeCell ref="AC9:AF9"/>
-    <mergeCell ref="AA8:AB8"/>
-    <mergeCell ref="AC8:AF8"/>
-    <mergeCell ref="AG8:AI8"/>
-    <mergeCell ref="AJ8:AL8"/>
-    <mergeCell ref="AM8:AO8"/>
-    <mergeCell ref="AP8:AR8"/>
-    <mergeCell ref="AG11:AI11"/>
-    <mergeCell ref="AJ11:AL11"/>
-    <mergeCell ref="AM11:AO11"/>
-    <mergeCell ref="AP11:AR11"/>
-    <mergeCell ref="AS11:AZ11"/>
-    <mergeCell ref="BA11:BC11"/>
-    <mergeCell ref="BD11:BI11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:J12"/>
-    <mergeCell ref="K12:R12"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="U12:V12"/>
-    <mergeCell ref="W12:X12"/>
-    <mergeCell ref="Y12:Z12"/>
-    <mergeCell ref="AA12:AB12"/>
-    <mergeCell ref="AC12:AF12"/>
-    <mergeCell ref="AG12:AI12"/>
-    <mergeCell ref="AJ12:AL12"/>
-    <mergeCell ref="AM12:AO12"/>
-    <mergeCell ref="AP12:AR12"/>
-    <mergeCell ref="AS12:AZ12"/>
-    <mergeCell ref="BA12:BC12"/>
-    <mergeCell ref="BD12:BI12"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="AJ13:AL13"/>
-    <mergeCell ref="AM13:AO13"/>
-    <mergeCell ref="AP13:AR13"/>
-    <mergeCell ref="AS13:AZ13"/>
-    <mergeCell ref="BA13:BC13"/>
-    <mergeCell ref="BD13:BI13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:J14"/>
-    <mergeCell ref="K14:R14"/>
-    <mergeCell ref="S14:T14"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="W14:X14"/>
-    <mergeCell ref="Y14:Z14"/>
-    <mergeCell ref="AA14:AB14"/>
-    <mergeCell ref="AC14:AF14"/>
-    <mergeCell ref="AG14:AI14"/>
-    <mergeCell ref="AJ14:AL14"/>
-    <mergeCell ref="AM14:AO14"/>
-    <mergeCell ref="AP14:AR14"/>
-    <mergeCell ref="AS14:AZ14"/>
-    <mergeCell ref="BA14:BC14"/>
-    <mergeCell ref="BD14:BI14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="K15:R15"/>
-    <mergeCell ref="S15:T15"/>
-    <mergeCell ref="U15:V15"/>
-    <mergeCell ref="W15:X15"/>
-    <mergeCell ref="Y15:Z15"/>
-    <mergeCell ref="AA15:AB15"/>
-    <mergeCell ref="AC15:AF15"/>
-    <mergeCell ref="AG13:AI13"/>
-    <mergeCell ref="K13:R13"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="W13:X13"/>
-    <mergeCell ref="Y13:Z13"/>
-    <mergeCell ref="AA13:AB13"/>
-    <mergeCell ref="AC13:AF13"/>
-    <mergeCell ref="AG15:AI15"/>
-    <mergeCell ref="AJ15:AL15"/>
-    <mergeCell ref="AM15:AO15"/>
-    <mergeCell ref="AP15:AR15"/>
-    <mergeCell ref="AS15:AZ15"/>
-    <mergeCell ref="BA15:BC15"/>
-    <mergeCell ref="BD15:BI15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:J16"/>
-    <mergeCell ref="K16:R16"/>
-    <mergeCell ref="S16:T16"/>
-    <mergeCell ref="U16:V16"/>
-    <mergeCell ref="W16:X16"/>
-    <mergeCell ref="Y16:Z16"/>
-    <mergeCell ref="AA16:AB16"/>
-    <mergeCell ref="AC16:AF16"/>
-    <mergeCell ref="AG16:AI16"/>
-    <mergeCell ref="AJ16:AL16"/>
-    <mergeCell ref="AM16:AO16"/>
-    <mergeCell ref="AP16:AR16"/>
-    <mergeCell ref="AS16:AZ16"/>
-    <mergeCell ref="BA16:BC16"/>
-    <mergeCell ref="BD16:BI16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:J15"/>
-    <mergeCell ref="AJ17:AL17"/>
-    <mergeCell ref="AM17:AO17"/>
-    <mergeCell ref="AP17:AR17"/>
-    <mergeCell ref="AS17:AZ17"/>
-    <mergeCell ref="BA17:BC17"/>
-    <mergeCell ref="BD17:BI17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:J18"/>
-    <mergeCell ref="K18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="U18:V18"/>
-    <mergeCell ref="W18:X18"/>
-    <mergeCell ref="Y18:Z18"/>
-    <mergeCell ref="AA18:AB18"/>
-    <mergeCell ref="AC18:AF18"/>
-    <mergeCell ref="AG18:AI18"/>
-    <mergeCell ref="AJ18:AL18"/>
-    <mergeCell ref="AM18:AO18"/>
-    <mergeCell ref="AP18:AR18"/>
-    <mergeCell ref="AS18:AZ18"/>
-    <mergeCell ref="BA18:BC18"/>
-    <mergeCell ref="BD18:BI18"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:J17"/>
-    <mergeCell ref="K19:R19"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="U19:V19"/>
-    <mergeCell ref="W19:X19"/>
-    <mergeCell ref="Y19:Z19"/>
-    <mergeCell ref="AA19:AB19"/>
-    <mergeCell ref="AC19:AF19"/>
-    <mergeCell ref="AG17:AI17"/>
-    <mergeCell ref="K17:R17"/>
-    <mergeCell ref="S17:T17"/>
-    <mergeCell ref="U17:V17"/>
-    <mergeCell ref="W17:X17"/>
-    <mergeCell ref="Y17:Z17"/>
-    <mergeCell ref="AA17:AB17"/>
-    <mergeCell ref="AC17:AF17"/>
-    <mergeCell ref="AG19:AI19"/>
-    <mergeCell ref="AJ19:AL19"/>
-    <mergeCell ref="AM19:AO19"/>
-    <mergeCell ref="AP19:AR19"/>
-    <mergeCell ref="AS19:AZ19"/>
-    <mergeCell ref="BA19:BC19"/>
-    <mergeCell ref="BD19:BI19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:J20"/>
-    <mergeCell ref="K20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="U20:V20"/>
-    <mergeCell ref="W20:X20"/>
-    <mergeCell ref="Y20:Z20"/>
-    <mergeCell ref="AA20:AB20"/>
-    <mergeCell ref="AC20:AF20"/>
-    <mergeCell ref="AG20:AI20"/>
-    <mergeCell ref="AJ20:AL20"/>
-    <mergeCell ref="AM20:AO20"/>
-    <mergeCell ref="AP20:AR20"/>
-    <mergeCell ref="AS20:AZ20"/>
-    <mergeCell ref="BA20:BC20"/>
-    <mergeCell ref="BD20:BI20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:J19"/>
-    <mergeCell ref="AC24:AF24"/>
-    <mergeCell ref="AP21:AR21"/>
-    <mergeCell ref="AS21:AZ21"/>
-    <mergeCell ref="BA21:BC21"/>
-    <mergeCell ref="BD21:BI21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:J22"/>
-    <mergeCell ref="K22:R22"/>
-    <mergeCell ref="S22:T22"/>
-    <mergeCell ref="U22:V22"/>
-    <mergeCell ref="W22:X22"/>
-    <mergeCell ref="Y22:Z22"/>
-    <mergeCell ref="AA22:AB22"/>
-    <mergeCell ref="AC22:AF22"/>
-    <mergeCell ref="AG22:AI22"/>
-    <mergeCell ref="AJ22:AL22"/>
-    <mergeCell ref="AM22:AO22"/>
-    <mergeCell ref="AP22:AR22"/>
-    <mergeCell ref="AS22:AZ22"/>
-    <mergeCell ref="BA22:BC22"/>
-    <mergeCell ref="BD22:BI22"/>
-    <mergeCell ref="AM21:AO21"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="W23:X23"/>
-    <mergeCell ref="Y23:Z23"/>
-    <mergeCell ref="AA23:AB23"/>
-    <mergeCell ref="W25:X25"/>
-    <mergeCell ref="Y25:Z25"/>
-    <mergeCell ref="AA25:AB25"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:J24"/>
-    <mergeCell ref="K24:R24"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="W24:X24"/>
-    <mergeCell ref="Y24:Z24"/>
-    <mergeCell ref="AA24:AB24"/>
-    <mergeCell ref="AP23:AR23"/>
-    <mergeCell ref="AC23:AF23"/>
-    <mergeCell ref="AG23:AI23"/>
-    <mergeCell ref="AJ23:AL23"/>
-    <mergeCell ref="AM23:AO23"/>
-    <mergeCell ref="AS25:AZ25"/>
-    <mergeCell ref="BA25:BC25"/>
-    <mergeCell ref="BD25:BI25"/>
-    <mergeCell ref="C23:J23"/>
-    <mergeCell ref="K23:R23"/>
-    <mergeCell ref="AG25:AI25"/>
-    <mergeCell ref="AJ25:AL25"/>
-    <mergeCell ref="AM25:AO25"/>
-    <mergeCell ref="AP25:AR25"/>
-    <mergeCell ref="AS23:AZ23"/>
-    <mergeCell ref="BA23:BC23"/>
-    <mergeCell ref="BD23:BI23"/>
-    <mergeCell ref="AG24:AI24"/>
-    <mergeCell ref="AJ24:AL24"/>
-    <mergeCell ref="AM24:AO24"/>
-    <mergeCell ref="AP24:AR24"/>
-    <mergeCell ref="AS24:AZ24"/>
-    <mergeCell ref="BA24:BC24"/>
-    <mergeCell ref="BD24:BI24"/>
-    <mergeCell ref="AG26:AI26"/>
-    <mergeCell ref="AJ26:AL26"/>
-    <mergeCell ref="AM26:AO26"/>
-    <mergeCell ref="AP26:AR26"/>
-    <mergeCell ref="AS26:AZ26"/>
-    <mergeCell ref="BA26:BC26"/>
-    <mergeCell ref="BD26:BI26"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:J25"/>
-    <mergeCell ref="K25:R25"/>
-    <mergeCell ref="S25:T25"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:J26"/>
-    <mergeCell ref="K26:R26"/>
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="U26:V26"/>
-    <mergeCell ref="W26:X26"/>
-    <mergeCell ref="Y26:Z26"/>
-    <mergeCell ref="AA26:AB26"/>
-    <mergeCell ref="AC26:AF26"/>
-    <mergeCell ref="AC25:AF25"/>
-    <mergeCell ref="AS27:AZ27"/>
-    <mergeCell ref="BA27:BC27"/>
-    <mergeCell ref="BD27:BI27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:J28"/>
-    <mergeCell ref="K28:R28"/>
-    <mergeCell ref="S28:T28"/>
-    <mergeCell ref="U28:V28"/>
-    <mergeCell ref="W28:X28"/>
-    <mergeCell ref="Y28:Z28"/>
-    <mergeCell ref="AA28:AB28"/>
-    <mergeCell ref="AC28:AF28"/>
-    <mergeCell ref="AG28:AI28"/>
-    <mergeCell ref="AJ28:AL28"/>
-    <mergeCell ref="AM28:AO28"/>
-    <mergeCell ref="AP28:AR28"/>
-    <mergeCell ref="AS28:AZ28"/>
-    <mergeCell ref="BA28:BC28"/>
-    <mergeCell ref="BD28:BI28"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:J27"/>
-    <mergeCell ref="K27:R27"/>
-    <mergeCell ref="S27:T27"/>
-    <mergeCell ref="U27:V27"/>
-    <mergeCell ref="AC29:AF29"/>
-    <mergeCell ref="AG27:AI27"/>
-    <mergeCell ref="AJ27:AL27"/>
-    <mergeCell ref="AM27:AO27"/>
-    <mergeCell ref="AP27:AR27"/>
-    <mergeCell ref="W27:X27"/>
-    <mergeCell ref="Y27:Z27"/>
-    <mergeCell ref="AA27:AB27"/>
-    <mergeCell ref="AC27:AF27"/>
-    <mergeCell ref="AG29:AI29"/>
-    <mergeCell ref="AJ29:AL29"/>
-    <mergeCell ref="AM29:AO29"/>
-    <mergeCell ref="AP29:AR29"/>
-    <mergeCell ref="AS29:AZ29"/>
-    <mergeCell ref="BA29:BC29"/>
-    <mergeCell ref="BD29:BI29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:J30"/>
-    <mergeCell ref="K30:R30"/>
-    <mergeCell ref="S30:T30"/>
-    <mergeCell ref="U30:V30"/>
-    <mergeCell ref="AA30:AB30"/>
-    <mergeCell ref="AC30:AF30"/>
-    <mergeCell ref="AJ30:AL30"/>
-    <mergeCell ref="AM30:AO30"/>
-    <mergeCell ref="AP30:AR30"/>
-    <mergeCell ref="AS30:AZ30"/>
-    <mergeCell ref="BA30:BC30"/>
-    <mergeCell ref="BD30:BI30"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:J29"/>
-    <mergeCell ref="K29:R29"/>
-    <mergeCell ref="S29:T29"/>
-    <mergeCell ref="U29:V29"/>
-    <mergeCell ref="W29:X29"/>
-    <mergeCell ref="Y29:Z29"/>
-    <mergeCell ref="AA29:AB29"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -5352,74 +5363,74 @@
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="32" t="s">
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="32" t="s">
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="33"/>
-      <c r="AA1" s="33"/>
-      <c r="AB1" s="33"/>
-      <c r="AC1" s="33"/>
-      <c r="AD1" s="33"/>
-      <c r="AE1" s="33"/>
-      <c r="AF1" s="33"/>
-      <c r="AG1" s="33"/>
-      <c r="AH1" s="34"/>
-      <c r="AI1" s="32" t="s">
+      <c r="X1" s="17"/>
+      <c r="Y1" s="17"/>
+      <c r="Z1" s="17"/>
+      <c r="AA1" s="17"/>
+      <c r="AB1" s="17"/>
+      <c r="AC1" s="17"/>
+      <c r="AD1" s="17"/>
+      <c r="AE1" s="17"/>
+      <c r="AF1" s="17"/>
+      <c r="AG1" s="17"/>
+      <c r="AH1" s="18"/>
+      <c r="AI1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="AJ1" s="33"/>
-      <c r="AK1" s="33"/>
-      <c r="AL1" s="33"/>
-      <c r="AM1" s="34"/>
-      <c r="AN1" s="32" t="s">
+      <c r="AJ1" s="17"/>
+      <c r="AK1" s="17"/>
+      <c r="AL1" s="17"/>
+      <c r="AM1" s="18"/>
+      <c r="AN1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="AO1" s="33"/>
-      <c r="AP1" s="33"/>
-      <c r="AQ1" s="33"/>
-      <c r="AR1" s="34"/>
+      <c r="AO1" s="17"/>
+      <c r="AP1" s="17"/>
+      <c r="AQ1" s="17"/>
+      <c r="AR1" s="18"/>
       <c r="AS1" s="7"/>
       <c r="AT1" s="7"/>
       <c r="AU1" s="7"/>
       <c r="AV1" s="7"/>
       <c r="AW1" s="7"/>
       <c r="AX1" s="7"/>
-      <c r="AY1" s="29" t="s">
+      <c r="AY1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="AZ1" s="29"/>
-      <c r="BA1" s="29"/>
-      <c r="BB1" s="29"/>
-      <c r="BC1" s="29"/>
-      <c r="BD1" s="29"/>
-      <c r="BE1" s="29"/>
-      <c r="BF1" s="29"/>
-      <c r="BG1" s="29"/>
-      <c r="BH1" s="29"/>
-      <c r="BI1" s="29"/>
+      <c r="AZ1" s="15"/>
+      <c r="BA1" s="15"/>
+      <c r="BB1" s="15"/>
+      <c r="BC1" s="15"/>
+      <c r="BD1" s="15"/>
+      <c r="BE1" s="15"/>
+      <c r="BF1" s="15"/>
+      <c r="BG1" s="15"/>
+      <c r="BH1" s="15"/>
+      <c r="BI1" s="15"/>
     </row>
     <row r="2" spans="1:61" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
@@ -5427,68 +5438,68 @@
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="41" t="s">
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
-      <c r="T2" s="42"/>
-      <c r="U2" s="42"/>
-      <c r="V2" s="43"/>
-      <c r="W2" s="41" t="s">
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="X2" s="42"/>
-      <c r="Y2" s="42"/>
-      <c r="Z2" s="42"/>
-      <c r="AA2" s="42"/>
-      <c r="AB2" s="42"/>
-      <c r="AC2" s="42"/>
-      <c r="AD2" s="42"/>
-      <c r="AE2" s="42"/>
-      <c r="AF2" s="42"/>
-      <c r="AG2" s="42"/>
-      <c r="AH2" s="43"/>
-      <c r="AI2" s="47" t="s">
+      <c r="X2" s="30"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="30"/>
+      <c r="AB2" s="30"/>
+      <c r="AC2" s="30"/>
+      <c r="AD2" s="30"/>
+      <c r="AE2" s="30"/>
+      <c r="AF2" s="30"/>
+      <c r="AG2" s="30"/>
+      <c r="AH2" s="31"/>
+      <c r="AI2" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="AJ2" s="48"/>
-      <c r="AK2" s="48"/>
-      <c r="AL2" s="48"/>
-      <c r="AM2" s="49"/>
-      <c r="AN2" s="47" t="s">
+      <c r="AJ2" s="36"/>
+      <c r="AK2" s="36"/>
+      <c r="AL2" s="36"/>
+      <c r="AM2" s="37"/>
+      <c r="AN2" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="AO2" s="48"/>
-      <c r="AP2" s="48"/>
-      <c r="AQ2" s="48"/>
-      <c r="AR2" s="49"/>
-      <c r="AY2" s="30" t="s">
+      <c r="AO2" s="36"/>
+      <c r="AP2" s="36"/>
+      <c r="AQ2" s="36"/>
+      <c r="AR2" s="37"/>
+      <c r="AY2" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="AZ2" s="30"/>
-      <c r="BA2" s="30"/>
-      <c r="BB2" s="30"/>
-      <c r="BC2" s="30"/>
-      <c r="BD2" s="30"/>
-      <c r="BE2" s="30"/>
-      <c r="BF2" s="30"/>
-      <c r="BG2" s="30"/>
-      <c r="BH2" s="30"/>
-      <c r="BI2" s="30"/>
+      <c r="AZ2" s="47"/>
+      <c r="BA2" s="47"/>
+      <c r="BB2" s="47"/>
+      <c r="BC2" s="47"/>
+      <c r="BD2" s="47"/>
+      <c r="BE2" s="47"/>
+      <c r="BF2" s="47"/>
+      <c r="BG2" s="47"/>
+      <c r="BH2" s="47"/>
+      <c r="BI2" s="47"/>
     </row>
     <row r="3" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4"/>
@@ -5496,56 +5507,56 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
-      <c r="V3" s="46"/>
-      <c r="W3" s="44"/>
-      <c r="X3" s="45"/>
-      <c r="Y3" s="45"/>
-      <c r="Z3" s="45"/>
-      <c r="AA3" s="45"/>
-      <c r="AB3" s="45"/>
-      <c r="AC3" s="45"/>
-      <c r="AD3" s="45"/>
-      <c r="AE3" s="45"/>
-      <c r="AF3" s="45"/>
-      <c r="AG3" s="45"/>
-      <c r="AH3" s="46"/>
-      <c r="AI3" s="50"/>
-      <c r="AJ3" s="51"/>
-      <c r="AK3" s="51"/>
-      <c r="AL3" s="51"/>
-      <c r="AM3" s="52"/>
-      <c r="AN3" s="50"/>
-      <c r="AO3" s="51"/>
-      <c r="AP3" s="51"/>
-      <c r="AQ3" s="51"/>
-      <c r="AR3" s="52"/>
-      <c r="AY3" s="31"/>
-      <c r="AZ3" s="31"/>
-      <c r="BA3" s="31"/>
-      <c r="BB3" s="31"/>
-      <c r="BC3" s="31"/>
-      <c r="BD3" s="31"/>
-      <c r="BE3" s="31"/>
-      <c r="BF3" s="31"/>
-      <c r="BG3" s="31"/>
-      <c r="BH3" s="31"/>
-      <c r="BI3" s="31"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="33"/>
+      <c r="O3" s="33"/>
+      <c r="P3" s="33"/>
+      <c r="Q3" s="33"/>
+      <c r="R3" s="33"/>
+      <c r="S3" s="33"/>
+      <c r="T3" s="33"/>
+      <c r="U3" s="33"/>
+      <c r="V3" s="34"/>
+      <c r="W3" s="32"/>
+      <c r="X3" s="33"/>
+      <c r="Y3" s="33"/>
+      <c r="Z3" s="33"/>
+      <c r="AA3" s="33"/>
+      <c r="AB3" s="33"/>
+      <c r="AC3" s="33"/>
+      <c r="AD3" s="33"/>
+      <c r="AE3" s="33"/>
+      <c r="AF3" s="33"/>
+      <c r="AG3" s="33"/>
+      <c r="AH3" s="34"/>
+      <c r="AI3" s="38"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="39"/>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="40"/>
+      <c r="AN3" s="38"/>
+      <c r="AO3" s="39"/>
+      <c r="AP3" s="39"/>
+      <c r="AQ3" s="39"/>
+      <c r="AR3" s="40"/>
+      <c r="AY3" s="48"/>
+      <c r="AZ3" s="48"/>
+      <c r="BA3" s="48"/>
+      <c r="BB3" s="48"/>
+      <c r="BC3" s="48"/>
+      <c r="BD3" s="48"/>
+      <c r="BE3" s="48"/>
+      <c r="BF3" s="48"/>
+      <c r="BG3" s="48"/>
+      <c r="BH3" s="48"/>
+      <c r="BI3" s="48"/>
     </row>
     <row r="4" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
@@ -5553,66 +5564,66 @@
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="53" t="s">
+      <c r="F4" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="53" t="s">
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="53" t="s">
+      <c r="L4" s="50"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="50"/>
+      <c r="O4" s="51"/>
+      <c r="P4" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="54"/>
-      <c r="T4" s="55"/>
-      <c r="U4" s="53" t="s">
+      <c r="Q4" s="50"/>
+      <c r="R4" s="50"/>
+      <c r="S4" s="50"/>
+      <c r="T4" s="51"/>
+      <c r="U4" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="V4" s="54"/>
-      <c r="W4" s="54"/>
-      <c r="X4" s="54"/>
-      <c r="Y4" s="54"/>
-      <c r="Z4" s="54"/>
-      <c r="AA4" s="54"/>
-      <c r="AB4" s="54"/>
-      <c r="AC4" s="54"/>
-      <c r="AD4" s="54"/>
-      <c r="AE4" s="54"/>
-      <c r="AF4" s="54"/>
-      <c r="AG4" s="54"/>
-      <c r="AH4" s="55"/>
-      <c r="AI4" s="56" t="s">
+      <c r="V4" s="50"/>
+      <c r="W4" s="50"/>
+      <c r="X4" s="50"/>
+      <c r="Y4" s="50"/>
+      <c r="Z4" s="50"/>
+      <c r="AA4" s="50"/>
+      <c r="AB4" s="50"/>
+      <c r="AC4" s="50"/>
+      <c r="AD4" s="50"/>
+      <c r="AE4" s="50"/>
+      <c r="AF4" s="50"/>
+      <c r="AG4" s="50"/>
+      <c r="AH4" s="51"/>
+      <c r="AI4" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="AJ4" s="57"/>
-      <c r="AK4" s="57"/>
-      <c r="AL4" s="57"/>
-      <c r="AM4" s="57"/>
-      <c r="AN4" s="57"/>
-      <c r="AO4" s="57"/>
-      <c r="AP4" s="57"/>
-      <c r="AQ4" s="57"/>
-      <c r="AR4" s="58"/>
-      <c r="AY4" s="31"/>
-      <c r="AZ4" s="31"/>
-      <c r="BA4" s="31"/>
-      <c r="BB4" s="31"/>
-      <c r="BC4" s="31"/>
-      <c r="BD4" s="31"/>
-      <c r="BE4" s="31"/>
-      <c r="BF4" s="31"/>
-      <c r="BG4" s="31"/>
-      <c r="BH4" s="31"/>
-      <c r="BI4" s="31"/>
+      <c r="AJ4" s="21"/>
+      <c r="AK4" s="21"/>
+      <c r="AL4" s="21"/>
+      <c r="AM4" s="21"/>
+      <c r="AN4" s="21"/>
+      <c r="AO4" s="21"/>
+      <c r="AP4" s="21"/>
+      <c r="AQ4" s="21"/>
+      <c r="AR4" s="22"/>
+      <c r="AY4" s="48"/>
+      <c r="AZ4" s="48"/>
+      <c r="BA4" s="48"/>
+      <c r="BB4" s="48"/>
+      <c r="BC4" s="48"/>
+      <c r="BD4" s="48"/>
+      <c r="BE4" s="48"/>
+      <c r="BF4" s="48"/>
+      <c r="BG4" s="48"/>
+      <c r="BH4" s="48"/>
+      <c r="BI4" s="48"/>
     </row>
     <row r="5" spans="1:61" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
@@ -5620,53 +5631,53 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
-      <c r="F5" s="41" t="s">
+      <c r="F5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="47" t="s">
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="L5" s="48"/>
-      <c r="M5" s="48"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="47" t="s">
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="67" t="s">
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="37"/>
+      <c r="U5" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="V5" s="68"/>
-      <c r="W5" s="68"/>
-      <c r="X5" s="68"/>
-      <c r="Y5" s="68"/>
-      <c r="Z5" s="68"/>
-      <c r="AA5" s="68"/>
-      <c r="AB5" s="68"/>
-      <c r="AC5" s="68"/>
-      <c r="AD5" s="68"/>
-      <c r="AE5" s="68"/>
-      <c r="AF5" s="68"/>
-      <c r="AG5" s="68"/>
-      <c r="AH5" s="69"/>
-      <c r="AI5" s="59"/>
-      <c r="AJ5" s="60"/>
-      <c r="AK5" s="60"/>
-      <c r="AL5" s="60"/>
-      <c r="AM5" s="60"/>
-      <c r="AN5" s="60"/>
-      <c r="AO5" s="60"/>
-      <c r="AP5" s="60"/>
-      <c r="AQ5" s="60"/>
-      <c r="AR5" s="61"/>
+      <c r="V5" s="42"/>
+      <c r="W5" s="42"/>
+      <c r="X5" s="42"/>
+      <c r="Y5" s="42"/>
+      <c r="Z5" s="42"/>
+      <c r="AA5" s="42"/>
+      <c r="AB5" s="42"/>
+      <c r="AC5" s="42"/>
+      <c r="AD5" s="42"/>
+      <c r="AE5" s="42"/>
+      <c r="AF5" s="42"/>
+      <c r="AG5" s="42"/>
+      <c r="AH5" s="43"/>
+      <c r="AI5" s="23"/>
+      <c r="AJ5" s="24"/>
+      <c r="AK5" s="24"/>
+      <c r="AL5" s="24"/>
+      <c r="AM5" s="24"/>
+      <c r="AN5" s="24"/>
+      <c r="AO5" s="24"/>
+      <c r="AP5" s="24"/>
+      <c r="AQ5" s="24"/>
+      <c r="AR5" s="25"/>
     </row>
     <row r="6" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
@@ -5674,45 +5685,45 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="52"/>
-      <c r="P6" s="50"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="51"/>
-      <c r="S6" s="51"/>
-      <c r="T6" s="52"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
-      <c r="W6" s="71"/>
-      <c r="X6" s="71"/>
-      <c r="Y6" s="71"/>
-      <c r="Z6" s="71"/>
-      <c r="AA6" s="71"/>
-      <c r="AB6" s="71"/>
-      <c r="AC6" s="71"/>
-      <c r="AD6" s="71"/>
-      <c r="AE6" s="71"/>
-      <c r="AF6" s="71"/>
-      <c r="AG6" s="71"/>
-      <c r="AH6" s="72"/>
-      <c r="AI6" s="62"/>
-      <c r="AJ6" s="63"/>
-      <c r="AK6" s="63"/>
-      <c r="AL6" s="63"/>
-      <c r="AM6" s="63"/>
-      <c r="AN6" s="63"/>
-      <c r="AO6" s="63"/>
-      <c r="AP6" s="63"/>
-      <c r="AQ6" s="63"/>
-      <c r="AR6" s="64"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="38"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="39"/>
+      <c r="T6" s="40"/>
+      <c r="U6" s="44"/>
+      <c r="V6" s="45"/>
+      <c r="W6" s="45"/>
+      <c r="X6" s="45"/>
+      <c r="Y6" s="45"/>
+      <c r="Z6" s="45"/>
+      <c r="AA6" s="45"/>
+      <c r="AB6" s="45"/>
+      <c r="AC6" s="45"/>
+      <c r="AD6" s="45"/>
+      <c r="AE6" s="45"/>
+      <c r="AF6" s="45"/>
+      <c r="AG6" s="45"/>
+      <c r="AH6" s="46"/>
+      <c r="AI6" s="26"/>
+      <c r="AJ6" s="27"/>
+      <c r="AK6" s="27"/>
+      <c r="AL6" s="27"/>
+      <c r="AM6" s="27"/>
+      <c r="AN6" s="27"/>
+      <c r="AO6" s="27"/>
+      <c r="AP6" s="27"/>
+      <c r="AQ6" s="27"/>
+      <c r="AR6" s="28"/>
     </row>
     <row r="7" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
@@ -5821,73 +5832,73 @@
       <c r="BI8" s="8"/>
     </row>
     <row r="9" spans="1:61" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="78"/>
-      <c r="C9" s="78"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="78"/>
-      <c r="H9" s="78"/>
-      <c r="I9" s="78"/>
-      <c r="J9" s="78"/>
-      <c r="K9" s="78"/>
-      <c r="L9" s="78"/>
-      <c r="M9" s="78"/>
-      <c r="N9" s="78"/>
-      <c r="O9" s="78"/>
-      <c r="P9" s="78"/>
-      <c r="Q9" s="78"/>
-      <c r="R9" s="78"/>
-      <c r="S9" s="78"/>
-      <c r="T9" s="79"/>
-      <c r="U9" s="77" t="s">
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="58"/>
+      <c r="K9" s="58"/>
+      <c r="L9" s="58"/>
+      <c r="M9" s="58"/>
+      <c r="N9" s="58"/>
+      <c r="O9" s="58"/>
+      <c r="P9" s="58"/>
+      <c r="Q9" s="58"/>
+      <c r="R9" s="58"/>
+      <c r="S9" s="58"/>
+      <c r="T9" s="59"/>
+      <c r="U9" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="V9" s="78"/>
-      <c r="W9" s="78"/>
-      <c r="X9" s="78"/>
-      <c r="Y9" s="78"/>
-      <c r="Z9" s="78"/>
-      <c r="AA9" s="78"/>
-      <c r="AB9" s="78"/>
-      <c r="AC9" s="78"/>
-      <c r="AD9" s="78"/>
-      <c r="AE9" s="78"/>
-      <c r="AF9" s="78"/>
-      <c r="AG9" s="78"/>
-      <c r="AH9" s="78"/>
-      <c r="AI9" s="78"/>
-      <c r="AJ9" s="78"/>
-      <c r="AK9" s="78"/>
-      <c r="AL9" s="78"/>
-      <c r="AM9" s="78"/>
-      <c r="AN9" s="78"/>
-      <c r="AO9" s="79"/>
-      <c r="AP9" s="77" t="s">
+      <c r="V9" s="58"/>
+      <c r="W9" s="58"/>
+      <c r="X9" s="58"/>
+      <c r="Y9" s="58"/>
+      <c r="Z9" s="58"/>
+      <c r="AA9" s="58"/>
+      <c r="AB9" s="58"/>
+      <c r="AC9" s="58"/>
+      <c r="AD9" s="58"/>
+      <c r="AE9" s="58"/>
+      <c r="AF9" s="58"/>
+      <c r="AG9" s="58"/>
+      <c r="AH9" s="58"/>
+      <c r="AI9" s="58"/>
+      <c r="AJ9" s="58"/>
+      <c r="AK9" s="58"/>
+      <c r="AL9" s="58"/>
+      <c r="AM9" s="58"/>
+      <c r="AN9" s="58"/>
+      <c r="AO9" s="59"/>
+      <c r="AP9" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="AQ9" s="78"/>
-      <c r="AR9" s="78"/>
-      <c r="AS9" s="78"/>
-      <c r="AT9" s="78"/>
-      <c r="AU9" s="78"/>
-      <c r="AV9" s="78"/>
-      <c r="AW9" s="78"/>
-      <c r="AX9" s="78"/>
-      <c r="AY9" s="78"/>
-      <c r="AZ9" s="78"/>
-      <c r="BA9" s="78"/>
-      <c r="BB9" s="78"/>
-      <c r="BC9" s="78"/>
-      <c r="BD9" s="78"/>
-      <c r="BE9" s="78"/>
-      <c r="BF9" s="78"/>
-      <c r="BG9" s="78"/>
-      <c r="BH9" s="78"/>
-      <c r="BI9" s="78"/>
+      <c r="AQ9" s="58"/>
+      <c r="AR9" s="58"/>
+      <c r="AS9" s="58"/>
+      <c r="AT9" s="58"/>
+      <c r="AU9" s="58"/>
+      <c r="AV9" s="58"/>
+      <c r="AW9" s="58"/>
+      <c r="AX9" s="58"/>
+      <c r="AY9" s="58"/>
+      <c r="AZ9" s="58"/>
+      <c r="BA9" s="58"/>
+      <c r="BB9" s="58"/>
+      <c r="BC9" s="58"/>
+      <c r="BD9" s="58"/>
+      <c r="BE9" s="58"/>
+      <c r="BF9" s="58"/>
+      <c r="BG9" s="58"/>
+      <c r="BH9" s="58"/>
+      <c r="BI9" s="58"/>
     </row>
     <row r="10" spans="1:61" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="11"/>
@@ -5952,121 +5963,121 @@
       <c r="BI10" s="10"/>
     </row>
     <row r="11" spans="1:61" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="73" t="s">
+      <c r="A11" s="88" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="73"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
-      <c r="G11" s="73"/>
-      <c r="H11" s="73"/>
-      <c r="I11" s="73"/>
-      <c r="J11" s="73"/>
+      <c r="B11" s="88"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="88"/>
+      <c r="G11" s="88"/>
+      <c r="H11" s="88"/>
+      <c r="I11" s="88"/>
+      <c r="J11" s="88"/>
       <c r="K11" s="9"/>
-      <c r="L11" s="73" t="s">
+      <c r="L11" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="M11" s="73"/>
-      <c r="O11" s="73" t="s">
+      <c r="M11" s="61"/>
+      <c r="O11" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="P11" s="73"/>
+      <c r="P11" s="61"/>
       <c r="Q11" s="9"/>
       <c r="R11" s="14"/>
       <c r="S11" s="9"/>
       <c r="T11" s="13"/>
-      <c r="U11" s="76" t="s">
+      <c r="U11" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="V11" s="73"/>
-      <c r="W11" s="73"/>
-      <c r="X11" s="73"/>
-      <c r="Y11" s="73"/>
-      <c r="Z11" s="73"/>
-      <c r="AA11" s="73"/>
-      <c r="AB11" s="73"/>
-      <c r="AC11" s="73"/>
-      <c r="AD11" s="73"/>
-      <c r="AE11" s="73"/>
+      <c r="V11" s="88"/>
+      <c r="W11" s="88"/>
+      <c r="X11" s="88"/>
+      <c r="Y11" s="88"/>
+      <c r="Z11" s="88"/>
+      <c r="AA11" s="88"/>
+      <c r="AB11" s="88"/>
+      <c r="AC11" s="88"/>
+      <c r="AD11" s="88"/>
+      <c r="AE11" s="88"/>
       <c r="AF11" s="9"/>
-      <c r="AG11" s="73" t="s">
+      <c r="AG11" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="AH11" s="73"/>
+      <c r="AH11" s="61"/>
       <c r="AI11" s="9"/>
-      <c r="AJ11" s="73" t="s">
+      <c r="AJ11" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="AK11" s="73"/>
+      <c r="AK11" s="61"/>
       <c r="AL11" s="9"/>
       <c r="AM11" s="14"/>
       <c r="AN11" s="9"/>
       <c r="AO11" s="13"/>
-      <c r="AP11" s="74" t="s">
+      <c r="AP11" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="AQ11" s="75"/>
-      <c r="AR11" s="75"/>
-      <c r="AS11" s="75"/>
-      <c r="AT11" s="75"/>
-      <c r="AU11" s="75"/>
-      <c r="AV11" s="75"/>
-      <c r="AW11" s="75"/>
-      <c r="AX11" s="75"/>
-      <c r="AY11" s="75"/>
-      <c r="AZ11" s="75"/>
-      <c r="BA11" s="75"/>
+      <c r="AQ11" s="91"/>
+      <c r="AR11" s="91"/>
+      <c r="AS11" s="91"/>
+      <c r="AT11" s="91"/>
+      <c r="AU11" s="91"/>
+      <c r="AV11" s="91"/>
+      <c r="AW11" s="91"/>
+      <c r="AX11" s="91"/>
+      <c r="AY11" s="91"/>
+      <c r="AZ11" s="91"/>
+      <c r="BA11" s="91"/>
       <c r="BB11" s="10"/>
-      <c r="BC11" s="75" t="s">
+      <c r="BC11" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="BD11" s="75"/>
-      <c r="BE11" s="75"/>
-      <c r="BF11" s="75"/>
-      <c r="BG11" s="75"/>
-      <c r="BH11" s="75"/>
-      <c r="BI11" s="75"/>
+      <c r="BD11" s="63"/>
+      <c r="BE11" s="63"/>
+      <c r="BF11" s="63"/>
+      <c r="BG11" s="63"/>
+      <c r="BH11" s="63"/>
+      <c r="BI11" s="63"/>
     </row>
     <row r="12" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="73"/>
-      <c r="B12" s="73"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="73"/>
-      <c r="J12" s="73"/>
+      <c r="A12" s="61"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="61"/>
       <c r="K12" s="9"/>
-      <c r="L12" s="73"/>
-      <c r="M12" s="73"/>
+      <c r="L12" s="61"/>
+      <c r="M12" s="61"/>
       <c r="N12" s="9"/>
-      <c r="O12" s="73"/>
-      <c r="P12" s="73"/>
+      <c r="O12" s="61"/>
+      <c r="P12" s="61"/>
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
       <c r="S12" s="9"/>
       <c r="T12" s="13"/>
-      <c r="U12" s="76"/>
-      <c r="V12" s="73"/>
-      <c r="W12" s="73"/>
-      <c r="X12" s="73"/>
-      <c r="Y12" s="73"/>
-      <c r="Z12" s="73"/>
-      <c r="AA12" s="73"/>
-      <c r="AB12" s="73"/>
-      <c r="AC12" s="73"/>
-      <c r="AD12" s="73"/>
-      <c r="AE12" s="73"/>
+      <c r="U12" s="62"/>
+      <c r="V12" s="61"/>
+      <c r="W12" s="61"/>
+      <c r="X12" s="61"/>
+      <c r="Y12" s="61"/>
+      <c r="Z12" s="61"/>
+      <c r="AA12" s="61"/>
+      <c r="AB12" s="61"/>
+      <c r="AC12" s="61"/>
+      <c r="AD12" s="61"/>
+      <c r="AE12" s="61"/>
       <c r="AF12" s="9"/>
-      <c r="AG12" s="73"/>
-      <c r="AH12" s="73"/>
+      <c r="AG12" s="61"/>
+      <c r="AH12" s="61"/>
       <c r="AI12" s="9"/>
-      <c r="AJ12" s="73"/>
-      <c r="AK12" s="73"/>
+      <c r="AJ12" s="61"/>
+      <c r="AK12" s="61"/>
       <c r="AL12" s="9"/>
       <c r="AM12" s="9"/>
       <c r="AN12" s="9"/>
@@ -6093,43 +6104,43 @@
       <c r="BI12" s="10"/>
     </row>
     <row r="13" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="73"/>
-      <c r="B13" s="73"/>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="73"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="73"/>
-      <c r="I13" s="73"/>
-      <c r="J13" s="73"/>
+      <c r="A13" s="61"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="61"/>
       <c r="K13" s="9"/>
-      <c r="L13" s="73"/>
-      <c r="M13" s="73"/>
+      <c r="L13" s="61"/>
+      <c r="M13" s="61"/>
       <c r="N13" s="9"/>
-      <c r="O13" s="73"/>
-      <c r="P13" s="73"/>
+      <c r="O13" s="61"/>
+      <c r="P13" s="61"/>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
       <c r="S13" s="9"/>
       <c r="T13" s="13"/>
-      <c r="U13" s="76"/>
-      <c r="V13" s="73"/>
-      <c r="W13" s="73"/>
-      <c r="X13" s="73"/>
-      <c r="Y13" s="73"/>
-      <c r="Z13" s="73"/>
-      <c r="AA13" s="73"/>
-      <c r="AB13" s="73"/>
-      <c r="AC13" s="73"/>
-      <c r="AD13" s="73"/>
-      <c r="AE13" s="73"/>
+      <c r="U13" s="62"/>
+      <c r="V13" s="61"/>
+      <c r="W13" s="61"/>
+      <c r="X13" s="61"/>
+      <c r="Y13" s="61"/>
+      <c r="Z13" s="61"/>
+      <c r="AA13" s="61"/>
+      <c r="AB13" s="61"/>
+      <c r="AC13" s="61"/>
+      <c r="AD13" s="61"/>
+      <c r="AE13" s="61"/>
       <c r="AF13" s="9"/>
-      <c r="AG13" s="73"/>
-      <c r="AH13" s="73"/>
+      <c r="AG13" s="61"/>
+      <c r="AH13" s="61"/>
       <c r="AI13" s="9"/>
-      <c r="AJ13" s="73"/>
-      <c r="AK13" s="73"/>
+      <c r="AJ13" s="61"/>
+      <c r="AK13" s="61"/>
       <c r="AL13" s="9"/>
       <c r="AM13" s="9"/>
       <c r="AN13" s="9"/>
@@ -6156,43 +6167,43 @@
       <c r="BI13" s="10"/>
     </row>
     <row r="14" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="73"/>
-      <c r="B14" s="73"/>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="73"/>
-      <c r="J14" s="73"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="61"/>
       <c r="K14" s="9"/>
-      <c r="L14" s="73"/>
-      <c r="M14" s="73"/>
+      <c r="L14" s="61"/>
+      <c r="M14" s="61"/>
       <c r="N14" s="9"/>
-      <c r="O14" s="73"/>
-      <c r="P14" s="73"/>
+      <c r="O14" s="61"/>
+      <c r="P14" s="61"/>
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
       <c r="S14" s="9"/>
       <c r="T14" s="13"/>
-      <c r="U14" s="76"/>
-      <c r="V14" s="73"/>
-      <c r="W14" s="73"/>
-      <c r="X14" s="73"/>
-      <c r="Y14" s="73"/>
-      <c r="Z14" s="73"/>
-      <c r="AA14" s="73"/>
-      <c r="AB14" s="73"/>
-      <c r="AC14" s="73"/>
-      <c r="AD14" s="73"/>
-      <c r="AE14" s="73"/>
+      <c r="U14" s="62"/>
+      <c r="V14" s="61"/>
+      <c r="W14" s="61"/>
+      <c r="X14" s="61"/>
+      <c r="Y14" s="61"/>
+      <c r="Z14" s="61"/>
+      <c r="AA14" s="61"/>
+      <c r="AB14" s="61"/>
+      <c r="AC14" s="61"/>
+      <c r="AD14" s="61"/>
+      <c r="AE14" s="61"/>
       <c r="AF14" s="9"/>
-      <c r="AG14" s="73"/>
-      <c r="AH14" s="73"/>
+      <c r="AG14" s="61"/>
+      <c r="AH14" s="61"/>
       <c r="AI14" s="9"/>
-      <c r="AJ14" s="73"/>
-      <c r="AK14" s="73"/>
+      <c r="AJ14" s="61"/>
+      <c r="AK14" s="61"/>
       <c r="AL14" s="9"/>
       <c r="AM14" s="9"/>
       <c r="AN14" s="9"/>
@@ -6219,43 +6230,43 @@
       <c r="BI14" s="10"/>
     </row>
     <row r="15" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="73"/>
-      <c r="B15" s="73"/>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="73"/>
-      <c r="H15" s="73"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="73"/>
+      <c r="A15" s="61"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="61"/>
       <c r="K15" s="9"/>
-      <c r="L15" s="73"/>
-      <c r="M15" s="73"/>
+      <c r="L15" s="61"/>
+      <c r="M15" s="61"/>
       <c r="N15" s="9"/>
-      <c r="O15" s="73"/>
-      <c r="P15" s="73"/>
+      <c r="O15" s="61"/>
+      <c r="P15" s="61"/>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
       <c r="S15" s="9"/>
       <c r="T15" s="13"/>
-      <c r="U15" s="76"/>
-      <c r="V15" s="73"/>
-      <c r="W15" s="73"/>
-      <c r="X15" s="73"/>
-      <c r="Y15" s="73"/>
-      <c r="Z15" s="73"/>
-      <c r="AA15" s="73"/>
-      <c r="AB15" s="73"/>
-      <c r="AC15" s="73"/>
-      <c r="AD15" s="73"/>
-      <c r="AE15" s="73"/>
+      <c r="U15" s="62"/>
+      <c r="V15" s="61"/>
+      <c r="W15" s="61"/>
+      <c r="X15" s="61"/>
+      <c r="Y15" s="61"/>
+      <c r="Z15" s="61"/>
+      <c r="AA15" s="61"/>
+      <c r="AB15" s="61"/>
+      <c r="AC15" s="61"/>
+      <c r="AD15" s="61"/>
+      <c r="AE15" s="61"/>
       <c r="AF15" s="9"/>
-      <c r="AG15" s="73"/>
-      <c r="AH15" s="73"/>
+      <c r="AG15" s="61"/>
+      <c r="AH15" s="61"/>
       <c r="AI15" s="9"/>
-      <c r="AJ15" s="73"/>
-      <c r="AK15" s="73"/>
+      <c r="AJ15" s="61"/>
+      <c r="AK15" s="61"/>
       <c r="AL15" s="9"/>
       <c r="AM15" s="9"/>
       <c r="AN15" s="9"/>
@@ -6282,43 +6293,43 @@
       <c r="BI15" s="10"/>
     </row>
     <row r="16" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="73"/>
-      <c r="B16" s="73"/>
-      <c r="C16" s="73"/>
-      <c r="D16" s="73"/>
-      <c r="E16" s="73"/>
-      <c r="F16" s="73"/>
-      <c r="G16" s="73"/>
-      <c r="H16" s="73"/>
-      <c r="I16" s="73"/>
-      <c r="J16" s="73"/>
+      <c r="A16" s="61"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="61"/>
       <c r="K16" s="9"/>
-      <c r="L16" s="73"/>
-      <c r="M16" s="73"/>
+      <c r="L16" s="61"/>
+      <c r="M16" s="61"/>
       <c r="N16" s="9"/>
-      <c r="O16" s="73"/>
-      <c r="P16" s="73"/>
+      <c r="O16" s="61"/>
+      <c r="P16" s="61"/>
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
       <c r="S16" s="9"/>
       <c r="T16" s="13"/>
-      <c r="U16" s="76"/>
-      <c r="V16" s="73"/>
-      <c r="W16" s="73"/>
-      <c r="X16" s="73"/>
-      <c r="Y16" s="73"/>
-      <c r="Z16" s="73"/>
-      <c r="AA16" s="73"/>
-      <c r="AB16" s="73"/>
-      <c r="AC16" s="73"/>
-      <c r="AD16" s="73"/>
-      <c r="AE16" s="73"/>
+      <c r="U16" s="62"/>
+      <c r="V16" s="61"/>
+      <c r="W16" s="61"/>
+      <c r="X16" s="61"/>
+      <c r="Y16" s="61"/>
+      <c r="Z16" s="61"/>
+      <c r="AA16" s="61"/>
+      <c r="AB16" s="61"/>
+      <c r="AC16" s="61"/>
+      <c r="AD16" s="61"/>
+      <c r="AE16" s="61"/>
       <c r="AF16" s="9"/>
-      <c r="AG16" s="73"/>
-      <c r="AH16" s="73"/>
+      <c r="AG16" s="61"/>
+      <c r="AH16" s="61"/>
       <c r="AI16" s="9"/>
-      <c r="AJ16" s="73"/>
-      <c r="AK16" s="73"/>
+      <c r="AJ16" s="61"/>
+      <c r="AK16" s="61"/>
       <c r="AL16" s="9"/>
       <c r="AM16" s="9"/>
       <c r="AN16" s="9"/>
@@ -6345,43 +6356,43 @@
       <c r="BI16" s="10"/>
     </row>
     <row r="17" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="73"/>
-      <c r="B17" s="73"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="73"/>
-      <c r="G17" s="73"/>
-      <c r="H17" s="73"/>
-      <c r="I17" s="73"/>
-      <c r="J17" s="73"/>
+      <c r="A17" s="61"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="61"/>
       <c r="K17" s="9"/>
-      <c r="L17" s="73"/>
-      <c r="M17" s="73"/>
+      <c r="L17" s="61"/>
+      <c r="M17" s="61"/>
       <c r="N17" s="9"/>
-      <c r="O17" s="73"/>
-      <c r="P17" s="73"/>
+      <c r="O17" s="61"/>
+      <c r="P17" s="61"/>
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
       <c r="S17" s="9"/>
       <c r="T17" s="13"/>
-      <c r="U17" s="76"/>
-      <c r="V17" s="73"/>
-      <c r="W17" s="73"/>
-      <c r="X17" s="73"/>
-      <c r="Y17" s="73"/>
-      <c r="Z17" s="73"/>
-      <c r="AA17" s="73"/>
-      <c r="AB17" s="73"/>
-      <c r="AC17" s="73"/>
-      <c r="AD17" s="73"/>
-      <c r="AE17" s="73"/>
+      <c r="U17" s="62"/>
+      <c r="V17" s="61"/>
+      <c r="W17" s="61"/>
+      <c r="X17" s="61"/>
+      <c r="Y17" s="61"/>
+      <c r="Z17" s="61"/>
+      <c r="AA17" s="61"/>
+      <c r="AB17" s="61"/>
+      <c r="AC17" s="61"/>
+      <c r="AD17" s="61"/>
+      <c r="AE17" s="61"/>
       <c r="AF17" s="9"/>
-      <c r="AG17" s="73"/>
-      <c r="AH17" s="73"/>
+      <c r="AG17" s="61"/>
+      <c r="AH17" s="61"/>
       <c r="AI17" s="9"/>
-      <c r="AJ17" s="73"/>
-      <c r="AK17" s="73"/>
+      <c r="AJ17" s="61"/>
+      <c r="AK17" s="61"/>
       <c r="AL17" s="9"/>
       <c r="AM17" s="9"/>
       <c r="AN17" s="9"/>
@@ -6408,43 +6419,43 @@
       <c r="BI17" s="10"/>
     </row>
     <row r="18" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="73"/>
-      <c r="B18" s="73"/>
-      <c r="C18" s="73"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
-      <c r="F18" s="73"/>
-      <c r="G18" s="73"/>
-      <c r="H18" s="73"/>
-      <c r="I18" s="73"/>
-      <c r="J18" s="73"/>
+      <c r="A18" s="61"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
       <c r="K18" s="9"/>
-      <c r="L18" s="73"/>
-      <c r="M18" s="73"/>
+      <c r="L18" s="61"/>
+      <c r="M18" s="61"/>
       <c r="N18" s="9"/>
-      <c r="O18" s="73"/>
-      <c r="P18" s="73"/>
+      <c r="O18" s="61"/>
+      <c r="P18" s="61"/>
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
       <c r="S18" s="9"/>
       <c r="T18" s="13"/>
-      <c r="U18" s="76"/>
-      <c r="V18" s="73"/>
-      <c r="W18" s="73"/>
-      <c r="X18" s="73"/>
-      <c r="Y18" s="73"/>
-      <c r="Z18" s="73"/>
-      <c r="AA18" s="73"/>
-      <c r="AB18" s="73"/>
-      <c r="AC18" s="73"/>
-      <c r="AD18" s="73"/>
-      <c r="AE18" s="73"/>
+      <c r="U18" s="62"/>
+      <c r="V18" s="61"/>
+      <c r="W18" s="61"/>
+      <c r="X18" s="61"/>
+      <c r="Y18" s="61"/>
+      <c r="Z18" s="61"/>
+      <c r="AA18" s="61"/>
+      <c r="AB18" s="61"/>
+      <c r="AC18" s="61"/>
+      <c r="AD18" s="61"/>
+      <c r="AE18" s="61"/>
       <c r="AF18" s="9"/>
-      <c r="AG18" s="73"/>
-      <c r="AH18" s="73"/>
+      <c r="AG18" s="61"/>
+      <c r="AH18" s="61"/>
       <c r="AI18" s="9"/>
-      <c r="AJ18" s="73"/>
-      <c r="AK18" s="73"/>
+      <c r="AJ18" s="61"/>
+      <c r="AK18" s="61"/>
       <c r="AL18" s="9"/>
       <c r="AM18" s="9"/>
       <c r="AN18" s="9"/>
@@ -6471,43 +6482,43 @@
       <c r="BI18" s="10"/>
     </row>
     <row r="19" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="73"/>
-      <c r="B19" s="73"/>
-      <c r="C19" s="73"/>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="73"/>
-      <c r="H19" s="73"/>
-      <c r="I19" s="73"/>
-      <c r="J19" s="73"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="61"/>
       <c r="K19" s="9"/>
-      <c r="L19" s="73"/>
-      <c r="M19" s="73"/>
+      <c r="L19" s="61"/>
+      <c r="M19" s="61"/>
       <c r="N19" s="9"/>
-      <c r="O19" s="73"/>
-      <c r="P19" s="73"/>
+      <c r="O19" s="61"/>
+      <c r="P19" s="61"/>
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
       <c r="S19" s="9"/>
       <c r="T19" s="13"/>
-      <c r="U19" s="76"/>
-      <c r="V19" s="73"/>
-      <c r="W19" s="73"/>
-      <c r="X19" s="73"/>
-      <c r="Y19" s="73"/>
-      <c r="Z19" s="73"/>
-      <c r="AA19" s="73"/>
-      <c r="AB19" s="73"/>
-      <c r="AC19" s="73"/>
-      <c r="AD19" s="73"/>
-      <c r="AE19" s="73"/>
+      <c r="U19" s="62"/>
+      <c r="V19" s="61"/>
+      <c r="W19" s="61"/>
+      <c r="X19" s="61"/>
+      <c r="Y19" s="61"/>
+      <c r="Z19" s="61"/>
+      <c r="AA19" s="61"/>
+      <c r="AB19" s="61"/>
+      <c r="AC19" s="61"/>
+      <c r="AD19" s="61"/>
+      <c r="AE19" s="61"/>
       <c r="AF19" s="9"/>
-      <c r="AG19" s="73"/>
-      <c r="AH19" s="73"/>
+      <c r="AG19" s="61"/>
+      <c r="AH19" s="61"/>
       <c r="AI19" s="9"/>
-      <c r="AJ19" s="73"/>
-      <c r="AK19" s="73"/>
+      <c r="AJ19" s="61"/>
+      <c r="AK19" s="61"/>
       <c r="AL19" s="9"/>
       <c r="AM19" s="9"/>
       <c r="AN19" s="9"/>
@@ -6534,43 +6545,43 @@
       <c r="BI19" s="10"/>
     </row>
     <row r="20" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="73"/>
-      <c r="B20" s="73"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="73"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="73"/>
-      <c r="G20" s="73"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="73"/>
-      <c r="J20" s="73"/>
+      <c r="A20" s="61"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
       <c r="K20" s="9"/>
-      <c r="L20" s="73"/>
-      <c r="M20" s="73"/>
+      <c r="L20" s="61"/>
+      <c r="M20" s="61"/>
       <c r="N20" s="9"/>
-      <c r="O20" s="73"/>
-      <c r="P20" s="73"/>
+      <c r="O20" s="61"/>
+      <c r="P20" s="61"/>
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
       <c r="S20" s="9"/>
       <c r="T20" s="13"/>
-      <c r="U20" s="76"/>
-      <c r="V20" s="73"/>
-      <c r="W20" s="73"/>
-      <c r="X20" s="73"/>
-      <c r="Y20" s="73"/>
-      <c r="Z20" s="73"/>
-      <c r="AA20" s="73"/>
-      <c r="AB20" s="73"/>
-      <c r="AC20" s="73"/>
-      <c r="AD20" s="73"/>
-      <c r="AE20" s="73"/>
+      <c r="U20" s="62"/>
+      <c r="V20" s="61"/>
+      <c r="W20" s="61"/>
+      <c r="X20" s="61"/>
+      <c r="Y20" s="61"/>
+      <c r="Z20" s="61"/>
+      <c r="AA20" s="61"/>
+      <c r="AB20" s="61"/>
+      <c r="AC20" s="61"/>
+      <c r="AD20" s="61"/>
+      <c r="AE20" s="61"/>
       <c r="AF20" s="9"/>
-      <c r="AG20" s="73"/>
-      <c r="AH20" s="73"/>
+      <c r="AG20" s="61"/>
+      <c r="AH20" s="61"/>
       <c r="AI20" s="9"/>
-      <c r="AJ20" s="73"/>
-      <c r="AK20" s="73"/>
+      <c r="AJ20" s="61"/>
+      <c r="AK20" s="61"/>
       <c r="AL20" s="9"/>
       <c r="AM20" s="9"/>
       <c r="AN20" s="9"/>
@@ -6597,43 +6608,43 @@
       <c r="BI20" s="10"/>
     </row>
     <row r="21" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="73"/>
-      <c r="B21" s="73"/>
-      <c r="C21" s="73"/>
-      <c r="D21" s="73"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="73"/>
-      <c r="G21" s="73"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="73"/>
-      <c r="J21" s="73"/>
+      <c r="A21" s="61"/>
+      <c r="B21" s="61"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="61"/>
       <c r="K21" s="9"/>
-      <c r="L21" s="73"/>
-      <c r="M21" s="73"/>
+      <c r="L21" s="61"/>
+      <c r="M21" s="61"/>
       <c r="N21" s="9"/>
-      <c r="O21" s="73"/>
-      <c r="P21" s="73"/>
+      <c r="O21" s="61"/>
+      <c r="P21" s="61"/>
       <c r="Q21" s="9"/>
       <c r="R21" s="9"/>
       <c r="S21" s="9"/>
       <c r="T21" s="13"/>
-      <c r="U21" s="76"/>
-      <c r="V21" s="73"/>
-      <c r="W21" s="73"/>
-      <c r="X21" s="73"/>
-      <c r="Y21" s="73"/>
-      <c r="Z21" s="73"/>
-      <c r="AA21" s="73"/>
-      <c r="AB21" s="73"/>
-      <c r="AC21" s="73"/>
-      <c r="AD21" s="73"/>
-      <c r="AE21" s="73"/>
+      <c r="U21" s="62"/>
+      <c r="V21" s="61"/>
+      <c r="W21" s="61"/>
+      <c r="X21" s="61"/>
+      <c r="Y21" s="61"/>
+      <c r="Z21" s="61"/>
+      <c r="AA21" s="61"/>
+      <c r="AB21" s="61"/>
+      <c r="AC21" s="61"/>
+      <c r="AD21" s="61"/>
+      <c r="AE21" s="61"/>
       <c r="AF21" s="9"/>
-      <c r="AG21" s="73"/>
-      <c r="AH21" s="73"/>
+      <c r="AG21" s="61"/>
+      <c r="AH21" s="61"/>
       <c r="AI21" s="9"/>
-      <c r="AJ21" s="73"/>
-      <c r="AK21" s="73"/>
+      <c r="AJ21" s="61"/>
+      <c r="AK21" s="61"/>
       <c r="AL21" s="9"/>
       <c r="AM21" s="9"/>
       <c r="AN21" s="9"/>
@@ -6660,43 +6671,43 @@
       <c r="BI21" s="10"/>
     </row>
     <row r="22" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="73"/>
-      <c r="B22" s="73"/>
-      <c r="C22" s="73"/>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="73"/>
-      <c r="G22" s="73"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="73"/>
-      <c r="J22" s="73"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="61"/>
       <c r="K22" s="9"/>
-      <c r="L22" s="73"/>
-      <c r="M22" s="73"/>
+      <c r="L22" s="61"/>
+      <c r="M22" s="61"/>
       <c r="N22" s="9"/>
-      <c r="O22" s="73"/>
-      <c r="P22" s="73"/>
+      <c r="O22" s="61"/>
+      <c r="P22" s="61"/>
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
       <c r="S22" s="9"/>
       <c r="T22" s="13"/>
-      <c r="U22" s="76"/>
-      <c r="V22" s="73"/>
-      <c r="W22" s="73"/>
-      <c r="X22" s="73"/>
-      <c r="Y22" s="73"/>
-      <c r="Z22" s="73"/>
-      <c r="AA22" s="73"/>
-      <c r="AB22" s="73"/>
-      <c r="AC22" s="73"/>
-      <c r="AD22" s="73"/>
-      <c r="AE22" s="73"/>
+      <c r="U22" s="62"/>
+      <c r="V22" s="61"/>
+      <c r="W22" s="61"/>
+      <c r="X22" s="61"/>
+      <c r="Y22" s="61"/>
+      <c r="Z22" s="61"/>
+      <c r="AA22" s="61"/>
+      <c r="AB22" s="61"/>
+      <c r="AC22" s="61"/>
+      <c r="AD22" s="61"/>
+      <c r="AE22" s="61"/>
       <c r="AF22" s="9"/>
-      <c r="AG22" s="73"/>
-      <c r="AH22" s="73"/>
+      <c r="AG22" s="61"/>
+      <c r="AH22" s="61"/>
       <c r="AI22" s="9"/>
-      <c r="AJ22" s="73"/>
-      <c r="AK22" s="73"/>
+      <c r="AJ22" s="61"/>
+      <c r="AK22" s="61"/>
       <c r="AL22" s="9"/>
       <c r="AM22" s="9"/>
       <c r="AN22" s="9"/>
@@ -6723,43 +6734,43 @@
       <c r="BI22" s="10"/>
     </row>
     <row r="23" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="73"/>
-      <c r="B23" s="73"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="73"/>
+      <c r="A23" s="61"/>
+      <c r="B23" s="61"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="61"/>
       <c r="K23" s="9"/>
-      <c r="L23" s="73"/>
-      <c r="M23" s="73"/>
+      <c r="L23" s="61"/>
+      <c r="M23" s="61"/>
       <c r="N23" s="9"/>
-      <c r="O23" s="73"/>
-      <c r="P23" s="73"/>
+      <c r="O23" s="61"/>
+      <c r="P23" s="61"/>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
       <c r="S23" s="9"/>
       <c r="T23" s="13"/>
-      <c r="U23" s="76"/>
-      <c r="V23" s="73"/>
-      <c r="W23" s="73"/>
-      <c r="X23" s="73"/>
-      <c r="Y23" s="73"/>
-      <c r="Z23" s="73"/>
-      <c r="AA23" s="73"/>
-      <c r="AB23" s="73"/>
-      <c r="AC23" s="73"/>
-      <c r="AD23" s="73"/>
-      <c r="AE23" s="73"/>
+      <c r="U23" s="62"/>
+      <c r="V23" s="61"/>
+      <c r="W23" s="61"/>
+      <c r="X23" s="61"/>
+      <c r="Y23" s="61"/>
+      <c r="Z23" s="61"/>
+      <c r="AA23" s="61"/>
+      <c r="AB23" s="61"/>
+      <c r="AC23" s="61"/>
+      <c r="AD23" s="61"/>
+      <c r="AE23" s="61"/>
       <c r="AF23" s="9"/>
-      <c r="AG23" s="73"/>
-      <c r="AH23" s="73"/>
+      <c r="AG23" s="61"/>
+      <c r="AH23" s="61"/>
       <c r="AI23" s="9"/>
-      <c r="AJ23" s="73"/>
-      <c r="AK23" s="73"/>
+      <c r="AJ23" s="61"/>
+      <c r="AK23" s="61"/>
       <c r="AL23" s="9"/>
       <c r="AM23" s="9"/>
       <c r="AN23" s="9"/>
@@ -6786,43 +6797,43 @@
       <c r="BI23" s="10"/>
     </row>
     <row r="24" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="73"/>
-      <c r="B24" s="73"/>
-      <c r="C24" s="73"/>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="73"/>
-      <c r="G24" s="73"/>
-      <c r="H24" s="73"/>
-      <c r="I24" s="73"/>
-      <c r="J24" s="73"/>
+      <c r="A24" s="61"/>
+      <c r="B24" s="61"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="61"/>
+      <c r="F24" s="61"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="61"/>
       <c r="K24" s="9"/>
-      <c r="L24" s="73"/>
-      <c r="M24" s="73"/>
+      <c r="L24" s="61"/>
+      <c r="M24" s="61"/>
       <c r="N24" s="9"/>
-      <c r="O24" s="73"/>
-      <c r="P24" s="73"/>
+      <c r="O24" s="61"/>
+      <c r="P24" s="61"/>
       <c r="Q24" s="9"/>
       <c r="R24" s="9"/>
       <c r="S24" s="9"/>
       <c r="T24" s="13"/>
-      <c r="U24" s="76"/>
-      <c r="V24" s="73"/>
-      <c r="W24" s="73"/>
-      <c r="X24" s="73"/>
-      <c r="Y24" s="73"/>
-      <c r="Z24" s="73"/>
-      <c r="AA24" s="73"/>
-      <c r="AB24" s="73"/>
-      <c r="AC24" s="73"/>
-      <c r="AD24" s="73"/>
-      <c r="AE24" s="73"/>
+      <c r="U24" s="62"/>
+      <c r="V24" s="61"/>
+      <c r="W24" s="61"/>
+      <c r="X24" s="61"/>
+      <c r="Y24" s="61"/>
+      <c r="Z24" s="61"/>
+      <c r="AA24" s="61"/>
+      <c r="AB24" s="61"/>
+      <c r="AC24" s="61"/>
+      <c r="AD24" s="61"/>
+      <c r="AE24" s="61"/>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="73"/>
-      <c r="AH24" s="73"/>
+      <c r="AG24" s="61"/>
+      <c r="AH24" s="61"/>
       <c r="AI24" s="9"/>
-      <c r="AJ24" s="73"/>
-      <c r="AK24" s="73"/>
+      <c r="AJ24" s="61"/>
+      <c r="AK24" s="61"/>
       <c r="AL24" s="9"/>
       <c r="AM24" s="9"/>
       <c r="AN24" s="9"/>
@@ -6849,43 +6860,43 @@
       <c r="BI24" s="10"/>
     </row>
     <row r="25" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="73"/>
-      <c r="B25" s="73"/>
-      <c r="C25" s="73"/>
-      <c r="D25" s="73"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="73"/>
-      <c r="G25" s="73"/>
-      <c r="H25" s="73"/>
-      <c r="I25" s="73"/>
-      <c r="J25" s="73"/>
+      <c r="A25" s="61"/>
+      <c r="B25" s="61"/>
+      <c r="C25" s="61"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="61"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="61"/>
       <c r="K25" s="9"/>
-      <c r="L25" s="73"/>
-      <c r="M25" s="73"/>
+      <c r="L25" s="61"/>
+      <c r="M25" s="61"/>
       <c r="N25" s="9"/>
-      <c r="O25" s="73"/>
-      <c r="P25" s="73"/>
+      <c r="O25" s="61"/>
+      <c r="P25" s="61"/>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
       <c r="S25" s="9"/>
       <c r="T25" s="13"/>
-      <c r="U25" s="76"/>
-      <c r="V25" s="73"/>
-      <c r="W25" s="73"/>
-      <c r="X25" s="73"/>
-      <c r="Y25" s="73"/>
-      <c r="Z25" s="73"/>
-      <c r="AA25" s="73"/>
-      <c r="AB25" s="73"/>
-      <c r="AC25" s="73"/>
-      <c r="AD25" s="73"/>
-      <c r="AE25" s="73"/>
+      <c r="U25" s="62"/>
+      <c r="V25" s="61"/>
+      <c r="W25" s="61"/>
+      <c r="X25" s="61"/>
+      <c r="Y25" s="61"/>
+      <c r="Z25" s="61"/>
+      <c r="AA25" s="61"/>
+      <c r="AB25" s="61"/>
+      <c r="AC25" s="61"/>
+      <c r="AD25" s="61"/>
+      <c r="AE25" s="61"/>
       <c r="AF25" s="9"/>
-      <c r="AG25" s="73"/>
-      <c r="AH25" s="73"/>
+      <c r="AG25" s="61"/>
+      <c r="AH25" s="61"/>
       <c r="AI25" s="9"/>
-      <c r="AJ25" s="73"/>
-      <c r="AK25" s="73"/>
+      <c r="AJ25" s="61"/>
+      <c r="AK25" s="61"/>
       <c r="AL25" s="9"/>
       <c r="AM25" s="9"/>
       <c r="AN25" s="9"/>
@@ -6912,43 +6923,43 @@
       <c r="BI25" s="10"/>
     </row>
     <row r="26" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="73"/>
-      <c r="B26" s="73"/>
-      <c r="C26" s="73"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="73"/>
-      <c r="G26" s="73"/>
-      <c r="H26" s="73"/>
-      <c r="I26" s="73"/>
-      <c r="J26" s="73"/>
+      <c r="A26" s="61"/>
+      <c r="B26" s="61"/>
+      <c r="C26" s="61"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="61"/>
       <c r="K26" s="9"/>
-      <c r="L26" s="73"/>
-      <c r="M26" s="73"/>
+      <c r="L26" s="61"/>
+      <c r="M26" s="61"/>
       <c r="N26" s="9"/>
-      <c r="O26" s="73"/>
-      <c r="P26" s="73"/>
+      <c r="O26" s="61"/>
+      <c r="P26" s="61"/>
       <c r="Q26" s="9"/>
       <c r="R26" s="9"/>
       <c r="S26" s="9"/>
       <c r="T26" s="13"/>
-      <c r="U26" s="76"/>
-      <c r="V26" s="73"/>
-      <c r="W26" s="73"/>
-      <c r="X26" s="73"/>
-      <c r="Y26" s="73"/>
-      <c r="Z26" s="73"/>
-      <c r="AA26" s="73"/>
-      <c r="AB26" s="73"/>
-      <c r="AC26" s="73"/>
-      <c r="AD26" s="73"/>
-      <c r="AE26" s="73"/>
+      <c r="U26" s="62"/>
+      <c r="V26" s="61"/>
+      <c r="W26" s="61"/>
+      <c r="X26" s="61"/>
+      <c r="Y26" s="61"/>
+      <c r="Z26" s="61"/>
+      <c r="AA26" s="61"/>
+      <c r="AB26" s="61"/>
+      <c r="AC26" s="61"/>
+      <c r="AD26" s="61"/>
+      <c r="AE26" s="61"/>
       <c r="AF26" s="9"/>
-      <c r="AG26" s="73"/>
-      <c r="AH26" s="73"/>
+      <c r="AG26" s="61"/>
+      <c r="AH26" s="61"/>
       <c r="AI26" s="9"/>
-      <c r="AJ26" s="73"/>
-      <c r="AK26" s="73"/>
+      <c r="AJ26" s="61"/>
+      <c r="AK26" s="61"/>
       <c r="AL26" s="9"/>
       <c r="AM26" s="9"/>
       <c r="AN26" s="9"/>
@@ -6975,43 +6986,43 @@
       <c r="BI26" s="10"/>
     </row>
     <row r="27" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="73"/>
-      <c r="B27" s="73"/>
-      <c r="C27" s="73"/>
-      <c r="D27" s="73"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="73"/>
-      <c r="H27" s="73"/>
-      <c r="I27" s="73"/>
-      <c r="J27" s="73"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="61"/>
+      <c r="C27" s="61"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="61"/>
+      <c r="F27" s="61"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="61"/>
       <c r="K27" s="9"/>
-      <c r="L27" s="73"/>
-      <c r="M27" s="73"/>
+      <c r="L27" s="61"/>
+      <c r="M27" s="61"/>
       <c r="N27" s="9"/>
-      <c r="O27" s="73"/>
-      <c r="P27" s="73"/>
+      <c r="O27" s="61"/>
+      <c r="P27" s="61"/>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="9"/>
       <c r="T27" s="13"/>
-      <c r="U27" s="76"/>
-      <c r="V27" s="73"/>
-      <c r="W27" s="73"/>
-      <c r="X27" s="73"/>
-      <c r="Y27" s="73"/>
-      <c r="Z27" s="73"/>
-      <c r="AA27" s="73"/>
-      <c r="AB27" s="73"/>
-      <c r="AC27" s="73"/>
-      <c r="AD27" s="73"/>
-      <c r="AE27" s="73"/>
+      <c r="U27" s="62"/>
+      <c r="V27" s="61"/>
+      <c r="W27" s="61"/>
+      <c r="X27" s="61"/>
+      <c r="Y27" s="61"/>
+      <c r="Z27" s="61"/>
+      <c r="AA27" s="61"/>
+      <c r="AB27" s="61"/>
+      <c r="AC27" s="61"/>
+      <c r="AD27" s="61"/>
+      <c r="AE27" s="61"/>
       <c r="AF27" s="9"/>
-      <c r="AG27" s="73"/>
-      <c r="AH27" s="73"/>
+      <c r="AG27" s="61"/>
+      <c r="AH27" s="61"/>
       <c r="AI27" s="9"/>
-      <c r="AJ27" s="73"/>
-      <c r="AK27" s="73"/>
+      <c r="AJ27" s="61"/>
+      <c r="AK27" s="61"/>
       <c r="AL27" s="9"/>
       <c r="AM27" s="9"/>
       <c r="AN27" s="9"/>
@@ -7038,43 +7049,43 @@
       <c r="BI27" s="10"/>
     </row>
     <row r="28" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="73"/>
-      <c r="B28" s="73"/>
-      <c r="C28" s="73"/>
-      <c r="D28" s="73"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="73"/>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
-      <c r="I28" s="73"/>
-      <c r="J28" s="73"/>
+      <c r="A28" s="61"/>
+      <c r="B28" s="61"/>
+      <c r="C28" s="61"/>
+      <c r="D28" s="61"/>
+      <c r="E28" s="61"/>
+      <c r="F28" s="61"/>
+      <c r="G28" s="61"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="61"/>
       <c r="K28" s="9"/>
-      <c r="L28" s="73"/>
-      <c r="M28" s="73"/>
+      <c r="L28" s="61"/>
+      <c r="M28" s="61"/>
       <c r="N28" s="9"/>
-      <c r="O28" s="73"/>
-      <c r="P28" s="73"/>
+      <c r="O28" s="61"/>
+      <c r="P28" s="61"/>
       <c r="Q28" s="9"/>
       <c r="R28" s="9"/>
       <c r="S28" s="9"/>
       <c r="T28" s="13"/>
-      <c r="U28" s="76"/>
-      <c r="V28" s="73"/>
-      <c r="W28" s="73"/>
-      <c r="X28" s="73"/>
-      <c r="Y28" s="73"/>
-      <c r="Z28" s="73"/>
-      <c r="AA28" s="73"/>
-      <c r="AB28" s="73"/>
-      <c r="AC28" s="73"/>
-      <c r="AD28" s="73"/>
-      <c r="AE28" s="73"/>
+      <c r="U28" s="62"/>
+      <c r="V28" s="61"/>
+      <c r="W28" s="61"/>
+      <c r="X28" s="61"/>
+      <c r="Y28" s="61"/>
+      <c r="Z28" s="61"/>
+      <c r="AA28" s="61"/>
+      <c r="AB28" s="61"/>
+      <c r="AC28" s="61"/>
+      <c r="AD28" s="61"/>
+      <c r="AE28" s="61"/>
       <c r="AF28" s="9"/>
-      <c r="AG28" s="73"/>
-      <c r="AH28" s="73"/>
+      <c r="AG28" s="61"/>
+      <c r="AH28" s="61"/>
       <c r="AI28" s="9"/>
-      <c r="AJ28" s="73"/>
-      <c r="AK28" s="73"/>
+      <c r="AJ28" s="61"/>
+      <c r="AK28" s="61"/>
       <c r="AL28" s="9"/>
       <c r="AM28" s="9"/>
       <c r="AN28" s="9"/>
@@ -7101,43 +7112,43 @@
       <c r="BI28" s="10"/>
     </row>
     <row r="29" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="73"/>
-      <c r="B29" s="73"/>
-      <c r="C29" s="73"/>
-      <c r="D29" s="73"/>
-      <c r="E29" s="73"/>
-      <c r="F29" s="73"/>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73"/>
-      <c r="I29" s="73"/>
-      <c r="J29" s="73"/>
+      <c r="A29" s="61"/>
+      <c r="B29" s="61"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="61"/>
+      <c r="E29" s="61"/>
+      <c r="F29" s="61"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="61"/>
+      <c r="J29" s="61"/>
       <c r="K29" s="9"/>
-      <c r="L29" s="73"/>
-      <c r="M29" s="73"/>
+      <c r="L29" s="61"/>
+      <c r="M29" s="61"/>
       <c r="N29" s="9"/>
-      <c r="O29" s="73"/>
-      <c r="P29" s="73"/>
+      <c r="O29" s="61"/>
+      <c r="P29" s="61"/>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="9"/>
       <c r="T29" s="13"/>
-      <c r="U29" s="76"/>
-      <c r="V29" s="73"/>
-      <c r="W29" s="73"/>
-      <c r="X29" s="73"/>
-      <c r="Y29" s="73"/>
-      <c r="Z29" s="73"/>
-      <c r="AA29" s="73"/>
-      <c r="AB29" s="73"/>
-      <c r="AC29" s="73"/>
-      <c r="AD29" s="73"/>
-      <c r="AE29" s="73"/>
+      <c r="U29" s="62"/>
+      <c r="V29" s="61"/>
+      <c r="W29" s="61"/>
+      <c r="X29" s="61"/>
+      <c r="Y29" s="61"/>
+      <c r="Z29" s="61"/>
+      <c r="AA29" s="61"/>
+      <c r="AB29" s="61"/>
+      <c r="AC29" s="61"/>
+      <c r="AD29" s="61"/>
+      <c r="AE29" s="61"/>
       <c r="AF29" s="9"/>
-      <c r="AG29" s="73"/>
-      <c r="AH29" s="73"/>
+      <c r="AG29" s="61"/>
+      <c r="AH29" s="61"/>
       <c r="AI29" s="9"/>
-      <c r="AJ29" s="73"/>
-      <c r="AK29" s="73"/>
+      <c r="AJ29" s="61"/>
+      <c r="AK29" s="61"/>
       <c r="AL29" s="9"/>
       <c r="AM29" s="9"/>
       <c r="AN29" s="9"/>
@@ -7164,43 +7175,43 @@
       <c r="BI29" s="10"/>
     </row>
     <row r="30" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="73"/>
-      <c r="B30" s="73"/>
-      <c r="C30" s="73"/>
-      <c r="D30" s="73"/>
-      <c r="E30" s="73"/>
-      <c r="F30" s="73"/>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73"/>
-      <c r="I30" s="73"/>
-      <c r="J30" s="73"/>
+      <c r="A30" s="61"/>
+      <c r="B30" s="61"/>
+      <c r="C30" s="61"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="61"/>
       <c r="K30" s="9"/>
-      <c r="L30" s="73"/>
-      <c r="M30" s="73"/>
+      <c r="L30" s="61"/>
+      <c r="M30" s="61"/>
       <c r="N30" s="9"/>
-      <c r="O30" s="73"/>
-      <c r="P30" s="73"/>
+      <c r="O30" s="61"/>
+      <c r="P30" s="61"/>
       <c r="Q30" s="9"/>
       <c r="R30" s="9"/>
       <c r="S30" s="9"/>
       <c r="T30" s="13"/>
-      <c r="U30" s="76"/>
-      <c r="V30" s="73"/>
-      <c r="W30" s="73"/>
-      <c r="X30" s="73"/>
-      <c r="Y30" s="73"/>
-      <c r="Z30" s="73"/>
-      <c r="AA30" s="73"/>
-      <c r="AB30" s="73"/>
-      <c r="AC30" s="73"/>
-      <c r="AD30" s="73"/>
-      <c r="AE30" s="73"/>
+      <c r="U30" s="62"/>
+      <c r="V30" s="61"/>
+      <c r="W30" s="61"/>
+      <c r="X30" s="61"/>
+      <c r="Y30" s="61"/>
+      <c r="Z30" s="61"/>
+      <c r="AA30" s="61"/>
+      <c r="AB30" s="61"/>
+      <c r="AC30" s="61"/>
+      <c r="AD30" s="61"/>
+      <c r="AE30" s="61"/>
       <c r="AF30" s="9"/>
-      <c r="AG30" s="73"/>
-      <c r="AH30" s="73"/>
+      <c r="AG30" s="61"/>
+      <c r="AH30" s="61"/>
       <c r="AI30" s="9"/>
-      <c r="AJ30" s="73"/>
-      <c r="AK30" s="73"/>
+      <c r="AJ30" s="61"/>
+      <c r="AK30" s="61"/>
       <c r="AL30" s="9"/>
       <c r="AM30" s="9"/>
       <c r="AN30" s="9"/>
@@ -7227,43 +7238,43 @@
       <c r="BI30" s="10"/>
     </row>
     <row r="31" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="73"/>
-      <c r="B31" s="73"/>
-      <c r="C31" s="73"/>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="73"/>
-      <c r="G31" s="73"/>
-      <c r="H31" s="73"/>
-      <c r="I31" s="73"/>
-      <c r="J31" s="73"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
+      <c r="C31" s="61"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="61"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="61"/>
       <c r="K31" s="9"/>
-      <c r="L31" s="73"/>
-      <c r="M31" s="73"/>
+      <c r="L31" s="61"/>
+      <c r="M31" s="61"/>
       <c r="N31" s="9"/>
-      <c r="O31" s="73"/>
-      <c r="P31" s="73"/>
+      <c r="O31" s="61"/>
+      <c r="P31" s="61"/>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
       <c r="S31" s="9"/>
       <c r="T31" s="13"/>
-      <c r="U31" s="76"/>
-      <c r="V31" s="73"/>
-      <c r="W31" s="73"/>
-      <c r="X31" s="73"/>
-      <c r="Y31" s="73"/>
-      <c r="Z31" s="73"/>
-      <c r="AA31" s="73"/>
-      <c r="AB31" s="73"/>
-      <c r="AC31" s="73"/>
-      <c r="AD31" s="73"/>
-      <c r="AE31" s="73"/>
+      <c r="U31" s="62"/>
+      <c r="V31" s="61"/>
+      <c r="W31" s="61"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="61"/>
+      <c r="Z31" s="61"/>
+      <c r="AA31" s="61"/>
+      <c r="AB31" s="61"/>
+      <c r="AC31" s="61"/>
+      <c r="AD31" s="61"/>
+      <c r="AE31" s="61"/>
       <c r="AF31" s="9"/>
-      <c r="AG31" s="73"/>
-      <c r="AH31" s="73"/>
+      <c r="AG31" s="61"/>
+      <c r="AH31" s="61"/>
       <c r="AI31" s="9"/>
-      <c r="AJ31" s="73"/>
-      <c r="AK31" s="73"/>
+      <c r="AJ31" s="61"/>
+      <c r="AK31" s="61"/>
       <c r="AL31" s="9"/>
       <c r="AM31" s="9"/>
       <c r="AN31" s="9"/>
@@ -7290,43 +7301,43 @@
       <c r="BI31" s="10"/>
     </row>
     <row r="32" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="73"/>
-      <c r="B32" s="73"/>
-      <c r="C32" s="73"/>
-      <c r="D32" s="73"/>
-      <c r="E32" s="73"/>
-      <c r="F32" s="73"/>
-      <c r="G32" s="73"/>
-      <c r="H32" s="73"/>
-      <c r="I32" s="73"/>
-      <c r="J32" s="73"/>
+      <c r="A32" s="61"/>
+      <c r="B32" s="61"/>
+      <c r="C32" s="61"/>
+      <c r="D32" s="61"/>
+      <c r="E32" s="61"/>
+      <c r="F32" s="61"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="61"/>
       <c r="K32" s="9"/>
-      <c r="L32" s="73"/>
-      <c r="M32" s="73"/>
+      <c r="L32" s="61"/>
+      <c r="M32" s="61"/>
       <c r="N32" s="9"/>
-      <c r="O32" s="73"/>
-      <c r="P32" s="73"/>
+      <c r="O32" s="61"/>
+      <c r="P32" s="61"/>
       <c r="Q32" s="9"/>
       <c r="R32" s="9"/>
       <c r="S32" s="9"/>
       <c r="T32" s="13"/>
-      <c r="U32" s="76"/>
-      <c r="V32" s="73"/>
-      <c r="W32" s="73"/>
-      <c r="X32" s="73"/>
-      <c r="Y32" s="73"/>
-      <c r="Z32" s="73"/>
-      <c r="AA32" s="73"/>
-      <c r="AB32" s="73"/>
-      <c r="AC32" s="73"/>
-      <c r="AD32" s="73"/>
-      <c r="AE32" s="73"/>
+      <c r="U32" s="62"/>
+      <c r="V32" s="61"/>
+      <c r="W32" s="61"/>
+      <c r="X32" s="61"/>
+      <c r="Y32" s="61"/>
+      <c r="Z32" s="61"/>
+      <c r="AA32" s="61"/>
+      <c r="AB32" s="61"/>
+      <c r="AC32" s="61"/>
+      <c r="AD32" s="61"/>
+      <c r="AE32" s="61"/>
       <c r="AF32" s="9"/>
-      <c r="AG32" s="73"/>
-      <c r="AH32" s="73"/>
+      <c r="AG32" s="61"/>
+      <c r="AH32" s="61"/>
       <c r="AI32" s="9"/>
-      <c r="AJ32" s="73"/>
-      <c r="AK32" s="73"/>
+      <c r="AJ32" s="61"/>
+      <c r="AK32" s="61"/>
       <c r="AL32" s="9"/>
       <c r="AM32" s="9"/>
       <c r="AN32" s="9"/>
@@ -7353,43 +7364,43 @@
       <c r="BI32" s="10"/>
     </row>
     <row r="33" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="73"/>
-      <c r="B33" s="73"/>
-      <c r="C33" s="73"/>
-      <c r="D33" s="73"/>
-      <c r="E33" s="73"/>
-      <c r="F33" s="73"/>
-      <c r="G33" s="73"/>
-      <c r="H33" s="73"/>
-      <c r="I33" s="73"/>
-      <c r="J33" s="73"/>
+      <c r="A33" s="61"/>
+      <c r="B33" s="61"/>
+      <c r="C33" s="61"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="61"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="61"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="61"/>
+      <c r="J33" s="61"/>
       <c r="K33" s="9"/>
-      <c r="L33" s="73"/>
-      <c r="M33" s="73"/>
+      <c r="L33" s="61"/>
+      <c r="M33" s="61"/>
       <c r="N33" s="9"/>
-      <c r="O33" s="73"/>
-      <c r="P33" s="73"/>
+      <c r="O33" s="61"/>
+      <c r="P33" s="61"/>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="9"/>
       <c r="T33" s="13"/>
-      <c r="U33" s="76"/>
-      <c r="V33" s="73"/>
-      <c r="W33" s="73"/>
-      <c r="X33" s="73"/>
-      <c r="Y33" s="73"/>
-      <c r="Z33" s="73"/>
-      <c r="AA33" s="73"/>
-      <c r="AB33" s="73"/>
-      <c r="AC33" s="73"/>
-      <c r="AD33" s="73"/>
-      <c r="AE33" s="73"/>
+      <c r="U33" s="62"/>
+      <c r="V33" s="61"/>
+      <c r="W33" s="61"/>
+      <c r="X33" s="61"/>
+      <c r="Y33" s="61"/>
+      <c r="Z33" s="61"/>
+      <c r="AA33" s="61"/>
+      <c r="AB33" s="61"/>
+      <c r="AC33" s="61"/>
+      <c r="AD33" s="61"/>
+      <c r="AE33" s="61"/>
       <c r="AF33" s="9"/>
-      <c r="AG33" s="73"/>
-      <c r="AH33" s="73"/>
+      <c r="AG33" s="61"/>
+      <c r="AH33" s="61"/>
       <c r="AI33" s="9"/>
-      <c r="AJ33" s="73"/>
-      <c r="AK33" s="73"/>
+      <c r="AJ33" s="61"/>
+      <c r="AK33" s="61"/>
       <c r="AL33" s="9"/>
       <c r="AM33" s="9"/>
       <c r="AN33" s="9"/>
@@ -7416,43 +7427,43 @@
       <c r="BI33" s="10"/>
     </row>
     <row r="34" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="73"/>
-      <c r="B34" s="73"/>
-      <c r="C34" s="73"/>
-      <c r="D34" s="73"/>
-      <c r="E34" s="73"/>
-      <c r="F34" s="73"/>
-      <c r="G34" s="73"/>
-      <c r="H34" s="73"/>
-      <c r="I34" s="73"/>
-      <c r="J34" s="73"/>
+      <c r="A34" s="61"/>
+      <c r="B34" s="61"/>
+      <c r="C34" s="61"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="61"/>
       <c r="K34" s="9"/>
-      <c r="L34" s="73"/>
-      <c r="M34" s="73"/>
+      <c r="L34" s="61"/>
+      <c r="M34" s="61"/>
       <c r="N34" s="9"/>
-      <c r="O34" s="73"/>
-      <c r="P34" s="73"/>
+      <c r="O34" s="61"/>
+      <c r="P34" s="61"/>
       <c r="Q34" s="9"/>
       <c r="R34" s="9"/>
       <c r="S34" s="9"/>
       <c r="T34" s="13"/>
-      <c r="U34" s="76"/>
-      <c r="V34" s="73"/>
-      <c r="W34" s="73"/>
-      <c r="X34" s="73"/>
-      <c r="Y34" s="73"/>
-      <c r="Z34" s="73"/>
-      <c r="AA34" s="73"/>
-      <c r="AB34" s="73"/>
-      <c r="AC34" s="73"/>
-      <c r="AD34" s="73"/>
-      <c r="AE34" s="73"/>
+      <c r="U34" s="62"/>
+      <c r="V34" s="61"/>
+      <c r="W34" s="61"/>
+      <c r="X34" s="61"/>
+      <c r="Y34" s="61"/>
+      <c r="Z34" s="61"/>
+      <c r="AA34" s="61"/>
+      <c r="AB34" s="61"/>
+      <c r="AC34" s="61"/>
+      <c r="AD34" s="61"/>
+      <c r="AE34" s="61"/>
       <c r="AF34" s="9"/>
-      <c r="AG34" s="73"/>
-      <c r="AH34" s="73"/>
+      <c r="AG34" s="61"/>
+      <c r="AH34" s="61"/>
       <c r="AI34" s="9"/>
-      <c r="AJ34" s="73"/>
-      <c r="AK34" s="73"/>
+      <c r="AJ34" s="61"/>
+      <c r="AK34" s="61"/>
       <c r="AL34" s="9"/>
       <c r="AM34" s="9"/>
       <c r="AN34" s="9"/>
@@ -7479,43 +7490,43 @@
       <c r="BI34" s="10"/>
     </row>
     <row r="35" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="73"/>
-      <c r="B35" s="73"/>
-      <c r="C35" s="73"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
-      <c r="F35" s="73"/>
-      <c r="G35" s="73"/>
-      <c r="H35" s="73"/>
-      <c r="I35" s="73"/>
-      <c r="J35" s="73"/>
+      <c r="A35" s="61"/>
+      <c r="B35" s="61"/>
+      <c r="C35" s="61"/>
+      <c r="D35" s="61"/>
+      <c r="E35" s="61"/>
+      <c r="F35" s="61"/>
+      <c r="G35" s="61"/>
+      <c r="H35" s="61"/>
+      <c r="I35" s="61"/>
+      <c r="J35" s="61"/>
       <c r="K35" s="9"/>
-      <c r="L35" s="73"/>
-      <c r="M35" s="73"/>
+      <c r="L35" s="61"/>
+      <c r="M35" s="61"/>
       <c r="N35" s="9"/>
-      <c r="O35" s="73"/>
-      <c r="P35" s="73"/>
+      <c r="O35" s="61"/>
+      <c r="P35" s="61"/>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
       <c r="S35" s="9"/>
       <c r="T35" s="13"/>
-      <c r="U35" s="76"/>
-      <c r="V35" s="73"/>
-      <c r="W35" s="73"/>
-      <c r="X35" s="73"/>
-      <c r="Y35" s="73"/>
-      <c r="Z35" s="73"/>
-      <c r="AA35" s="73"/>
-      <c r="AB35" s="73"/>
-      <c r="AC35" s="73"/>
-      <c r="AD35" s="73"/>
-      <c r="AE35" s="73"/>
+      <c r="U35" s="62"/>
+      <c r="V35" s="61"/>
+      <c r="W35" s="61"/>
+      <c r="X35" s="61"/>
+      <c r="Y35" s="61"/>
+      <c r="Z35" s="61"/>
+      <c r="AA35" s="61"/>
+      <c r="AB35" s="61"/>
+      <c r="AC35" s="61"/>
+      <c r="AD35" s="61"/>
+      <c r="AE35" s="61"/>
       <c r="AF35" s="9"/>
-      <c r="AG35" s="73"/>
-      <c r="AH35" s="73"/>
+      <c r="AG35" s="61"/>
+      <c r="AH35" s="61"/>
       <c r="AI35" s="9"/>
-      <c r="AJ35" s="73"/>
-      <c r="AK35" s="73"/>
+      <c r="AJ35" s="61"/>
+      <c r="AK35" s="61"/>
       <c r="AL35" s="9"/>
       <c r="AM35" s="9"/>
       <c r="AN35" s="9"/>
@@ -7542,43 +7553,43 @@
       <c r="BI35" s="10"/>
     </row>
     <row r="36" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="73"/>
-      <c r="B36" s="73"/>
-      <c r="C36" s="73"/>
-      <c r="D36" s="73"/>
-      <c r="E36" s="73"/>
-      <c r="F36" s="73"/>
-      <c r="G36" s="73"/>
-      <c r="H36" s="73"/>
-      <c r="I36" s="73"/>
-      <c r="J36" s="73"/>
+      <c r="A36" s="61"/>
+      <c r="B36" s="61"/>
+      <c r="C36" s="61"/>
+      <c r="D36" s="61"/>
+      <c r="E36" s="61"/>
+      <c r="F36" s="61"/>
+      <c r="G36" s="61"/>
+      <c r="H36" s="61"/>
+      <c r="I36" s="61"/>
+      <c r="J36" s="61"/>
       <c r="K36" s="9"/>
-      <c r="L36" s="73"/>
-      <c r="M36" s="73"/>
+      <c r="L36" s="61"/>
+      <c r="M36" s="61"/>
       <c r="N36" s="9"/>
-      <c r="O36" s="73"/>
-      <c r="P36" s="73"/>
+      <c r="O36" s="61"/>
+      <c r="P36" s="61"/>
       <c r="Q36" s="9"/>
       <c r="R36" s="9"/>
       <c r="S36" s="9"/>
       <c r="T36" s="13"/>
-      <c r="U36" s="76"/>
-      <c r="V36" s="73"/>
-      <c r="W36" s="73"/>
-      <c r="X36" s="73"/>
-      <c r="Y36" s="73"/>
-      <c r="Z36" s="73"/>
-      <c r="AA36" s="73"/>
-      <c r="AB36" s="73"/>
-      <c r="AC36" s="73"/>
-      <c r="AD36" s="73"/>
-      <c r="AE36" s="73"/>
+      <c r="U36" s="62"/>
+      <c r="V36" s="61"/>
+      <c r="W36" s="61"/>
+      <c r="X36" s="61"/>
+      <c r="Y36" s="61"/>
+      <c r="Z36" s="61"/>
+      <c r="AA36" s="61"/>
+      <c r="AB36" s="61"/>
+      <c r="AC36" s="61"/>
+      <c r="AD36" s="61"/>
+      <c r="AE36" s="61"/>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="73"/>
-      <c r="AH36" s="73"/>
+      <c r="AG36" s="61"/>
+      <c r="AH36" s="61"/>
       <c r="AI36" s="9"/>
-      <c r="AJ36" s="73"/>
-      <c r="AK36" s="73"/>
+      <c r="AJ36" s="61"/>
+      <c r="AK36" s="61"/>
       <c r="AL36" s="9"/>
       <c r="AM36" s="9"/>
       <c r="AN36" s="9"/>
@@ -7605,43 +7616,43 @@
       <c r="BI36" s="10"/>
     </row>
     <row r="37" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="73"/>
-      <c r="B37" s="73"/>
-      <c r="C37" s="73"/>
-      <c r="D37" s="73"/>
-      <c r="E37" s="73"/>
-      <c r="F37" s="73"/>
-      <c r="G37" s="73"/>
-      <c r="H37" s="73"/>
-      <c r="I37" s="73"/>
-      <c r="J37" s="73"/>
+      <c r="A37" s="61"/>
+      <c r="B37" s="61"/>
+      <c r="C37" s="61"/>
+      <c r="D37" s="61"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="61"/>
+      <c r="G37" s="61"/>
+      <c r="H37" s="61"/>
+      <c r="I37" s="61"/>
+      <c r="J37" s="61"/>
       <c r="K37" s="9"/>
-      <c r="L37" s="73"/>
-      <c r="M37" s="73"/>
+      <c r="L37" s="61"/>
+      <c r="M37" s="61"/>
       <c r="N37" s="9"/>
-      <c r="O37" s="73"/>
-      <c r="P37" s="73"/>
+      <c r="O37" s="61"/>
+      <c r="P37" s="61"/>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="9"/>
       <c r="T37" s="13"/>
-      <c r="U37" s="76"/>
-      <c r="V37" s="73"/>
-      <c r="W37" s="73"/>
-      <c r="X37" s="73"/>
-      <c r="Y37" s="73"/>
-      <c r="Z37" s="73"/>
-      <c r="AA37" s="73"/>
-      <c r="AB37" s="73"/>
-      <c r="AC37" s="73"/>
-      <c r="AD37" s="73"/>
-      <c r="AE37" s="73"/>
+      <c r="U37" s="62"/>
+      <c r="V37" s="61"/>
+      <c r="W37" s="61"/>
+      <c r="X37" s="61"/>
+      <c r="Y37" s="61"/>
+      <c r="Z37" s="61"/>
+      <c r="AA37" s="61"/>
+      <c r="AB37" s="61"/>
+      <c r="AC37" s="61"/>
+      <c r="AD37" s="61"/>
+      <c r="AE37" s="61"/>
       <c r="AF37" s="9"/>
-      <c r="AG37" s="73"/>
-      <c r="AH37" s="73"/>
+      <c r="AG37" s="61"/>
+      <c r="AH37" s="61"/>
       <c r="AI37" s="9"/>
-      <c r="AJ37" s="73"/>
-      <c r="AK37" s="73"/>
+      <c r="AJ37" s="61"/>
+      <c r="AK37" s="61"/>
       <c r="AL37" s="9"/>
       <c r="AM37" s="9"/>
       <c r="AN37" s="9"/>
@@ -7668,43 +7679,43 @@
       <c r="BI37" s="10"/>
     </row>
     <row r="38" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="73"/>
-      <c r="B38" s="73"/>
-      <c r="C38" s="73"/>
-      <c r="D38" s="73"/>
-      <c r="E38" s="73"/>
-      <c r="F38" s="73"/>
-      <c r="G38" s="73"/>
-      <c r="H38" s="73"/>
-      <c r="I38" s="73"/>
-      <c r="J38" s="73"/>
+      <c r="A38" s="61"/>
+      <c r="B38" s="61"/>
+      <c r="C38" s="61"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="61"/>
+      <c r="F38" s="61"/>
+      <c r="G38" s="61"/>
+      <c r="H38" s="61"/>
+      <c r="I38" s="61"/>
+      <c r="J38" s="61"/>
       <c r="K38" s="9"/>
-      <c r="L38" s="73"/>
-      <c r="M38" s="73"/>
+      <c r="L38" s="61"/>
+      <c r="M38" s="61"/>
       <c r="N38" s="9"/>
-      <c r="O38" s="73"/>
-      <c r="P38" s="73"/>
+      <c r="O38" s="61"/>
+      <c r="P38" s="61"/>
       <c r="Q38" s="9"/>
       <c r="R38" s="9"/>
       <c r="S38" s="9"/>
       <c r="T38" s="13"/>
-      <c r="U38" s="76"/>
-      <c r="V38" s="73"/>
-      <c r="W38" s="73"/>
-      <c r="X38" s="73"/>
-      <c r="Y38" s="73"/>
-      <c r="Z38" s="73"/>
-      <c r="AA38" s="73"/>
-      <c r="AB38" s="73"/>
-      <c r="AC38" s="73"/>
-      <c r="AD38" s="73"/>
-      <c r="AE38" s="73"/>
+      <c r="U38" s="62"/>
+      <c r="V38" s="61"/>
+      <c r="W38" s="61"/>
+      <c r="X38" s="61"/>
+      <c r="Y38" s="61"/>
+      <c r="Z38" s="61"/>
+      <c r="AA38" s="61"/>
+      <c r="AB38" s="61"/>
+      <c r="AC38" s="61"/>
+      <c r="AD38" s="61"/>
+      <c r="AE38" s="61"/>
       <c r="AF38" s="9"/>
-      <c r="AG38" s="73"/>
-      <c r="AH38" s="73"/>
+      <c r="AG38" s="61"/>
+      <c r="AH38" s="61"/>
       <c r="AI38" s="9"/>
-      <c r="AJ38" s="73"/>
-      <c r="AK38" s="73"/>
+      <c r="AJ38" s="61"/>
+      <c r="AK38" s="61"/>
       <c r="AL38" s="9"/>
       <c r="AM38" s="9"/>
       <c r="AN38" s="9"/>
@@ -7731,43 +7742,43 @@
       <c r="BI38" s="10"/>
     </row>
     <row r="39" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="73"/>
-      <c r="B39" s="73"/>
-      <c r="C39" s="73"/>
-      <c r="D39" s="73"/>
-      <c r="E39" s="73"/>
-      <c r="F39" s="73"/>
-      <c r="G39" s="73"/>
-      <c r="H39" s="73"/>
-      <c r="I39" s="73"/>
-      <c r="J39" s="73"/>
+      <c r="A39" s="61"/>
+      <c r="B39" s="61"/>
+      <c r="C39" s="61"/>
+      <c r="D39" s="61"/>
+      <c r="E39" s="61"/>
+      <c r="F39" s="61"/>
+      <c r="G39" s="61"/>
+      <c r="H39" s="61"/>
+      <c r="I39" s="61"/>
+      <c r="J39" s="61"/>
       <c r="K39" s="9"/>
-      <c r="L39" s="73"/>
-      <c r="M39" s="73"/>
+      <c r="L39" s="61"/>
+      <c r="M39" s="61"/>
       <c r="N39" s="9"/>
-      <c r="O39" s="73"/>
-      <c r="P39" s="73"/>
+      <c r="O39" s="61"/>
+      <c r="P39" s="61"/>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
       <c r="S39" s="9"/>
       <c r="T39" s="13"/>
-      <c r="U39" s="76"/>
-      <c r="V39" s="73"/>
-      <c r="W39" s="73"/>
-      <c r="X39" s="73"/>
-      <c r="Y39" s="73"/>
-      <c r="Z39" s="73"/>
-      <c r="AA39" s="73"/>
-      <c r="AB39" s="73"/>
-      <c r="AC39" s="73"/>
-      <c r="AD39" s="73"/>
-      <c r="AE39" s="73"/>
+      <c r="U39" s="62"/>
+      <c r="V39" s="61"/>
+      <c r="W39" s="61"/>
+      <c r="X39" s="61"/>
+      <c r="Y39" s="61"/>
+      <c r="Z39" s="61"/>
+      <c r="AA39" s="61"/>
+      <c r="AB39" s="61"/>
+      <c r="AC39" s="61"/>
+      <c r="AD39" s="61"/>
+      <c r="AE39" s="61"/>
       <c r="AF39" s="9"/>
-      <c r="AG39" s="73"/>
-      <c r="AH39" s="73"/>
+      <c r="AG39" s="61"/>
+      <c r="AH39" s="61"/>
       <c r="AI39" s="9"/>
-      <c r="AJ39" s="73"/>
-      <c r="AK39" s="73"/>
+      <c r="AJ39" s="61"/>
+      <c r="AK39" s="61"/>
       <c r="AL39" s="9"/>
       <c r="AM39" s="9"/>
       <c r="AN39" s="9"/>
@@ -7794,43 +7805,43 @@
       <c r="BI39" s="10"/>
     </row>
     <row r="40" spans="1:61" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="73"/>
-      <c r="B40" s="73"/>
-      <c r="C40" s="73"/>
-      <c r="D40" s="73"/>
-      <c r="E40" s="73"/>
-      <c r="F40" s="73"/>
-      <c r="G40" s="73"/>
-      <c r="H40" s="73"/>
-      <c r="I40" s="73"/>
-      <c r="J40" s="73"/>
+      <c r="A40" s="61"/>
+      <c r="B40" s="61"/>
+      <c r="C40" s="61"/>
+      <c r="D40" s="61"/>
+      <c r="E40" s="61"/>
+      <c r="F40" s="61"/>
+      <c r="G40" s="61"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="61"/>
+      <c r="J40" s="61"/>
       <c r="K40" s="9"/>
-      <c r="L40" s="73"/>
-      <c r="M40" s="73"/>
+      <c r="L40" s="61"/>
+      <c r="M40" s="61"/>
       <c r="N40" s="9"/>
-      <c r="O40" s="73"/>
-      <c r="P40" s="73"/>
+      <c r="O40" s="61"/>
+      <c r="P40" s="61"/>
       <c r="Q40" s="9"/>
       <c r="R40" s="9"/>
       <c r="S40" s="9"/>
       <c r="T40" s="13"/>
-      <c r="U40" s="76"/>
-      <c r="V40" s="73"/>
-      <c r="W40" s="73"/>
-      <c r="X40" s="73"/>
-      <c r="Y40" s="73"/>
-      <c r="Z40" s="73"/>
-      <c r="AA40" s="73"/>
-      <c r="AB40" s="73"/>
-      <c r="AC40" s="73"/>
-      <c r="AD40" s="73"/>
-      <c r="AE40" s="73"/>
+      <c r="U40" s="62"/>
+      <c r="V40" s="61"/>
+      <c r="W40" s="61"/>
+      <c r="X40" s="61"/>
+      <c r="Y40" s="61"/>
+      <c r="Z40" s="61"/>
+      <c r="AA40" s="61"/>
+      <c r="AB40" s="61"/>
+      <c r="AC40" s="61"/>
+      <c r="AD40" s="61"/>
+      <c r="AE40" s="61"/>
       <c r="AF40" s="9"/>
-      <c r="AG40" s="73"/>
-      <c r="AH40" s="73"/>
+      <c r="AG40" s="61"/>
+      <c r="AH40" s="61"/>
       <c r="AI40" s="9"/>
-      <c r="AJ40" s="73"/>
-      <c r="AK40" s="73"/>
+      <c r="AJ40" s="61"/>
+      <c r="AK40" s="61"/>
       <c r="AL40" s="9"/>
       <c r="AM40" s="9"/>
       <c r="AN40" s="9"/>
@@ -8965,9 +8976,9 @@
       <c r="AI66" s="6"/>
       <c r="AJ66" s="6"/>
       <c r="AK66" s="6"/>
-      <c r="AL66" s="66"/>
-      <c r="AM66" s="66"/>
-      <c r="AN66" s="66"/>
+      <c r="AL66" s="19"/>
+      <c r="AM66" s="19"/>
+      <c r="AN66" s="19"/>
     </row>
     <row r="67" spans="1:41" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4"/>
@@ -9143,6 +9154,189 @@
     </row>
   </sheetData>
   <mergeCells count="207">
+    <mergeCell ref="AJ38:AK38"/>
+    <mergeCell ref="AJ39:AK39"/>
+    <mergeCell ref="AJ40:AK40"/>
+    <mergeCell ref="AP11:BA11"/>
+    <mergeCell ref="BC11:BI11"/>
+    <mergeCell ref="AJ33:AK33"/>
+    <mergeCell ref="AJ34:AK34"/>
+    <mergeCell ref="AJ35:AK35"/>
+    <mergeCell ref="AJ36:AK36"/>
+    <mergeCell ref="AJ37:AK37"/>
+    <mergeCell ref="AJ28:AK28"/>
+    <mergeCell ref="AJ29:AK29"/>
+    <mergeCell ref="AJ30:AK30"/>
+    <mergeCell ref="AJ31:AK31"/>
+    <mergeCell ref="AJ32:AK32"/>
+    <mergeCell ref="AJ12:AK12"/>
+    <mergeCell ref="AG40:AH40"/>
+    <mergeCell ref="AJ13:AK13"/>
+    <mergeCell ref="AJ14:AK14"/>
+    <mergeCell ref="AJ15:AK15"/>
+    <mergeCell ref="AJ16:AK16"/>
+    <mergeCell ref="AJ17:AK17"/>
+    <mergeCell ref="AJ18:AK18"/>
+    <mergeCell ref="AJ19:AK19"/>
+    <mergeCell ref="AJ20:AK20"/>
+    <mergeCell ref="AJ21:AK21"/>
+    <mergeCell ref="AJ22:AK22"/>
+    <mergeCell ref="AJ23:AK23"/>
+    <mergeCell ref="AJ24:AK24"/>
+    <mergeCell ref="AJ25:AK25"/>
+    <mergeCell ref="AJ26:AK26"/>
+    <mergeCell ref="AJ27:AK27"/>
+    <mergeCell ref="AG35:AH35"/>
+    <mergeCell ref="AG36:AH36"/>
+    <mergeCell ref="AG37:AH37"/>
+    <mergeCell ref="AG38:AH38"/>
+    <mergeCell ref="AG39:AH39"/>
+    <mergeCell ref="AG30:AH30"/>
+    <mergeCell ref="AG31:AH31"/>
+    <mergeCell ref="AG32:AH32"/>
+    <mergeCell ref="AG33:AH33"/>
+    <mergeCell ref="AG34:AH34"/>
+    <mergeCell ref="AG25:AH25"/>
+    <mergeCell ref="AG26:AH26"/>
+    <mergeCell ref="AG27:AH27"/>
+    <mergeCell ref="AG28:AH28"/>
+    <mergeCell ref="AG29:AH29"/>
+    <mergeCell ref="U37:AE37"/>
+    <mergeCell ref="U38:AE38"/>
+    <mergeCell ref="U39:AE39"/>
+    <mergeCell ref="U40:AE40"/>
+    <mergeCell ref="AG13:AH13"/>
+    <mergeCell ref="AG14:AH14"/>
+    <mergeCell ref="AG15:AH15"/>
+    <mergeCell ref="AG16:AH16"/>
+    <mergeCell ref="AG17:AH17"/>
+    <mergeCell ref="AG18:AH18"/>
+    <mergeCell ref="AG19:AH19"/>
+    <mergeCell ref="AG20:AH20"/>
+    <mergeCell ref="AG21:AH21"/>
+    <mergeCell ref="AG22:AH22"/>
+    <mergeCell ref="AG23:AH23"/>
+    <mergeCell ref="AG24:AH24"/>
+    <mergeCell ref="U32:AE32"/>
+    <mergeCell ref="U33:AE33"/>
+    <mergeCell ref="U34:AE34"/>
+    <mergeCell ref="U35:AE35"/>
+    <mergeCell ref="U36:AE36"/>
+    <mergeCell ref="U27:AE27"/>
+    <mergeCell ref="U28:AE28"/>
+    <mergeCell ref="U29:AE29"/>
+    <mergeCell ref="U30:AE30"/>
+    <mergeCell ref="U31:AE31"/>
+    <mergeCell ref="AG12:AH12"/>
+    <mergeCell ref="U13:AE13"/>
+    <mergeCell ref="U14:AE14"/>
+    <mergeCell ref="U15:AE15"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="U12:AE12"/>
+    <mergeCell ref="U16:AE16"/>
+    <mergeCell ref="U17:AE17"/>
+    <mergeCell ref="U18:AE18"/>
+    <mergeCell ref="U19:AE19"/>
+    <mergeCell ref="U20:AE20"/>
+    <mergeCell ref="U21:AE21"/>
+    <mergeCell ref="U22:AE22"/>
+    <mergeCell ref="U23:AE23"/>
+    <mergeCell ref="U24:AE24"/>
+    <mergeCell ref="U25:AE25"/>
+    <mergeCell ref="U26:AE26"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="AP9:BI9"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="AJ11:AK11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="AG11:AH11"/>
+    <mergeCell ref="U11:AE11"/>
+    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A19:J19"/>
     <mergeCell ref="AY1:BI1"/>
     <mergeCell ref="F1:J1"/>
     <mergeCell ref="K1:V1"/>
@@ -9167,189 +9361,6 @@
     <mergeCell ref="AN2:AR3"/>
     <mergeCell ref="A9:T9"/>
     <mergeCell ref="U9:AO9"/>
-    <mergeCell ref="AP9:BI9"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="A12:J12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="AJ11:AK11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="AG11:AH11"/>
-    <mergeCell ref="U11:AE11"/>
-    <mergeCell ref="A15:J15"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A38:J38"/>
-    <mergeCell ref="A39:J39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="A33:J33"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A35:J35"/>
-    <mergeCell ref="A36:J36"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="AG12:AH12"/>
-    <mergeCell ref="U13:AE13"/>
-    <mergeCell ref="U14:AE14"/>
-    <mergeCell ref="U15:AE15"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="U12:AE12"/>
-    <mergeCell ref="U16:AE16"/>
-    <mergeCell ref="U17:AE17"/>
-    <mergeCell ref="U18:AE18"/>
-    <mergeCell ref="U19:AE19"/>
-    <mergeCell ref="U20:AE20"/>
-    <mergeCell ref="U21:AE21"/>
-    <mergeCell ref="U22:AE22"/>
-    <mergeCell ref="U23:AE23"/>
-    <mergeCell ref="U24:AE24"/>
-    <mergeCell ref="U25:AE25"/>
-    <mergeCell ref="U26:AE26"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="U39:AE39"/>
-    <mergeCell ref="U40:AE40"/>
-    <mergeCell ref="AG13:AH13"/>
-    <mergeCell ref="AG14:AH14"/>
-    <mergeCell ref="AG15:AH15"/>
-    <mergeCell ref="AG16:AH16"/>
-    <mergeCell ref="AG17:AH17"/>
-    <mergeCell ref="AG18:AH18"/>
-    <mergeCell ref="AG19:AH19"/>
-    <mergeCell ref="AG20:AH20"/>
-    <mergeCell ref="AG21:AH21"/>
-    <mergeCell ref="AG22:AH22"/>
-    <mergeCell ref="AG23:AH23"/>
-    <mergeCell ref="AG24:AH24"/>
-    <mergeCell ref="U32:AE32"/>
-    <mergeCell ref="U33:AE33"/>
-    <mergeCell ref="U34:AE34"/>
-    <mergeCell ref="U35:AE35"/>
-    <mergeCell ref="U36:AE36"/>
-    <mergeCell ref="U27:AE27"/>
-    <mergeCell ref="U28:AE28"/>
-    <mergeCell ref="U29:AE29"/>
-    <mergeCell ref="U30:AE30"/>
-    <mergeCell ref="U31:AE31"/>
-    <mergeCell ref="AG33:AH33"/>
-    <mergeCell ref="AG34:AH34"/>
-    <mergeCell ref="AG25:AH25"/>
-    <mergeCell ref="AG26:AH26"/>
-    <mergeCell ref="AG27:AH27"/>
-    <mergeCell ref="AG28:AH28"/>
-    <mergeCell ref="AG29:AH29"/>
-    <mergeCell ref="U37:AE37"/>
-    <mergeCell ref="U38:AE38"/>
-    <mergeCell ref="AG40:AH40"/>
-    <mergeCell ref="AJ13:AK13"/>
-    <mergeCell ref="AJ14:AK14"/>
-    <mergeCell ref="AJ15:AK15"/>
-    <mergeCell ref="AJ16:AK16"/>
-    <mergeCell ref="AJ17:AK17"/>
-    <mergeCell ref="AJ18:AK18"/>
-    <mergeCell ref="AJ19:AK19"/>
-    <mergeCell ref="AJ20:AK20"/>
-    <mergeCell ref="AJ21:AK21"/>
-    <mergeCell ref="AJ22:AK22"/>
-    <mergeCell ref="AJ23:AK23"/>
-    <mergeCell ref="AJ24:AK24"/>
-    <mergeCell ref="AJ25:AK25"/>
-    <mergeCell ref="AJ26:AK26"/>
-    <mergeCell ref="AJ27:AK27"/>
-    <mergeCell ref="AG35:AH35"/>
-    <mergeCell ref="AG36:AH36"/>
-    <mergeCell ref="AG37:AH37"/>
-    <mergeCell ref="AG38:AH38"/>
-    <mergeCell ref="AG39:AH39"/>
-    <mergeCell ref="AG30:AH30"/>
-    <mergeCell ref="AG31:AH31"/>
-    <mergeCell ref="AG32:AH32"/>
-    <mergeCell ref="AJ38:AK38"/>
-    <mergeCell ref="AJ39:AK39"/>
-    <mergeCell ref="AJ40:AK40"/>
-    <mergeCell ref="AP11:BA11"/>
-    <mergeCell ref="BC11:BI11"/>
-    <mergeCell ref="AJ33:AK33"/>
-    <mergeCell ref="AJ34:AK34"/>
-    <mergeCell ref="AJ35:AK35"/>
-    <mergeCell ref="AJ36:AK36"/>
-    <mergeCell ref="AJ37:AK37"/>
-    <mergeCell ref="AJ28:AK28"/>
-    <mergeCell ref="AJ29:AK29"/>
-    <mergeCell ref="AJ30:AK30"/>
-    <mergeCell ref="AJ31:AK31"/>
-    <mergeCell ref="AJ32:AK32"/>
-    <mergeCell ref="AJ12:AK12"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -9360,12 +9371,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="bdc2d3d5-fc31-4d65-8e89-042f9aabae79" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="13b50d63-4097-4260-987b-0df3cda3515c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9570,20 +9583,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="bdc2d3d5-fc31-4d65-8e89-042f9aabae79" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="13b50d63-4097-4260-987b-0df3cda3515c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED9081D4-7DA8-4E8C-9299-427A52260533}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA865533-0B77-4147-AA92-F0C2FDB2E315}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bdc2d3d5-fc31-4d65-8e89-042f9aabae79"/>
+    <ds:schemaRef ds:uri="13b50d63-4097-4260-987b-0df3cda3515c"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9608,12 +9622,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA865533-0B77-4147-AA92-F0C2FDB2E315}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED9081D4-7DA8-4E8C-9299-427A52260533}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bdc2d3d5-fc31-4d65-8e89-042f9aabae79"/>
-    <ds:schemaRef ds:uri="13b50d63-4097-4260-987b-0df3cda3515c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>